--- a/artfynd/A 43504-2025 artfynd.xlsx
+++ b/artfynd/A 43504-2025 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>129249084</v>
       </c>
       <c r="B8" t="n">
-        <v>79656</v>
+        <v>79658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129248989</v>
+        <v>129250233</v>
       </c>
       <c r="B9" t="n">
-        <v>78795</v>
+        <v>78797</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445037</v>
+        <v>444881</v>
       </c>
       <c r="R9" t="n">
-        <v>6734946</v>
+        <v>6735300</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,11 +1475,6 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>1 bild, tall i bakgrund</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,45 +1501,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129253634</v>
+        <v>129248937</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>57722</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444917</v>
+        <v>445066</v>
       </c>
       <c r="R10" t="n">
-        <v>6735361</v>
+        <v>6734914</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,11 +1587,6 @@
       <c r="AB10" t="inlineStr">
         <is>
           <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2 Miljöbilder</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129250233</v>
+        <v>129249372</v>
       </c>
       <c r="B11" t="n">
-        <v>78795</v>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1629,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444881</v>
+        <v>444977</v>
       </c>
       <c r="R11" t="n">
-        <v>6735300</v>
+        <v>6735277</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129248937</v>
+        <v>129254011</v>
       </c>
       <c r="B12" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1736,39 +1731,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445066</v>
+        <v>444965</v>
       </c>
       <c r="R12" t="n">
-        <v>6734914</v>
+        <v>6735354</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1837,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129249372</v>
+        <v>129253379</v>
       </c>
       <c r="B13" t="n">
-        <v>79037</v>
+        <v>79039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1872,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>444977</v>
+        <v>444917</v>
       </c>
       <c r="R13" t="n">
-        <v>6735277</v>
+        <v>6735361</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129254011</v>
+        <v>129249212</v>
       </c>
       <c r="B14" t="n">
-        <v>79037</v>
+        <v>79039</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444965</v>
+        <v>444962</v>
       </c>
       <c r="R14" t="n">
-        <v>6735354</v>
+        <v>6735315</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129251241</v>
+        <v>129249287</v>
       </c>
       <c r="B15" t="n">
-        <v>78795</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2062,21 +2052,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444800</v>
+        <v>444980</v>
       </c>
       <c r="R15" t="n">
-        <v>6735299</v>
+        <v>6735302</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,11 +2122,6 @@
       <c r="AB15" t="inlineStr">
         <is>
           <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>1 bild kolad stubbe med hål</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129253379</v>
+        <v>129248989</v>
       </c>
       <c r="B16" t="n">
-        <v>79037</v>
+        <v>78797</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2174,21 +2159,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444917</v>
+        <v>445037</v>
       </c>
       <c r="R16" t="n">
-        <v>6735361</v>
+        <v>6734946</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2244,6 +2229,11 @@
       <c r="AB16" t="inlineStr">
         <is>
           <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>1 bild, tall i bakgrund</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,32 +2260,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129254098</v>
+        <v>129253634</v>
       </c>
       <c r="B17" t="n">
-        <v>79037</v>
+        <v>8450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444984</v>
+        <v>444917</v>
       </c>
       <c r="R17" t="n">
-        <v>6735330</v>
+        <v>6735361</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,7 +2345,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>1 bild, gran med stenar</t>
+          <t>2 Miljöbilder</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2382,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129249212</v>
+        <v>129251241</v>
       </c>
       <c r="B18" t="n">
-        <v>79037</v>
+        <v>78797</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2393,21 +2383,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2417,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444962</v>
+        <v>444800</v>
       </c>
       <c r="R18" t="n">
-        <v>6735315</v>
+        <v>6735299</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2463,6 +2453,11 @@
       <c r="AB18" t="inlineStr">
         <is>
           <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>1 bild kolad stubbe med hål</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2489,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129248688</v>
+        <v>129254098</v>
       </c>
       <c r="B19" t="n">
-        <v>79132</v>
+        <v>79039</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2500,38 +2495,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445078</v>
+        <v>444984</v>
       </c>
       <c r="R19" t="n">
-        <v>6734933</v>
+        <v>6735330</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2578,7 +2569,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>3 bilder</t>
+          <t>1 bild, gran med stenar</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2608,7 +2599,7 @@
         <v>129248920</v>
       </c>
       <c r="B20" t="n">
-        <v>79656</v>
+        <v>79658</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2717,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129250170</v>
+        <v>129248688</v>
       </c>
       <c r="B21" t="n">
-        <v>57722</v>
+        <v>79134</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2728,27 +2719,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>967</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2757,10 +2747,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444948</v>
+        <v>445078</v>
       </c>
       <c r="R21" t="n">
-        <v>6735278</v>
+        <v>6734933</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2807,7 +2797,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>1 bild och 1 miljöbild</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2834,10 +2824,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129249287</v>
+        <v>129250170</v>
       </c>
       <c r="B22" t="n">
-        <v>79037</v>
+        <v>57722</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2845,34 +2835,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444980</v>
+        <v>444948</v>
       </c>
       <c r="R22" t="n">
-        <v>6735302</v>
+        <v>6735278</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2915,6 +2910,11 @@
       <c r="AB22" t="inlineStr">
         <is>
           <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>1 bild och 1 miljöbild</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -4165,32 +4165,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129237324</v>
+        <v>129237525</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445263</v>
+        <v>445251</v>
       </c>
       <c r="R35" t="n">
-        <v>6735122</v>
+        <v>6735185</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4272,32 +4272,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129237525</v>
+        <v>129237324</v>
       </c>
       <c r="B36" t="n">
-        <v>79037</v>
+        <v>8450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4307,10 +4307,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445251</v>
+        <v>445263</v>
       </c>
       <c r="R36" t="n">
-        <v>6735185</v>
+        <v>6735122</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4379,10 +4379,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129239693</v>
+        <v>129243809</v>
       </c>
       <c r="B37" t="n">
-        <v>79037</v>
+        <v>57722</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4390,34 +4390,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445362</v>
+        <v>445358</v>
       </c>
       <c r="R37" t="n">
-        <v>6735341</v>
+        <v>6735035</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4449,7 +4454,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4459,12 +4464,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>5 bilder, sumpskog</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4491,45 +4491,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129243051</v>
+        <v>129239467</v>
       </c>
       <c r="B38" t="n">
-        <v>79132</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>967</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445339</v>
+        <v>445379</v>
       </c>
       <c r="R38" t="n">
-        <v>6734920</v>
+        <v>6735294</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4561,7 +4566,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4571,12 +4576,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>3 bilder</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4715,7 +4715,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129239467</v>
+        <v>129240788</v>
       </c>
       <c r="B40" t="n">
         <v>8450</v>
@@ -4744,21 +4744,16 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445379</v>
+        <v>445491</v>
       </c>
       <c r="R40" t="n">
-        <v>6735294</v>
+        <v>6735426</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4790,7 +4785,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4800,7 +4795,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4827,10 +4822,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129240510</v>
+        <v>129238576</v>
       </c>
       <c r="B41" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4838,39 +4833,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445439</v>
+        <v>445336</v>
       </c>
       <c r="R41" t="n">
-        <v>6735533</v>
+        <v>6735162</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4902,7 +4892,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4912,12 +4902,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>1 bild med kolad stubbe i bakgrund</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4944,10 +4929,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129243809</v>
+        <v>129238322</v>
       </c>
       <c r="B42" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4955,39 +4940,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445358</v>
+        <v>445325</v>
       </c>
       <c r="R42" t="n">
-        <v>6735035</v>
+        <v>6735153</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5019,7 +4999,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5029,7 +5009,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5056,10 +5036,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129238322</v>
+        <v>129239093</v>
       </c>
       <c r="B43" t="n">
-        <v>79037</v>
+        <v>79039</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5091,10 +5071,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445325</v>
+        <v>445324</v>
       </c>
       <c r="R43" t="n">
-        <v>6735153</v>
+        <v>6735285</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5166,7 +5146,7 @@
         <v>129238704</v>
       </c>
       <c r="B44" t="n">
-        <v>79037</v>
+        <v>79039</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5275,10 +5255,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129239093</v>
+        <v>129237826</v>
       </c>
       <c r="B45" t="n">
-        <v>79037</v>
+        <v>79658</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5286,21 +5266,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5310,10 +5290,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>445324</v>
+        <v>445225</v>
       </c>
       <c r="R45" t="n">
-        <v>6735285</v>
+        <v>6735226</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5345,7 +5325,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5355,7 +5335,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5382,10 +5362,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129238576</v>
+        <v>129237683</v>
       </c>
       <c r="B46" t="n">
-        <v>79037</v>
+        <v>79039</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5417,10 +5397,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>445336</v>
+        <v>445282</v>
       </c>
       <c r="R46" t="n">
-        <v>6735162</v>
+        <v>6735211</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5452,7 +5432,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5462,7 +5442,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5489,10 +5469,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129240492</v>
+        <v>129238645</v>
       </c>
       <c r="B47" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5500,39 +5480,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>445440</v>
+        <v>445322</v>
       </c>
       <c r="R47" t="n">
-        <v>6735522</v>
+        <v>6735197</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5564,7 +5539,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5574,12 +5549,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>1 bild</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5606,10 +5576,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129240471</v>
+        <v>129243087</v>
       </c>
       <c r="B48" t="n">
-        <v>78795</v>
+        <v>78797</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5641,10 +5611,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445438</v>
+        <v>445378</v>
       </c>
       <c r="R48" t="n">
-        <v>6735509</v>
+        <v>6734906</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5676,7 +5646,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5686,12 +5656,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>2 bilder, kolad stubbe samt på spiklav</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5718,32 +5683,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129240788</v>
+        <v>129237277</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>79629</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5753,10 +5718,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445491</v>
+        <v>445252</v>
       </c>
       <c r="R49" t="n">
-        <v>6735426</v>
+        <v>6735079</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5788,7 +5753,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5798,7 +5763,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5825,10 +5790,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129240554</v>
+        <v>129237483</v>
       </c>
       <c r="B50" t="n">
-        <v>79627</v>
+        <v>79039</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5836,21 +5801,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5860,10 +5825,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>445435</v>
+        <v>445260</v>
       </c>
       <c r="R50" t="n">
-        <v>6735582</v>
+        <v>6735185</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5895,7 +5860,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5905,12 +5870,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>1 bild på högstubbe med låga i bakgrund</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5937,10 +5897,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129240621</v>
+        <v>129237299</v>
       </c>
       <c r="B51" t="n">
-        <v>78795</v>
+        <v>79039</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5948,21 +5908,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5972,10 +5932,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>445517</v>
+        <v>445260</v>
       </c>
       <c r="R51" t="n">
-        <v>6735559</v>
+        <v>6735095</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6007,7 +5967,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6017,12 +5977,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>1 bild, kolad stubbe</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6049,10 +6004,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129237826</v>
+        <v>129237617</v>
       </c>
       <c r="B52" t="n">
-        <v>79656</v>
+        <v>79658</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6084,10 +6039,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445225</v>
+        <v>445279</v>
       </c>
       <c r="R52" t="n">
-        <v>6735226</v>
+        <v>6735197</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6156,10 +6111,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129237683</v>
+        <v>129239857</v>
       </c>
       <c r="B53" t="n">
-        <v>79037</v>
+        <v>57722</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6167,34 +6122,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445282</v>
+        <v>445369</v>
       </c>
       <c r="R53" t="n">
-        <v>6735211</v>
+        <v>6735411</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6226,7 +6186,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6236,7 +6196,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6263,10 +6223,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129237880</v>
+        <v>129243753</v>
       </c>
       <c r="B54" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6274,39 +6234,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>445206</v>
+        <v>445384</v>
       </c>
       <c r="R54" t="n">
-        <v>6735207</v>
+        <v>6734985</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6338,7 +6293,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6348,12 +6303,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Bild, torraka med hack</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6380,10 +6330,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129238645</v>
+        <v>129239740</v>
       </c>
       <c r="B55" t="n">
-        <v>79037</v>
+        <v>79039</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6415,10 +6365,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445322</v>
+        <v>445356</v>
       </c>
       <c r="R55" t="n">
-        <v>6735197</v>
+        <v>6735366</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6487,10 +6437,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129238933</v>
+        <v>129237544</v>
       </c>
       <c r="B56" t="n">
-        <v>79037</v>
+        <v>79039</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6522,10 +6472,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>445307</v>
+        <v>445264</v>
       </c>
       <c r="R56" t="n">
-        <v>6735277</v>
+        <v>6735197</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6557,7 +6507,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6567,12 +6517,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter 3 bilder, sista på två tallstammar</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6599,10 +6544,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129238758</v>
+        <v>129240724</v>
       </c>
       <c r="B57" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6610,39 +6555,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445349</v>
+        <v>445509</v>
       </c>
       <c r="R57" t="n">
-        <v>6735194</v>
+        <v>6735455</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6674,7 +6614,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6684,12 +6624,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>2 bilder på torraka med hack</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6716,27 +6651,27 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129243098</v>
+        <v>129242999</v>
       </c>
       <c r="B58" t="n">
-        <v>57722</v>
+        <v>58095</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6747,7 +6682,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6756,10 +6691,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>445374</v>
+        <v>445292</v>
       </c>
       <c r="R58" t="n">
-        <v>6734891</v>
+        <v>6734957</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6802,11 +6737,6 @@
       <c r="AB58" t="inlineStr">
         <is>
           <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>1 bild</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6833,10 +6763,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129243087</v>
+        <v>129237764</v>
       </c>
       <c r="B59" t="n">
-        <v>78795</v>
+        <v>79039</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6844,21 +6774,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6868,10 +6798,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>445378</v>
+        <v>445275</v>
       </c>
       <c r="R59" t="n">
-        <v>6734906</v>
+        <v>6735223</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6903,7 +6833,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6913,7 +6843,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6940,10 +6870,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129248843</v>
+        <v>129243054</v>
       </c>
       <c r="B60" t="n">
-        <v>91551</v>
+        <v>78797</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6951,38 +6881,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445140</v>
+        <v>445339</v>
       </c>
       <c r="R60" t="n">
-        <v>6734876</v>
+        <v>6734920</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7014,7 +6940,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7024,12 +6950,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>1 bild</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7056,10 +6977,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129237273</v>
+        <v>129240566</v>
       </c>
       <c r="B61" t="n">
-        <v>78795</v>
+        <v>79039</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7067,21 +6988,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7091,10 +7012,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>445252</v>
+        <v>445481</v>
       </c>
       <c r="R61" t="n">
-        <v>6735079</v>
+        <v>6735582</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7126,7 +7047,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7136,12 +7057,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Bild 4, högstubbe</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7168,10 +7084,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129237277</v>
+        <v>129239929</v>
       </c>
       <c r="B62" t="n">
-        <v>79627</v>
+        <v>79039</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7179,21 +7095,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7203,10 +7119,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>445252</v>
+        <v>445421</v>
       </c>
       <c r="R62" t="n">
-        <v>6735079</v>
+        <v>6735402</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7238,7 +7154,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7248,7 +7164,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7275,10 +7196,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129237299</v>
+        <v>129240474</v>
       </c>
       <c r="B63" t="n">
-        <v>79037</v>
+        <v>79039</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7310,10 +7231,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>445260</v>
+        <v>445438</v>
       </c>
       <c r="R63" t="n">
-        <v>6735095</v>
+        <v>6735509</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7345,7 +7266,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7355,7 +7276,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7382,10 +7303,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129237350</v>
+        <v>129240967</v>
       </c>
       <c r="B64" t="n">
-        <v>78795</v>
+        <v>79039</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7393,21 +7314,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7417,10 +7338,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>445248</v>
+        <v>445414</v>
       </c>
       <c r="R64" t="n">
-        <v>6735139</v>
+        <v>6735285</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7452,7 +7373,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7462,12 +7383,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Bild 5, högstubbe</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7494,32 +7410,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129237617</v>
+        <v>129240494</v>
       </c>
       <c r="B65" t="n">
-        <v>79656</v>
+        <v>8450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7529,10 +7445,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445279</v>
+        <v>445440</v>
       </c>
       <c r="R65" t="n">
-        <v>6735197</v>
+        <v>6735522</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7564,7 +7480,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7574,7 +7490,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7601,10 +7517,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129237483</v>
+        <v>129237820</v>
       </c>
       <c r="B66" t="n">
-        <v>79037</v>
+        <v>78796</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7612,21 +7528,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7636,10 +7552,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445260</v>
+        <v>445225</v>
       </c>
       <c r="R66" t="n">
-        <v>6735185</v>
+        <v>6735226</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7708,10 +7624,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129238052</v>
+        <v>129247898</v>
       </c>
       <c r="B67" t="n">
-        <v>57885</v>
+        <v>79658</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7719,46 +7635,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445240</v>
+        <v>445107</v>
       </c>
       <c r="R67" t="n">
-        <v>6735230</v>
+        <v>6735004</v>
       </c>
       <c r="S67" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7787,7 +7694,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7797,7 +7704,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7824,10 +7731,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129239857</v>
+        <v>129238475</v>
       </c>
       <c r="B68" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7835,39 +7742,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445369</v>
+        <v>445322</v>
       </c>
       <c r="R68" t="n">
-        <v>6735411</v>
+        <v>6735128</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7936,10 +7838,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129239740</v>
+        <v>129238815</v>
       </c>
       <c r="B69" t="n">
-        <v>79037</v>
+        <v>57885</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7947,37 +7849,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>445356</v>
+        <v>445313</v>
       </c>
       <c r="R69" t="n">
-        <v>6735366</v>
+        <v>6735262</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8043,10 +7950,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129243753</v>
+        <v>129244530</v>
       </c>
       <c r="B70" t="n">
-        <v>79037</v>
+        <v>79658</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8054,21 +7961,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8078,10 +7985,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>445384</v>
+        <v>445217</v>
       </c>
       <c r="R70" t="n">
-        <v>6734985</v>
+        <v>6734997</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8113,7 +8020,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8123,7 +8030,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8150,32 +8057,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129240724</v>
+        <v>129238778</v>
       </c>
       <c r="B71" t="n">
-        <v>79037</v>
+        <v>8450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8185,10 +8092,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445509</v>
+        <v>445322</v>
       </c>
       <c r="R71" t="n">
-        <v>6735455</v>
+        <v>6735197</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8220,7 +8127,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8230,7 +8137,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8257,27 +8164,27 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129242999</v>
+        <v>129240193</v>
       </c>
       <c r="B72" t="n">
-        <v>58095</v>
+        <v>57722</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8288,7 +8195,7 @@
       <c r="I72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8297,10 +8204,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>445292</v>
+        <v>445445</v>
       </c>
       <c r="R72" t="n">
-        <v>6734957</v>
+        <v>6735438</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8332,7 +8239,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8342,7 +8249,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8369,10 +8276,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129237544</v>
+        <v>129238788</v>
       </c>
       <c r="B73" t="n">
-        <v>79037</v>
+        <v>79039</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8404,10 +8311,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445264</v>
+        <v>445316</v>
       </c>
       <c r="R73" t="n">
-        <v>6735197</v>
+        <v>6735207</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8439,7 +8346,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8449,7 +8356,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Rikligt i närområdet</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8476,10 +8388,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129244433</v>
+        <v>129237274</v>
       </c>
       <c r="B74" t="n">
-        <v>79627</v>
+        <v>79658</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8487,21 +8399,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8511,10 +8423,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>445217</v>
+        <v>445252</v>
       </c>
       <c r="R74" t="n">
-        <v>6734997</v>
+        <v>6735079</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8546,7 +8458,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8556,12 +8468,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>1 bild på högstubbe</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8588,10 +8495,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129237764</v>
+        <v>129239479</v>
       </c>
       <c r="B75" t="n">
-        <v>79037</v>
+        <v>79039</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8623,10 +8530,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>445275</v>
+        <v>445379</v>
       </c>
       <c r="R75" t="n">
-        <v>6735223</v>
+        <v>6735294</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8658,7 +8565,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8668,7 +8575,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8695,32 +8602,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129239929</v>
+        <v>129237286</v>
       </c>
       <c r="B76" t="n">
-        <v>79037</v>
+        <v>8450</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8730,10 +8637,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>445421</v>
+        <v>445252</v>
       </c>
       <c r="R76" t="n">
-        <v>6735402</v>
+        <v>6735079</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8765,7 +8672,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8775,12 +8682,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8807,10 +8709,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129238770</v>
+        <v>129244655</v>
       </c>
       <c r="B77" t="n">
-        <v>57722</v>
+        <v>79629</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8818,39 +8720,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>445322</v>
+        <v>445217</v>
       </c>
       <c r="R77" t="n">
-        <v>6735197</v>
+        <v>6734997</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8882,7 +8779,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8892,12 +8789,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Bild på torraka, färska hack</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8924,10 +8816,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129240474</v>
+        <v>129243245</v>
       </c>
       <c r="B78" t="n">
-        <v>79037</v>
+        <v>78796</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8935,21 +8827,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8959,10 +8851,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>445438</v>
+        <v>445422</v>
       </c>
       <c r="R78" t="n">
-        <v>6735509</v>
+        <v>6734878</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8994,7 +8886,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9004,7 +8896,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9031,32 +8923,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129240566</v>
+        <v>129243104</v>
       </c>
       <c r="B79" t="n">
-        <v>79037</v>
+        <v>8450</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9066,10 +8958,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>445481</v>
+        <v>445374</v>
       </c>
       <c r="R79" t="n">
-        <v>6735582</v>
+        <v>6734891</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9101,7 +8993,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9111,7 +9003,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9138,10 +9030,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129240967</v>
+        <v>129243192</v>
       </c>
       <c r="B80" t="n">
-        <v>79037</v>
+        <v>78797</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9149,21 +9041,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9173,10 +9065,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445414</v>
+        <v>445401</v>
       </c>
       <c r="R80" t="n">
-        <v>6735285</v>
+        <v>6734884</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9208,7 +9100,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9218,7 +9110,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9245,10 +9137,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129243188</v>
+        <v>129237621</v>
       </c>
       <c r="B81" t="n">
-        <v>79132</v>
+        <v>79629</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9256,21 +9148,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>967</v>
+        <v>229821</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9280,10 +9172,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>445401</v>
+        <v>445279</v>
       </c>
       <c r="R81" t="n">
-        <v>6734884</v>
+        <v>6735197</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9315,7 +9207,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9325,12 +9217,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>3 bilder</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9357,10 +9244,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129243054</v>
+        <v>129237829</v>
       </c>
       <c r="B82" t="n">
-        <v>78795</v>
+        <v>79629</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9368,21 +9255,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9392,10 +9279,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445339</v>
+        <v>445225</v>
       </c>
       <c r="R82" t="n">
-        <v>6734920</v>
+        <v>6735226</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9427,7 +9314,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9437,7 +9324,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9464,32 +9351,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129240494</v>
+        <v>129237650</v>
       </c>
       <c r="B83" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9499,10 +9386,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445440</v>
+        <v>445279</v>
       </c>
       <c r="R83" t="n">
-        <v>6735522</v>
+        <v>6735197</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9534,7 +9421,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9544,7 +9431,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9571,10 +9458,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129237820</v>
+        <v>129238241</v>
       </c>
       <c r="B84" t="n">
-        <v>78794</v>
+        <v>79039</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9582,21 +9469,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9606,10 +9493,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445225</v>
+        <v>445313</v>
       </c>
       <c r="R84" t="n">
-        <v>6735226</v>
+        <v>6735165</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9641,7 +9528,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9651,7 +9538,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9678,10 +9565,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129239898</v>
+        <v>129237533</v>
       </c>
       <c r="B85" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9689,39 +9576,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445362</v>
+        <v>445256</v>
       </c>
       <c r="R85" t="n">
-        <v>6735431</v>
+        <v>6735194</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9753,7 +9635,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9763,12 +9645,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>2 bilder, låga, torraka</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9795,32 +9672,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129247898</v>
+        <v>129239850</v>
       </c>
       <c r="B86" t="n">
-        <v>79656</v>
+        <v>8450</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9830,10 +9707,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445107</v>
+        <v>445369</v>
       </c>
       <c r="R86" t="n">
-        <v>6735004</v>
+        <v>6735411</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9865,7 +9742,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9875,7 +9752,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9902,32 +9779,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129238475</v>
+        <v>129242957</v>
       </c>
       <c r="B87" t="n">
-        <v>79037</v>
+        <v>8450</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9937,10 +9814,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445322</v>
+        <v>445292</v>
       </c>
       <c r="R87" t="n">
-        <v>6735128</v>
+        <v>6734957</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9972,7 +9849,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9982,7 +9859,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10009,10 +9886,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129238815</v>
+        <v>129247020</v>
       </c>
       <c r="B88" t="n">
-        <v>57885</v>
+        <v>78797</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10020,42 +9897,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>445313</v>
+        <v>445135</v>
       </c>
       <c r="R88" t="n">
-        <v>6735262</v>
+        <v>6734998</v>
       </c>
       <c r="S88" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10084,7 +9956,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10094,7 +9966,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10121,32 +9993,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129238778</v>
+        <v>129243217</v>
       </c>
       <c r="B89" t="n">
-        <v>8450</v>
+        <v>78797</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10156,10 +10028,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>445322</v>
+        <v>445422</v>
       </c>
       <c r="R89" t="n">
-        <v>6735197</v>
+        <v>6734878</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10191,7 +10063,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10201,7 +10073,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10228,10 +10100,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129244530</v>
+        <v>129243589</v>
       </c>
       <c r="B90" t="n">
-        <v>79656</v>
+        <v>79039</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10239,21 +10111,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10263,10 +10135,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>445217</v>
+        <v>445385</v>
       </c>
       <c r="R90" t="n">
-        <v>6734997</v>
+        <v>6734971</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10298,7 +10170,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10308,7 +10180,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10335,10 +10207,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129240193</v>
+        <v>129240662</v>
       </c>
       <c r="B91" t="n">
-        <v>57722</v>
+        <v>79658</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10346,39 +10218,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>445445</v>
+        <v>445517</v>
       </c>
       <c r="R91" t="n">
-        <v>6735438</v>
+        <v>6735559</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10447,10 +10314,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129237274</v>
+        <v>129248776</v>
       </c>
       <c r="B92" t="n">
-        <v>79656</v>
+        <v>57722</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10458,34 +10325,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>445252</v>
+        <v>445137</v>
       </c>
       <c r="R92" t="n">
-        <v>6735079</v>
+        <v>6734922</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10517,7 +10389,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10527,7 +10399,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10554,7 +10426,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129237286</v>
+        <v>129239096</v>
       </c>
       <c r="B93" t="n">
         <v>8450</v>
@@ -10589,10 +10461,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>445252</v>
+        <v>445324</v>
       </c>
       <c r="R93" t="n">
-        <v>6735079</v>
+        <v>6735285</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10624,7 +10496,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10634,7 +10506,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10661,10 +10533,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129239384</v>
+        <v>129239693</v>
       </c>
       <c r="B94" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10672,39 +10544,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445379</v>
+        <v>445362</v>
       </c>
       <c r="R94" t="n">
-        <v>6735294</v>
+        <v>6735341</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10751,7 +10618,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>2 bilder</t>
+          <t>5 bilder, sumpskog</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10778,10 +10645,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129239479</v>
+        <v>129243051</v>
       </c>
       <c r="B95" t="n">
-        <v>79037</v>
+        <v>79134</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10789,34 +10656,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445379</v>
+        <v>445339</v>
       </c>
       <c r="R95" t="n">
-        <v>6735294</v>
+        <v>6734920</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10848,7 +10718,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10858,7 +10728,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10867,6 +10742,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10885,10 +10761,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129238788</v>
+        <v>129240510</v>
       </c>
       <c r="B96" t="n">
-        <v>79037</v>
+        <v>57722</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10896,34 +10772,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>445316</v>
+        <v>445439</v>
       </c>
       <c r="R96" t="n">
-        <v>6735207</v>
+        <v>6735533</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10955,7 +10836,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10965,12 +10846,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Rikligt i närområdet</t>
+          <t>1 bild med kolad stubbe i bakgrund</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10997,32 +10878,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129243104</v>
+        <v>129240554</v>
       </c>
       <c r="B97" t="n">
-        <v>8450</v>
+        <v>79629</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11032,10 +10913,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>445374</v>
+        <v>445435</v>
       </c>
       <c r="R97" t="n">
-        <v>6734891</v>
+        <v>6735582</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11067,7 +10948,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11077,7 +10958,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>1 bild på högstubbe med låga i bakgrund</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11104,10 +10990,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129243245</v>
+        <v>129240492</v>
       </c>
       <c r="B98" t="n">
-        <v>78794</v>
+        <v>57722</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11115,34 +11001,39 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>445422</v>
+        <v>445440</v>
       </c>
       <c r="R98" t="n">
-        <v>6734878</v>
+        <v>6735522</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11174,7 +11065,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11184,7 +11075,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11211,10 +11107,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129243192</v>
+        <v>129240471</v>
       </c>
       <c r="B99" t="n">
-        <v>78795</v>
+        <v>78797</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11246,10 +11142,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>445401</v>
+        <v>445438</v>
       </c>
       <c r="R99" t="n">
-        <v>6734884</v>
+        <v>6735509</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11281,7 +11177,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11291,7 +11187,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>2 bilder, kolad stubbe samt på spiklav</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11318,10 +11219,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129237621</v>
+        <v>129240621</v>
       </c>
       <c r="B100" t="n">
-        <v>79627</v>
+        <v>78797</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11329,21 +11230,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11353,10 +11254,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>445279</v>
+        <v>445517</v>
       </c>
       <c r="R100" t="n">
-        <v>6735197</v>
+        <v>6735559</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11388,7 +11289,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11398,7 +11299,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>1 bild, kolad stubbe</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11425,32 +11331,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129239850</v>
+        <v>129238933</v>
       </c>
       <c r="B101" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11460,10 +11366,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445369</v>
+        <v>445307</v>
       </c>
       <c r="R101" t="n">
-        <v>6735411</v>
+        <v>6735277</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11506,6 +11412,11 @@
       <c r="AB101" t="inlineStr">
         <is>
           <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter 3 bilder, sista på två tallstammar</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11532,10 +11443,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129237533</v>
+        <v>129237880</v>
       </c>
       <c r="B102" t="n">
-        <v>79037</v>
+        <v>57722</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11543,34 +11454,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445256</v>
+        <v>445206</v>
       </c>
       <c r="R102" t="n">
-        <v>6735194</v>
+        <v>6735207</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11613,6 +11529,11 @@
       <c r="AB102" t="inlineStr">
         <is>
           <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Bild, torraka med hack</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11639,10 +11560,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129238241</v>
+        <v>129248843</v>
       </c>
       <c r="B103" t="n">
-        <v>79037</v>
+        <v>91553</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11650,34 +11571,38 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445313</v>
+        <v>445140</v>
       </c>
       <c r="R103" t="n">
-        <v>6735165</v>
+        <v>6734876</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11709,7 +11634,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11719,7 +11644,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11746,10 +11676,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129237639</v>
+        <v>129237350</v>
       </c>
       <c r="B104" t="n">
-        <v>79037</v>
+        <v>78797</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11757,21 +11687,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11781,10 +11711,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445279</v>
+        <v>445248</v>
       </c>
       <c r="R104" t="n">
-        <v>6735197</v>
+        <v>6735139</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11827,6 +11757,11 @@
       <c r="AB104" t="inlineStr">
         <is>
           <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Bild 5, högstubbe</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11853,10 +11788,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129237829</v>
+        <v>129237273</v>
       </c>
       <c r="B105" t="n">
-        <v>79627</v>
+        <v>78797</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11864,21 +11799,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11888,10 +11823,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445225</v>
+        <v>445252</v>
       </c>
       <c r="R105" t="n">
-        <v>6735226</v>
+        <v>6735079</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11934,6 +11869,11 @@
       <c r="AB105" t="inlineStr">
         <is>
           <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Bild 4, högstubbe</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11960,45 +11900,50 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129242957</v>
+        <v>129243098</v>
       </c>
       <c r="B106" t="n">
-        <v>8450</v>
+        <v>57722</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445292</v>
+        <v>445374</v>
       </c>
       <c r="R106" t="n">
-        <v>6734957</v>
+        <v>6734891</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12041,6 +11986,11 @@
       <c r="AB106" t="inlineStr">
         <is>
           <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12067,10 +12017,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129243589</v>
+        <v>129238758</v>
       </c>
       <c r="B107" t="n">
-        <v>79037</v>
+        <v>57722</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12078,34 +12028,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445385</v>
+        <v>445349</v>
       </c>
       <c r="R107" t="n">
-        <v>6734971</v>
+        <v>6735194</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12137,7 +12092,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12147,7 +12102,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>2 bilder på torraka med hack</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12174,10 +12134,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129243085</v>
+        <v>129238052</v>
       </c>
       <c r="B108" t="n">
-        <v>79627</v>
+        <v>57885</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12185,37 +12145,46 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>445378</v>
+        <v>445240</v>
       </c>
       <c r="R108" t="n">
-        <v>6734906</v>
+        <v>6735230</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12244,7 +12213,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12254,12 +12223,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>1 bild</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12286,10 +12250,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129243217</v>
+        <v>129238770</v>
       </c>
       <c r="B109" t="n">
-        <v>78795</v>
+        <v>57722</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12297,34 +12261,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>445422</v>
+        <v>445322</v>
       </c>
       <c r="R109" t="n">
-        <v>6734878</v>
+        <v>6735197</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12356,7 +12325,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12366,7 +12335,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Bild på torraka, färska hack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12393,10 +12367,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129237668</v>
+        <v>129243188</v>
       </c>
       <c r="B110" t="n">
-        <v>79037</v>
+        <v>79134</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12404,21 +12378,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12428,10 +12402,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>445302</v>
+        <v>445401</v>
       </c>
       <c r="R110" t="n">
-        <v>6735183</v>
+        <v>6734884</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12463,7 +12437,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12473,12 +12447,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Bild på äldre tall, stam uppåt</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12505,10 +12479,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129247020</v>
+        <v>129239898</v>
       </c>
       <c r="B111" t="n">
-        <v>78795</v>
+        <v>57722</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12516,34 +12490,39 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>445135</v>
+        <v>445362</v>
       </c>
       <c r="R111" t="n">
-        <v>6734998</v>
+        <v>6735431</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12575,7 +12554,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12585,7 +12564,12 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>2 bilder, låga, torraka</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12612,7 +12596,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129240918</v>
+        <v>129239384</v>
       </c>
       <c r="B112" t="n">
         <v>57722</v>
@@ -12652,10 +12636,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>445417</v>
+        <v>445379</v>
       </c>
       <c r="R112" t="n">
-        <v>6735368</v>
+        <v>6735294</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12687,7 +12671,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12697,12 +12681,12 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>2 bilder</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12729,10 +12713,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129240662</v>
+        <v>129243085</v>
       </c>
       <c r="B113" t="n">
-        <v>79656</v>
+        <v>79629</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12740,21 +12724,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12764,10 +12748,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>445517</v>
+        <v>445378</v>
       </c>
       <c r="R113" t="n">
-        <v>6735559</v>
+        <v>6734906</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12799,7 +12783,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12809,7 +12793,12 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12836,10 +12825,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129237612</v>
+        <v>129237668</v>
       </c>
       <c r="B114" t="n">
-        <v>78795</v>
+        <v>79039</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12847,21 +12836,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12871,10 +12860,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>445279</v>
+        <v>445302</v>
       </c>
       <c r="R114" t="n">
-        <v>6735197</v>
+        <v>6735183</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12921,7 +12910,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Bild på två stubbar med äldre tall i bakgrund</t>
+          <t>Bild på äldre tall, stam uppåt</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12951,7 +12940,7 @@
         <v>129238380</v>
       </c>
       <c r="B115" t="n">
-        <v>79627</v>
+        <v>79629</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13060,7 +13049,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129248776</v>
+        <v>129240918</v>
       </c>
       <c r="B116" t="n">
         <v>57722</v>
@@ -13091,7 +13080,7 @@
       <c r="I116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -13100,10 +13089,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>445137</v>
+        <v>445417</v>
       </c>
       <c r="R116" t="n">
-        <v>6734922</v>
+        <v>6735368</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13135,7 +13124,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13145,7 +13134,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13172,32 +13166,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129239096</v>
+        <v>129237612</v>
       </c>
       <c r="B117" t="n">
-        <v>8450</v>
+        <v>78797</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13207,10 +13201,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>445324</v>
+        <v>445279</v>
       </c>
       <c r="R117" t="n">
-        <v>6735285</v>
+        <v>6735197</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13242,7 +13236,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13252,7 +13246,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Bild på två stubbar med äldre tall i bakgrund</t>
         </is>
       </c>
       <c r="AD117" t="b">

--- a/artfynd/A 43504-2025 artfynd.xlsx
+++ b/artfynd/A 43504-2025 artfynd.xlsx
@@ -4491,10 +4491,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129239467</v>
+        <v>129237782</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>58095</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4502,27 +4502,27 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445379</v>
+        <v>445267</v>
       </c>
       <c r="R38" t="n">
-        <v>6735294</v>
+        <v>6735219</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4603,10 +4603,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129237782</v>
+        <v>129239467</v>
       </c>
       <c r="B39" t="n">
-        <v>58095</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4614,27 +4614,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445267</v>
+        <v>445379</v>
       </c>
       <c r="R39" t="n">
-        <v>6735219</v>
+        <v>6735294</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4715,32 +4715,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129240788</v>
+        <v>129238576</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445491</v>
+        <v>445336</v>
       </c>
       <c r="R40" t="n">
-        <v>6735426</v>
+        <v>6735162</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4822,7 +4822,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129238576</v>
+        <v>129238322</v>
       </c>
       <c r="B41" t="n">
         <v>79039</v>
@@ -4857,10 +4857,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445336</v>
+        <v>445325</v>
       </c>
       <c r="R41" t="n">
-        <v>6735162</v>
+        <v>6735153</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4929,7 +4929,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129238322</v>
+        <v>129239093</v>
       </c>
       <c r="B42" t="n">
         <v>79039</v>
@@ -4964,10 +4964,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445325</v>
+        <v>445324</v>
       </c>
       <c r="R42" t="n">
-        <v>6735153</v>
+        <v>6735285</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5036,7 +5036,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129239093</v>
+        <v>129238704</v>
       </c>
       <c r="B43" t="n">
         <v>79039</v>
@@ -5071,10 +5071,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445324</v>
+        <v>445349</v>
       </c>
       <c r="R43" t="n">
-        <v>6735285</v>
+        <v>6735178</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5117,6 +5117,11 @@
       <c r="AB43" t="inlineStr">
         <is>
           <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5143,32 +5148,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129238704</v>
+        <v>129240788</v>
       </c>
       <c r="B44" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5178,10 +5183,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>445349</v>
+        <v>445491</v>
       </c>
       <c r="R44" t="n">
-        <v>6735178</v>
+        <v>6735426</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5213,7 +5218,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5223,12 +5228,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i närområdet</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5576,10 +5576,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129243087</v>
+        <v>129237483</v>
       </c>
       <c r="B48" t="n">
-        <v>78797</v>
+        <v>79039</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5587,21 +5587,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445378</v>
+        <v>445260</v>
       </c>
       <c r="R48" t="n">
-        <v>6734906</v>
+        <v>6735185</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5683,10 +5683,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129237277</v>
+        <v>129237299</v>
       </c>
       <c r="B49" t="n">
-        <v>79629</v>
+        <v>79039</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5694,21 +5694,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5718,10 +5718,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445252</v>
+        <v>445260</v>
       </c>
       <c r="R49" t="n">
-        <v>6735079</v>
+        <v>6735095</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5790,10 +5790,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129237483</v>
+        <v>129237617</v>
       </c>
       <c r="B50" t="n">
-        <v>79039</v>
+        <v>79658</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5801,21 +5801,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5825,10 +5825,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>445260</v>
+        <v>445279</v>
       </c>
       <c r="R50" t="n">
-        <v>6735185</v>
+        <v>6735197</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5897,10 +5897,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129237299</v>
+        <v>129243087</v>
       </c>
       <c r="B51" t="n">
-        <v>79039</v>
+        <v>78797</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5908,21 +5908,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5932,10 +5932,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>445260</v>
+        <v>445378</v>
       </c>
       <c r="R51" t="n">
-        <v>6735095</v>
+        <v>6734906</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6004,10 +6004,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129237617</v>
+        <v>129237277</v>
       </c>
       <c r="B52" t="n">
-        <v>79658</v>
+        <v>79629</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6015,21 +6015,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445279</v>
+        <v>445252</v>
       </c>
       <c r="R52" t="n">
-        <v>6735197</v>
+        <v>6735079</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6870,10 +6870,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129243054</v>
+        <v>129240566</v>
       </c>
       <c r="B60" t="n">
-        <v>78797</v>
+        <v>79039</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6881,21 +6881,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6905,10 +6905,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445339</v>
+        <v>445481</v>
       </c>
       <c r="R60" t="n">
-        <v>6734920</v>
+        <v>6735582</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6940,7 +6940,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6977,7 +6977,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129240566</v>
+        <v>129239929</v>
       </c>
       <c r="B61" t="n">
         <v>79039</v>
@@ -7012,10 +7012,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>445481</v>
+        <v>445421</v>
       </c>
       <c r="R61" t="n">
-        <v>6735582</v>
+        <v>6735402</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7057,7 +7057,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7084,7 +7089,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129239929</v>
+        <v>129240474</v>
       </c>
       <c r="B62" t="n">
         <v>79039</v>
@@ -7119,10 +7124,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>445421</v>
+        <v>445438</v>
       </c>
       <c r="R62" t="n">
-        <v>6735402</v>
+        <v>6735509</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7154,7 +7159,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7164,12 +7169,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7196,7 +7196,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129240474</v>
+        <v>129240967</v>
       </c>
       <c r="B63" t="n">
         <v>79039</v>
@@ -7231,10 +7231,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>445438</v>
+        <v>445414</v>
       </c>
       <c r="R63" t="n">
-        <v>6735509</v>
+        <v>6735285</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7303,10 +7303,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129240967</v>
+        <v>129243054</v>
       </c>
       <c r="B64" t="n">
-        <v>79039</v>
+        <v>78797</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7314,21 +7314,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>445414</v>
+        <v>445339</v>
       </c>
       <c r="R64" t="n">
-        <v>6735285</v>
+        <v>6734920</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8816,32 +8816,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129243245</v>
+        <v>129243104</v>
       </c>
       <c r="B78" t="n">
-        <v>78796</v>
+        <v>8450</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>445422</v>
+        <v>445374</v>
       </c>
       <c r="R78" t="n">
-        <v>6734878</v>
+        <v>6734891</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8923,32 +8923,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129243104</v>
+        <v>129243192</v>
       </c>
       <c r="B79" t="n">
-        <v>8450</v>
+        <v>78797</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8958,10 +8958,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>445374</v>
+        <v>445401</v>
       </c>
       <c r="R79" t="n">
-        <v>6734891</v>
+        <v>6734884</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9030,10 +9030,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129243192</v>
+        <v>129243245</v>
       </c>
       <c r="B80" t="n">
-        <v>78797</v>
+        <v>78796</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9041,21 +9041,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9065,10 +9065,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445401</v>
+        <v>445422</v>
       </c>
       <c r="R80" t="n">
-        <v>6734884</v>
+        <v>6734878</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9244,32 +9244,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129237829</v>
+        <v>129239850</v>
       </c>
       <c r="B82" t="n">
-        <v>79629</v>
+        <v>8450</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9279,10 +9279,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445225</v>
+        <v>445369</v>
       </c>
       <c r="R82" t="n">
-        <v>6735226</v>
+        <v>6735411</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9351,32 +9351,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129237650</v>
+        <v>129242957</v>
       </c>
       <c r="B83" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445279</v>
+        <v>445292</v>
       </c>
       <c r="R83" t="n">
-        <v>6735197</v>
+        <v>6734957</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9458,10 +9458,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129238241</v>
+        <v>129237829</v>
       </c>
       <c r="B84" t="n">
-        <v>79039</v>
+        <v>79629</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9469,21 +9469,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445313</v>
+        <v>445225</v>
       </c>
       <c r="R84" t="n">
-        <v>6735165</v>
+        <v>6735226</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9528,7 +9528,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9565,7 +9565,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129237533</v>
+        <v>129237650</v>
       </c>
       <c r="B85" t="n">
         <v>79039</v>
@@ -9600,10 +9600,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445256</v>
+        <v>445279</v>
       </c>
       <c r="R85" t="n">
-        <v>6735194</v>
+        <v>6735197</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9672,32 +9672,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129239850</v>
+        <v>129238241</v>
       </c>
       <c r="B86" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9707,10 +9707,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445369</v>
+        <v>445313</v>
       </c>
       <c r="R86" t="n">
-        <v>6735411</v>
+        <v>6735165</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9779,32 +9779,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129242957</v>
+        <v>129237533</v>
       </c>
       <c r="B87" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9814,10 +9814,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445292</v>
+        <v>445256</v>
       </c>
       <c r="R87" t="n">
-        <v>6734957</v>
+        <v>6735194</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11560,10 +11560,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129248843</v>
+        <v>129237350</v>
       </c>
       <c r="B103" t="n">
-        <v>91553</v>
+        <v>78797</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11571,38 +11571,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445140</v>
+        <v>445248</v>
       </c>
       <c r="R103" t="n">
-        <v>6734876</v>
+        <v>6735139</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11634,7 +11630,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11644,12 +11640,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild 5, högstubbe</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11676,7 +11672,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129237350</v>
+        <v>129237273</v>
       </c>
       <c r="B104" t="n">
         <v>78797</v>
@@ -11711,10 +11707,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445248</v>
+        <v>445252</v>
       </c>
       <c r="R104" t="n">
-        <v>6735139</v>
+        <v>6735079</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11761,7 +11757,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Bild 5, högstubbe</t>
+          <t>Bild 4, högstubbe</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11788,10 +11784,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129237273</v>
+        <v>129243098</v>
       </c>
       <c r="B105" t="n">
-        <v>78797</v>
+        <v>57722</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11799,34 +11795,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445252</v>
+        <v>445374</v>
       </c>
       <c r="R105" t="n">
-        <v>6735079</v>
+        <v>6734891</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11858,7 +11859,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11868,12 +11869,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Bild 4, högstubbe</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11900,7 +11901,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129243098</v>
+        <v>129238758</v>
       </c>
       <c r="B106" t="n">
         <v>57722</v>
@@ -11931,7 +11932,7 @@
       <c r="I106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -11940,10 +11941,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445374</v>
+        <v>445349</v>
       </c>
       <c r="R106" t="n">
-        <v>6734891</v>
+        <v>6735194</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11975,7 +11976,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11985,12 +11986,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>2 bilder på torraka med hack</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12017,10 +12018,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129238758</v>
+        <v>129248843</v>
       </c>
       <c r="B107" t="n">
-        <v>57722</v>
+        <v>91553</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12028,27 +12029,26 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -12057,10 +12057,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445349</v>
+        <v>445140</v>
       </c>
       <c r="R107" t="n">
-        <v>6735194</v>
+        <v>6734876</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12092,7 +12092,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12102,12 +12102,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>2 bilder på torraka med hack</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD107" t="b">

--- a/artfynd/A 43504-2025 artfynd.xlsx
+++ b/artfynd/A 43504-2025 artfynd.xlsx
@@ -2596,10 +2596,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129248920</v>
+        <v>129248688</v>
       </c>
       <c r="B20" t="n">
-        <v>79658</v>
+        <v>79134</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2607,34 +2607,38 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>967</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445066</v>
+        <v>445078</v>
       </c>
       <c r="R20" t="n">
-        <v>6734914</v>
+        <v>6734933</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,7 +2685,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2712,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129248688</v>
+        <v>129248920</v>
       </c>
       <c r="B21" t="n">
-        <v>79134</v>
+        <v>79658</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,38 +2723,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>967</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>445078</v>
+        <v>445066</v>
       </c>
       <c r="R21" t="n">
-        <v>6734933</v>
+        <v>6734914</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>3 bilder</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4379,38 +4379,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129243809</v>
+        <v>129239467</v>
       </c>
       <c r="B37" t="n">
-        <v>57722</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4419,10 +4419,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445358</v>
+        <v>445379</v>
       </c>
       <c r="R37" t="n">
-        <v>6735035</v>
+        <v>6735294</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4491,27 +4491,27 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129237782</v>
+        <v>129243809</v>
       </c>
       <c r="B38" t="n">
-        <v>58095</v>
+        <v>57722</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4522,7 +4522,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445267</v>
+        <v>445358</v>
       </c>
       <c r="R38" t="n">
-        <v>6735219</v>
+        <v>6735035</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4603,10 +4603,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129239467</v>
+        <v>129237782</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>58095</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4614,27 +4614,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445379</v>
+        <v>445267</v>
       </c>
       <c r="R39" t="n">
-        <v>6735294</v>
+        <v>6735219</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -6111,10 +6111,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129239857</v>
+        <v>129243753</v>
       </c>
       <c r="B53" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6122,39 +6122,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445369</v>
+        <v>445384</v>
       </c>
       <c r="R53" t="n">
-        <v>6735411</v>
+        <v>6734985</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6186,7 +6181,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6196,7 +6191,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6223,7 +6218,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129243753</v>
+        <v>129239740</v>
       </c>
       <c r="B54" t="n">
         <v>79039</v>
@@ -6258,10 +6253,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>445384</v>
+        <v>445356</v>
       </c>
       <c r="R54" t="n">
-        <v>6734985</v>
+        <v>6735366</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6293,7 +6288,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6303,7 +6298,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6330,10 +6325,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129239740</v>
+        <v>129239857</v>
       </c>
       <c r="B55" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6341,34 +6336,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445356</v>
+        <v>445369</v>
       </c>
       <c r="R55" t="n">
-        <v>6735366</v>
+        <v>6735411</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7624,10 +7624,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129247898</v>
+        <v>129238475</v>
       </c>
       <c r="B67" t="n">
-        <v>79658</v>
+        <v>79039</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7635,21 +7635,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7659,10 +7659,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445107</v>
+        <v>445322</v>
       </c>
       <c r="R67" t="n">
-        <v>6735004</v>
+        <v>6735128</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7731,10 +7731,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129238475</v>
+        <v>129247898</v>
       </c>
       <c r="B68" t="n">
-        <v>79039</v>
+        <v>79658</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7742,21 +7742,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7766,10 +7766,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445322</v>
+        <v>445107</v>
       </c>
       <c r="R68" t="n">
-        <v>6735128</v>
+        <v>6735004</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8276,32 +8276,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129238788</v>
+        <v>129237286</v>
       </c>
       <c r="B73" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8311,10 +8311,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445316</v>
+        <v>445252</v>
       </c>
       <c r="R73" t="n">
-        <v>6735207</v>
+        <v>6735079</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8346,7 +8346,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8356,12 +8356,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Rikligt i närområdet</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8388,10 +8383,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129237274</v>
+        <v>129244655</v>
       </c>
       <c r="B74" t="n">
-        <v>79658</v>
+        <v>79629</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8399,21 +8394,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8423,10 +8418,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>445252</v>
+        <v>445217</v>
       </c>
       <c r="R74" t="n">
-        <v>6735079</v>
+        <v>6734997</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8458,7 +8453,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8468,7 +8463,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8495,7 +8490,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129239479</v>
+        <v>129238788</v>
       </c>
       <c r="B75" t="n">
         <v>79039</v>
@@ -8530,10 +8525,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>445379</v>
+        <v>445316</v>
       </c>
       <c r="R75" t="n">
-        <v>6735294</v>
+        <v>6735207</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8576,6 +8571,11 @@
       <c r="AB75" t="inlineStr">
         <is>
           <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Rikligt i närområdet</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8602,32 +8602,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129237286</v>
+        <v>129239479</v>
       </c>
       <c r="B76" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8637,10 +8637,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>445252</v>
+        <v>445379</v>
       </c>
       <c r="R76" t="n">
-        <v>6735079</v>
+        <v>6735294</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8672,7 +8672,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8709,10 +8709,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129244655</v>
+        <v>129237274</v>
       </c>
       <c r="B77" t="n">
-        <v>79629</v>
+        <v>79658</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8720,21 +8720,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8744,10 +8744,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>445217</v>
+        <v>445252</v>
       </c>
       <c r="R77" t="n">
-        <v>6734997</v>
+        <v>6735079</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8779,7 +8779,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8816,32 +8816,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129243104</v>
+        <v>129243245</v>
       </c>
       <c r="B78" t="n">
-        <v>8450</v>
+        <v>78796</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>445374</v>
+        <v>445422</v>
       </c>
       <c r="R78" t="n">
-        <v>6734891</v>
+        <v>6734878</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8923,32 +8923,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129243192</v>
+        <v>129243104</v>
       </c>
       <c r="B79" t="n">
-        <v>78797</v>
+        <v>8450</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8958,10 +8958,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>445401</v>
+        <v>445374</v>
       </c>
       <c r="R79" t="n">
-        <v>6734884</v>
+        <v>6734891</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9030,10 +9030,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129243245</v>
+        <v>129243192</v>
       </c>
       <c r="B80" t="n">
-        <v>78796</v>
+        <v>78797</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9041,21 +9041,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9065,10 +9065,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445422</v>
+        <v>445401</v>
       </c>
       <c r="R80" t="n">
-        <v>6734878</v>
+        <v>6734884</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9244,32 +9244,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129239850</v>
+        <v>129237829</v>
       </c>
       <c r="B82" t="n">
-        <v>8450</v>
+        <v>79629</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9279,10 +9279,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445369</v>
+        <v>445225</v>
       </c>
       <c r="R82" t="n">
-        <v>6735411</v>
+        <v>6735226</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9351,32 +9351,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129242957</v>
+        <v>129237650</v>
       </c>
       <c r="B83" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445292</v>
+        <v>445279</v>
       </c>
       <c r="R83" t="n">
-        <v>6734957</v>
+        <v>6735197</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9458,10 +9458,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129237829</v>
+        <v>129238241</v>
       </c>
       <c r="B84" t="n">
-        <v>79629</v>
+        <v>79039</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9469,21 +9469,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445225</v>
+        <v>445313</v>
       </c>
       <c r="R84" t="n">
-        <v>6735226</v>
+        <v>6735165</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9528,7 +9528,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9565,7 +9565,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129237650</v>
+        <v>129237533</v>
       </c>
       <c r="B85" t="n">
         <v>79039</v>
@@ -9600,10 +9600,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445279</v>
+        <v>445256</v>
       </c>
       <c r="R85" t="n">
-        <v>6735197</v>
+        <v>6735194</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9672,32 +9672,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129238241</v>
+        <v>129239850</v>
       </c>
       <c r="B86" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9707,10 +9707,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445313</v>
+        <v>445369</v>
       </c>
       <c r="R86" t="n">
-        <v>6735165</v>
+        <v>6735411</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9779,32 +9779,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129237533</v>
+        <v>129242957</v>
       </c>
       <c r="B87" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9814,10 +9814,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445256</v>
+        <v>445292</v>
       </c>
       <c r="R87" t="n">
-        <v>6735194</v>
+        <v>6734957</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9886,10 +9886,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129247020</v>
+        <v>129243589</v>
       </c>
       <c r="B88" t="n">
-        <v>78797</v>
+        <v>79039</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9897,21 +9897,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9921,10 +9921,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>445135</v>
+        <v>445385</v>
       </c>
       <c r="R88" t="n">
-        <v>6734998</v>
+        <v>6734971</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9956,7 +9956,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9966,7 +9966,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9993,7 +9993,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129243217</v>
+        <v>129247020</v>
       </c>
       <c r="B89" t="n">
         <v>78797</v>
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>445422</v>
+        <v>445135</v>
       </c>
       <c r="R89" t="n">
-        <v>6734878</v>
+        <v>6734998</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10063,7 +10063,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10100,10 +10100,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129243589</v>
+        <v>129243217</v>
       </c>
       <c r="B90" t="n">
-        <v>79039</v>
+        <v>78797</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10111,21 +10111,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10135,10 +10135,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>445385</v>
+        <v>445422</v>
       </c>
       <c r="R90" t="n">
-        <v>6734971</v>
+        <v>6734878</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10533,10 +10533,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129239693</v>
+        <v>129243051</v>
       </c>
       <c r="B94" t="n">
-        <v>79039</v>
+        <v>79134</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10544,34 +10544,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445362</v>
+        <v>445339</v>
       </c>
       <c r="R94" t="n">
-        <v>6735341</v>
+        <v>6734920</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10603,7 +10606,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10613,12 +10616,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>5 bilder, sumpskog</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10627,6 +10630,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10645,10 +10649,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129243051</v>
+        <v>129239693</v>
       </c>
       <c r="B95" t="n">
-        <v>79134</v>
+        <v>79039</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10656,37 +10660,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445339</v>
+        <v>445362</v>
       </c>
       <c r="R95" t="n">
-        <v>6734920</v>
+        <v>6735341</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10718,7 +10719,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10728,12 +10729,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>3 bilder</t>
+          <t>5 bilder, sumpskog</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10742,7 +10743,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10878,10 +10878,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129240554</v>
+        <v>129240471</v>
       </c>
       <c r="B97" t="n">
-        <v>79629</v>
+        <v>78797</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10889,21 +10889,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10913,10 +10913,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>445435</v>
+        <v>445438</v>
       </c>
       <c r="R97" t="n">
-        <v>6735582</v>
+        <v>6735509</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10963,7 +10963,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>1 bild på högstubbe med låga i bakgrund</t>
+          <t>2 bilder, kolad stubbe samt på spiklav</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10990,10 +10990,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129240492</v>
+        <v>129240554</v>
       </c>
       <c r="B98" t="n">
-        <v>57722</v>
+        <v>79629</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11001,39 +11001,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>445440</v>
+        <v>445435</v>
       </c>
       <c r="R98" t="n">
-        <v>6735522</v>
+        <v>6735582</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11080,7 +11075,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>1 bild på högstubbe med låga i bakgrund</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11107,10 +11102,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129240471</v>
+        <v>129240492</v>
       </c>
       <c r="B99" t="n">
-        <v>78797</v>
+        <v>57722</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11118,34 +11113,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>445438</v>
+        <v>445440</v>
       </c>
       <c r="R99" t="n">
-        <v>6735509</v>
+        <v>6735522</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11192,7 +11192,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>2 bilder, kolad stubbe samt på spiklav</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11560,10 +11560,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129237350</v>
+        <v>129248843</v>
       </c>
       <c r="B103" t="n">
-        <v>78797</v>
+        <v>91560</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11571,34 +11571,38 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445248</v>
+        <v>445140</v>
       </c>
       <c r="R103" t="n">
-        <v>6735139</v>
+        <v>6734876</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11630,7 +11634,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11640,12 +11644,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Bild 5, högstubbe</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11784,10 +11788,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129243098</v>
+        <v>129237350</v>
       </c>
       <c r="B105" t="n">
-        <v>57722</v>
+        <v>78797</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11795,39 +11799,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445374</v>
+        <v>445248</v>
       </c>
       <c r="R105" t="n">
-        <v>6734891</v>
+        <v>6735139</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11859,7 +11858,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11869,12 +11868,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild 5, högstubbe</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11901,7 +11900,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129238758</v>
+        <v>129243098</v>
       </c>
       <c r="B106" t="n">
         <v>57722</v>
@@ -11932,7 +11931,7 @@
       <c r="I106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -11941,10 +11940,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445349</v>
+        <v>445374</v>
       </c>
       <c r="R106" t="n">
-        <v>6735194</v>
+        <v>6734891</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11976,7 +11975,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11986,12 +11985,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>2 bilder på torraka med hack</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12018,10 +12017,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129248843</v>
+        <v>129238758</v>
       </c>
       <c r="B107" t="n">
-        <v>91553</v>
+        <v>57722</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12029,26 +12028,27 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -12057,10 +12057,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445140</v>
+        <v>445349</v>
       </c>
       <c r="R107" t="n">
-        <v>6734876</v>
+        <v>6735194</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12092,7 +12092,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12102,12 +12102,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>2 bilder på torraka med hack</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12250,10 +12250,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129238770</v>
+        <v>129243188</v>
       </c>
       <c r="B109" t="n">
-        <v>57722</v>
+        <v>79134</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12261,39 +12261,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100049</v>
+        <v>967</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>445322</v>
+        <v>445401</v>
       </c>
       <c r="R109" t="n">
-        <v>6735197</v>
+        <v>6734884</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12325,7 +12320,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12335,12 +12330,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Bild på torraka, färska hack</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12367,10 +12362,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129243188</v>
+        <v>129238770</v>
       </c>
       <c r="B110" t="n">
-        <v>79134</v>
+        <v>57722</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12378,34 +12373,39 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>967</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>445401</v>
+        <v>445322</v>
       </c>
       <c r="R110" t="n">
-        <v>6734884</v>
+        <v>6735197</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12437,7 +12437,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12447,12 +12447,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>3 bilder</t>
+          <t>Bild på torraka, färska hack</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12713,10 +12713,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129243085</v>
+        <v>129237668</v>
       </c>
       <c r="B113" t="n">
-        <v>79629</v>
+        <v>79039</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12724,21 +12724,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12748,10 +12748,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>445378</v>
+        <v>445302</v>
       </c>
       <c r="R113" t="n">
-        <v>6734906</v>
+        <v>6735183</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12783,7 +12783,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12793,12 +12793,12 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild på äldre tall, stam uppåt</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12825,10 +12825,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129237668</v>
+        <v>129243085</v>
       </c>
       <c r="B114" t="n">
-        <v>79039</v>
+        <v>79629</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12836,21 +12836,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12860,10 +12860,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>445302</v>
+        <v>445378</v>
       </c>
       <c r="R114" t="n">
-        <v>6735183</v>
+        <v>6734906</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12895,7 +12895,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Bild på äldre tall, stam uppåt</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12937,10 +12937,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129238380</v>
+        <v>129237612</v>
       </c>
       <c r="B115" t="n">
-        <v>79629</v>
+        <v>78797</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12948,21 +12948,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12972,10 +12972,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>445322</v>
+        <v>445279</v>
       </c>
       <c r="R115" t="n">
-        <v>6735151</v>
+        <v>6735197</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13007,7 +13007,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13017,12 +13017,12 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Bild på grov kolad stuppe/låga, tall</t>
+          <t>Bild på två stubbar med äldre tall i bakgrund</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13049,10 +13049,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129240918</v>
+        <v>129238380</v>
       </c>
       <c r="B116" t="n">
-        <v>57722</v>
+        <v>79629</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13060,39 +13060,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>445417</v>
+        <v>445322</v>
       </c>
       <c r="R116" t="n">
-        <v>6735368</v>
+        <v>6735151</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13124,7 +13119,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13134,12 +13129,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild på grov kolad stuppe/låga, tall</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13166,10 +13161,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129237612</v>
+        <v>129240918</v>
       </c>
       <c r="B117" t="n">
-        <v>78797</v>
+        <v>57722</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13177,34 +13172,39 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>445279</v>
+        <v>445417</v>
       </c>
       <c r="R117" t="n">
-        <v>6735197</v>
+        <v>6735368</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13236,7 +13236,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13246,12 +13246,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Bild på två stubbar med äldre tall i bakgrund</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD117" t="b">

--- a/artfynd/A 43504-2025 artfynd.xlsx
+++ b/artfynd/A 43504-2025 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>129249084</v>
       </c>
       <c r="B8" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>129250233</v>
       </c>
       <c r="B9" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>129248937</v>
       </c>
       <c r="B10" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>129249372</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>129254011</v>
       </c>
       <c r="B12" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>129253379</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>129249212</v>
       </c>
       <c r="B14" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>129249287</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>129248989</v>
       </c>
       <c r="B16" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>129251241</v>
       </c>
       <c r="B18" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>129254098</v>
       </c>
       <c r="B19" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>129248688</v>
       </c>
       <c r="B20" t="n">
-        <v>79134</v>
+        <v>79136</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>129248920</v>
       </c>
       <c r="B21" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>129250170</v>
       </c>
       <c r="B22" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>129237525</v>
       </c>
       <c r="B35" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4379,38 +4379,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129239467</v>
+        <v>129243809</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4419,10 +4419,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445379</v>
+        <v>445358</v>
       </c>
       <c r="R37" t="n">
-        <v>6735294</v>
+        <v>6735035</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4491,27 +4491,27 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129243809</v>
+        <v>129237782</v>
       </c>
       <c r="B38" t="n">
-        <v>57722</v>
+        <v>58097</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4522,7 +4522,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445358</v>
+        <v>445267</v>
       </c>
       <c r="R38" t="n">
-        <v>6735035</v>
+        <v>6735219</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4603,10 +4603,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129237782</v>
+        <v>129239467</v>
       </c>
       <c r="B39" t="n">
-        <v>58095</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4614,27 +4614,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445267</v>
+        <v>445379</v>
       </c>
       <c r="R39" t="n">
-        <v>6735219</v>
+        <v>6735294</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4718,7 +4718,7 @@
         <v>129238576</v>
       </c>
       <c r="B40" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>129238322</v>
       </c>
       <c r="B41" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>129239093</v>
       </c>
       <c r="B42" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>129238704</v>
       </c>
       <c r="B43" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>129237826</v>
       </c>
       <c r="B45" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>129237683</v>
       </c>
       <c r="B46" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>129238645</v>
       </c>
       <c r="B47" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5576,10 +5576,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129237483</v>
+        <v>129243087</v>
       </c>
       <c r="B48" t="n">
-        <v>79039</v>
+        <v>78799</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5587,21 +5587,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445260</v>
+        <v>445378</v>
       </c>
       <c r="R48" t="n">
-        <v>6735185</v>
+        <v>6734906</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5683,10 +5683,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129237299</v>
+        <v>129237277</v>
       </c>
       <c r="B49" t="n">
-        <v>79039</v>
+        <v>79631</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5694,21 +5694,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5718,10 +5718,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445260</v>
+        <v>445252</v>
       </c>
       <c r="R49" t="n">
-        <v>6735095</v>
+        <v>6735079</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5790,10 +5790,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129237617</v>
+        <v>129237483</v>
       </c>
       <c r="B50" t="n">
-        <v>79658</v>
+        <v>79041</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5801,21 +5801,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5825,10 +5825,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>445279</v>
+        <v>445260</v>
       </c>
       <c r="R50" t="n">
-        <v>6735197</v>
+        <v>6735185</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5897,10 +5897,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129243087</v>
+        <v>129237299</v>
       </c>
       <c r="B51" t="n">
-        <v>78797</v>
+        <v>79041</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5908,21 +5908,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5932,10 +5932,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>445378</v>
+        <v>445260</v>
       </c>
       <c r="R51" t="n">
-        <v>6734906</v>
+        <v>6735095</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6004,10 +6004,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129237277</v>
+        <v>129237617</v>
       </c>
       <c r="B52" t="n">
-        <v>79629</v>
+        <v>79660</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6015,21 +6015,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445252</v>
+        <v>445279</v>
       </c>
       <c r="R52" t="n">
-        <v>6735079</v>
+        <v>6735197</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6111,10 +6111,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129243753</v>
+        <v>129239857</v>
       </c>
       <c r="B53" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6122,34 +6122,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445384</v>
+        <v>445369</v>
       </c>
       <c r="R53" t="n">
-        <v>6734985</v>
+        <v>6735411</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6181,7 +6186,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6191,7 +6196,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6218,10 +6223,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129239740</v>
+        <v>129243753</v>
       </c>
       <c r="B54" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6253,10 +6258,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>445356</v>
+        <v>445384</v>
       </c>
       <c r="R54" t="n">
-        <v>6735366</v>
+        <v>6734985</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6288,7 +6293,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6298,7 +6303,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6325,10 +6330,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129239857</v>
+        <v>129239740</v>
       </c>
       <c r="B55" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6336,39 +6341,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445369</v>
+        <v>445356</v>
       </c>
       <c r="R55" t="n">
-        <v>6735411</v>
+        <v>6735366</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6437,45 +6437,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129237544</v>
+        <v>129242999</v>
       </c>
       <c r="B56" t="n">
-        <v>79039</v>
+        <v>58097</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>445264</v>
+        <v>445292</v>
       </c>
       <c r="R56" t="n">
-        <v>6735197</v>
+        <v>6734957</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6507,7 +6512,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6517,7 +6522,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6544,10 +6549,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129240724</v>
+        <v>129237544</v>
       </c>
       <c r="B57" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6579,10 +6584,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445509</v>
+        <v>445264</v>
       </c>
       <c r="R57" t="n">
-        <v>6735455</v>
+        <v>6735197</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6614,7 +6619,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6624,7 +6629,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6651,50 +6656,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129242999</v>
+        <v>129240724</v>
       </c>
       <c r="B58" t="n">
-        <v>58095</v>
+        <v>79041</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>445292</v>
+        <v>445509</v>
       </c>
       <c r="R58" t="n">
-        <v>6734957</v>
+        <v>6735455</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6766,7 +6766,7 @@
         <v>129237764</v>
       </c>
       <c r="B59" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         <v>129240566</v>
       </c>
       <c r="B60" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>129239929</v>
       </c>
       <c r="B61" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>129240474</v>
       </c>
       <c r="B62" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>129240967</v>
       </c>
       <c r="B63" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>129243054</v>
       </c>
       <c r="B64" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>129237820</v>
       </c>
       <c r="B66" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7624,10 +7624,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129238475</v>
+        <v>129247898</v>
       </c>
       <c r="B67" t="n">
-        <v>79039</v>
+        <v>79660</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7635,21 +7635,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7659,10 +7659,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445322</v>
+        <v>445107</v>
       </c>
       <c r="R67" t="n">
-        <v>6735128</v>
+        <v>6735004</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7731,10 +7731,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129247898</v>
+        <v>129238475</v>
       </c>
       <c r="B68" t="n">
-        <v>79658</v>
+        <v>79041</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7742,21 +7742,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7766,10 +7766,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445107</v>
+        <v>445322</v>
       </c>
       <c r="R68" t="n">
-        <v>6735004</v>
+        <v>6735128</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7841,7 +7841,7 @@
         <v>129238815</v>
       </c>
       <c r="B69" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>129244530</v>
       </c>
       <c r="B70" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
         <v>129240193</v>
       </c>
       <c r="B72" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8276,32 +8276,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129237286</v>
+        <v>129244655</v>
       </c>
       <c r="B73" t="n">
-        <v>8450</v>
+        <v>79631</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8311,10 +8311,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445252</v>
+        <v>445217</v>
       </c>
       <c r="R73" t="n">
-        <v>6735079</v>
+        <v>6734997</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8346,7 +8346,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8383,32 +8383,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129244655</v>
+        <v>129237286</v>
       </c>
       <c r="B74" t="n">
-        <v>79629</v>
+        <v>8450</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8418,10 +8418,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>445217</v>
+        <v>445252</v>
       </c>
       <c r="R74" t="n">
-        <v>6734997</v>
+        <v>6735079</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8493,7 +8493,7 @@
         <v>129238788</v>
       </c>
       <c r="B75" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8602,10 +8602,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129239479</v>
+        <v>129237274</v>
       </c>
       <c r="B76" t="n">
-        <v>79039</v>
+        <v>79660</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8613,21 +8613,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8637,10 +8637,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>445379</v>
+        <v>445252</v>
       </c>
       <c r="R76" t="n">
-        <v>6735294</v>
+        <v>6735079</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8672,7 +8672,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8709,10 +8709,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129237274</v>
+        <v>129239479</v>
       </c>
       <c r="B77" t="n">
-        <v>79658</v>
+        <v>79041</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8720,21 +8720,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8744,10 +8744,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>445252</v>
+        <v>445379</v>
       </c>
       <c r="R77" t="n">
-        <v>6735079</v>
+        <v>6735294</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8779,7 +8779,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8816,32 +8816,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129243245</v>
+        <v>129243104</v>
       </c>
       <c r="B78" t="n">
-        <v>78796</v>
+        <v>8450</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>445422</v>
+        <v>445374</v>
       </c>
       <c r="R78" t="n">
-        <v>6734878</v>
+        <v>6734891</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8923,32 +8923,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129243104</v>
+        <v>129243245</v>
       </c>
       <c r="B79" t="n">
-        <v>8450</v>
+        <v>78798</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8958,10 +8958,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>445374</v>
+        <v>445422</v>
       </c>
       <c r="R79" t="n">
-        <v>6734891</v>
+        <v>6734878</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9033,7 +9033,7 @@
         <v>129243192</v>
       </c>
       <c r="B80" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>129237621</v>
       </c>
       <c r="B81" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9244,10 +9244,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129237829</v>
+        <v>129237650</v>
       </c>
       <c r="B82" t="n">
-        <v>79629</v>
+        <v>79041</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9255,21 +9255,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9279,10 +9279,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445225</v>
+        <v>445279</v>
       </c>
       <c r="R82" t="n">
-        <v>6735226</v>
+        <v>6735197</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9351,10 +9351,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129237650</v>
+        <v>129238241</v>
       </c>
       <c r="B83" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445279</v>
+        <v>445313</v>
       </c>
       <c r="R83" t="n">
-        <v>6735197</v>
+        <v>6735165</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9458,10 +9458,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129238241</v>
+        <v>129237533</v>
       </c>
       <c r="B84" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445313</v>
+        <v>445256</v>
       </c>
       <c r="R84" t="n">
-        <v>6735165</v>
+        <v>6735194</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9528,7 +9528,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9565,10 +9565,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129237533</v>
+        <v>129237829</v>
       </c>
       <c r="B85" t="n">
-        <v>79039</v>
+        <v>79631</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9576,21 +9576,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9600,10 +9600,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445256</v>
+        <v>445225</v>
       </c>
       <c r="R85" t="n">
-        <v>6735194</v>
+        <v>6735226</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9672,7 +9672,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129239850</v>
+        <v>129242957</v>
       </c>
       <c r="B86" t="n">
         <v>8450</v>
@@ -9707,10 +9707,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445369</v>
+        <v>445292</v>
       </c>
       <c r="R86" t="n">
-        <v>6735411</v>
+        <v>6734957</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9742,7 +9742,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9752,7 +9752,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9779,7 +9779,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129242957</v>
+        <v>129239850</v>
       </c>
       <c r="B87" t="n">
         <v>8450</v>
@@ -9814,10 +9814,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445292</v>
+        <v>445369</v>
       </c>
       <c r="R87" t="n">
-        <v>6734957</v>
+        <v>6735411</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9886,10 +9886,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129243589</v>
+        <v>129247020</v>
       </c>
       <c r="B88" t="n">
-        <v>79039</v>
+        <v>78799</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9897,21 +9897,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9921,10 +9921,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>445385</v>
+        <v>445135</v>
       </c>
       <c r="R88" t="n">
-        <v>6734971</v>
+        <v>6734998</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9956,7 +9956,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9966,7 +9966,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9993,10 +9993,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129247020</v>
+        <v>129243217</v>
       </c>
       <c r="B89" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>445135</v>
+        <v>445422</v>
       </c>
       <c r="R89" t="n">
-        <v>6734998</v>
+        <v>6734878</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10063,7 +10063,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10100,10 +10100,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129243217</v>
+        <v>129243589</v>
       </c>
       <c r="B90" t="n">
-        <v>78797</v>
+        <v>79041</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10111,21 +10111,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10135,10 +10135,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>445422</v>
+        <v>445385</v>
       </c>
       <c r="R90" t="n">
-        <v>6734878</v>
+        <v>6734971</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10207,10 +10207,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129240662</v>
+        <v>129248776</v>
       </c>
       <c r="B91" t="n">
-        <v>79658</v>
+        <v>57724</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10218,34 +10218,39 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>445517</v>
+        <v>445137</v>
       </c>
       <c r="R91" t="n">
-        <v>6735559</v>
+        <v>6734922</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10277,7 +10282,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10287,7 +10292,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10314,10 +10319,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129248776</v>
+        <v>129240662</v>
       </c>
       <c r="B92" t="n">
-        <v>57722</v>
+        <v>79660</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10325,39 +10330,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>445137</v>
+        <v>445517</v>
       </c>
       <c r="R92" t="n">
-        <v>6734922</v>
+        <v>6735559</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10399,7 +10399,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10536,7 +10536,7 @@
         <v>129243051</v>
       </c>
       <c r="B94" t="n">
-        <v>79134</v>
+        <v>79136</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>129239693</v>
       </c>
       <c r="B95" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>129240510</v>
       </c>
       <c r="B96" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10878,10 +10878,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129240471</v>
+        <v>129240492</v>
       </c>
       <c r="B97" t="n">
-        <v>78797</v>
+        <v>57724</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10889,34 +10889,39 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>445438</v>
+        <v>445440</v>
       </c>
       <c r="R97" t="n">
-        <v>6735509</v>
+        <v>6735522</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10963,7 +10968,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>2 bilder, kolad stubbe samt på spiklav</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10990,10 +10995,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129240554</v>
+        <v>129240471</v>
       </c>
       <c r="B98" t="n">
-        <v>79629</v>
+        <v>78799</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11001,21 +11006,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11025,10 +11030,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>445435</v>
+        <v>445438</v>
       </c>
       <c r="R98" t="n">
-        <v>6735582</v>
+        <v>6735509</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11075,7 +11080,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>1 bild på högstubbe med låga i bakgrund</t>
+          <t>2 bilder, kolad stubbe samt på spiklav</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11102,10 +11107,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129240492</v>
+        <v>129240554</v>
       </c>
       <c r="B99" t="n">
-        <v>57722</v>
+        <v>79631</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11113,39 +11118,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>445440</v>
+        <v>445435</v>
       </c>
       <c r="R99" t="n">
-        <v>6735522</v>
+        <v>6735582</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11192,7 +11192,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>1 bild på högstubbe med låga i bakgrund</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11222,7 +11222,7 @@
         <v>129240621</v>
       </c>
       <c r="B100" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11331,10 +11331,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129238933</v>
+        <v>129237880</v>
       </c>
       <c r="B101" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11342,34 +11342,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445307</v>
+        <v>445206</v>
       </c>
       <c r="R101" t="n">
-        <v>6735277</v>
+        <v>6735207</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11401,7 +11406,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11411,12 +11416,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter 3 bilder, sista på två tallstammar</t>
+          <t>Bild, torraka med hack</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11443,10 +11448,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129237880</v>
+        <v>129238933</v>
       </c>
       <c r="B102" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11454,39 +11459,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445206</v>
+        <v>445307</v>
       </c>
       <c r="R102" t="n">
-        <v>6735207</v>
+        <v>6735277</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11528,12 +11528,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Bild, torraka med hack</t>
+          <t>Rikligt i en radie av ca 50 meter 3 bilder, sista på två tallstammar</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11560,10 +11560,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129248843</v>
+        <v>129237273</v>
       </c>
       <c r="B103" t="n">
-        <v>91560</v>
+        <v>78799</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11571,38 +11571,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445140</v>
+        <v>445252</v>
       </c>
       <c r="R103" t="n">
-        <v>6734876</v>
+        <v>6735079</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11634,7 +11630,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11644,12 +11640,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild 4, högstubbe</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11676,10 +11672,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129237273</v>
+        <v>129237350</v>
       </c>
       <c r="B104" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11711,10 +11707,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445252</v>
+        <v>445248</v>
       </c>
       <c r="R104" t="n">
-        <v>6735079</v>
+        <v>6735139</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11761,7 +11757,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Bild 4, högstubbe</t>
+          <t>Bild 5, högstubbe</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11788,10 +11784,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129237350</v>
+        <v>129243098</v>
       </c>
       <c r="B105" t="n">
-        <v>78797</v>
+        <v>57724</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11799,34 +11795,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445248</v>
+        <v>445374</v>
       </c>
       <c r="R105" t="n">
-        <v>6735139</v>
+        <v>6734891</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11858,7 +11859,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11868,12 +11869,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Bild 5, högstubbe</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11900,10 +11901,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129243098</v>
+        <v>129238758</v>
       </c>
       <c r="B106" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11931,7 +11932,7 @@
       <c r="I106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -11940,10 +11941,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445374</v>
+        <v>445349</v>
       </c>
       <c r="R106" t="n">
-        <v>6734891</v>
+        <v>6735194</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11975,7 +11976,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11985,12 +11986,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>2 bilder på torraka med hack</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12017,10 +12018,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129238758</v>
+        <v>129248843</v>
       </c>
       <c r="B107" t="n">
-        <v>57722</v>
+        <v>91562</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12028,27 +12029,26 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -12057,10 +12057,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445349</v>
+        <v>445140</v>
       </c>
       <c r="R107" t="n">
-        <v>6735194</v>
+        <v>6734876</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12092,7 +12092,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12102,12 +12102,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>2 bilder på torraka med hack</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12137,7 +12137,7 @@
         <v>129238052</v>
       </c>
       <c r="B108" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>129243188</v>
       </c>
       <c r="B109" t="n">
-        <v>79134</v>
+        <v>79136</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>129238770</v>
       </c>
       <c r="B110" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12482,7 +12482,7 @@
         <v>129239898</v>
       </c>
       <c r="B111" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>129239384</v>
       </c>
       <c r="B112" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
         <v>129237668</v>
       </c>
       <c r="B113" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>129243085</v>
       </c>
       <c r="B114" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12937,10 +12937,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129237612</v>
+        <v>129240918</v>
       </c>
       <c r="B115" t="n">
-        <v>78797</v>
+        <v>57724</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12948,34 +12948,39 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>445279</v>
+        <v>445417</v>
       </c>
       <c r="R115" t="n">
-        <v>6735197</v>
+        <v>6735368</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13007,7 +13012,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13017,12 +13022,12 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Bild på två stubbar med äldre tall i bakgrund</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13049,10 +13054,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129238380</v>
+        <v>129237612</v>
       </c>
       <c r="B116" t="n">
-        <v>79629</v>
+        <v>78799</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13060,21 +13065,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13084,10 +13089,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>445322</v>
+        <v>445279</v>
       </c>
       <c r="R116" t="n">
-        <v>6735151</v>
+        <v>6735197</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13119,7 +13124,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13129,12 +13134,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Bild på grov kolad stuppe/låga, tall</t>
+          <t>Bild på två stubbar med äldre tall i bakgrund</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13161,10 +13166,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129240918</v>
+        <v>129238380</v>
       </c>
       <c r="B117" t="n">
-        <v>57722</v>
+        <v>79631</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13172,39 +13177,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>445417</v>
+        <v>445322</v>
       </c>
       <c r="R117" t="n">
-        <v>6735368</v>
+        <v>6735151</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13236,7 +13236,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13246,12 +13246,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild på grov kolad stuppe/låga, tall</t>
         </is>
       </c>
       <c r="AD117" t="b">

--- a/artfynd/A 43504-2025 artfynd.xlsx
+++ b/artfynd/A 43504-2025 artfynd.xlsx
@@ -4379,38 +4379,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129243809</v>
+        <v>129239467</v>
       </c>
       <c r="B37" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4419,10 +4419,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445358</v>
+        <v>445379</v>
       </c>
       <c r="R37" t="n">
-        <v>6735035</v>
+        <v>6735294</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4491,27 +4491,27 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129237782</v>
+        <v>129243809</v>
       </c>
       <c r="B38" t="n">
-        <v>58097</v>
+        <v>57724</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4522,7 +4522,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445267</v>
+        <v>445358</v>
       </c>
       <c r="R38" t="n">
-        <v>6735219</v>
+        <v>6735035</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4603,10 +4603,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129239467</v>
+        <v>129237782</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>58097</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4614,27 +4614,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445379</v>
+        <v>445267</v>
       </c>
       <c r="R39" t="n">
-        <v>6735294</v>
+        <v>6735219</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4822,7 +4822,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129238322</v>
+        <v>129238704</v>
       </c>
       <c r="B41" t="n">
         <v>79041</v>
@@ -4857,10 +4857,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445325</v>
+        <v>445349</v>
       </c>
       <c r="R41" t="n">
-        <v>6735153</v>
+        <v>6735178</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4903,6 +4903,11 @@
       <c r="AB41" t="inlineStr">
         <is>
           <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5036,7 +5041,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129238704</v>
+        <v>129238322</v>
       </c>
       <c r="B43" t="n">
         <v>79041</v>
@@ -5071,10 +5076,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445349</v>
+        <v>445325</v>
       </c>
       <c r="R43" t="n">
-        <v>6735178</v>
+        <v>6735153</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5117,11 +5122,6 @@
       <c r="AB43" t="inlineStr">
         <is>
           <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5362,7 +5362,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129237683</v>
+        <v>129238645</v>
       </c>
       <c r="B46" t="n">
         <v>79041</v>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>445282</v>
+        <v>445322</v>
       </c>
       <c r="R46" t="n">
-        <v>6735211</v>
+        <v>6735197</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5469,7 +5469,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129238645</v>
+        <v>129237683</v>
       </c>
       <c r="B47" t="n">
         <v>79041</v>
@@ -5504,10 +5504,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>445322</v>
+        <v>445282</v>
       </c>
       <c r="R47" t="n">
-        <v>6735197</v>
+        <v>6735211</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5576,10 +5576,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129243087</v>
+        <v>129237617</v>
       </c>
       <c r="B48" t="n">
-        <v>78799</v>
+        <v>79660</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5587,21 +5587,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445378</v>
+        <v>445279</v>
       </c>
       <c r="R48" t="n">
-        <v>6734906</v>
+        <v>6735197</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5683,10 +5683,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129237277</v>
+        <v>129237483</v>
       </c>
       <c r="B49" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5694,21 +5694,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5718,10 +5718,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445252</v>
+        <v>445260</v>
       </c>
       <c r="R49" t="n">
-        <v>6735079</v>
+        <v>6735185</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5790,7 +5790,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129237483</v>
+        <v>129237299</v>
       </c>
       <c r="B50" t="n">
         <v>79041</v>
@@ -5828,7 +5828,7 @@
         <v>445260</v>
       </c>
       <c r="R50" t="n">
-        <v>6735185</v>
+        <v>6735095</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5897,10 +5897,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129237299</v>
+        <v>129243087</v>
       </c>
       <c r="B51" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5908,21 +5908,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5932,10 +5932,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>445260</v>
+        <v>445378</v>
       </c>
       <c r="R51" t="n">
-        <v>6735095</v>
+        <v>6734906</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6004,10 +6004,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129237617</v>
+        <v>129237277</v>
       </c>
       <c r="B52" t="n">
-        <v>79660</v>
+        <v>79631</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6015,21 +6015,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445279</v>
+        <v>445252</v>
       </c>
       <c r="R52" t="n">
-        <v>6735197</v>
+        <v>6735079</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6111,10 +6111,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129239857</v>
+        <v>129243753</v>
       </c>
       <c r="B53" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6122,39 +6122,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445369</v>
+        <v>445384</v>
       </c>
       <c r="R53" t="n">
-        <v>6735411</v>
+        <v>6734985</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6186,7 +6181,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6196,7 +6191,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6223,7 +6218,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129243753</v>
+        <v>129239740</v>
       </c>
       <c r="B54" t="n">
         <v>79041</v>
@@ -6258,10 +6253,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>445384</v>
+        <v>445356</v>
       </c>
       <c r="R54" t="n">
-        <v>6734985</v>
+        <v>6735366</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6293,7 +6288,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6303,7 +6298,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6330,10 +6325,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129239740</v>
+        <v>129239857</v>
       </c>
       <c r="B55" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6341,34 +6336,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445356</v>
+        <v>445369</v>
       </c>
       <c r="R55" t="n">
-        <v>6735366</v>
+        <v>6735411</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6437,50 +6437,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129242999</v>
+        <v>129237544</v>
       </c>
       <c r="B56" t="n">
-        <v>58097</v>
+        <v>79041</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>445292</v>
+        <v>445264</v>
       </c>
       <c r="R56" t="n">
-        <v>6734957</v>
+        <v>6735197</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6512,7 +6507,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6522,7 +6517,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6549,7 +6544,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129237544</v>
+        <v>129240724</v>
       </c>
       <c r="B57" t="n">
         <v>79041</v>
@@ -6584,10 +6579,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445264</v>
+        <v>445509</v>
       </c>
       <c r="R57" t="n">
-        <v>6735197</v>
+        <v>6735455</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6619,7 +6614,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6629,7 +6624,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6656,45 +6651,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129240724</v>
+        <v>129242999</v>
       </c>
       <c r="B58" t="n">
-        <v>79041</v>
+        <v>58097</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>445509</v>
+        <v>445292</v>
       </c>
       <c r="R58" t="n">
-        <v>6735455</v>
+        <v>6734957</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6870,7 +6870,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129240566</v>
+        <v>129240967</v>
       </c>
       <c r="B60" t="n">
         <v>79041</v>
@@ -6905,10 +6905,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445481</v>
+        <v>445414</v>
       </c>
       <c r="R60" t="n">
-        <v>6735582</v>
+        <v>6735285</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6977,7 +6977,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129239929</v>
+        <v>129240474</v>
       </c>
       <c r="B61" t="n">
         <v>79041</v>
@@ -7012,10 +7012,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>445421</v>
+        <v>445438</v>
       </c>
       <c r="R61" t="n">
-        <v>6735402</v>
+        <v>6735509</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7057,12 +7057,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7089,7 +7084,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129240474</v>
+        <v>129240566</v>
       </c>
       <c r="B62" t="n">
         <v>79041</v>
@@ -7124,10 +7119,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>445438</v>
+        <v>445481</v>
       </c>
       <c r="R62" t="n">
-        <v>6735509</v>
+        <v>6735582</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7196,7 +7191,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129240967</v>
+        <v>129239929</v>
       </c>
       <c r="B63" t="n">
         <v>79041</v>
@@ -7231,10 +7226,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>445414</v>
+        <v>445421</v>
       </c>
       <c r="R63" t="n">
-        <v>6735285</v>
+        <v>6735402</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7266,7 +7261,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7276,7 +7271,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7410,32 +7410,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129240494</v>
+        <v>129237820</v>
       </c>
       <c r="B65" t="n">
-        <v>8450</v>
+        <v>78798</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7445,10 +7445,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445440</v>
+        <v>445225</v>
       </c>
       <c r="R65" t="n">
-        <v>6735522</v>
+        <v>6735226</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7480,7 +7480,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7517,32 +7517,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129237820</v>
+        <v>129240494</v>
       </c>
       <c r="B66" t="n">
-        <v>78798</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7552,10 +7552,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445225</v>
+        <v>445440</v>
       </c>
       <c r="R66" t="n">
-        <v>6735226</v>
+        <v>6735522</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7587,7 +7587,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7624,10 +7624,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129247898</v>
+        <v>129238815</v>
       </c>
       <c r="B67" t="n">
-        <v>79660</v>
+        <v>57887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7635,37 +7635,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445107</v>
+        <v>445313</v>
       </c>
       <c r="R67" t="n">
-        <v>6735004</v>
+        <v>6735262</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7694,7 +7699,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7704,7 +7709,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7731,10 +7736,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129238475</v>
+        <v>129247898</v>
       </c>
       <c r="B68" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7742,21 +7747,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7766,10 +7771,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445322</v>
+        <v>445107</v>
       </c>
       <c r="R68" t="n">
-        <v>6735128</v>
+        <v>6735004</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7801,7 +7806,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7811,7 +7816,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7838,10 +7843,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129238815</v>
+        <v>129238475</v>
       </c>
       <c r="B69" t="n">
-        <v>57887</v>
+        <v>79041</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7849,42 +7854,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>445313</v>
+        <v>445322</v>
       </c>
       <c r="R69" t="n">
-        <v>6735262</v>
+        <v>6735128</v>
       </c>
       <c r="S69" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8276,32 +8276,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129244655</v>
+        <v>129237286</v>
       </c>
       <c r="B73" t="n">
-        <v>79631</v>
+        <v>8450</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8311,10 +8311,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445217</v>
+        <v>445252</v>
       </c>
       <c r="R73" t="n">
-        <v>6734997</v>
+        <v>6735079</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8346,7 +8346,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8383,32 +8383,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129237286</v>
+        <v>129237274</v>
       </c>
       <c r="B74" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8490,7 +8490,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129238788</v>
+        <v>129239479</v>
       </c>
       <c r="B75" t="n">
         <v>79041</v>
@@ -8525,10 +8525,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>445316</v>
+        <v>445379</v>
       </c>
       <c r="R75" t="n">
-        <v>6735207</v>
+        <v>6735294</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8571,11 +8571,6 @@
       <c r="AB75" t="inlineStr">
         <is>
           <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Rikligt i närområdet</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8602,10 +8597,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129237274</v>
+        <v>129238788</v>
       </c>
       <c r="B76" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8613,21 +8608,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8637,10 +8632,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>445252</v>
+        <v>445316</v>
       </c>
       <c r="R76" t="n">
-        <v>6735079</v>
+        <v>6735207</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8672,7 +8667,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8682,7 +8677,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Rikligt i närområdet</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8709,10 +8709,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129239479</v>
+        <v>129244655</v>
       </c>
       <c r="B77" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8720,21 +8720,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8744,10 +8744,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>445379</v>
+        <v>445217</v>
       </c>
       <c r="R77" t="n">
-        <v>6735294</v>
+        <v>6734997</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8779,7 +8779,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8816,32 +8816,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129243104</v>
+        <v>129243245</v>
       </c>
       <c r="B78" t="n">
-        <v>8450</v>
+        <v>78798</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>445374</v>
+        <v>445422</v>
       </c>
       <c r="R78" t="n">
-        <v>6734891</v>
+        <v>6734878</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8923,10 +8923,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129243245</v>
+        <v>129243192</v>
       </c>
       <c r="B79" t="n">
-        <v>78798</v>
+        <v>78799</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8934,21 +8934,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8958,10 +8958,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>445422</v>
+        <v>445401</v>
       </c>
       <c r="R79" t="n">
-        <v>6734878</v>
+        <v>6734884</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9030,32 +9030,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129243192</v>
+        <v>129243104</v>
       </c>
       <c r="B80" t="n">
-        <v>78799</v>
+        <v>8450</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9065,10 +9065,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445401</v>
+        <v>445374</v>
       </c>
       <c r="R80" t="n">
-        <v>6734884</v>
+        <v>6734891</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9244,7 +9244,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129237650</v>
+        <v>129237639</v>
       </c>
       <c r="B82" t="n">
         <v>79041</v>
@@ -9351,7 +9351,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129238241</v>
+        <v>129237533</v>
       </c>
       <c r="B83" t="n">
         <v>79041</v>
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445313</v>
+        <v>445256</v>
       </c>
       <c r="R83" t="n">
-        <v>6735165</v>
+        <v>6735194</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9458,7 +9458,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129237533</v>
+        <v>129238241</v>
       </c>
       <c r="B84" t="n">
         <v>79041</v>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445256</v>
+        <v>445313</v>
       </c>
       <c r="R84" t="n">
-        <v>6735194</v>
+        <v>6735165</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9528,7 +9528,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9565,32 +9565,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129237829</v>
+        <v>129239850</v>
       </c>
       <c r="B85" t="n">
-        <v>79631</v>
+        <v>8450</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9600,10 +9600,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445225</v>
+        <v>445369</v>
       </c>
       <c r="R85" t="n">
-        <v>6735226</v>
+        <v>6735411</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9635,7 +9635,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9645,7 +9645,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9779,32 +9779,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129239850</v>
+        <v>129237829</v>
       </c>
       <c r="B87" t="n">
-        <v>8450</v>
+        <v>79631</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9814,10 +9814,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445369</v>
+        <v>445225</v>
       </c>
       <c r="R87" t="n">
-        <v>6735411</v>
+        <v>6735226</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9886,10 +9886,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129247020</v>
+        <v>129243589</v>
       </c>
       <c r="B88" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9897,21 +9897,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9921,10 +9921,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>445135</v>
+        <v>445385</v>
       </c>
       <c r="R88" t="n">
-        <v>6734998</v>
+        <v>6734971</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9956,7 +9956,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9966,7 +9966,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9993,7 +9993,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129243217</v>
+        <v>129247020</v>
       </c>
       <c r="B89" t="n">
         <v>78799</v>
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>445422</v>
+        <v>445135</v>
       </c>
       <c r="R89" t="n">
-        <v>6734878</v>
+        <v>6734998</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10063,7 +10063,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10100,10 +10100,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129243589</v>
+        <v>129243217</v>
       </c>
       <c r="B90" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10111,21 +10111,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10135,10 +10135,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>445385</v>
+        <v>445422</v>
       </c>
       <c r="R90" t="n">
-        <v>6734971</v>
+        <v>6734878</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10319,32 +10319,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129240662</v>
+        <v>129239096</v>
       </c>
       <c r="B92" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10354,10 +10354,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>445517</v>
+        <v>445324</v>
       </c>
       <c r="R92" t="n">
-        <v>6735559</v>
+        <v>6735285</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10399,7 +10399,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10426,32 +10426,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129239096</v>
+        <v>129240662</v>
       </c>
       <c r="B93" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10461,10 +10461,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>445324</v>
+        <v>445517</v>
       </c>
       <c r="R93" t="n">
-        <v>6735285</v>
+        <v>6735559</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10496,7 +10496,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11331,10 +11331,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129237880</v>
+        <v>129238933</v>
       </c>
       <c r="B101" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11342,39 +11342,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445206</v>
+        <v>445307</v>
       </c>
       <c r="R101" t="n">
-        <v>6735207</v>
+        <v>6735277</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11406,7 +11401,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11416,12 +11411,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Bild, torraka med hack</t>
+          <t>Rikligt i en radie av ca 50 meter 3 bilder, sista på två tallstammar</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11448,10 +11443,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129238933</v>
+        <v>129237880</v>
       </c>
       <c r="B102" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11459,34 +11454,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445307</v>
+        <v>445206</v>
       </c>
       <c r="R102" t="n">
-        <v>6735277</v>
+        <v>6735207</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11528,12 +11528,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter 3 bilder, sista på två tallstammar</t>
+          <t>Bild, torraka med hack</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11560,10 +11560,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129237273</v>
+        <v>129248843</v>
       </c>
       <c r="B103" t="n">
-        <v>78799</v>
+        <v>91562</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11571,34 +11571,38 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445252</v>
+        <v>445140</v>
       </c>
       <c r="R103" t="n">
-        <v>6735079</v>
+        <v>6734876</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11630,7 +11634,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11640,12 +11644,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Bild 4, högstubbe</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11672,10 +11676,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129237350</v>
+        <v>129243098</v>
       </c>
       <c r="B104" t="n">
-        <v>78799</v>
+        <v>57724</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11683,34 +11687,39 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445248</v>
+        <v>445374</v>
       </c>
       <c r="R104" t="n">
-        <v>6735139</v>
+        <v>6734891</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11742,7 +11751,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11752,12 +11761,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Bild 5, högstubbe</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11784,7 +11793,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129243098</v>
+        <v>129238758</v>
       </c>
       <c r="B105" t="n">
         <v>57724</v>
@@ -11815,7 +11824,7 @@
       <c r="I105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -11824,10 +11833,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445374</v>
+        <v>445349</v>
       </c>
       <c r="R105" t="n">
-        <v>6734891</v>
+        <v>6735194</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11859,7 +11868,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11869,12 +11878,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>2 bilder på torraka med hack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11901,10 +11910,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129238758</v>
+        <v>129237273</v>
       </c>
       <c r="B106" t="n">
-        <v>57724</v>
+        <v>78799</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11912,39 +11921,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445349</v>
+        <v>445252</v>
       </c>
       <c r="R106" t="n">
-        <v>6735194</v>
+        <v>6735079</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11976,7 +11980,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11986,12 +11990,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>2 bilder på torraka med hack</t>
+          <t>Bild 4, högstubbe</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12018,10 +12022,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129248843</v>
+        <v>129237350</v>
       </c>
       <c r="B107" t="n">
-        <v>91562</v>
+        <v>78799</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12029,38 +12033,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445140</v>
+        <v>445248</v>
       </c>
       <c r="R107" t="n">
-        <v>6734876</v>
+        <v>6735139</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12092,7 +12092,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12102,12 +12102,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild 5, högstubbe</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12250,10 +12250,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129243188</v>
+        <v>129238770</v>
       </c>
       <c r="B109" t="n">
-        <v>79136</v>
+        <v>57724</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12261,34 +12261,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>967</v>
+        <v>100049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>445401</v>
+        <v>445322</v>
       </c>
       <c r="R109" t="n">
-        <v>6734884</v>
+        <v>6735197</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12320,7 +12325,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12330,12 +12335,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>3 bilder</t>
+          <t>Bild på torraka, färska hack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12362,10 +12367,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129238770</v>
+        <v>129243188</v>
       </c>
       <c r="B110" t="n">
-        <v>57724</v>
+        <v>79136</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12373,39 +12378,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>967</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>445322</v>
+        <v>445401</v>
       </c>
       <c r="R110" t="n">
-        <v>6735197</v>
+        <v>6734884</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12437,7 +12437,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12447,12 +12447,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Bild på torraka, färska hack</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 43504-2025 artfynd.xlsx
+++ b/artfynd/A 43504-2025 artfynd.xlsx
@@ -4715,32 +4715,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129238576</v>
+        <v>129240788</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445336</v>
+        <v>445491</v>
       </c>
       <c r="R40" t="n">
-        <v>6735162</v>
+        <v>6735426</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4822,7 +4822,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129238704</v>
+        <v>129238576</v>
       </c>
       <c r="B41" t="n">
         <v>79041</v>
@@ -4857,10 +4857,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445349</v>
+        <v>445336</v>
       </c>
       <c r="R41" t="n">
-        <v>6735178</v>
+        <v>6735162</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4903,11 +4903,6 @@
       <c r="AB41" t="inlineStr">
         <is>
           <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4934,7 +4929,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129239093</v>
+        <v>129238704</v>
       </c>
       <c r="B42" t="n">
         <v>79041</v>
@@ -4969,10 +4964,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445324</v>
+        <v>445349</v>
       </c>
       <c r="R42" t="n">
-        <v>6735285</v>
+        <v>6735178</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5015,6 +5010,11 @@
       <c r="AB42" t="inlineStr">
         <is>
           <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5041,7 +5041,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129238322</v>
+        <v>129239093</v>
       </c>
       <c r="B43" t="n">
         <v>79041</v>
@@ -5076,10 +5076,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445325</v>
+        <v>445324</v>
       </c>
       <c r="R43" t="n">
-        <v>6735153</v>
+        <v>6735285</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5148,32 +5148,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129240788</v>
+        <v>129238322</v>
       </c>
       <c r="B44" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5183,10 +5183,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>445491</v>
+        <v>445325</v>
       </c>
       <c r="R44" t="n">
-        <v>6735426</v>
+        <v>6735153</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6870,10 +6870,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129240967</v>
+        <v>129243054</v>
       </c>
       <c r="B60" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6881,21 +6881,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6905,10 +6905,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445414</v>
+        <v>445339</v>
       </c>
       <c r="R60" t="n">
-        <v>6735285</v>
+        <v>6734920</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6940,7 +6940,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6977,7 +6977,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129240474</v>
+        <v>129240967</v>
       </c>
       <c r="B61" t="n">
         <v>79041</v>
@@ -7012,10 +7012,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>445438</v>
+        <v>445414</v>
       </c>
       <c r="R61" t="n">
-        <v>6735509</v>
+        <v>6735285</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7084,7 +7084,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129240566</v>
+        <v>129240474</v>
       </c>
       <c r="B62" t="n">
         <v>79041</v>
@@ -7119,10 +7119,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>445481</v>
+        <v>445438</v>
       </c>
       <c r="R62" t="n">
-        <v>6735582</v>
+        <v>6735509</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7191,7 +7191,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129239929</v>
+        <v>129240566</v>
       </c>
       <c r="B63" t="n">
         <v>79041</v>
@@ -7226,10 +7226,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>445421</v>
+        <v>445481</v>
       </c>
       <c r="R63" t="n">
-        <v>6735402</v>
+        <v>6735582</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7261,7 +7261,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7271,12 +7271,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7303,10 +7298,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129243054</v>
+        <v>129239929</v>
       </c>
       <c r="B64" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7314,21 +7309,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7338,10 +7333,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>445339</v>
+        <v>445421</v>
       </c>
       <c r="R64" t="n">
-        <v>6734920</v>
+        <v>6735402</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7373,7 +7368,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7383,7 +7378,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8276,32 +8276,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129237286</v>
+        <v>129244655</v>
       </c>
       <c r="B73" t="n">
-        <v>8450</v>
+        <v>79631</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8311,10 +8311,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445252</v>
+        <v>445217</v>
       </c>
       <c r="R73" t="n">
-        <v>6735079</v>
+        <v>6734997</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8346,7 +8346,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8709,32 +8709,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129244655</v>
+        <v>129237286</v>
       </c>
       <c r="B77" t="n">
-        <v>79631</v>
+        <v>8450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8744,10 +8744,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>445217</v>
+        <v>445252</v>
       </c>
       <c r="R77" t="n">
-        <v>6734997</v>
+        <v>6735079</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8779,7 +8779,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8923,32 +8923,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129243192</v>
+        <v>129243104</v>
       </c>
       <c r="B79" t="n">
-        <v>78799</v>
+        <v>8450</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8958,10 +8958,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>445401</v>
+        <v>445374</v>
       </c>
       <c r="R79" t="n">
-        <v>6734884</v>
+        <v>6734891</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9030,32 +9030,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129243104</v>
+        <v>129243192</v>
       </c>
       <c r="B80" t="n">
-        <v>8450</v>
+        <v>78799</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9065,10 +9065,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445374</v>
+        <v>445401</v>
       </c>
       <c r="R80" t="n">
-        <v>6734891</v>
+        <v>6734884</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9565,7 +9565,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129239850</v>
+        <v>129242957</v>
       </c>
       <c r="B85" t="n">
         <v>8450</v>
@@ -9600,10 +9600,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445369</v>
+        <v>445292</v>
       </c>
       <c r="R85" t="n">
-        <v>6735411</v>
+        <v>6734957</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9635,7 +9635,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9645,7 +9645,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9672,7 +9672,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129242957</v>
+        <v>129239850</v>
       </c>
       <c r="B86" t="n">
         <v>8450</v>
@@ -9707,10 +9707,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445292</v>
+        <v>445369</v>
       </c>
       <c r="R86" t="n">
-        <v>6734957</v>
+        <v>6735411</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9742,7 +9742,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9752,7 +9752,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10207,10 +10207,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129248776</v>
+        <v>129240662</v>
       </c>
       <c r="B91" t="n">
-        <v>57724</v>
+        <v>79660</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10218,39 +10218,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>445137</v>
+        <v>445517</v>
       </c>
       <c r="R91" t="n">
-        <v>6734922</v>
+        <v>6735559</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10282,7 +10277,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10292,7 +10287,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10319,45 +10314,50 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129239096</v>
+        <v>129248776</v>
       </c>
       <c r="B92" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>445324</v>
+        <v>445137</v>
       </c>
       <c r="R92" t="n">
-        <v>6735285</v>
+        <v>6734922</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10399,7 +10399,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10426,32 +10426,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129240662</v>
+        <v>129239096</v>
       </c>
       <c r="B93" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10461,10 +10461,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>445517</v>
+        <v>445324</v>
       </c>
       <c r="R93" t="n">
-        <v>6735559</v>
+        <v>6735285</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10496,7 +10496,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10878,10 +10878,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129240492</v>
+        <v>129240471</v>
       </c>
       <c r="B97" t="n">
-        <v>57724</v>
+        <v>78799</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10889,39 +10889,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>445440</v>
+        <v>445438</v>
       </c>
       <c r="R97" t="n">
-        <v>6735522</v>
+        <v>6735509</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10968,7 +10963,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>2 bilder, kolad stubbe samt på spiklav</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10995,10 +10990,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129240471</v>
+        <v>129240554</v>
       </c>
       <c r="B98" t="n">
-        <v>78799</v>
+        <v>79631</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11006,21 +11001,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11030,10 +11025,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>445438</v>
+        <v>445435</v>
       </c>
       <c r="R98" t="n">
-        <v>6735509</v>
+        <v>6735582</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11080,7 +11075,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>2 bilder, kolad stubbe samt på spiklav</t>
+          <t>1 bild på högstubbe med låga i bakgrund</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11107,10 +11102,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129240554</v>
+        <v>129240492</v>
       </c>
       <c r="B99" t="n">
-        <v>79631</v>
+        <v>57724</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11118,34 +11113,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>445435</v>
+        <v>445440</v>
       </c>
       <c r="R99" t="n">
-        <v>6735582</v>
+        <v>6735522</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11192,7 +11192,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>1 bild på högstubbe med låga i bakgrund</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11560,10 +11560,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129248843</v>
+        <v>129237273</v>
       </c>
       <c r="B103" t="n">
-        <v>91562</v>
+        <v>78799</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11571,38 +11571,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445140</v>
+        <v>445252</v>
       </c>
       <c r="R103" t="n">
-        <v>6734876</v>
+        <v>6735079</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11634,7 +11630,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11644,12 +11640,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild 4, högstubbe</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11676,10 +11672,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129243098</v>
+        <v>129237350</v>
       </c>
       <c r="B104" t="n">
-        <v>57724</v>
+        <v>78799</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11687,39 +11683,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445374</v>
+        <v>445248</v>
       </c>
       <c r="R104" t="n">
-        <v>6734891</v>
+        <v>6735139</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11751,7 +11742,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11761,12 +11752,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild 5, högstubbe</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11793,10 +11784,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129238758</v>
+        <v>129248843</v>
       </c>
       <c r="B105" t="n">
-        <v>57724</v>
+        <v>91562</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11804,27 +11795,26 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -11833,10 +11823,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445349</v>
+        <v>445140</v>
       </c>
       <c r="R105" t="n">
-        <v>6735194</v>
+        <v>6734876</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11868,7 +11858,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11878,12 +11868,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>2 bilder på torraka med hack</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11910,10 +11900,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129237273</v>
+        <v>129243098</v>
       </c>
       <c r="B106" t="n">
-        <v>78799</v>
+        <v>57724</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11921,34 +11911,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445252</v>
+        <v>445374</v>
       </c>
       <c r="R106" t="n">
-        <v>6735079</v>
+        <v>6734891</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11980,7 +11975,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11990,12 +11985,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Bild 4, högstubbe</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12022,10 +12017,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129237350</v>
+        <v>129238758</v>
       </c>
       <c r="B107" t="n">
-        <v>78799</v>
+        <v>57724</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12033,34 +12028,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445248</v>
+        <v>445349</v>
       </c>
       <c r="R107" t="n">
-        <v>6735139</v>
+        <v>6735194</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12092,7 +12092,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12102,12 +12102,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Bild 5, högstubbe</t>
+          <t>2 bilder på torraka med hack</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12250,10 +12250,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129238770</v>
+        <v>129243188</v>
       </c>
       <c r="B109" t="n">
-        <v>57724</v>
+        <v>79136</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12261,39 +12261,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100049</v>
+        <v>967</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>445322</v>
+        <v>445401</v>
       </c>
       <c r="R109" t="n">
-        <v>6735197</v>
+        <v>6734884</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12325,7 +12320,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12335,12 +12330,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Bild på torraka, färska hack</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12367,10 +12362,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129243188</v>
+        <v>129238770</v>
       </c>
       <c r="B110" t="n">
-        <v>79136</v>
+        <v>57724</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12378,34 +12373,39 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>967</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>445401</v>
+        <v>445322</v>
       </c>
       <c r="R110" t="n">
-        <v>6734884</v>
+        <v>6735197</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12437,7 +12437,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12447,12 +12447,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>3 bilder</t>
+          <t>Bild på torraka, färska hack</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12713,10 +12713,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129237668</v>
+        <v>129243085</v>
       </c>
       <c r="B113" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12724,21 +12724,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12748,10 +12748,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>445302</v>
+        <v>445378</v>
       </c>
       <c r="R113" t="n">
-        <v>6735183</v>
+        <v>6734906</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12783,7 +12783,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12793,12 +12793,12 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Bild på äldre tall, stam uppåt</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12825,10 +12825,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129243085</v>
+        <v>129237668</v>
       </c>
       <c r="B114" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12836,21 +12836,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12860,10 +12860,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>445378</v>
+        <v>445302</v>
       </c>
       <c r="R114" t="n">
-        <v>6734906</v>
+        <v>6735183</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12895,7 +12895,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild på äldre tall, stam uppåt</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12937,10 +12937,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129240918</v>
+        <v>129237612</v>
       </c>
       <c r="B115" t="n">
-        <v>57724</v>
+        <v>78799</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12948,39 +12948,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>445417</v>
+        <v>445279</v>
       </c>
       <c r="R115" t="n">
-        <v>6735368</v>
+        <v>6735197</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13012,7 +13007,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13022,12 +13017,12 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild på två stubbar med äldre tall i bakgrund</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13054,10 +13049,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129237612</v>
+        <v>129238380</v>
       </c>
       <c r="B116" t="n">
-        <v>78799</v>
+        <v>79631</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13065,21 +13060,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13089,10 +13084,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>445279</v>
+        <v>445322</v>
       </c>
       <c r="R116" t="n">
-        <v>6735197</v>
+        <v>6735151</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13124,7 +13119,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13134,12 +13129,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Bild på två stubbar med äldre tall i bakgrund</t>
+          <t>Bild på grov kolad stuppe/låga, tall</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13166,10 +13161,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129238380</v>
+        <v>129240918</v>
       </c>
       <c r="B117" t="n">
-        <v>79631</v>
+        <v>57724</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13177,34 +13172,39 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>445322</v>
+        <v>445417</v>
       </c>
       <c r="R117" t="n">
-        <v>6735151</v>
+        <v>6735368</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13236,7 +13236,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13246,12 +13246,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Bild på grov kolad stuppe/låga, tall</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD117" t="b">

--- a/artfynd/A 43504-2025 artfynd.xlsx
+++ b/artfynd/A 43504-2025 artfynd.xlsx
@@ -4379,38 +4379,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129239467</v>
+        <v>129243809</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4419,10 +4419,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445379</v>
+        <v>445358</v>
       </c>
       <c r="R37" t="n">
-        <v>6735294</v>
+        <v>6735035</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4491,38 +4491,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129243809</v>
+        <v>129239467</v>
       </c>
       <c r="B38" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445358</v>
+        <v>445379</v>
       </c>
       <c r="R38" t="n">
-        <v>6735035</v>
+        <v>6735294</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4715,32 +4715,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129240788</v>
+        <v>129238576</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445491</v>
+        <v>445336</v>
       </c>
       <c r="R40" t="n">
-        <v>6735426</v>
+        <v>6735162</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4822,7 +4822,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129238576</v>
+        <v>129238322</v>
       </c>
       <c r="B41" t="n">
         <v>79041</v>
@@ -4857,10 +4857,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445336</v>
+        <v>445325</v>
       </c>
       <c r="R41" t="n">
-        <v>6735162</v>
+        <v>6735153</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4929,7 +4929,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129238704</v>
+        <v>129239093</v>
       </c>
       <c r="B42" t="n">
         <v>79041</v>
@@ -4964,10 +4964,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445349</v>
+        <v>445324</v>
       </c>
       <c r="R42" t="n">
-        <v>6735178</v>
+        <v>6735285</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5010,11 +5010,6 @@
       <c r="AB42" t="inlineStr">
         <is>
           <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5041,7 +5036,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129239093</v>
+        <v>129238704</v>
       </c>
       <c r="B43" t="n">
         <v>79041</v>
@@ -5076,10 +5071,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445324</v>
+        <v>445349</v>
       </c>
       <c r="R43" t="n">
-        <v>6735285</v>
+        <v>6735178</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5122,6 +5117,11 @@
       <c r="AB43" t="inlineStr">
         <is>
           <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5148,32 +5148,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129238322</v>
+        <v>129240788</v>
       </c>
       <c r="B44" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5183,10 +5183,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>445325</v>
+        <v>445491</v>
       </c>
       <c r="R44" t="n">
-        <v>6735153</v>
+        <v>6735426</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5362,7 +5362,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129238645</v>
+        <v>129237683</v>
       </c>
       <c r="B46" t="n">
         <v>79041</v>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>445322</v>
+        <v>445282</v>
       </c>
       <c r="R46" t="n">
-        <v>6735197</v>
+        <v>6735211</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5469,7 +5469,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129237683</v>
+        <v>129238645</v>
       </c>
       <c r="B47" t="n">
         <v>79041</v>
@@ -5504,10 +5504,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>445282</v>
+        <v>445322</v>
       </c>
       <c r="R47" t="n">
-        <v>6735211</v>
+        <v>6735197</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5576,10 +5576,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129237617</v>
+        <v>129237483</v>
       </c>
       <c r="B48" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5587,21 +5587,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445279</v>
+        <v>445260</v>
       </c>
       <c r="R48" t="n">
-        <v>6735197</v>
+        <v>6735185</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5683,7 +5683,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129237483</v>
+        <v>129237299</v>
       </c>
       <c r="B49" t="n">
         <v>79041</v>
@@ -5721,7 +5721,7 @@
         <v>445260</v>
       </c>
       <c r="R49" t="n">
-        <v>6735185</v>
+        <v>6735095</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5790,10 +5790,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129237299</v>
+        <v>129237617</v>
       </c>
       <c r="B50" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5801,21 +5801,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5825,10 +5825,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>445260</v>
+        <v>445279</v>
       </c>
       <c r="R50" t="n">
-        <v>6735095</v>
+        <v>6735197</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6111,10 +6111,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129243753</v>
+        <v>129239857</v>
       </c>
       <c r="B53" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6122,34 +6122,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445384</v>
+        <v>445369</v>
       </c>
       <c r="R53" t="n">
-        <v>6734985</v>
+        <v>6735411</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6181,7 +6186,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6191,7 +6196,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6218,7 +6223,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129239740</v>
+        <v>129243753</v>
       </c>
       <c r="B54" t="n">
         <v>79041</v>
@@ -6253,10 +6258,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>445356</v>
+        <v>445384</v>
       </c>
       <c r="R54" t="n">
-        <v>6735366</v>
+        <v>6734985</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6288,7 +6293,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6298,7 +6303,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6325,10 +6330,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129239857</v>
+        <v>129239740</v>
       </c>
       <c r="B55" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6336,39 +6341,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445369</v>
+        <v>445356</v>
       </c>
       <c r="R55" t="n">
-        <v>6735411</v>
+        <v>6735366</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6437,45 +6437,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129237544</v>
+        <v>129242999</v>
       </c>
       <c r="B56" t="n">
-        <v>79041</v>
+        <v>58097</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>445264</v>
+        <v>445292</v>
       </c>
       <c r="R56" t="n">
-        <v>6735197</v>
+        <v>6734957</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6507,7 +6512,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6517,7 +6522,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6544,7 +6549,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129240724</v>
+        <v>129237544</v>
       </c>
       <c r="B57" t="n">
         <v>79041</v>
@@ -6579,10 +6584,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445509</v>
+        <v>445264</v>
       </c>
       <c r="R57" t="n">
-        <v>6735455</v>
+        <v>6735197</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6614,7 +6619,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6624,7 +6629,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6651,50 +6656,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129242999</v>
+        <v>129240724</v>
       </c>
       <c r="B58" t="n">
-        <v>58097</v>
+        <v>79041</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>445292</v>
+        <v>445509</v>
       </c>
       <c r="R58" t="n">
-        <v>6734957</v>
+        <v>6735455</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6977,7 +6977,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129240967</v>
+        <v>129240566</v>
       </c>
       <c r="B61" t="n">
         <v>79041</v>
@@ -7012,10 +7012,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>445414</v>
+        <v>445481</v>
       </c>
       <c r="R61" t="n">
-        <v>6735285</v>
+        <v>6735582</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7084,7 +7084,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129240474</v>
+        <v>129239929</v>
       </c>
       <c r="B62" t="n">
         <v>79041</v>
@@ -7119,10 +7119,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>445438</v>
+        <v>445421</v>
       </c>
       <c r="R62" t="n">
-        <v>6735509</v>
+        <v>6735402</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7154,7 +7154,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7164,7 +7164,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7191,7 +7196,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129240566</v>
+        <v>129240474</v>
       </c>
       <c r="B63" t="n">
         <v>79041</v>
@@ -7226,10 +7231,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>445481</v>
+        <v>445438</v>
       </c>
       <c r="R63" t="n">
-        <v>6735582</v>
+        <v>6735509</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7298,7 +7303,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129239929</v>
+        <v>129240967</v>
       </c>
       <c r="B64" t="n">
         <v>79041</v>
@@ -7333,10 +7338,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>445421</v>
+        <v>445414</v>
       </c>
       <c r="R64" t="n">
-        <v>6735402</v>
+        <v>6735285</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7368,7 +7373,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7378,12 +7383,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7624,10 +7624,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129238815</v>
+        <v>129247898</v>
       </c>
       <c r="B67" t="n">
-        <v>57887</v>
+        <v>79660</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7635,42 +7635,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445313</v>
+        <v>445107</v>
       </c>
       <c r="R67" t="n">
-        <v>6735262</v>
+        <v>6735004</v>
       </c>
       <c r="S67" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7699,7 +7694,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7709,7 +7704,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7736,10 +7731,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129247898</v>
+        <v>129238475</v>
       </c>
       <c r="B68" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7747,21 +7742,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7771,10 +7766,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445107</v>
+        <v>445322</v>
       </c>
       <c r="R68" t="n">
-        <v>6735004</v>
+        <v>6735128</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7806,7 +7801,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7816,7 +7811,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7843,10 +7838,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129238475</v>
+        <v>129238815</v>
       </c>
       <c r="B69" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7854,37 +7849,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>445322</v>
+        <v>445313</v>
       </c>
       <c r="R69" t="n">
-        <v>6735128</v>
+        <v>6735262</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7950,32 +7950,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129244530</v>
+        <v>129238778</v>
       </c>
       <c r="B70" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>445217</v>
+        <v>445322</v>
       </c>
       <c r="R70" t="n">
-        <v>6734997</v>
+        <v>6735197</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8020,7 +8020,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8057,32 +8057,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129238778</v>
+        <v>129244530</v>
       </c>
       <c r="B71" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8092,10 +8092,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445322</v>
+        <v>445217</v>
       </c>
       <c r="R71" t="n">
-        <v>6735197</v>
+        <v>6734997</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8276,10 +8276,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129244655</v>
+        <v>129238788</v>
       </c>
       <c r="B73" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8287,21 +8287,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8311,10 +8311,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445217</v>
+        <v>445316</v>
       </c>
       <c r="R73" t="n">
-        <v>6734997</v>
+        <v>6735207</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8346,7 +8346,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8356,7 +8356,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Rikligt i närområdet</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8597,32 +8602,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129238788</v>
+        <v>129237286</v>
       </c>
       <c r="B76" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8632,10 +8637,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>445316</v>
+        <v>445252</v>
       </c>
       <c r="R76" t="n">
-        <v>6735207</v>
+        <v>6735079</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8667,7 +8672,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8677,12 +8682,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Rikligt i närområdet</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8709,32 +8709,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129237286</v>
+        <v>129244655</v>
       </c>
       <c r="B77" t="n">
-        <v>8450</v>
+        <v>79631</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8744,10 +8744,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>445252</v>
+        <v>445217</v>
       </c>
       <c r="R77" t="n">
-        <v>6735079</v>
+        <v>6734997</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8779,7 +8779,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9244,32 +9244,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129237639</v>
+        <v>129239850</v>
       </c>
       <c r="B82" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9279,10 +9279,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445279</v>
+        <v>445369</v>
       </c>
       <c r="R82" t="n">
-        <v>6735197</v>
+        <v>6735411</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9351,32 +9351,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129237533</v>
+        <v>129242957</v>
       </c>
       <c r="B83" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445256</v>
+        <v>445292</v>
       </c>
       <c r="R83" t="n">
-        <v>6735194</v>
+        <v>6734957</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9458,10 +9458,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129238241</v>
+        <v>129237829</v>
       </c>
       <c r="B84" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9469,21 +9469,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445313</v>
+        <v>445225</v>
       </c>
       <c r="R84" t="n">
-        <v>6735165</v>
+        <v>6735226</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9528,7 +9528,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9565,32 +9565,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129242957</v>
+        <v>129237650</v>
       </c>
       <c r="B85" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9600,10 +9600,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445292</v>
+        <v>445279</v>
       </c>
       <c r="R85" t="n">
-        <v>6734957</v>
+        <v>6735197</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9635,7 +9635,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9645,7 +9645,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9672,32 +9672,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129239850</v>
+        <v>129238241</v>
       </c>
       <c r="B86" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9707,10 +9707,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445369</v>
+        <v>445313</v>
       </c>
       <c r="R86" t="n">
-        <v>6735411</v>
+        <v>6735165</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9779,10 +9779,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129237829</v>
+        <v>129237533</v>
       </c>
       <c r="B87" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9790,21 +9790,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9814,10 +9814,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445225</v>
+        <v>445256</v>
       </c>
       <c r="R87" t="n">
-        <v>6735226</v>
+        <v>6735194</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10878,10 +10878,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129240471</v>
+        <v>129240492</v>
       </c>
       <c r="B97" t="n">
-        <v>78799</v>
+        <v>57724</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10889,34 +10889,39 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>445438</v>
+        <v>445440</v>
       </c>
       <c r="R97" t="n">
-        <v>6735509</v>
+        <v>6735522</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10963,7 +10968,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>2 bilder, kolad stubbe samt på spiklav</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10990,10 +10995,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129240554</v>
+        <v>129240471</v>
       </c>
       <c r="B98" t="n">
-        <v>79631</v>
+        <v>78799</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11001,21 +11006,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11025,10 +11030,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>445435</v>
+        <v>445438</v>
       </c>
       <c r="R98" t="n">
-        <v>6735582</v>
+        <v>6735509</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11075,7 +11080,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>1 bild på högstubbe med låga i bakgrund</t>
+          <t>2 bilder, kolad stubbe samt på spiklav</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11102,10 +11107,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129240492</v>
+        <v>129240554</v>
       </c>
       <c r="B99" t="n">
-        <v>57724</v>
+        <v>79631</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11113,39 +11118,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>445440</v>
+        <v>445435</v>
       </c>
       <c r="R99" t="n">
-        <v>6735522</v>
+        <v>6735582</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11192,7 +11192,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>1 bild på högstubbe med låga i bakgrund</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11331,10 +11331,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129238933</v>
+        <v>129237880</v>
       </c>
       <c r="B101" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11342,34 +11342,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445307</v>
+        <v>445206</v>
       </c>
       <c r="R101" t="n">
-        <v>6735277</v>
+        <v>6735207</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11401,7 +11406,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11411,12 +11416,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter 3 bilder, sista på två tallstammar</t>
+          <t>Bild, torraka med hack</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11443,10 +11448,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129237880</v>
+        <v>129238933</v>
       </c>
       <c r="B102" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11454,39 +11459,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445206</v>
+        <v>445307</v>
       </c>
       <c r="R102" t="n">
-        <v>6735207</v>
+        <v>6735277</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11528,12 +11528,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Bild, torraka med hack</t>
+          <t>Rikligt i en radie av ca 50 meter 3 bilder, sista på två tallstammar</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11560,10 +11560,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129237273</v>
+        <v>129243098</v>
       </c>
       <c r="B103" t="n">
-        <v>78799</v>
+        <v>57724</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11571,34 +11571,39 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445252</v>
+        <v>445374</v>
       </c>
       <c r="R103" t="n">
-        <v>6735079</v>
+        <v>6734891</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11630,7 +11635,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11640,12 +11645,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Bild 4, högstubbe</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11672,10 +11677,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129237350</v>
+        <v>129238758</v>
       </c>
       <c r="B104" t="n">
-        <v>78799</v>
+        <v>57724</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11683,34 +11688,39 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445248</v>
+        <v>445349</v>
       </c>
       <c r="R104" t="n">
-        <v>6735139</v>
+        <v>6735194</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11742,7 +11752,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11752,12 +11762,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Bild 5, högstubbe</t>
+          <t>2 bilder på torraka med hack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11787,7 +11797,7 @@
         <v>129248843</v>
       </c>
       <c r="B105" t="n">
-        <v>91562</v>
+        <v>91560</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11900,10 +11910,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129243098</v>
+        <v>129237273</v>
       </c>
       <c r="B106" t="n">
-        <v>57724</v>
+        <v>78799</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11911,39 +11921,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445374</v>
+        <v>445252</v>
       </c>
       <c r="R106" t="n">
-        <v>6734891</v>
+        <v>6735079</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11975,7 +11980,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11985,12 +11990,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild 4, högstubbe</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12017,10 +12022,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129238758</v>
+        <v>129237350</v>
       </c>
       <c r="B107" t="n">
-        <v>57724</v>
+        <v>78799</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12028,39 +12033,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445349</v>
+        <v>445248</v>
       </c>
       <c r="R107" t="n">
-        <v>6735194</v>
+        <v>6735139</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12092,7 +12092,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12102,12 +12102,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>2 bilder på torraka med hack</t>
+          <t>Bild 5, högstubbe</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12937,10 +12937,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129237612</v>
+        <v>129238380</v>
       </c>
       <c r="B115" t="n">
-        <v>78799</v>
+        <v>79631</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12948,21 +12948,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12972,10 +12972,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>445279</v>
+        <v>445322</v>
       </c>
       <c r="R115" t="n">
-        <v>6735197</v>
+        <v>6735151</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13007,7 +13007,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13017,12 +13017,12 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Bild på två stubbar med äldre tall i bakgrund</t>
+          <t>Bild på grov kolad stuppe/låga, tall</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13049,10 +13049,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129238380</v>
+        <v>129237612</v>
       </c>
       <c r="B116" t="n">
-        <v>79631</v>
+        <v>78799</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13060,21 +13060,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13084,10 +13084,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>445322</v>
+        <v>445279</v>
       </c>
       <c r="R116" t="n">
-        <v>6735151</v>
+        <v>6735197</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13119,7 +13119,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13129,12 +13129,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Bild på grov kolad stuppe/låga, tall</t>
+          <t>Bild på två stubbar med äldre tall i bakgrund</t>
         </is>
       </c>
       <c r="AD116" t="b">

--- a/artfynd/A 43504-2025 artfynd.xlsx
+++ b/artfynd/A 43504-2025 artfynd.xlsx
@@ -2596,10 +2596,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129248688</v>
+        <v>129248920</v>
       </c>
       <c r="B20" t="n">
-        <v>79136</v>
+        <v>79660</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2607,38 +2607,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>967</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445078</v>
+        <v>445066</v>
       </c>
       <c r="R20" t="n">
-        <v>6734933</v>
+        <v>6734914</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2685,7 +2681,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>3 bilder</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2712,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129248920</v>
+        <v>129248688</v>
       </c>
       <c r="B21" t="n">
-        <v>79660</v>
+        <v>79136</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,34 +2719,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>967</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>445066</v>
+        <v>445078</v>
       </c>
       <c r="R21" t="n">
-        <v>6734914</v>
+        <v>6734933</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4165,32 +4165,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129237525</v>
+        <v>129237324</v>
       </c>
       <c r="B35" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445251</v>
+        <v>445263</v>
       </c>
       <c r="R35" t="n">
-        <v>6735185</v>
+        <v>6735122</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4272,32 +4272,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129237324</v>
+        <v>129237525</v>
       </c>
       <c r="B36" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4307,10 +4307,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445263</v>
+        <v>445251</v>
       </c>
       <c r="R36" t="n">
-        <v>6735122</v>
+        <v>6735185</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4491,10 +4491,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129239467</v>
+        <v>129237782</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>58097</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4502,27 +4502,27 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445379</v>
+        <v>445267</v>
       </c>
       <c r="R38" t="n">
-        <v>6735294</v>
+        <v>6735219</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4603,10 +4603,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129237782</v>
+        <v>129239467</v>
       </c>
       <c r="B39" t="n">
-        <v>58097</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4614,27 +4614,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445267</v>
+        <v>445379</v>
       </c>
       <c r="R39" t="n">
-        <v>6735219</v>
+        <v>6735294</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4822,7 +4822,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129238322</v>
+        <v>129239093</v>
       </c>
       <c r="B41" t="n">
         <v>79041</v>
@@ -4857,10 +4857,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445325</v>
+        <v>445324</v>
       </c>
       <c r="R41" t="n">
-        <v>6735153</v>
+        <v>6735285</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4929,7 +4929,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129239093</v>
+        <v>129238704</v>
       </c>
       <c r="B42" t="n">
         <v>79041</v>
@@ -4964,10 +4964,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445324</v>
+        <v>445349</v>
       </c>
       <c r="R42" t="n">
-        <v>6735285</v>
+        <v>6735178</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5010,6 +5010,11 @@
       <c r="AB42" t="inlineStr">
         <is>
           <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5036,7 +5041,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129238704</v>
+        <v>129238322</v>
       </c>
       <c r="B43" t="n">
         <v>79041</v>
@@ -5071,10 +5076,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445349</v>
+        <v>445325</v>
       </c>
       <c r="R43" t="n">
-        <v>6735178</v>
+        <v>6735153</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5117,11 +5122,6 @@
       <c r="AB43" t="inlineStr">
         <is>
           <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5362,7 +5362,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129237683</v>
+        <v>129238645</v>
       </c>
       <c r="B46" t="n">
         <v>79041</v>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>445282</v>
+        <v>445322</v>
       </c>
       <c r="R46" t="n">
-        <v>6735211</v>
+        <v>6735197</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5469,7 +5469,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129238645</v>
+        <v>129237683</v>
       </c>
       <c r="B47" t="n">
         <v>79041</v>
@@ -5504,10 +5504,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>445322</v>
+        <v>445282</v>
       </c>
       <c r="R47" t="n">
-        <v>6735197</v>
+        <v>6735211</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5576,10 +5576,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129237483</v>
+        <v>129243087</v>
       </c>
       <c r="B48" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5587,21 +5587,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445260</v>
+        <v>445378</v>
       </c>
       <c r="R48" t="n">
-        <v>6735185</v>
+        <v>6734906</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5683,10 +5683,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129237299</v>
+        <v>129237277</v>
       </c>
       <c r="B49" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5694,21 +5694,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5718,10 +5718,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445260</v>
+        <v>445252</v>
       </c>
       <c r="R49" t="n">
-        <v>6735095</v>
+        <v>6735079</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5790,10 +5790,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129237617</v>
+        <v>129237483</v>
       </c>
       <c r="B50" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5801,21 +5801,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5825,10 +5825,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>445279</v>
+        <v>445260</v>
       </c>
       <c r="R50" t="n">
-        <v>6735197</v>
+        <v>6735185</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5897,10 +5897,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129243087</v>
+        <v>129237617</v>
       </c>
       <c r="B51" t="n">
-        <v>78799</v>
+        <v>79660</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5908,21 +5908,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5932,10 +5932,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>445378</v>
+        <v>445279</v>
       </c>
       <c r="R51" t="n">
-        <v>6734906</v>
+        <v>6735197</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6004,10 +6004,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129237277</v>
+        <v>129237299</v>
       </c>
       <c r="B52" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6015,21 +6015,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445252</v>
+        <v>445260</v>
       </c>
       <c r="R52" t="n">
-        <v>6735079</v>
+        <v>6735095</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6111,10 +6111,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129239857</v>
+        <v>129243753</v>
       </c>
       <c r="B53" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6122,39 +6122,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445369</v>
+        <v>445384</v>
       </c>
       <c r="R53" t="n">
-        <v>6735411</v>
+        <v>6734985</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6186,7 +6181,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6196,7 +6191,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6223,7 +6218,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129243753</v>
+        <v>129239740</v>
       </c>
       <c r="B54" t="n">
         <v>79041</v>
@@ -6258,10 +6253,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>445384</v>
+        <v>445356</v>
       </c>
       <c r="R54" t="n">
-        <v>6734985</v>
+        <v>6735366</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6293,7 +6288,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6303,7 +6298,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6330,10 +6325,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129239740</v>
+        <v>129239857</v>
       </c>
       <c r="B55" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6341,34 +6336,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445356</v>
+        <v>445369</v>
       </c>
       <c r="R55" t="n">
-        <v>6735366</v>
+        <v>6735411</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6437,50 +6437,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129242999</v>
+        <v>129237544</v>
       </c>
       <c r="B56" t="n">
-        <v>58097</v>
+        <v>79041</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>445292</v>
+        <v>445264</v>
       </c>
       <c r="R56" t="n">
-        <v>6734957</v>
+        <v>6735197</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6512,7 +6507,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6522,7 +6517,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6549,7 +6544,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129237544</v>
+        <v>129240724</v>
       </c>
       <c r="B57" t="n">
         <v>79041</v>
@@ -6584,10 +6579,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445264</v>
+        <v>445509</v>
       </c>
       <c r="R57" t="n">
-        <v>6735197</v>
+        <v>6735455</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6619,7 +6614,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6629,7 +6624,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6656,45 +6651,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129240724</v>
+        <v>129242999</v>
       </c>
       <c r="B58" t="n">
-        <v>79041</v>
+        <v>58097</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>445509</v>
+        <v>445292</v>
       </c>
       <c r="R58" t="n">
-        <v>6735455</v>
+        <v>6734957</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6870,10 +6870,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129243054</v>
+        <v>129240566</v>
       </c>
       <c r="B60" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6881,21 +6881,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6905,10 +6905,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445339</v>
+        <v>445481</v>
       </c>
       <c r="R60" t="n">
-        <v>6734920</v>
+        <v>6735582</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6940,7 +6940,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6977,7 +6977,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129240566</v>
+        <v>129240967</v>
       </c>
       <c r="B61" t="n">
         <v>79041</v>
@@ -7012,10 +7012,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>445481</v>
+        <v>445414</v>
       </c>
       <c r="R61" t="n">
-        <v>6735582</v>
+        <v>6735285</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7084,7 +7084,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129239929</v>
+        <v>129240474</v>
       </c>
       <c r="B62" t="n">
         <v>79041</v>
@@ -7119,10 +7119,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>445421</v>
+        <v>445438</v>
       </c>
       <c r="R62" t="n">
-        <v>6735402</v>
+        <v>6735509</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7154,7 +7154,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7164,12 +7164,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7196,7 +7191,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129240474</v>
+        <v>129239929</v>
       </c>
       <c r="B63" t="n">
         <v>79041</v>
@@ -7231,10 +7226,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>445438</v>
+        <v>445421</v>
       </c>
       <c r="R63" t="n">
-        <v>6735509</v>
+        <v>6735402</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7266,7 +7261,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7276,7 +7271,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7303,10 +7303,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129240967</v>
+        <v>129243054</v>
       </c>
       <c r="B64" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7314,21 +7314,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>445414</v>
+        <v>445339</v>
       </c>
       <c r="R64" t="n">
-        <v>6735285</v>
+        <v>6734920</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7410,32 +7410,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129237820</v>
+        <v>129240494</v>
       </c>
       <c r="B65" t="n">
-        <v>78798</v>
+        <v>8450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7445,10 +7445,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445225</v>
+        <v>445440</v>
       </c>
       <c r="R65" t="n">
-        <v>6735226</v>
+        <v>6735522</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7480,7 +7480,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7517,32 +7517,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129240494</v>
+        <v>129237820</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>78798</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7552,10 +7552,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445440</v>
+        <v>445225</v>
       </c>
       <c r="R66" t="n">
-        <v>6735522</v>
+        <v>6735226</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7587,7 +7587,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7950,32 +7950,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129238778</v>
+        <v>129244530</v>
       </c>
       <c r="B70" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>445322</v>
+        <v>445217</v>
       </c>
       <c r="R70" t="n">
-        <v>6735197</v>
+        <v>6734997</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8020,7 +8020,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8057,32 +8057,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129244530</v>
+        <v>129238778</v>
       </c>
       <c r="B71" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8092,10 +8092,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445217</v>
+        <v>445322</v>
       </c>
       <c r="R71" t="n">
-        <v>6734997</v>
+        <v>6735197</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8276,10 +8276,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129238788</v>
+        <v>129237274</v>
       </c>
       <c r="B73" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8287,21 +8287,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8311,10 +8311,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445316</v>
+        <v>445252</v>
       </c>
       <c r="R73" t="n">
-        <v>6735207</v>
+        <v>6735079</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8346,7 +8346,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8356,12 +8356,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Rikligt i närområdet</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8388,10 +8383,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129237274</v>
+        <v>129239479</v>
       </c>
       <c r="B74" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8399,21 +8394,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8423,10 +8418,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>445252</v>
+        <v>445379</v>
       </c>
       <c r="R74" t="n">
-        <v>6735079</v>
+        <v>6735294</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8458,7 +8453,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8468,7 +8463,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8495,7 +8490,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129239479</v>
+        <v>129238788</v>
       </c>
       <c r="B75" t="n">
         <v>79041</v>
@@ -8530,10 +8525,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>445379</v>
+        <v>445316</v>
       </c>
       <c r="R75" t="n">
-        <v>6735294</v>
+        <v>6735207</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8576,6 +8571,11 @@
       <c r="AB75" t="inlineStr">
         <is>
           <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Rikligt i närområdet</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8816,32 +8816,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129243245</v>
+        <v>129243104</v>
       </c>
       <c r="B78" t="n">
-        <v>78798</v>
+        <v>8450</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>445422</v>
+        <v>445374</v>
       </c>
       <c r="R78" t="n">
-        <v>6734878</v>
+        <v>6734891</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8923,32 +8923,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129243104</v>
+        <v>129243192</v>
       </c>
       <c r="B79" t="n">
-        <v>8450</v>
+        <v>78799</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8958,10 +8958,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>445374</v>
+        <v>445401</v>
       </c>
       <c r="R79" t="n">
-        <v>6734891</v>
+        <v>6734884</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9030,10 +9030,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129243192</v>
+        <v>129243245</v>
       </c>
       <c r="B80" t="n">
-        <v>78799</v>
+        <v>78798</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9041,21 +9041,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9065,10 +9065,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445401</v>
+        <v>445422</v>
       </c>
       <c r="R80" t="n">
-        <v>6734884</v>
+        <v>6734878</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9244,32 +9244,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129239850</v>
+        <v>129237533</v>
       </c>
       <c r="B82" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9279,10 +9279,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445369</v>
+        <v>445256</v>
       </c>
       <c r="R82" t="n">
-        <v>6735411</v>
+        <v>6735194</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9351,7 +9351,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129242957</v>
+        <v>129239850</v>
       </c>
       <c r="B83" t="n">
         <v>8450</v>
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445292</v>
+        <v>445369</v>
       </c>
       <c r="R83" t="n">
-        <v>6734957</v>
+        <v>6735411</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9458,32 +9458,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129237829</v>
+        <v>129242957</v>
       </c>
       <c r="B84" t="n">
-        <v>79631</v>
+        <v>8450</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445225</v>
+        <v>445292</v>
       </c>
       <c r="R84" t="n">
-        <v>6735226</v>
+        <v>6734957</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9528,7 +9528,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9565,7 +9565,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129237650</v>
+        <v>129237639</v>
       </c>
       <c r="B85" t="n">
         <v>79041</v>
@@ -9779,10 +9779,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129237533</v>
+        <v>129237829</v>
       </c>
       <c r="B87" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9790,21 +9790,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9814,10 +9814,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445256</v>
+        <v>445225</v>
       </c>
       <c r="R87" t="n">
-        <v>6735194</v>
+        <v>6735226</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9886,10 +9886,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129243589</v>
+        <v>129247020</v>
       </c>
       <c r="B88" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9897,21 +9897,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9921,10 +9921,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>445385</v>
+        <v>445135</v>
       </c>
       <c r="R88" t="n">
-        <v>6734971</v>
+        <v>6734998</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9956,7 +9956,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9966,7 +9966,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9993,7 +9993,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129247020</v>
+        <v>129243217</v>
       </c>
       <c r="B89" t="n">
         <v>78799</v>
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>445135</v>
+        <v>445422</v>
       </c>
       <c r="R89" t="n">
-        <v>6734998</v>
+        <v>6734878</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10063,7 +10063,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10100,10 +10100,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129243217</v>
+        <v>129243589</v>
       </c>
       <c r="B90" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10111,21 +10111,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10135,10 +10135,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>445422</v>
+        <v>445385</v>
       </c>
       <c r="R90" t="n">
-        <v>6734878</v>
+        <v>6734971</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10533,10 +10533,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129243051</v>
+        <v>129239693</v>
       </c>
       <c r="B94" t="n">
-        <v>79136</v>
+        <v>79041</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10544,37 +10544,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445339</v>
+        <v>445362</v>
       </c>
       <c r="R94" t="n">
-        <v>6734920</v>
+        <v>6735341</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10606,7 +10603,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10616,12 +10613,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>3 bilder</t>
+          <t>5 bilder, sumpskog</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10630,7 +10627,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10649,10 +10645,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129239693</v>
+        <v>129243051</v>
       </c>
       <c r="B95" t="n">
-        <v>79041</v>
+        <v>79136</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10660,34 +10656,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445362</v>
+        <v>445339</v>
       </c>
       <c r="R95" t="n">
-        <v>6735341</v>
+        <v>6734920</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10719,7 +10718,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10729,12 +10728,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>5 bilder, sumpskog</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10743,6 +10742,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -11331,10 +11331,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129237880</v>
+        <v>129238933</v>
       </c>
       <c r="B101" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11342,39 +11342,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445206</v>
+        <v>445307</v>
       </c>
       <c r="R101" t="n">
-        <v>6735207</v>
+        <v>6735277</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11406,7 +11401,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11416,12 +11411,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Bild, torraka med hack</t>
+          <t>Rikligt i en radie av ca 50 meter 3 bilder, sista på två tallstammar</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11448,10 +11443,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129238933</v>
+        <v>129237880</v>
       </c>
       <c r="B102" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11459,34 +11454,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445307</v>
+        <v>445206</v>
       </c>
       <c r="R102" t="n">
-        <v>6735277</v>
+        <v>6735207</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11528,12 +11528,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter 3 bilder, sista på två tallstammar</t>
+          <t>Bild, torraka med hack</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11797,7 +11797,7 @@
         <v>129248843</v>
       </c>
       <c r="B105" t="n">
-        <v>91560</v>
+        <v>91561</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12250,10 +12250,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129243188</v>
+        <v>129238770</v>
       </c>
       <c r="B109" t="n">
-        <v>79136</v>
+        <v>57724</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12261,34 +12261,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>967</v>
+        <v>100049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>445401</v>
+        <v>445322</v>
       </c>
       <c r="R109" t="n">
-        <v>6734884</v>
+        <v>6735197</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12320,7 +12325,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12330,12 +12335,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>3 bilder</t>
+          <t>Bild på torraka, färska hack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12362,10 +12367,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129238770</v>
+        <v>129243188</v>
       </c>
       <c r="B110" t="n">
-        <v>57724</v>
+        <v>79136</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12373,39 +12378,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>967</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>445322</v>
+        <v>445401</v>
       </c>
       <c r="R110" t="n">
-        <v>6735197</v>
+        <v>6734884</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12437,7 +12437,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12447,12 +12447,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Bild på torraka, färska hack</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12937,10 +12937,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129238380</v>
+        <v>129240918</v>
       </c>
       <c r="B115" t="n">
-        <v>79631</v>
+        <v>57724</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12948,34 +12948,39 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>445322</v>
+        <v>445417</v>
       </c>
       <c r="R115" t="n">
-        <v>6735151</v>
+        <v>6735368</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13007,7 +13012,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13017,12 +13022,12 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Bild på grov kolad stuppe/låga, tall</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13161,10 +13166,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129240918</v>
+        <v>129238380</v>
       </c>
       <c r="B117" t="n">
-        <v>57724</v>
+        <v>79631</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13172,39 +13177,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>445417</v>
+        <v>445322</v>
       </c>
       <c r="R117" t="n">
-        <v>6735368</v>
+        <v>6735151</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13236,7 +13236,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13246,12 +13246,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild på grov kolad stuppe/låga, tall</t>
         </is>
       </c>
       <c r="AD117" t="b">

--- a/artfynd/A 43504-2025 artfynd.xlsx
+++ b/artfynd/A 43504-2025 artfynd.xlsx
@@ -2596,10 +2596,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129248920</v>
+        <v>129248688</v>
       </c>
       <c r="B20" t="n">
-        <v>79660</v>
+        <v>79136</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2607,34 +2607,38 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>967</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445066</v>
+        <v>445078</v>
       </c>
       <c r="R20" t="n">
-        <v>6734914</v>
+        <v>6734933</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,7 +2685,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2712,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129248688</v>
+        <v>129248920</v>
       </c>
       <c r="B21" t="n">
-        <v>79136</v>
+        <v>79660</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,38 +2723,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>967</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>445078</v>
+        <v>445066</v>
       </c>
       <c r="R21" t="n">
-        <v>6734933</v>
+        <v>6734914</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>3 bilder</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4379,27 +4379,27 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129243809</v>
+        <v>129237782</v>
       </c>
       <c r="B37" t="n">
-        <v>57724</v>
+        <v>58097</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4410,7 +4410,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4419,10 +4419,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445358</v>
+        <v>445267</v>
       </c>
       <c r="R37" t="n">
-        <v>6735035</v>
+        <v>6735219</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4491,27 +4491,27 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129237782</v>
+        <v>129243809</v>
       </c>
       <c r="B38" t="n">
-        <v>58097</v>
+        <v>57724</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4522,7 +4522,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445267</v>
+        <v>445358</v>
       </c>
       <c r="R38" t="n">
-        <v>6735219</v>
+        <v>6735035</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4715,32 +4715,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129238576</v>
+        <v>129240788</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445336</v>
+        <v>445491</v>
       </c>
       <c r="R40" t="n">
-        <v>6735162</v>
+        <v>6735426</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4822,7 +4822,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129239093</v>
+        <v>129238576</v>
       </c>
       <c r="B41" t="n">
         <v>79041</v>
@@ -4857,10 +4857,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445324</v>
+        <v>445336</v>
       </c>
       <c r="R41" t="n">
-        <v>6735285</v>
+        <v>6735162</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4929,7 +4929,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129238704</v>
+        <v>129238322</v>
       </c>
       <c r="B42" t="n">
         <v>79041</v>
@@ -4964,10 +4964,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445349</v>
+        <v>445325</v>
       </c>
       <c r="R42" t="n">
-        <v>6735178</v>
+        <v>6735153</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5010,11 +5010,6 @@
       <c r="AB42" t="inlineStr">
         <is>
           <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5041,7 +5036,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129238322</v>
+        <v>129239093</v>
       </c>
       <c r="B43" t="n">
         <v>79041</v>
@@ -5076,10 +5071,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445325</v>
+        <v>445324</v>
       </c>
       <c r="R43" t="n">
-        <v>6735153</v>
+        <v>6735285</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5148,32 +5143,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129240788</v>
+        <v>129238704</v>
       </c>
       <c r="B44" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5183,10 +5178,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>445491</v>
+        <v>445349</v>
       </c>
       <c r="R44" t="n">
-        <v>6735426</v>
+        <v>6735178</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5218,7 +5213,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5228,7 +5223,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5362,7 +5362,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129238645</v>
+        <v>129237683</v>
       </c>
       <c r="B46" t="n">
         <v>79041</v>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>445322</v>
+        <v>445282</v>
       </c>
       <c r="R46" t="n">
-        <v>6735197</v>
+        <v>6735211</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5469,7 +5469,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129237683</v>
+        <v>129238645</v>
       </c>
       <c r="B47" t="n">
         <v>79041</v>
@@ -5504,10 +5504,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>445282</v>
+        <v>445322</v>
       </c>
       <c r="R47" t="n">
-        <v>6735211</v>
+        <v>6735197</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5576,10 +5576,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129243087</v>
+        <v>129237483</v>
       </c>
       <c r="B48" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5587,21 +5587,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445378</v>
+        <v>445260</v>
       </c>
       <c r="R48" t="n">
-        <v>6734906</v>
+        <v>6735185</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5683,10 +5683,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129237277</v>
+        <v>129243087</v>
       </c>
       <c r="B49" t="n">
-        <v>79631</v>
+        <v>78799</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5694,21 +5694,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5718,10 +5718,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445252</v>
+        <v>445378</v>
       </c>
       <c r="R49" t="n">
-        <v>6735079</v>
+        <v>6734906</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5753,7 +5753,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5790,10 +5790,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129237483</v>
+        <v>129237277</v>
       </c>
       <c r="B50" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5801,21 +5801,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5825,10 +5825,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>445260</v>
+        <v>445252</v>
       </c>
       <c r="R50" t="n">
-        <v>6735185</v>
+        <v>6735079</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5897,10 +5897,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129237617</v>
+        <v>129237299</v>
       </c>
       <c r="B51" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5908,21 +5908,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5932,10 +5932,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>445279</v>
+        <v>445260</v>
       </c>
       <c r="R51" t="n">
-        <v>6735197</v>
+        <v>6735095</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6004,10 +6004,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129237299</v>
+        <v>129237617</v>
       </c>
       <c r="B52" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6015,21 +6015,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445260</v>
+        <v>445279</v>
       </c>
       <c r="R52" t="n">
-        <v>6735095</v>
+        <v>6735197</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6977,7 +6977,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129240967</v>
+        <v>129239929</v>
       </c>
       <c r="B61" t="n">
         <v>79041</v>
@@ -7012,10 +7012,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>445414</v>
+        <v>445421</v>
       </c>
       <c r="R61" t="n">
-        <v>6735285</v>
+        <v>6735402</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7057,7 +7057,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7191,7 +7196,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129239929</v>
+        <v>129240967</v>
       </c>
       <c r="B63" t="n">
         <v>79041</v>
@@ -7226,10 +7231,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>445421</v>
+        <v>445414</v>
       </c>
       <c r="R63" t="n">
-        <v>6735402</v>
+        <v>6735285</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7261,7 +7266,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7271,12 +7276,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7410,32 +7410,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129240494</v>
+        <v>129237820</v>
       </c>
       <c r="B65" t="n">
-        <v>8450</v>
+        <v>78798</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7445,10 +7445,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445440</v>
+        <v>445225</v>
       </c>
       <c r="R65" t="n">
-        <v>6735522</v>
+        <v>6735226</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7480,7 +7480,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7517,32 +7517,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129237820</v>
+        <v>129240494</v>
       </c>
       <c r="B66" t="n">
-        <v>78798</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7552,10 +7552,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445225</v>
+        <v>445440</v>
       </c>
       <c r="R66" t="n">
-        <v>6735226</v>
+        <v>6735522</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7587,7 +7587,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7950,32 +7950,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129244530</v>
+        <v>129238778</v>
       </c>
       <c r="B70" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>445217</v>
+        <v>445322</v>
       </c>
       <c r="R70" t="n">
-        <v>6734997</v>
+        <v>6735197</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8020,7 +8020,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8057,32 +8057,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129238778</v>
+        <v>129244530</v>
       </c>
       <c r="B71" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8092,10 +8092,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445322</v>
+        <v>445217</v>
       </c>
       <c r="R71" t="n">
-        <v>6735197</v>
+        <v>6734997</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8276,10 +8276,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129237274</v>
+        <v>129238788</v>
       </c>
       <c r="B73" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8287,21 +8287,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8311,10 +8311,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445252</v>
+        <v>445316</v>
       </c>
       <c r="R73" t="n">
-        <v>6735079</v>
+        <v>6735207</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8346,7 +8346,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8356,7 +8356,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Rikligt i närområdet</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8490,10 +8495,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129238788</v>
+        <v>129237274</v>
       </c>
       <c r="B75" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8501,21 +8506,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8525,10 +8530,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>445316</v>
+        <v>445252</v>
       </c>
       <c r="R75" t="n">
-        <v>6735207</v>
+        <v>6735079</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8560,7 +8565,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8570,12 +8575,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Rikligt i närområdet</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8816,32 +8816,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129243104</v>
+        <v>129243192</v>
       </c>
       <c r="B78" t="n">
-        <v>8450</v>
+        <v>78799</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>445374</v>
+        <v>445401</v>
       </c>
       <c r="R78" t="n">
-        <v>6734891</v>
+        <v>6734884</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8923,10 +8923,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129243192</v>
+        <v>129243245</v>
       </c>
       <c r="B79" t="n">
-        <v>78799</v>
+        <v>78798</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8934,21 +8934,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8958,10 +8958,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>445401</v>
+        <v>445422</v>
       </c>
       <c r="R79" t="n">
-        <v>6734884</v>
+        <v>6734878</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9030,32 +9030,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129243245</v>
+        <v>129243104</v>
       </c>
       <c r="B80" t="n">
-        <v>78798</v>
+        <v>8450</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9065,10 +9065,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445422</v>
+        <v>445374</v>
       </c>
       <c r="R80" t="n">
-        <v>6734878</v>
+        <v>6734891</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9244,7 +9244,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129237533</v>
+        <v>129237650</v>
       </c>
       <c r="B82" t="n">
         <v>79041</v>
@@ -9279,10 +9279,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445256</v>
+        <v>445279</v>
       </c>
       <c r="R82" t="n">
-        <v>6735194</v>
+        <v>6735197</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9351,32 +9351,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129239850</v>
+        <v>129238241</v>
       </c>
       <c r="B83" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445369</v>
+        <v>445313</v>
       </c>
       <c r="R83" t="n">
-        <v>6735411</v>
+        <v>6735165</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9458,32 +9458,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129242957</v>
+        <v>129237533</v>
       </c>
       <c r="B84" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445292</v>
+        <v>445256</v>
       </c>
       <c r="R84" t="n">
-        <v>6734957</v>
+        <v>6735194</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9528,7 +9528,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9565,10 +9565,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129237639</v>
+        <v>129237829</v>
       </c>
       <c r="B85" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9576,21 +9576,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9600,10 +9600,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445279</v>
+        <v>445225</v>
       </c>
       <c r="R85" t="n">
-        <v>6735197</v>
+        <v>6735226</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9672,32 +9672,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129238241</v>
+        <v>129239850</v>
       </c>
       <c r="B86" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9707,10 +9707,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445313</v>
+        <v>445369</v>
       </c>
       <c r="R86" t="n">
-        <v>6735165</v>
+        <v>6735411</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9779,32 +9779,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129237829</v>
+        <v>129242957</v>
       </c>
       <c r="B87" t="n">
-        <v>79631</v>
+        <v>8450</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9814,10 +9814,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445225</v>
+        <v>445292</v>
       </c>
       <c r="R87" t="n">
-        <v>6735226</v>
+        <v>6734957</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9886,10 +9886,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129247020</v>
+        <v>129243589</v>
       </c>
       <c r="B88" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9897,21 +9897,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9921,10 +9921,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>445135</v>
+        <v>445385</v>
       </c>
       <c r="R88" t="n">
-        <v>6734998</v>
+        <v>6734971</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9956,7 +9956,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9966,7 +9966,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9993,7 +9993,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129243217</v>
+        <v>129247020</v>
       </c>
       <c r="B89" t="n">
         <v>78799</v>
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>445422</v>
+        <v>445135</v>
       </c>
       <c r="R89" t="n">
-        <v>6734878</v>
+        <v>6734998</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10063,7 +10063,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10100,10 +10100,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129243589</v>
+        <v>129243217</v>
       </c>
       <c r="B90" t="n">
-        <v>79041</v>
+        <v>78799</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10111,21 +10111,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10135,10 +10135,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>445385</v>
+        <v>445422</v>
       </c>
       <c r="R90" t="n">
-        <v>6734971</v>
+        <v>6734878</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10533,10 +10533,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129239693</v>
+        <v>129243051</v>
       </c>
       <c r="B94" t="n">
-        <v>79041</v>
+        <v>79136</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10544,34 +10544,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445362</v>
+        <v>445339</v>
       </c>
       <c r="R94" t="n">
-        <v>6735341</v>
+        <v>6734920</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10603,7 +10606,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10613,12 +10616,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>5 bilder, sumpskog</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10627,6 +10630,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10645,10 +10649,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129243051</v>
+        <v>129239693</v>
       </c>
       <c r="B95" t="n">
-        <v>79136</v>
+        <v>79041</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10656,37 +10660,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445339</v>
+        <v>445362</v>
       </c>
       <c r="R95" t="n">
-        <v>6734920</v>
+        <v>6735341</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10718,7 +10719,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10728,12 +10729,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>3 bilder</t>
+          <t>5 bilder, sumpskog</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10742,7 +10743,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -11560,10 +11560,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129243098</v>
+        <v>129248843</v>
       </c>
       <c r="B103" t="n">
-        <v>57724</v>
+        <v>91561</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11571,27 +11571,26 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -11600,10 +11599,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445374</v>
+        <v>445140</v>
       </c>
       <c r="R103" t="n">
-        <v>6734891</v>
+        <v>6734876</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11635,7 +11634,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11645,7 +11644,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
@@ -11677,10 +11676,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129238758</v>
+        <v>129237273</v>
       </c>
       <c r="B104" t="n">
-        <v>57724</v>
+        <v>78799</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11688,39 +11687,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445349</v>
+        <v>445252</v>
       </c>
       <c r="R104" t="n">
-        <v>6735194</v>
+        <v>6735079</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11752,7 +11746,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11762,12 +11756,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>2 bilder på torraka med hack</t>
+          <t>Bild 4, högstubbe</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11794,10 +11788,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129248843</v>
+        <v>129237350</v>
       </c>
       <c r="B105" t="n">
-        <v>91561</v>
+        <v>78799</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11805,38 +11799,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445140</v>
+        <v>445248</v>
       </c>
       <c r="R105" t="n">
-        <v>6734876</v>
+        <v>6735139</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11868,7 +11858,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11878,12 +11868,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild 5, högstubbe</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11910,10 +11900,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129237273</v>
+        <v>129243098</v>
       </c>
       <c r="B106" t="n">
-        <v>78799</v>
+        <v>57724</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11921,34 +11911,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445252</v>
+        <v>445374</v>
       </c>
       <c r="R106" t="n">
-        <v>6735079</v>
+        <v>6734891</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11980,7 +11975,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11990,12 +11985,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Bild 4, högstubbe</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12022,10 +12017,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129237350</v>
+        <v>129238758</v>
       </c>
       <c r="B107" t="n">
-        <v>78799</v>
+        <v>57724</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12033,34 +12028,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445248</v>
+        <v>445349</v>
       </c>
       <c r="R107" t="n">
-        <v>6735139</v>
+        <v>6735194</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12092,7 +12092,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12102,12 +12102,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Bild 5, högstubbe</t>
+          <t>2 bilder på torraka med hack</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12250,10 +12250,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129238770</v>
+        <v>129243188</v>
       </c>
       <c r="B109" t="n">
-        <v>57724</v>
+        <v>79136</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12261,39 +12261,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100049</v>
+        <v>967</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>445322</v>
+        <v>445401</v>
       </c>
       <c r="R109" t="n">
-        <v>6735197</v>
+        <v>6734884</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12325,7 +12320,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12335,12 +12330,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Bild på torraka, färska hack</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12367,10 +12362,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129243188</v>
+        <v>129238770</v>
       </c>
       <c r="B110" t="n">
-        <v>79136</v>
+        <v>57724</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12378,34 +12373,39 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>967</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>445401</v>
+        <v>445322</v>
       </c>
       <c r="R110" t="n">
-        <v>6734884</v>
+        <v>6735197</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12437,7 +12437,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12447,12 +12447,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>3 bilder</t>
+          <t>Bild på torraka, färska hack</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12713,10 +12713,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129243085</v>
+        <v>129237668</v>
       </c>
       <c r="B113" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12724,21 +12724,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12748,10 +12748,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>445378</v>
+        <v>445302</v>
       </c>
       <c r="R113" t="n">
-        <v>6734906</v>
+        <v>6735183</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12783,7 +12783,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12793,12 +12793,12 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild på äldre tall, stam uppåt</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12825,10 +12825,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129237668</v>
+        <v>129243085</v>
       </c>
       <c r="B114" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12836,21 +12836,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12860,10 +12860,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>445302</v>
+        <v>445378</v>
       </c>
       <c r="R114" t="n">
-        <v>6735183</v>
+        <v>6734906</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12895,7 +12895,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Bild på äldre tall, stam uppåt</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD114" t="b">

--- a/artfynd/A 43504-2025 artfynd.xlsx
+++ b/artfynd/A 43504-2025 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>129249084</v>
       </c>
       <c r="B8" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>129250233</v>
       </c>
       <c r="B9" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>129249372</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>129254011</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>129253379</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>129249212</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>129249287</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>129248989</v>
       </c>
       <c r="B16" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>129251241</v>
       </c>
       <c r="B18" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>129254098</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>129248688</v>
       </c>
       <c r="B20" t="n">
-        <v>79136</v>
+        <v>79138</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>129248920</v>
       </c>
       <c r="B21" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4165,32 +4165,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129237324</v>
+        <v>129237525</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445263</v>
+        <v>445251</v>
       </c>
       <c r="R35" t="n">
-        <v>6735122</v>
+        <v>6735185</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4272,32 +4272,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129237525</v>
+        <v>129237324</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4307,10 +4307,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445251</v>
+        <v>445263</v>
       </c>
       <c r="R36" t="n">
-        <v>6735185</v>
+        <v>6735122</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4379,27 +4379,27 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129237782</v>
+        <v>129243809</v>
       </c>
       <c r="B37" t="n">
-        <v>58097</v>
+        <v>57724</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4410,7 +4410,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4419,10 +4419,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445267</v>
+        <v>445358</v>
       </c>
       <c r="R37" t="n">
-        <v>6735219</v>
+        <v>6735035</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4491,38 +4491,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129243809</v>
+        <v>129239467</v>
       </c>
       <c r="B38" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445358</v>
+        <v>445379</v>
       </c>
       <c r="R38" t="n">
-        <v>6735035</v>
+        <v>6735294</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4603,10 +4603,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129239467</v>
+        <v>129237782</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>58097</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4614,27 +4614,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445379</v>
+        <v>445267</v>
       </c>
       <c r="R39" t="n">
-        <v>6735294</v>
+        <v>6735219</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4715,32 +4715,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129240788</v>
+        <v>129238576</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445491</v>
+        <v>445336</v>
       </c>
       <c r="R40" t="n">
-        <v>6735426</v>
+        <v>6735162</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4822,10 +4822,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129238576</v>
+        <v>129238322</v>
       </c>
       <c r="B41" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4857,10 +4857,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445336</v>
+        <v>445325</v>
       </c>
       <c r="R41" t="n">
-        <v>6735162</v>
+        <v>6735153</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4929,10 +4929,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129238322</v>
+        <v>129239093</v>
       </c>
       <c r="B42" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4964,10 +4964,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445325</v>
+        <v>445324</v>
       </c>
       <c r="R42" t="n">
-        <v>6735153</v>
+        <v>6735285</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5036,10 +5036,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129239093</v>
+        <v>129238704</v>
       </c>
       <c r="B43" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5071,10 +5071,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445324</v>
+        <v>445349</v>
       </c>
       <c r="R43" t="n">
-        <v>6735285</v>
+        <v>6735178</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5117,6 +5117,11 @@
       <c r="AB43" t="inlineStr">
         <is>
           <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5143,32 +5148,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129238704</v>
+        <v>129240788</v>
       </c>
       <c r="B44" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5178,10 +5183,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>445349</v>
+        <v>445491</v>
       </c>
       <c r="R44" t="n">
-        <v>6735178</v>
+        <v>6735426</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5213,7 +5218,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5223,12 +5228,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i närområdet</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5258,7 +5258,7 @@
         <v>129237826</v>
       </c>
       <c r="B45" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>129237683</v>
       </c>
       <c r="B46" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>129238645</v>
       </c>
       <c r="B47" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>129237483</v>
       </c>
       <c r="B48" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5683,10 +5683,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129243087</v>
+        <v>129237299</v>
       </c>
       <c r="B49" t="n">
-        <v>78799</v>
+        <v>79043</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5694,21 +5694,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5718,10 +5718,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445378</v>
+        <v>445260</v>
       </c>
       <c r="R49" t="n">
-        <v>6734906</v>
+        <v>6735095</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5753,7 +5753,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5790,10 +5790,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129237277</v>
+        <v>129237617</v>
       </c>
       <c r="B50" t="n">
-        <v>79631</v>
+        <v>79662</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5801,21 +5801,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5825,10 +5825,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>445252</v>
+        <v>445279</v>
       </c>
       <c r="R50" t="n">
-        <v>6735079</v>
+        <v>6735197</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5897,10 +5897,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129237299</v>
+        <v>129243087</v>
       </c>
       <c r="B51" t="n">
-        <v>79041</v>
+        <v>78801</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5908,21 +5908,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5932,10 +5932,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>445260</v>
+        <v>445378</v>
       </c>
       <c r="R51" t="n">
-        <v>6735095</v>
+        <v>6734906</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6004,10 +6004,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129237617</v>
+        <v>129237277</v>
       </c>
       <c r="B52" t="n">
-        <v>79660</v>
+        <v>79633</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6015,21 +6015,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445279</v>
+        <v>445252</v>
       </c>
       <c r="R52" t="n">
-        <v>6735197</v>
+        <v>6735079</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6111,10 +6111,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129243753</v>
+        <v>129239857</v>
       </c>
       <c r="B53" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6122,34 +6122,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445384</v>
+        <v>445369</v>
       </c>
       <c r="R53" t="n">
-        <v>6734985</v>
+        <v>6735411</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6181,7 +6186,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6191,7 +6196,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6218,10 +6223,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129239740</v>
+        <v>129243753</v>
       </c>
       <c r="B54" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6253,10 +6258,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>445356</v>
+        <v>445384</v>
       </c>
       <c r="R54" t="n">
-        <v>6735366</v>
+        <v>6734985</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6288,7 +6293,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6298,7 +6303,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6325,10 +6330,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129239857</v>
+        <v>129239740</v>
       </c>
       <c r="B55" t="n">
-        <v>57724</v>
+        <v>79043</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6336,39 +6341,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445369</v>
+        <v>445356</v>
       </c>
       <c r="R55" t="n">
-        <v>6735411</v>
+        <v>6735366</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6437,45 +6437,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129237544</v>
+        <v>129242999</v>
       </c>
       <c r="B56" t="n">
-        <v>79041</v>
+        <v>58097</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>445264</v>
+        <v>445292</v>
       </c>
       <c r="R56" t="n">
-        <v>6735197</v>
+        <v>6734957</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6507,7 +6512,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6517,7 +6522,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6544,10 +6549,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129240724</v>
+        <v>129237544</v>
       </c>
       <c r="B57" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6579,10 +6584,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445509</v>
+        <v>445264</v>
       </c>
       <c r="R57" t="n">
-        <v>6735455</v>
+        <v>6735197</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6614,7 +6619,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6624,7 +6629,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6651,50 +6656,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129242999</v>
+        <v>129240724</v>
       </c>
       <c r="B58" t="n">
-        <v>58097</v>
+        <v>79043</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>445292</v>
+        <v>445509</v>
       </c>
       <c r="R58" t="n">
-        <v>6734957</v>
+        <v>6735455</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6766,7 +6766,7 @@
         <v>129237764</v>
       </c>
       <c r="B59" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         <v>129240566</v>
       </c>
       <c r="B60" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>129239929</v>
       </c>
       <c r="B61" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>129240474</v>
       </c>
       <c r="B62" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>129240967</v>
       </c>
       <c r="B63" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>129243054</v>
       </c>
       <c r="B64" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7410,32 +7410,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129237820</v>
+        <v>129240494</v>
       </c>
       <c r="B65" t="n">
-        <v>78798</v>
+        <v>8450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7445,10 +7445,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445225</v>
+        <v>445440</v>
       </c>
       <c r="R65" t="n">
-        <v>6735226</v>
+        <v>6735522</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7480,7 +7480,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7517,32 +7517,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129240494</v>
+        <v>129237820</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>78800</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7552,10 +7552,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445440</v>
+        <v>445225</v>
       </c>
       <c r="R66" t="n">
-        <v>6735522</v>
+        <v>6735226</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7587,7 +7587,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7627,7 +7627,7 @@
         <v>129247898</v>
       </c>
       <c r="B67" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>129238475</v>
       </c>
       <c r="B68" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7950,32 +7950,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129238778</v>
+        <v>129244530</v>
       </c>
       <c r="B70" t="n">
-        <v>8450</v>
+        <v>79662</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>445322</v>
+        <v>445217</v>
       </c>
       <c r="R70" t="n">
-        <v>6735197</v>
+        <v>6734997</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8020,7 +8020,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8057,32 +8057,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129244530</v>
+        <v>129238778</v>
       </c>
       <c r="B71" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8092,10 +8092,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445217</v>
+        <v>445322</v>
       </c>
       <c r="R71" t="n">
-        <v>6734997</v>
+        <v>6735197</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8276,32 +8276,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129238788</v>
+        <v>129237286</v>
       </c>
       <c r="B73" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8311,10 +8311,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445316</v>
+        <v>445252</v>
       </c>
       <c r="R73" t="n">
-        <v>6735207</v>
+        <v>6735079</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8346,7 +8346,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8356,12 +8356,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Rikligt i närområdet</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8388,10 +8383,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129239479</v>
+        <v>129238788</v>
       </c>
       <c r="B74" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8423,10 +8418,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>445379</v>
+        <v>445316</v>
       </c>
       <c r="R74" t="n">
-        <v>6735294</v>
+        <v>6735207</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8469,6 +8464,11 @@
       <c r="AB74" t="inlineStr">
         <is>
           <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Rikligt i närområdet</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8498,7 +8498,7 @@
         <v>129237274</v>
       </c>
       <c r="B75" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8602,32 +8602,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129237286</v>
+        <v>129239479</v>
       </c>
       <c r="B76" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8637,10 +8637,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>445252</v>
+        <v>445379</v>
       </c>
       <c r="R76" t="n">
-        <v>6735079</v>
+        <v>6735294</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8672,7 +8672,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8712,7 +8712,7 @@
         <v>129244655</v>
       </c>
       <c r="B77" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8816,10 +8816,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129243192</v>
+        <v>129243245</v>
       </c>
       <c r="B78" t="n">
-        <v>78799</v>
+        <v>78800</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8827,21 +8827,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>445401</v>
+        <v>445422</v>
       </c>
       <c r="R78" t="n">
-        <v>6734884</v>
+        <v>6734878</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8923,32 +8923,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129243245</v>
+        <v>129243104</v>
       </c>
       <c r="B79" t="n">
-        <v>78798</v>
+        <v>8450</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8958,10 +8958,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>445422</v>
+        <v>445374</v>
       </c>
       <c r="R79" t="n">
-        <v>6734878</v>
+        <v>6734891</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9030,32 +9030,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129243104</v>
+        <v>129243192</v>
       </c>
       <c r="B80" t="n">
-        <v>8450</v>
+        <v>78801</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9065,10 +9065,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445374</v>
+        <v>445401</v>
       </c>
       <c r="R80" t="n">
-        <v>6734891</v>
+        <v>6734884</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9140,7 +9140,7 @@
         <v>129237621</v>
       </c>
       <c r="B81" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9244,32 +9244,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129237650</v>
+        <v>129239850</v>
       </c>
       <c r="B82" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9279,10 +9279,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445279</v>
+        <v>445369</v>
       </c>
       <c r="R82" t="n">
-        <v>6735197</v>
+        <v>6735411</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9351,32 +9351,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129238241</v>
+        <v>129242957</v>
       </c>
       <c r="B83" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445313</v>
+        <v>445292</v>
       </c>
       <c r="R83" t="n">
-        <v>6735165</v>
+        <v>6734957</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9458,10 +9458,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129237533</v>
+        <v>129237650</v>
       </c>
       <c r="B84" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445256</v>
+        <v>445279</v>
       </c>
       <c r="R84" t="n">
-        <v>6735194</v>
+        <v>6735197</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9565,10 +9565,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129237829</v>
+        <v>129238241</v>
       </c>
       <c r="B85" t="n">
-        <v>79631</v>
+        <v>79043</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9576,21 +9576,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9600,10 +9600,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445225</v>
+        <v>445313</v>
       </c>
       <c r="R85" t="n">
-        <v>6735226</v>
+        <v>6735165</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9635,7 +9635,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9645,7 +9645,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9672,32 +9672,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129239850</v>
+        <v>129237533</v>
       </c>
       <c r="B86" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9707,10 +9707,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445369</v>
+        <v>445256</v>
       </c>
       <c r="R86" t="n">
-        <v>6735411</v>
+        <v>6735194</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9742,7 +9742,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9752,7 +9752,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9779,32 +9779,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129242957</v>
+        <v>129237829</v>
       </c>
       <c r="B87" t="n">
-        <v>8450</v>
+        <v>79633</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9814,10 +9814,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445292</v>
+        <v>445225</v>
       </c>
       <c r="R87" t="n">
-        <v>6734957</v>
+        <v>6735226</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9886,10 +9886,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129243589</v>
+        <v>129247020</v>
       </c>
       <c r="B88" t="n">
-        <v>79041</v>
+        <v>78801</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9897,21 +9897,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9921,10 +9921,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>445385</v>
+        <v>445135</v>
       </c>
       <c r="R88" t="n">
-        <v>6734971</v>
+        <v>6734998</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9956,7 +9956,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9966,7 +9966,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9993,10 +9993,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129247020</v>
+        <v>129243217</v>
       </c>
       <c r="B89" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>445135</v>
+        <v>445422</v>
       </c>
       <c r="R89" t="n">
-        <v>6734998</v>
+        <v>6734878</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10063,7 +10063,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10100,10 +10100,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129243217</v>
+        <v>129243589</v>
       </c>
       <c r="B90" t="n">
-        <v>78799</v>
+        <v>79043</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10111,21 +10111,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10135,10 +10135,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>445422</v>
+        <v>445385</v>
       </c>
       <c r="R90" t="n">
-        <v>6734878</v>
+        <v>6734971</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10210,7 +10210,7 @@
         <v>129240662</v>
       </c>
       <c r="B91" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10533,10 +10533,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129243051</v>
+        <v>129239693</v>
       </c>
       <c r="B94" t="n">
-        <v>79136</v>
+        <v>79043</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10544,37 +10544,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445339</v>
+        <v>445362</v>
       </c>
       <c r="R94" t="n">
-        <v>6734920</v>
+        <v>6735341</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10606,7 +10603,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10616,12 +10613,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>3 bilder</t>
+          <t>5 bilder, sumpskog</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10630,7 +10627,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10649,10 +10645,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129239693</v>
+        <v>129243051</v>
       </c>
       <c r="B95" t="n">
-        <v>79041</v>
+        <v>79138</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10660,34 +10656,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445362</v>
+        <v>445339</v>
       </c>
       <c r="R95" t="n">
-        <v>6735341</v>
+        <v>6734920</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10719,7 +10718,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10729,12 +10728,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>5 bilder, sumpskog</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10743,6 +10742,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10998,7 +10998,7 @@
         <v>129240471</v>
       </c>
       <c r="B98" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>129240554</v>
       </c>
       <c r="B99" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>129240621</v>
       </c>
       <c r="B100" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>129238933</v>
       </c>
       <c r="B101" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>129248843</v>
       </c>
       <c r="B103" t="n">
-        <v>91561</v>
+        <v>91564</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11676,10 +11676,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129237273</v>
+        <v>129243098</v>
       </c>
       <c r="B104" t="n">
-        <v>78799</v>
+        <v>57724</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11687,34 +11687,39 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445252</v>
+        <v>445374</v>
       </c>
       <c r="R104" t="n">
-        <v>6735079</v>
+        <v>6734891</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11746,7 +11751,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11756,12 +11761,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Bild 4, högstubbe</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11788,10 +11793,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129237350</v>
+        <v>129238758</v>
       </c>
       <c r="B105" t="n">
-        <v>78799</v>
+        <v>57724</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11799,34 +11804,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445248</v>
+        <v>445349</v>
       </c>
       <c r="R105" t="n">
-        <v>6735139</v>
+        <v>6735194</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11858,7 +11868,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11868,12 +11878,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Bild 5, högstubbe</t>
+          <t>2 bilder på torraka med hack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11900,10 +11910,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129243098</v>
+        <v>129237273</v>
       </c>
       <c r="B106" t="n">
-        <v>57724</v>
+        <v>78801</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11911,39 +11921,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445374</v>
+        <v>445252</v>
       </c>
       <c r="R106" t="n">
-        <v>6734891</v>
+        <v>6735079</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11975,7 +11980,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11985,12 +11990,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild 4, högstubbe</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12017,10 +12022,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129238758</v>
+        <v>129237350</v>
       </c>
       <c r="B107" t="n">
-        <v>57724</v>
+        <v>78801</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12028,39 +12033,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445349</v>
+        <v>445248</v>
       </c>
       <c r="R107" t="n">
-        <v>6735194</v>
+        <v>6735139</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12092,7 +12092,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12102,12 +12102,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>2 bilder på torraka med hack</t>
+          <t>Bild 5, högstubbe</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12253,7 +12253,7 @@
         <v>129243188</v>
       </c>
       <c r="B109" t="n">
-        <v>79136</v>
+        <v>79138</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12713,10 +12713,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129237668</v>
+        <v>129243085</v>
       </c>
       <c r="B113" t="n">
-        <v>79041</v>
+        <v>79633</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12724,21 +12724,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12748,10 +12748,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>445302</v>
+        <v>445378</v>
       </c>
       <c r="R113" t="n">
-        <v>6735183</v>
+        <v>6734906</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12783,7 +12783,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12793,12 +12793,12 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Bild på äldre tall, stam uppåt</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12825,10 +12825,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129243085</v>
+        <v>129237668</v>
       </c>
       <c r="B114" t="n">
-        <v>79631</v>
+        <v>79043</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12836,21 +12836,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12860,10 +12860,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>445378</v>
+        <v>445302</v>
       </c>
       <c r="R114" t="n">
-        <v>6734906</v>
+        <v>6735183</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12895,7 +12895,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild på äldre tall, stam uppåt</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13057,7 +13057,7 @@
         <v>129237612</v>
       </c>
       <c r="B116" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>129238380</v>
       </c>
       <c r="B117" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>

--- a/artfynd/A 43504-2025 artfynd.xlsx
+++ b/artfynd/A 43504-2025 artfynd.xlsx
@@ -5576,10 +5576,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129237483</v>
+        <v>129243087</v>
       </c>
       <c r="B48" t="n">
-        <v>79043</v>
+        <v>78801</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5587,21 +5587,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445260</v>
+        <v>445378</v>
       </c>
       <c r="R48" t="n">
-        <v>6735185</v>
+        <v>6734906</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5683,10 +5683,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129237299</v>
+        <v>129237277</v>
       </c>
       <c r="B49" t="n">
-        <v>79043</v>
+        <v>79633</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5694,21 +5694,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5718,10 +5718,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445260</v>
+        <v>445252</v>
       </c>
       <c r="R49" t="n">
-        <v>6735095</v>
+        <v>6735079</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5790,10 +5790,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129237617</v>
+        <v>129237483</v>
       </c>
       <c r="B50" t="n">
-        <v>79662</v>
+        <v>79043</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5801,21 +5801,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5825,10 +5825,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>445279</v>
+        <v>445260</v>
       </c>
       <c r="R50" t="n">
-        <v>6735197</v>
+        <v>6735185</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5897,10 +5897,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129243087</v>
+        <v>129237299</v>
       </c>
       <c r="B51" t="n">
-        <v>78801</v>
+        <v>79043</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5908,21 +5908,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5932,10 +5932,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>445378</v>
+        <v>445260</v>
       </c>
       <c r="R51" t="n">
-        <v>6734906</v>
+        <v>6735095</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6004,10 +6004,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129237277</v>
+        <v>129237617</v>
       </c>
       <c r="B52" t="n">
-        <v>79633</v>
+        <v>79662</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6015,21 +6015,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445252</v>
+        <v>445279</v>
       </c>
       <c r="R52" t="n">
-        <v>6735079</v>
+        <v>6735197</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7624,10 +7624,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129247898</v>
+        <v>129238815</v>
       </c>
       <c r="B67" t="n">
-        <v>79662</v>
+        <v>57887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7635,37 +7635,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445107</v>
+        <v>445313</v>
       </c>
       <c r="R67" t="n">
-        <v>6735004</v>
+        <v>6735262</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7694,7 +7699,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7704,7 +7709,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7731,10 +7736,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129238475</v>
+        <v>129247898</v>
       </c>
       <c r="B68" t="n">
-        <v>79043</v>
+        <v>79662</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7742,21 +7747,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7766,10 +7771,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445322</v>
+        <v>445107</v>
       </c>
       <c r="R68" t="n">
-        <v>6735128</v>
+        <v>6735004</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7801,7 +7806,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7811,7 +7816,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7838,10 +7843,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129238815</v>
+        <v>129238475</v>
       </c>
       <c r="B69" t="n">
-        <v>57887</v>
+        <v>79043</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7849,42 +7854,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>445313</v>
+        <v>445322</v>
       </c>
       <c r="R69" t="n">
-        <v>6735262</v>
+        <v>6735128</v>
       </c>
       <c r="S69" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7950,32 +7950,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129244530</v>
+        <v>129238778</v>
       </c>
       <c r="B70" t="n">
-        <v>79662</v>
+        <v>8450</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>445217</v>
+        <v>445322</v>
       </c>
       <c r="R70" t="n">
-        <v>6734997</v>
+        <v>6735197</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8020,7 +8020,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8057,32 +8057,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129238778</v>
+        <v>129244530</v>
       </c>
       <c r="B71" t="n">
-        <v>8450</v>
+        <v>79662</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8092,10 +8092,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445322</v>
+        <v>445217</v>
       </c>
       <c r="R71" t="n">
-        <v>6735197</v>
+        <v>6734997</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 43504-2025 artfynd.xlsx
+++ b/artfynd/A 43504-2025 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>129249084</v>
       </c>
       <c r="B8" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>129250233</v>
       </c>
       <c r="B9" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>129249372</v>
       </c>
       <c r="B11" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>129254011</v>
       </c>
       <c r="B12" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>129253379</v>
       </c>
       <c r="B13" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>129249212</v>
       </c>
       <c r="B14" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>129249287</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>129248989</v>
       </c>
       <c r="B16" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>129251241</v>
       </c>
       <c r="B18" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>129254098</v>
       </c>
       <c r="B19" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>129248688</v>
       </c>
       <c r="B20" t="n">
-        <v>79138</v>
+        <v>79139</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>129248920</v>
       </c>
       <c r="B21" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>129237525</v>
       </c>
       <c r="B35" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4379,27 +4379,27 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129243809</v>
+        <v>129237782</v>
       </c>
       <c r="B37" t="n">
-        <v>57724</v>
+        <v>58097</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4410,7 +4410,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4419,10 +4419,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445358</v>
+        <v>445267</v>
       </c>
       <c r="R37" t="n">
-        <v>6735035</v>
+        <v>6735219</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4603,27 +4603,27 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129237782</v>
+        <v>129243809</v>
       </c>
       <c r="B39" t="n">
-        <v>58097</v>
+        <v>57724</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4634,7 +4634,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445267</v>
+        <v>445358</v>
       </c>
       <c r="R39" t="n">
-        <v>6735219</v>
+        <v>6735035</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4718,7 +4718,7 @@
         <v>129238576</v>
       </c>
       <c r="B40" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>129238322</v>
       </c>
       <c r="B41" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>129239093</v>
       </c>
       <c r="B42" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>129238704</v>
       </c>
       <c r="B43" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>129237826</v>
       </c>
       <c r="B45" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>129237683</v>
       </c>
       <c r="B46" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>129238645</v>
       </c>
       <c r="B47" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5576,10 +5576,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129243087</v>
+        <v>129237483</v>
       </c>
       <c r="B48" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5587,21 +5587,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445378</v>
+        <v>445260</v>
       </c>
       <c r="R48" t="n">
-        <v>6734906</v>
+        <v>6735185</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5683,10 +5683,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129237277</v>
+        <v>129237299</v>
       </c>
       <c r="B49" t="n">
-        <v>79633</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5694,21 +5694,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5718,10 +5718,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445252</v>
+        <v>445260</v>
       </c>
       <c r="R49" t="n">
-        <v>6735079</v>
+        <v>6735095</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5790,10 +5790,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129237483</v>
+        <v>129237617</v>
       </c>
       <c r="B50" t="n">
-        <v>79043</v>
+        <v>79663</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5801,21 +5801,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5825,10 +5825,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>445260</v>
+        <v>445279</v>
       </c>
       <c r="R50" t="n">
-        <v>6735185</v>
+        <v>6735197</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5897,10 +5897,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129237299</v>
+        <v>129243087</v>
       </c>
       <c r="B51" t="n">
-        <v>79043</v>
+        <v>78802</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5908,21 +5908,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5932,10 +5932,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>445260</v>
+        <v>445378</v>
       </c>
       <c r="R51" t="n">
-        <v>6735095</v>
+        <v>6734906</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6004,10 +6004,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129237617</v>
+        <v>129237277</v>
       </c>
       <c r="B52" t="n">
-        <v>79662</v>
+        <v>79634</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6015,21 +6015,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445279</v>
+        <v>445252</v>
       </c>
       <c r="R52" t="n">
-        <v>6735197</v>
+        <v>6735079</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6111,10 +6111,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129239857</v>
+        <v>129243753</v>
       </c>
       <c r="B53" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6122,39 +6122,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445369</v>
+        <v>445384</v>
       </c>
       <c r="R53" t="n">
-        <v>6735411</v>
+        <v>6734985</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6186,7 +6181,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6196,7 +6191,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6223,10 +6218,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129243753</v>
+        <v>129239740</v>
       </c>
       <c r="B54" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6258,10 +6253,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>445384</v>
+        <v>445356</v>
       </c>
       <c r="R54" t="n">
-        <v>6734985</v>
+        <v>6735366</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6293,7 +6288,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6303,7 +6298,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6330,10 +6325,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129239740</v>
+        <v>129239857</v>
       </c>
       <c r="B55" t="n">
-        <v>79043</v>
+        <v>57724</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6341,34 +6336,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445356</v>
+        <v>445369</v>
       </c>
       <c r="R55" t="n">
-        <v>6735366</v>
+        <v>6735411</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6437,50 +6437,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129242999</v>
+        <v>129237544</v>
       </c>
       <c r="B56" t="n">
-        <v>58097</v>
+        <v>79044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>445292</v>
+        <v>445264</v>
       </c>
       <c r="R56" t="n">
-        <v>6734957</v>
+        <v>6735197</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6512,7 +6507,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6522,7 +6517,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6549,10 +6544,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129237544</v>
+        <v>129240724</v>
       </c>
       <c r="B57" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6584,10 +6579,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445264</v>
+        <v>445509</v>
       </c>
       <c r="R57" t="n">
-        <v>6735197</v>
+        <v>6735455</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6619,7 +6614,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6629,7 +6624,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6656,45 +6651,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129240724</v>
+        <v>129242999</v>
       </c>
       <c r="B58" t="n">
-        <v>79043</v>
+        <v>58097</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>445509</v>
+        <v>445292</v>
       </c>
       <c r="R58" t="n">
-        <v>6735455</v>
+        <v>6734957</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6766,7 +6766,7 @@
         <v>129237764</v>
       </c>
       <c r="B59" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         <v>129240566</v>
       </c>
       <c r="B60" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>129239929</v>
       </c>
       <c r="B61" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>129240474</v>
       </c>
       <c r="B62" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         <v>129240967</v>
       </c>
       <c r="B63" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>129243054</v>
       </c>
       <c r="B64" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7410,32 +7410,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129240494</v>
+        <v>129237820</v>
       </c>
       <c r="B65" t="n">
-        <v>8450</v>
+        <v>78801</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7445,10 +7445,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445440</v>
+        <v>445225</v>
       </c>
       <c r="R65" t="n">
-        <v>6735522</v>
+        <v>6735226</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7480,7 +7480,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7517,32 +7517,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129237820</v>
+        <v>129240494</v>
       </c>
       <c r="B66" t="n">
-        <v>78800</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7552,10 +7552,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445225</v>
+        <v>445440</v>
       </c>
       <c r="R66" t="n">
-        <v>6735226</v>
+        <v>6735522</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7587,7 +7587,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7624,10 +7624,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129238815</v>
+        <v>129247898</v>
       </c>
       <c r="B67" t="n">
-        <v>57887</v>
+        <v>79663</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7635,42 +7635,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445313</v>
+        <v>445107</v>
       </c>
       <c r="R67" t="n">
-        <v>6735262</v>
+        <v>6735004</v>
       </c>
       <c r="S67" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7699,7 +7694,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7709,7 +7704,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7736,10 +7731,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129247898</v>
+        <v>129238475</v>
       </c>
       <c r="B68" t="n">
-        <v>79662</v>
+        <v>79044</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7747,21 +7742,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7771,10 +7766,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445107</v>
+        <v>445322</v>
       </c>
       <c r="R68" t="n">
-        <v>6735004</v>
+        <v>6735128</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7806,7 +7801,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7816,7 +7811,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7843,10 +7838,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129238475</v>
+        <v>129238815</v>
       </c>
       <c r="B69" t="n">
-        <v>79043</v>
+        <v>57887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7854,37 +7849,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>445322</v>
+        <v>445313</v>
       </c>
       <c r="R69" t="n">
-        <v>6735128</v>
+        <v>6735262</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7950,32 +7950,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129238778</v>
+        <v>129244530</v>
       </c>
       <c r="B70" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>445322</v>
+        <v>445217</v>
       </c>
       <c r="R70" t="n">
-        <v>6735197</v>
+        <v>6734997</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8020,7 +8020,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8057,32 +8057,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129244530</v>
+        <v>129238778</v>
       </c>
       <c r="B71" t="n">
-        <v>79662</v>
+        <v>8450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8092,10 +8092,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445217</v>
+        <v>445322</v>
       </c>
       <c r="R71" t="n">
-        <v>6734997</v>
+        <v>6735197</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8383,10 +8383,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129238788</v>
+        <v>129244655</v>
       </c>
       <c r="B74" t="n">
-        <v>79043</v>
+        <v>79634</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8394,21 +8394,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8418,10 +8418,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>445316</v>
+        <v>445217</v>
       </c>
       <c r="R74" t="n">
-        <v>6735207</v>
+        <v>6734997</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8463,12 +8463,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Rikligt i närområdet</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8495,10 +8490,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129237274</v>
+        <v>129238788</v>
       </c>
       <c r="B75" t="n">
-        <v>79662</v>
+        <v>79044</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8506,21 +8501,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8530,10 +8525,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>445252</v>
+        <v>445316</v>
       </c>
       <c r="R75" t="n">
-        <v>6735079</v>
+        <v>6735207</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8565,7 +8560,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8575,7 +8570,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Rikligt i närområdet</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8602,10 +8602,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129239479</v>
+        <v>129237274</v>
       </c>
       <c r="B76" t="n">
-        <v>79043</v>
+        <v>79663</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8613,21 +8613,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8637,10 +8637,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>445379</v>
+        <v>445252</v>
       </c>
       <c r="R76" t="n">
-        <v>6735294</v>
+        <v>6735079</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8672,7 +8672,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8709,10 +8709,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129244655</v>
+        <v>129239479</v>
       </c>
       <c r="B77" t="n">
-        <v>79633</v>
+        <v>79044</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8720,21 +8720,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8744,10 +8744,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>445217</v>
+        <v>445379</v>
       </c>
       <c r="R77" t="n">
-        <v>6734997</v>
+        <v>6735294</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8779,7 +8779,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8819,7 +8819,7 @@
         <v>129243245</v>
       </c>
       <c r="B78" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>129243192</v>
       </c>
       <c r="B80" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>129237621</v>
       </c>
       <c r="B81" t="n">
-        <v>79633</v>
+        <v>79634</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9244,32 +9244,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129239850</v>
+        <v>129237650</v>
       </c>
       <c r="B82" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9279,10 +9279,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445369</v>
+        <v>445279</v>
       </c>
       <c r="R82" t="n">
-        <v>6735411</v>
+        <v>6735197</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9351,32 +9351,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129242957</v>
+        <v>129238241</v>
       </c>
       <c r="B83" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445292</v>
+        <v>445313</v>
       </c>
       <c r="R83" t="n">
-        <v>6734957</v>
+        <v>6735165</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9458,10 +9458,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129237650</v>
+        <v>129237533</v>
       </c>
       <c r="B84" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445279</v>
+        <v>445256</v>
       </c>
       <c r="R84" t="n">
-        <v>6735197</v>
+        <v>6735194</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9565,32 +9565,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129238241</v>
+        <v>129239850</v>
       </c>
       <c r="B85" t="n">
-        <v>79043</v>
+        <v>8450</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9600,10 +9600,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445313</v>
+        <v>445369</v>
       </c>
       <c r="R85" t="n">
-        <v>6735165</v>
+        <v>6735411</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9672,32 +9672,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129237533</v>
+        <v>129242957</v>
       </c>
       <c r="B86" t="n">
-        <v>79043</v>
+        <v>8450</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9707,10 +9707,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445256</v>
+        <v>445292</v>
       </c>
       <c r="R86" t="n">
-        <v>6735194</v>
+        <v>6734957</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9742,7 +9742,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9752,7 +9752,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9782,7 +9782,7 @@
         <v>129237829</v>
       </c>
       <c r="B87" t="n">
-        <v>79633</v>
+        <v>79634</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9886,10 +9886,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129247020</v>
+        <v>129243589</v>
       </c>
       <c r="B88" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9897,21 +9897,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9921,10 +9921,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>445135</v>
+        <v>445385</v>
       </c>
       <c r="R88" t="n">
-        <v>6734998</v>
+        <v>6734971</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9956,7 +9956,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9966,7 +9966,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9993,10 +9993,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129243217</v>
+        <v>129247020</v>
       </c>
       <c r="B89" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>445422</v>
+        <v>445135</v>
       </c>
       <c r="R89" t="n">
-        <v>6734878</v>
+        <v>6734998</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10063,7 +10063,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10100,10 +10100,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129243589</v>
+        <v>129243217</v>
       </c>
       <c r="B90" t="n">
-        <v>79043</v>
+        <v>78802</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10111,21 +10111,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10135,10 +10135,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>445385</v>
+        <v>445422</v>
       </c>
       <c r="R90" t="n">
-        <v>6734971</v>
+        <v>6734878</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10210,7 +10210,7 @@
         <v>129240662</v>
       </c>
       <c r="B91" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10533,10 +10533,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129239693</v>
+        <v>129243051</v>
       </c>
       <c r="B94" t="n">
-        <v>79043</v>
+        <v>79139</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10544,34 +10544,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445362</v>
+        <v>445339</v>
       </c>
       <c r="R94" t="n">
-        <v>6735341</v>
+        <v>6734920</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10603,7 +10606,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10613,12 +10616,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>5 bilder, sumpskog</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10627,6 +10630,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10645,10 +10649,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129243051</v>
+        <v>129239693</v>
       </c>
       <c r="B95" t="n">
-        <v>79138</v>
+        <v>79044</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10656,37 +10660,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445339</v>
+        <v>445362</v>
       </c>
       <c r="R95" t="n">
-        <v>6734920</v>
+        <v>6735341</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10718,7 +10719,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10728,12 +10729,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>3 bilder</t>
+          <t>5 bilder, sumpskog</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10742,7 +10743,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10998,7 +10998,7 @@
         <v>129240471</v>
       </c>
       <c r="B98" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>129240554</v>
       </c>
       <c r="B99" t="n">
-        <v>79633</v>
+        <v>79634</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>129240621</v>
       </c>
       <c r="B100" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>129238933</v>
       </c>
       <c r="B101" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>129248843</v>
       </c>
       <c r="B103" t="n">
-        <v>91564</v>
+        <v>91566</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>129237273</v>
       </c>
       <c r="B106" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         <v>129237350</v>
       </c>
       <c r="B107" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>129243188</v>
       </c>
       <c r="B109" t="n">
-        <v>79138</v>
+        <v>79139</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12713,10 +12713,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129243085</v>
+        <v>129237668</v>
       </c>
       <c r="B113" t="n">
-        <v>79633</v>
+        <v>79044</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12724,21 +12724,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12748,10 +12748,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>445378</v>
+        <v>445302</v>
       </c>
       <c r="R113" t="n">
-        <v>6734906</v>
+        <v>6735183</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12783,7 +12783,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12793,12 +12793,12 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild på äldre tall, stam uppåt</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12825,10 +12825,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129237668</v>
+        <v>129243085</v>
       </c>
       <c r="B114" t="n">
-        <v>79043</v>
+        <v>79634</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12836,21 +12836,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12860,10 +12860,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>445302</v>
+        <v>445378</v>
       </c>
       <c r="R114" t="n">
-        <v>6735183</v>
+        <v>6734906</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12895,7 +12895,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Bild på äldre tall, stam uppåt</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13057,7 +13057,7 @@
         <v>129237612</v>
       </c>
       <c r="B116" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>129238380</v>
       </c>
       <c r="B117" t="n">
-        <v>79633</v>
+        <v>79634</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>

--- a/artfynd/A 43504-2025 artfynd.xlsx
+++ b/artfynd/A 43504-2025 artfynd.xlsx
@@ -4491,38 +4491,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129239467</v>
+        <v>129243809</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445379</v>
+        <v>445358</v>
       </c>
       <c r="R38" t="n">
-        <v>6735294</v>
+        <v>6735035</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4603,38 +4603,38 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129243809</v>
+        <v>129239467</v>
       </c>
       <c r="B39" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445358</v>
+        <v>445379</v>
       </c>
       <c r="R39" t="n">
-        <v>6735035</v>
+        <v>6735294</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5897,10 +5897,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129243087</v>
+        <v>129237277</v>
       </c>
       <c r="B51" t="n">
-        <v>78802</v>
+        <v>79634</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5908,21 +5908,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5932,10 +5932,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>445378</v>
+        <v>445252</v>
       </c>
       <c r="R51" t="n">
-        <v>6734906</v>
+        <v>6735079</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6004,10 +6004,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129237277</v>
+        <v>129243087</v>
       </c>
       <c r="B52" t="n">
-        <v>79634</v>
+        <v>78802</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6015,21 +6015,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445252</v>
+        <v>445378</v>
       </c>
       <c r="R52" t="n">
-        <v>6735079</v>
+        <v>6734906</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6437,45 +6437,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129237544</v>
+        <v>129242999</v>
       </c>
       <c r="B56" t="n">
-        <v>79044</v>
+        <v>58097</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>445264</v>
+        <v>445292</v>
       </c>
       <c r="R56" t="n">
-        <v>6735197</v>
+        <v>6734957</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6507,7 +6512,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6517,7 +6522,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6544,7 +6549,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129240724</v>
+        <v>129237544</v>
       </c>
       <c r="B57" t="n">
         <v>79044</v>
@@ -6579,10 +6584,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445509</v>
+        <v>445264</v>
       </c>
       <c r="R57" t="n">
-        <v>6735455</v>
+        <v>6735197</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6614,7 +6619,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6624,7 +6629,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6651,50 +6656,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129242999</v>
+        <v>129240724</v>
       </c>
       <c r="B58" t="n">
-        <v>58097</v>
+        <v>79044</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>445292</v>
+        <v>445509</v>
       </c>
       <c r="R58" t="n">
-        <v>6734957</v>
+        <v>6735455</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7624,10 +7624,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129247898</v>
+        <v>129238815</v>
       </c>
       <c r="B67" t="n">
-        <v>79663</v>
+        <v>57887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7635,37 +7635,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445107</v>
+        <v>445313</v>
       </c>
       <c r="R67" t="n">
-        <v>6735004</v>
+        <v>6735262</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7694,7 +7699,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7704,7 +7709,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7731,10 +7736,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129238475</v>
+        <v>129247898</v>
       </c>
       <c r="B68" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7742,21 +7747,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7766,10 +7771,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445322</v>
+        <v>445107</v>
       </c>
       <c r="R68" t="n">
-        <v>6735128</v>
+        <v>6735004</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7801,7 +7806,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7811,7 +7816,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7838,10 +7843,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129238815</v>
+        <v>129238475</v>
       </c>
       <c r="B69" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7849,42 +7854,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>445313</v>
+        <v>445322</v>
       </c>
       <c r="R69" t="n">
-        <v>6735262</v>
+        <v>6735128</v>
       </c>
       <c r="S69" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7950,32 +7950,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129244530</v>
+        <v>129238778</v>
       </c>
       <c r="B70" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>445217</v>
+        <v>445322</v>
       </c>
       <c r="R70" t="n">
-        <v>6734997</v>
+        <v>6735197</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8020,7 +8020,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8057,32 +8057,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129238778</v>
+        <v>129244530</v>
       </c>
       <c r="B71" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8092,10 +8092,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445322</v>
+        <v>445217</v>
       </c>
       <c r="R71" t="n">
-        <v>6735197</v>
+        <v>6734997</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8276,32 +8276,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129237286</v>
+        <v>129237274</v>
       </c>
       <c r="B73" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8490,32 +8490,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129238788</v>
+        <v>129237286</v>
       </c>
       <c r="B75" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8525,10 +8525,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>445316</v>
+        <v>445252</v>
       </c>
       <c r="R75" t="n">
-        <v>6735207</v>
+        <v>6735079</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8570,12 +8570,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Rikligt i närområdet</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8602,10 +8597,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129237274</v>
+        <v>129238788</v>
       </c>
       <c r="B76" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8613,21 +8608,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8637,10 +8632,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>445252</v>
+        <v>445316</v>
       </c>
       <c r="R76" t="n">
-        <v>6735079</v>
+        <v>6735207</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8672,7 +8667,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8682,7 +8677,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Rikligt i närområdet</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9244,32 +9244,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129237650</v>
+        <v>129239850</v>
       </c>
       <c r="B82" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9279,10 +9279,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445279</v>
+        <v>445369</v>
       </c>
       <c r="R82" t="n">
-        <v>6735197</v>
+        <v>6735411</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9351,32 +9351,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129238241</v>
+        <v>129242957</v>
       </c>
       <c r="B83" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445313</v>
+        <v>445292</v>
       </c>
       <c r="R83" t="n">
-        <v>6735165</v>
+        <v>6734957</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9458,10 +9458,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129237533</v>
+        <v>129237829</v>
       </c>
       <c r="B84" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9469,21 +9469,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445256</v>
+        <v>445225</v>
       </c>
       <c r="R84" t="n">
-        <v>6735194</v>
+        <v>6735226</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9565,32 +9565,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129239850</v>
+        <v>129237650</v>
       </c>
       <c r="B85" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9600,10 +9600,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445369</v>
+        <v>445279</v>
       </c>
       <c r="R85" t="n">
-        <v>6735411</v>
+        <v>6735197</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9635,7 +9635,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9645,7 +9645,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9672,32 +9672,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129242957</v>
+        <v>129238241</v>
       </c>
       <c r="B86" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9707,10 +9707,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445292</v>
+        <v>445313</v>
       </c>
       <c r="R86" t="n">
-        <v>6734957</v>
+        <v>6735165</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9742,7 +9742,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9752,7 +9752,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9779,10 +9779,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129237829</v>
+        <v>129237533</v>
       </c>
       <c r="B87" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9790,21 +9790,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9814,10 +9814,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445225</v>
+        <v>445256</v>
       </c>
       <c r="R87" t="n">
-        <v>6735226</v>
+        <v>6735194</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10207,10 +10207,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129240662</v>
+        <v>129248776</v>
       </c>
       <c r="B91" t="n">
-        <v>79663</v>
+        <v>57724</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10218,34 +10218,39 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>445517</v>
+        <v>445137</v>
       </c>
       <c r="R91" t="n">
-        <v>6735559</v>
+        <v>6734922</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10277,7 +10282,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10287,7 +10292,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10314,50 +10319,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129248776</v>
+        <v>129239096</v>
       </c>
       <c r="B92" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>445137</v>
+        <v>445324</v>
       </c>
       <c r="R92" t="n">
-        <v>6734922</v>
+        <v>6735285</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10399,7 +10399,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10426,32 +10426,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129239096</v>
+        <v>129240662</v>
       </c>
       <c r="B93" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10461,10 +10461,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>445324</v>
+        <v>445517</v>
       </c>
       <c r="R93" t="n">
-        <v>6735285</v>
+        <v>6735559</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10496,7 +10496,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10533,10 +10533,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129243051</v>
+        <v>129239693</v>
       </c>
       <c r="B94" t="n">
-        <v>79139</v>
+        <v>79044</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10544,37 +10544,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445339</v>
+        <v>445362</v>
       </c>
       <c r="R94" t="n">
-        <v>6734920</v>
+        <v>6735341</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10606,7 +10603,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10616,12 +10613,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>3 bilder</t>
+          <t>5 bilder, sumpskog</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10630,7 +10627,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10649,10 +10645,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129239693</v>
+        <v>129243051</v>
       </c>
       <c r="B95" t="n">
-        <v>79044</v>
+        <v>79139</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10660,34 +10656,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445362</v>
+        <v>445339</v>
       </c>
       <c r="R95" t="n">
-        <v>6735341</v>
+        <v>6734920</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10719,7 +10718,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10729,12 +10728,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>5 bilder, sumpskog</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10743,6 +10742,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10995,10 +10995,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129240471</v>
+        <v>129240554</v>
       </c>
       <c r="B98" t="n">
-        <v>78802</v>
+        <v>79634</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11006,21 +11006,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11030,10 +11030,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>445438</v>
+        <v>445435</v>
       </c>
       <c r="R98" t="n">
-        <v>6735509</v>
+        <v>6735582</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11080,7 +11080,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>2 bilder, kolad stubbe samt på spiklav</t>
+          <t>1 bild på högstubbe med låga i bakgrund</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11107,10 +11107,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129240554</v>
+        <v>129240471</v>
       </c>
       <c r="B99" t="n">
-        <v>79634</v>
+        <v>78802</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11118,21 +11118,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11142,10 +11142,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>445435</v>
+        <v>445438</v>
       </c>
       <c r="R99" t="n">
-        <v>6735582</v>
+        <v>6735509</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11192,7 +11192,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>1 bild på högstubbe med låga i bakgrund</t>
+          <t>2 bilder, kolad stubbe samt på spiklav</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11331,10 +11331,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129238933</v>
+        <v>129237880</v>
       </c>
       <c r="B101" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11342,34 +11342,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445307</v>
+        <v>445206</v>
       </c>
       <c r="R101" t="n">
-        <v>6735277</v>
+        <v>6735207</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11401,7 +11406,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11411,12 +11416,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter 3 bilder, sista på två tallstammar</t>
+          <t>Bild, torraka med hack</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11443,10 +11448,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129237880</v>
+        <v>129238933</v>
       </c>
       <c r="B102" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11454,39 +11459,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445206</v>
+        <v>445307</v>
       </c>
       <c r="R102" t="n">
-        <v>6735207</v>
+        <v>6735277</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11528,12 +11528,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Bild, torraka med hack</t>
+          <t>Rikligt i en radie av ca 50 meter 3 bilder, sista på två tallstammar</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11563,7 +11563,7 @@
         <v>129248843</v>
       </c>
       <c r="B103" t="n">
-        <v>91566</v>
+        <v>91570</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12250,10 +12250,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129243188</v>
+        <v>129238770</v>
       </c>
       <c r="B109" t="n">
-        <v>79139</v>
+        <v>57724</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12261,34 +12261,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>967</v>
+        <v>100049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>445401</v>
+        <v>445322</v>
       </c>
       <c r="R109" t="n">
-        <v>6734884</v>
+        <v>6735197</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12320,7 +12325,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12330,12 +12335,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>3 bilder</t>
+          <t>Bild på torraka, färska hack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12362,10 +12367,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129238770</v>
+        <v>129243188</v>
       </c>
       <c r="B110" t="n">
-        <v>57724</v>
+        <v>79139</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12373,39 +12378,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>967</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>445322</v>
+        <v>445401</v>
       </c>
       <c r="R110" t="n">
-        <v>6735197</v>
+        <v>6734884</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12437,7 +12437,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12447,12 +12447,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Bild på torraka, färska hack</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12937,10 +12937,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129240918</v>
+        <v>129237612</v>
       </c>
       <c r="B115" t="n">
-        <v>57724</v>
+        <v>78802</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12948,39 +12948,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>445417</v>
+        <v>445279</v>
       </c>
       <c r="R115" t="n">
-        <v>6735368</v>
+        <v>6735197</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13012,7 +13007,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13022,12 +13017,12 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild på två stubbar med äldre tall i bakgrund</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13054,10 +13049,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129237612</v>
+        <v>129238380</v>
       </c>
       <c r="B116" t="n">
-        <v>78802</v>
+        <v>79634</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13065,21 +13060,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13089,10 +13084,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>445279</v>
+        <v>445322</v>
       </c>
       <c r="R116" t="n">
-        <v>6735197</v>
+        <v>6735151</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13124,7 +13119,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13134,12 +13129,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Bild på två stubbar med äldre tall i bakgrund</t>
+          <t>Bild på grov kolad stuppe/låga, tall</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13166,10 +13161,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129238380</v>
+        <v>129240918</v>
       </c>
       <c r="B117" t="n">
-        <v>79634</v>
+        <v>57724</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13177,34 +13172,39 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>445322</v>
+        <v>445417</v>
       </c>
       <c r="R117" t="n">
-        <v>6735151</v>
+        <v>6735368</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13236,7 +13236,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13246,12 +13246,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Bild på grov kolad stuppe/låga, tall</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD117" t="b">

--- a/artfynd/A 43504-2025 artfynd.xlsx
+++ b/artfynd/A 43504-2025 artfynd.xlsx
@@ -4379,10 +4379,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129237782</v>
+        <v>129239467</v>
       </c>
       <c r="B37" t="n">
-        <v>58097</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4390,27 +4390,27 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4419,10 +4419,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445267</v>
+        <v>445379</v>
       </c>
       <c r="R37" t="n">
-        <v>6735219</v>
+        <v>6735294</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4603,10 +4603,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129239467</v>
+        <v>129237782</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>58097</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4614,27 +4614,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445379</v>
+        <v>445267</v>
       </c>
       <c r="R39" t="n">
-        <v>6735294</v>
+        <v>6735219</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4715,32 +4715,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129238576</v>
+        <v>129240788</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445336</v>
+        <v>445491</v>
       </c>
       <c r="R40" t="n">
-        <v>6735162</v>
+        <v>6735426</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4822,7 +4822,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129238322</v>
+        <v>129238576</v>
       </c>
       <c r="B41" t="n">
         <v>79044</v>
@@ -4857,10 +4857,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445325</v>
+        <v>445336</v>
       </c>
       <c r="R41" t="n">
-        <v>6735153</v>
+        <v>6735162</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4929,7 +4929,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129239093</v>
+        <v>129238322</v>
       </c>
       <c r="B42" t="n">
         <v>79044</v>
@@ -4964,10 +4964,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445324</v>
+        <v>445325</v>
       </c>
       <c r="R42" t="n">
-        <v>6735285</v>
+        <v>6735153</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5036,7 +5036,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129238704</v>
+        <v>129239093</v>
       </c>
       <c r="B43" t="n">
         <v>79044</v>
@@ -5071,10 +5071,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445349</v>
+        <v>445324</v>
       </c>
       <c r="R43" t="n">
-        <v>6735178</v>
+        <v>6735285</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5117,11 +5117,6 @@
       <c r="AB43" t="inlineStr">
         <is>
           <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5148,32 +5143,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129240788</v>
+        <v>129238704</v>
       </c>
       <c r="B44" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5183,10 +5178,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>445491</v>
+        <v>445349</v>
       </c>
       <c r="R44" t="n">
-        <v>6735426</v>
+        <v>6735178</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5218,7 +5213,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5228,7 +5223,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5576,10 +5576,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129237483</v>
+        <v>129243087</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5587,21 +5587,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445260</v>
+        <v>445378</v>
       </c>
       <c r="R48" t="n">
-        <v>6735185</v>
+        <v>6734906</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5683,10 +5683,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129237299</v>
+        <v>129237277</v>
       </c>
       <c r="B49" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5694,21 +5694,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5718,10 +5718,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445260</v>
+        <v>445252</v>
       </c>
       <c r="R49" t="n">
-        <v>6735095</v>
+        <v>6735079</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5790,10 +5790,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129237617</v>
+        <v>129237483</v>
       </c>
       <c r="B50" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5801,21 +5801,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5825,10 +5825,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>445279</v>
+        <v>445260</v>
       </c>
       <c r="R50" t="n">
-        <v>6735197</v>
+        <v>6735185</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5897,10 +5897,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129237277</v>
+        <v>129237299</v>
       </c>
       <c r="B51" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5908,21 +5908,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5932,10 +5932,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>445252</v>
+        <v>445260</v>
       </c>
       <c r="R51" t="n">
-        <v>6735079</v>
+        <v>6735095</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6004,10 +6004,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129243087</v>
+        <v>129237617</v>
       </c>
       <c r="B52" t="n">
-        <v>78802</v>
+        <v>79663</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6015,21 +6015,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445378</v>
+        <v>445279</v>
       </c>
       <c r="R52" t="n">
-        <v>6734906</v>
+        <v>6735197</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6437,50 +6437,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129242999</v>
+        <v>129237544</v>
       </c>
       <c r="B56" t="n">
-        <v>58097</v>
+        <v>79044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>445292</v>
+        <v>445264</v>
       </c>
       <c r="R56" t="n">
-        <v>6734957</v>
+        <v>6735197</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6512,7 +6507,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6522,7 +6517,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6549,7 +6544,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129237544</v>
+        <v>129240724</v>
       </c>
       <c r="B57" t="n">
         <v>79044</v>
@@ -6584,10 +6579,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445264</v>
+        <v>445509</v>
       </c>
       <c r="R57" t="n">
-        <v>6735197</v>
+        <v>6735455</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6619,7 +6614,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6629,7 +6624,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6656,45 +6651,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129240724</v>
+        <v>129242999</v>
       </c>
       <c r="B58" t="n">
-        <v>79044</v>
+        <v>58097</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>445509</v>
+        <v>445292</v>
       </c>
       <c r="R58" t="n">
-        <v>6735455</v>
+        <v>6734957</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7624,10 +7624,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129238815</v>
+        <v>129247898</v>
       </c>
       <c r="B67" t="n">
-        <v>57887</v>
+        <v>79663</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7635,42 +7635,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445313</v>
+        <v>445107</v>
       </c>
       <c r="R67" t="n">
-        <v>6735262</v>
+        <v>6735004</v>
       </c>
       <c r="S67" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7699,7 +7694,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7709,7 +7704,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7736,10 +7731,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129247898</v>
+        <v>129238475</v>
       </c>
       <c r="B68" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7747,21 +7742,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7771,10 +7766,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445107</v>
+        <v>445322</v>
       </c>
       <c r="R68" t="n">
-        <v>6735004</v>
+        <v>6735128</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7806,7 +7801,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7816,7 +7811,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7843,10 +7838,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129238475</v>
+        <v>129238815</v>
       </c>
       <c r="B69" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7854,37 +7849,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>445322</v>
+        <v>445313</v>
       </c>
       <c r="R69" t="n">
-        <v>6735128</v>
+        <v>6735262</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7950,32 +7950,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129238778</v>
+        <v>129244530</v>
       </c>
       <c r="B70" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>445322</v>
+        <v>445217</v>
       </c>
       <c r="R70" t="n">
-        <v>6735197</v>
+        <v>6734997</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8020,7 +8020,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8057,32 +8057,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129244530</v>
+        <v>129238778</v>
       </c>
       <c r="B71" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8092,10 +8092,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445217</v>
+        <v>445322</v>
       </c>
       <c r="R71" t="n">
-        <v>6734997</v>
+        <v>6735197</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8276,10 +8276,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129237274</v>
+        <v>129238788</v>
       </c>
       <c r="B73" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8287,21 +8287,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8311,10 +8311,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445252</v>
+        <v>445316</v>
       </c>
       <c r="R73" t="n">
-        <v>6735079</v>
+        <v>6735207</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8346,7 +8346,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8356,7 +8356,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Rikligt i närområdet</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8383,10 +8388,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129244655</v>
+        <v>129237274</v>
       </c>
       <c r="B74" t="n">
-        <v>79634</v>
+        <v>79663</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8394,21 +8399,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8418,10 +8423,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>445217</v>
+        <v>445252</v>
       </c>
       <c r="R74" t="n">
-        <v>6734997</v>
+        <v>6735079</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8453,7 +8458,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8463,7 +8468,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8490,32 +8495,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129237286</v>
+        <v>129239479</v>
       </c>
       <c r="B75" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8525,10 +8530,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>445252</v>
+        <v>445379</v>
       </c>
       <c r="R75" t="n">
-        <v>6735079</v>
+        <v>6735294</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8560,7 +8565,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8570,7 +8575,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8597,32 +8602,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129238788</v>
+        <v>129237286</v>
       </c>
       <c r="B76" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8632,10 +8637,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>445316</v>
+        <v>445252</v>
       </c>
       <c r="R76" t="n">
-        <v>6735207</v>
+        <v>6735079</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8667,7 +8672,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8677,12 +8682,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Rikligt i närområdet</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8709,10 +8709,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129239479</v>
+        <v>129244655</v>
       </c>
       <c r="B77" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8720,21 +8720,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8744,10 +8744,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>445379</v>
+        <v>445217</v>
       </c>
       <c r="R77" t="n">
-        <v>6735294</v>
+        <v>6734997</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8779,7 +8779,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9244,32 +9244,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129239850</v>
+        <v>129237650</v>
       </c>
       <c r="B82" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9279,10 +9279,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445369</v>
+        <v>445279</v>
       </c>
       <c r="R82" t="n">
-        <v>6735411</v>
+        <v>6735197</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9351,32 +9351,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129242957</v>
+        <v>129238241</v>
       </c>
       <c r="B83" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445292</v>
+        <v>445313</v>
       </c>
       <c r="R83" t="n">
-        <v>6734957</v>
+        <v>6735165</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9458,10 +9458,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129237829</v>
+        <v>129237533</v>
       </c>
       <c r="B84" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9469,21 +9469,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445225</v>
+        <v>445256</v>
       </c>
       <c r="R84" t="n">
-        <v>6735226</v>
+        <v>6735194</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9565,32 +9565,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129237650</v>
+        <v>129239850</v>
       </c>
       <c r="B85" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9600,10 +9600,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445279</v>
+        <v>445369</v>
       </c>
       <c r="R85" t="n">
-        <v>6735197</v>
+        <v>6735411</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9635,7 +9635,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9645,7 +9645,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9672,32 +9672,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129238241</v>
+        <v>129242957</v>
       </c>
       <c r="B86" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9707,10 +9707,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445313</v>
+        <v>445292</v>
       </c>
       <c r="R86" t="n">
-        <v>6735165</v>
+        <v>6734957</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9742,7 +9742,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9752,7 +9752,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9779,10 +9779,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129237533</v>
+        <v>129237829</v>
       </c>
       <c r="B87" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9790,21 +9790,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9814,10 +9814,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445256</v>
+        <v>445225</v>
       </c>
       <c r="R87" t="n">
-        <v>6735194</v>
+        <v>6735226</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9886,10 +9886,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129243589</v>
+        <v>129247020</v>
       </c>
       <c r="B88" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9897,21 +9897,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9921,10 +9921,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>445385</v>
+        <v>445135</v>
       </c>
       <c r="R88" t="n">
-        <v>6734971</v>
+        <v>6734998</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9956,7 +9956,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9966,7 +9966,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9993,7 +9993,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129247020</v>
+        <v>129243217</v>
       </c>
       <c r="B89" t="n">
         <v>78802</v>
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>445135</v>
+        <v>445422</v>
       </c>
       <c r="R89" t="n">
-        <v>6734998</v>
+        <v>6734878</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10063,7 +10063,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10100,10 +10100,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129243217</v>
+        <v>129243589</v>
       </c>
       <c r="B90" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10111,21 +10111,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10135,10 +10135,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>445422</v>
+        <v>445385</v>
       </c>
       <c r="R90" t="n">
-        <v>6734878</v>
+        <v>6734971</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10207,10 +10207,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129248776</v>
+        <v>129240662</v>
       </c>
       <c r="B91" t="n">
-        <v>57724</v>
+        <v>79663</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10218,39 +10218,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>445137</v>
+        <v>445517</v>
       </c>
       <c r="R91" t="n">
-        <v>6734922</v>
+        <v>6735559</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10282,7 +10277,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10292,7 +10287,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10426,10 +10421,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129240662</v>
+        <v>129248776</v>
       </c>
       <c r="B93" t="n">
-        <v>79663</v>
+        <v>57724</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10437,34 +10432,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>445517</v>
+        <v>445137</v>
       </c>
       <c r="R93" t="n">
-        <v>6735559</v>
+        <v>6734922</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10496,7 +10496,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10995,10 +10995,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129240554</v>
+        <v>129240471</v>
       </c>
       <c r="B98" t="n">
-        <v>79634</v>
+        <v>78802</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11006,21 +11006,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11030,10 +11030,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>445435</v>
+        <v>445438</v>
       </c>
       <c r="R98" t="n">
-        <v>6735582</v>
+        <v>6735509</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11080,7 +11080,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>1 bild på högstubbe med låga i bakgrund</t>
+          <t>2 bilder, kolad stubbe samt på spiklav</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11107,10 +11107,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129240471</v>
+        <v>129240554</v>
       </c>
       <c r="B99" t="n">
-        <v>78802</v>
+        <v>79634</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11118,21 +11118,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11142,10 +11142,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>445438</v>
+        <v>445435</v>
       </c>
       <c r="R99" t="n">
-        <v>6735509</v>
+        <v>6735582</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11192,7 +11192,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>2 bilder, kolad stubbe samt på spiklav</t>
+          <t>1 bild på högstubbe med låga i bakgrund</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11331,10 +11331,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129237880</v>
+        <v>129238933</v>
       </c>
       <c r="B101" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11342,39 +11342,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445206</v>
+        <v>445307</v>
       </c>
       <c r="R101" t="n">
-        <v>6735207</v>
+        <v>6735277</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11406,7 +11401,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11416,12 +11411,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Bild, torraka med hack</t>
+          <t>Rikligt i en radie av ca 50 meter 3 bilder, sista på två tallstammar</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11448,10 +11443,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129238933</v>
+        <v>129237880</v>
       </c>
       <c r="B102" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11459,34 +11454,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445307</v>
+        <v>445206</v>
       </c>
       <c r="R102" t="n">
-        <v>6735277</v>
+        <v>6735207</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11528,12 +11528,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter 3 bilder, sista på två tallstammar</t>
+          <t>Bild, torraka med hack</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11560,10 +11560,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129248843</v>
+        <v>129243098</v>
       </c>
       <c r="B103" t="n">
-        <v>91570</v>
+        <v>57724</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11571,26 +11571,27 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -11599,10 +11600,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445140</v>
+        <v>445374</v>
       </c>
       <c r="R103" t="n">
-        <v>6734876</v>
+        <v>6734891</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11634,7 +11635,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11644,7 +11645,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
@@ -11676,7 +11677,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129243098</v>
+        <v>129238758</v>
       </c>
       <c r="B104" t="n">
         <v>57724</v>
@@ -11707,7 +11708,7 @@
       <c r="I104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -11716,10 +11717,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445374</v>
+        <v>445349</v>
       </c>
       <c r="R104" t="n">
-        <v>6734891</v>
+        <v>6735194</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11751,7 +11752,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11761,12 +11762,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>2 bilder på torraka med hack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11793,10 +11794,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129238758</v>
+        <v>129237273</v>
       </c>
       <c r="B105" t="n">
-        <v>57724</v>
+        <v>78802</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11804,39 +11805,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445349</v>
+        <v>445252</v>
       </c>
       <c r="R105" t="n">
-        <v>6735194</v>
+        <v>6735079</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11868,7 +11864,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11878,12 +11874,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>2 bilder på torraka med hack</t>
+          <t>Bild 4, högstubbe</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11910,7 +11906,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129237273</v>
+        <v>129237350</v>
       </c>
       <c r="B106" t="n">
         <v>78802</v>
@@ -11945,10 +11941,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445252</v>
+        <v>445248</v>
       </c>
       <c r="R106" t="n">
-        <v>6735079</v>
+        <v>6735139</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11995,7 +11991,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Bild 4, högstubbe</t>
+          <t>Bild 5, högstubbe</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12022,10 +12018,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129237350</v>
+        <v>129248843</v>
       </c>
       <c r="B107" t="n">
-        <v>78802</v>
+        <v>91571</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12033,34 +12029,38 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445248</v>
+        <v>445140</v>
       </c>
       <c r="R107" t="n">
-        <v>6735139</v>
+        <v>6734876</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12092,7 +12092,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12102,12 +12102,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Bild 5, högstubbe</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12250,10 +12250,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129238770</v>
+        <v>129243188</v>
       </c>
       <c r="B109" t="n">
-        <v>57724</v>
+        <v>79139</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12261,39 +12261,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100049</v>
+        <v>967</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>445322</v>
+        <v>445401</v>
       </c>
       <c r="R109" t="n">
-        <v>6735197</v>
+        <v>6734884</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12325,7 +12320,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12335,12 +12330,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Bild på torraka, färska hack</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12367,10 +12362,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129243188</v>
+        <v>129238770</v>
       </c>
       <c r="B110" t="n">
-        <v>79139</v>
+        <v>57724</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12378,34 +12373,39 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>967</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>445401</v>
+        <v>445322</v>
       </c>
       <c r="R110" t="n">
-        <v>6734884</v>
+        <v>6735197</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12437,7 +12437,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12447,12 +12447,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>3 bilder</t>
+          <t>Bild på torraka, färska hack</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12713,10 +12713,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129237668</v>
+        <v>129243085</v>
       </c>
       <c r="B113" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12724,21 +12724,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12748,10 +12748,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>445302</v>
+        <v>445378</v>
       </c>
       <c r="R113" t="n">
-        <v>6735183</v>
+        <v>6734906</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12783,7 +12783,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12793,12 +12793,12 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Bild på äldre tall, stam uppåt</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12825,10 +12825,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129243085</v>
+        <v>129237668</v>
       </c>
       <c r="B114" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12836,21 +12836,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12860,10 +12860,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>445378</v>
+        <v>445302</v>
       </c>
       <c r="R114" t="n">
-        <v>6734906</v>
+        <v>6735183</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12895,7 +12895,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild på äldre tall, stam uppåt</t>
         </is>
       </c>
       <c r="AD114" t="b">

--- a/artfynd/A 43504-2025 artfynd.xlsx
+++ b/artfynd/A 43504-2025 artfynd.xlsx
@@ -2596,10 +2596,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129248688</v>
+        <v>129248920</v>
       </c>
       <c r="B20" t="n">
-        <v>79139</v>
+        <v>79663</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2607,38 +2607,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>967</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445078</v>
+        <v>445066</v>
       </c>
       <c r="R20" t="n">
-        <v>6734933</v>
+        <v>6734914</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2685,7 +2681,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>3 bilder</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2712,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129248920</v>
+        <v>129248688</v>
       </c>
       <c r="B21" t="n">
-        <v>79663</v>
+        <v>79139</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,34 +2719,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>967</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>445066</v>
+        <v>445078</v>
       </c>
       <c r="R21" t="n">
-        <v>6734914</v>
+        <v>6734933</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4379,38 +4379,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129239467</v>
+        <v>129243809</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4419,10 +4419,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445379</v>
+        <v>445358</v>
       </c>
       <c r="R37" t="n">
-        <v>6735294</v>
+        <v>6735035</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4491,27 +4491,27 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129243809</v>
+        <v>129237782</v>
       </c>
       <c r="B38" t="n">
-        <v>57724</v>
+        <v>58097</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4522,7 +4522,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445358</v>
+        <v>445267</v>
       </c>
       <c r="R38" t="n">
-        <v>6735035</v>
+        <v>6735219</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4603,10 +4603,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129237782</v>
+        <v>129239467</v>
       </c>
       <c r="B39" t="n">
-        <v>58097</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4614,27 +4614,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445267</v>
+        <v>445379</v>
       </c>
       <c r="R39" t="n">
-        <v>6735219</v>
+        <v>6735294</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4929,7 +4929,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129238322</v>
+        <v>129239093</v>
       </c>
       <c r="B42" t="n">
         <v>79044</v>
@@ -4964,10 +4964,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445325</v>
+        <v>445324</v>
       </c>
       <c r="R42" t="n">
-        <v>6735153</v>
+        <v>6735285</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5036,7 +5036,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129239093</v>
+        <v>129238322</v>
       </c>
       <c r="B43" t="n">
         <v>79044</v>
@@ -5071,10 +5071,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445324</v>
+        <v>445325</v>
       </c>
       <c r="R43" t="n">
-        <v>6735285</v>
+        <v>6735153</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5790,10 +5790,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129237483</v>
+        <v>129237617</v>
       </c>
       <c r="B50" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5801,21 +5801,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5825,10 +5825,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>445260</v>
+        <v>445279</v>
       </c>
       <c r="R50" t="n">
-        <v>6735185</v>
+        <v>6735197</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5897,7 +5897,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129237299</v>
+        <v>129237483</v>
       </c>
       <c r="B51" t="n">
         <v>79044</v>
@@ -5935,7 +5935,7 @@
         <v>445260</v>
       </c>
       <c r="R51" t="n">
-        <v>6735095</v>
+        <v>6735185</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6004,10 +6004,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129237617</v>
+        <v>129237299</v>
       </c>
       <c r="B52" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6015,21 +6015,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445279</v>
+        <v>445260</v>
       </c>
       <c r="R52" t="n">
-        <v>6735197</v>
+        <v>6735095</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6870,7 +6870,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129240566</v>
+        <v>129240967</v>
       </c>
       <c r="B60" t="n">
         <v>79044</v>
@@ -6905,10 +6905,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445481</v>
+        <v>445414</v>
       </c>
       <c r="R60" t="n">
-        <v>6735582</v>
+        <v>6735285</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7089,7 +7089,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129240474</v>
+        <v>129240566</v>
       </c>
       <c r="B62" t="n">
         <v>79044</v>
@@ -7124,10 +7124,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>445438</v>
+        <v>445481</v>
       </c>
       <c r="R62" t="n">
-        <v>6735509</v>
+        <v>6735582</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7196,7 +7196,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129240967</v>
+        <v>129240474</v>
       </c>
       <c r="B63" t="n">
         <v>79044</v>
@@ -7231,10 +7231,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>445414</v>
+        <v>445438</v>
       </c>
       <c r="R63" t="n">
-        <v>6735285</v>
+        <v>6735509</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7624,10 +7624,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129247898</v>
+        <v>129238475</v>
       </c>
       <c r="B67" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7635,21 +7635,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7659,10 +7659,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445107</v>
+        <v>445322</v>
       </c>
       <c r="R67" t="n">
-        <v>6735004</v>
+        <v>6735128</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7731,10 +7731,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129238475</v>
+        <v>129238815</v>
       </c>
       <c r="B68" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7742,37 +7742,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445322</v>
+        <v>445313</v>
       </c>
       <c r="R68" t="n">
-        <v>6735128</v>
+        <v>6735262</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7838,10 +7843,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129238815</v>
+        <v>129247898</v>
       </c>
       <c r="B69" t="n">
-        <v>57887</v>
+        <v>79663</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7849,42 +7854,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>445313</v>
+        <v>445107</v>
       </c>
       <c r="R69" t="n">
-        <v>6735262</v>
+        <v>6735004</v>
       </c>
       <c r="S69" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8276,10 +8276,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129238788</v>
+        <v>129244655</v>
       </c>
       <c r="B73" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8287,21 +8287,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8311,10 +8311,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445316</v>
+        <v>445217</v>
       </c>
       <c r="R73" t="n">
-        <v>6735207</v>
+        <v>6734997</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8346,7 +8346,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8356,12 +8356,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Rikligt i närområdet</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8388,10 +8383,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129237274</v>
+        <v>129238788</v>
       </c>
       <c r="B74" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8399,21 +8394,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8423,10 +8418,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>445252</v>
+        <v>445316</v>
       </c>
       <c r="R74" t="n">
-        <v>6735079</v>
+        <v>6735207</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8458,7 +8453,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8468,7 +8463,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Rikligt i närområdet</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8495,32 +8495,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129239479</v>
+        <v>129237286</v>
       </c>
       <c r="B75" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8530,10 +8530,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>445379</v>
+        <v>445252</v>
       </c>
       <c r="R75" t="n">
-        <v>6735294</v>
+        <v>6735079</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8602,32 +8602,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129237286</v>
+        <v>129237274</v>
       </c>
       <c r="B76" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8709,10 +8709,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129244655</v>
+        <v>129239479</v>
       </c>
       <c r="B77" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8720,21 +8720,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8744,10 +8744,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>445217</v>
+        <v>445379</v>
       </c>
       <c r="R77" t="n">
-        <v>6734997</v>
+        <v>6735294</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8779,7 +8779,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9244,7 +9244,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129237650</v>
+        <v>129237533</v>
       </c>
       <c r="B82" t="n">
         <v>79044</v>
@@ -9279,10 +9279,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445279</v>
+        <v>445256</v>
       </c>
       <c r="R82" t="n">
-        <v>6735197</v>
+        <v>6735194</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9458,32 +9458,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129237533</v>
+        <v>129239850</v>
       </c>
       <c r="B84" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445256</v>
+        <v>445369</v>
       </c>
       <c r="R84" t="n">
-        <v>6735194</v>
+        <v>6735411</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9528,7 +9528,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9565,7 +9565,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129239850</v>
+        <v>129242957</v>
       </c>
       <c r="B85" t="n">
         <v>8450</v>
@@ -9600,10 +9600,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445369</v>
+        <v>445292</v>
       </c>
       <c r="R85" t="n">
-        <v>6735411</v>
+        <v>6734957</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9635,7 +9635,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9645,7 +9645,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9672,32 +9672,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129242957</v>
+        <v>129237829</v>
       </c>
       <c r="B86" t="n">
-        <v>8450</v>
+        <v>79634</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9707,10 +9707,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445292</v>
+        <v>445225</v>
       </c>
       <c r="R86" t="n">
-        <v>6734957</v>
+        <v>6735226</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9742,7 +9742,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9752,7 +9752,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9779,10 +9779,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129237829</v>
+        <v>129237650</v>
       </c>
       <c r="B87" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9790,21 +9790,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9814,10 +9814,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445225</v>
+        <v>445279</v>
       </c>
       <c r="R87" t="n">
-        <v>6735226</v>
+        <v>6735197</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9886,10 +9886,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129247020</v>
+        <v>129243589</v>
       </c>
       <c r="B88" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9897,21 +9897,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9921,10 +9921,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>445135</v>
+        <v>445385</v>
       </c>
       <c r="R88" t="n">
-        <v>6734998</v>
+        <v>6734971</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9956,7 +9956,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9966,7 +9966,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9993,7 +9993,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129243217</v>
+        <v>129247020</v>
       </c>
       <c r="B89" t="n">
         <v>78802</v>
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>445422</v>
+        <v>445135</v>
       </c>
       <c r="R89" t="n">
-        <v>6734878</v>
+        <v>6734998</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10063,7 +10063,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10100,10 +10100,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129243589</v>
+        <v>129243217</v>
       </c>
       <c r="B90" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10111,21 +10111,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10135,10 +10135,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>445385</v>
+        <v>445422</v>
       </c>
       <c r="R90" t="n">
-        <v>6734971</v>
+        <v>6734878</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10314,45 +10314,50 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129239096</v>
+        <v>129248776</v>
       </c>
       <c r="B92" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>445324</v>
+        <v>445137</v>
       </c>
       <c r="R92" t="n">
-        <v>6735285</v>
+        <v>6734922</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10384,7 +10389,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10394,7 +10399,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10421,50 +10426,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129248776</v>
+        <v>129239096</v>
       </c>
       <c r="B93" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>445137</v>
+        <v>445324</v>
       </c>
       <c r="R93" t="n">
-        <v>6734922</v>
+        <v>6735285</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10496,7 +10496,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10533,10 +10533,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129239693</v>
+        <v>129243051</v>
       </c>
       <c r="B94" t="n">
-        <v>79044</v>
+        <v>79139</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10544,34 +10544,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445362</v>
+        <v>445339</v>
       </c>
       <c r="R94" t="n">
-        <v>6735341</v>
+        <v>6734920</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10603,7 +10606,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10613,12 +10616,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>5 bilder, sumpskog</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10627,6 +10630,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10645,10 +10649,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129243051</v>
+        <v>129239693</v>
       </c>
       <c r="B95" t="n">
-        <v>79139</v>
+        <v>79044</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10656,37 +10660,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445339</v>
+        <v>445362</v>
       </c>
       <c r="R95" t="n">
-        <v>6734920</v>
+        <v>6735341</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10718,7 +10719,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10728,12 +10729,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>3 bilder</t>
+          <t>5 bilder, sumpskog</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10742,7 +10743,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -11560,10 +11560,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129243098</v>
+        <v>129248843</v>
       </c>
       <c r="B103" t="n">
-        <v>57724</v>
+        <v>91571</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11571,27 +11571,26 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -11600,10 +11599,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445374</v>
+        <v>445140</v>
       </c>
       <c r="R103" t="n">
-        <v>6734891</v>
+        <v>6734876</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11635,7 +11634,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11645,7 +11644,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
@@ -11677,7 +11676,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129238758</v>
+        <v>129243098</v>
       </c>
       <c r="B104" t="n">
         <v>57724</v>
@@ -11708,7 +11707,7 @@
       <c r="I104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -11717,10 +11716,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445349</v>
+        <v>445374</v>
       </c>
       <c r="R104" t="n">
-        <v>6735194</v>
+        <v>6734891</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11752,7 +11751,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11762,12 +11761,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>2 bilder på torraka med hack</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11794,10 +11793,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129237273</v>
+        <v>129238758</v>
       </c>
       <c r="B105" t="n">
-        <v>78802</v>
+        <v>57724</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11805,34 +11804,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445252</v>
+        <v>445349</v>
       </c>
       <c r="R105" t="n">
-        <v>6735079</v>
+        <v>6735194</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11864,7 +11868,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11874,12 +11878,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Bild 4, högstubbe</t>
+          <t>2 bilder på torraka med hack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11906,7 +11910,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129237350</v>
+        <v>129237273</v>
       </c>
       <c r="B106" t="n">
         <v>78802</v>
@@ -11941,10 +11945,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445248</v>
+        <v>445252</v>
       </c>
       <c r="R106" t="n">
-        <v>6735139</v>
+        <v>6735079</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11991,7 +11995,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Bild 5, högstubbe</t>
+          <t>Bild 4, högstubbe</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12018,10 +12022,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129248843</v>
+        <v>129237350</v>
       </c>
       <c r="B107" t="n">
-        <v>91571</v>
+        <v>78802</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12029,38 +12033,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445140</v>
+        <v>445248</v>
       </c>
       <c r="R107" t="n">
-        <v>6734876</v>
+        <v>6735139</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12092,7 +12092,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12102,12 +12102,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild 5, högstubbe</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12713,10 +12713,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129243085</v>
+        <v>129237668</v>
       </c>
       <c r="B113" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12724,21 +12724,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12748,10 +12748,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>445378</v>
+        <v>445302</v>
       </c>
       <c r="R113" t="n">
-        <v>6734906</v>
+        <v>6735183</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12783,7 +12783,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12793,12 +12793,12 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild på äldre tall, stam uppåt</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12825,10 +12825,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129237668</v>
+        <v>129243085</v>
       </c>
       <c r="B114" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12836,21 +12836,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12860,10 +12860,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>445302</v>
+        <v>445378</v>
       </c>
       <c r="R114" t="n">
-        <v>6735183</v>
+        <v>6734906</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12895,7 +12895,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Bild på äldre tall, stam uppåt</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD114" t="b">

--- a/artfynd/A 43504-2025 artfynd.xlsx
+++ b/artfynd/A 43504-2025 artfynd.xlsx
@@ -2596,10 +2596,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129248920</v>
+        <v>129248688</v>
       </c>
       <c r="B20" t="n">
-        <v>79663</v>
+        <v>79139</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2607,34 +2607,38 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>967</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445066</v>
+        <v>445078</v>
       </c>
       <c r="R20" t="n">
-        <v>6734914</v>
+        <v>6734933</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,7 +2685,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2712,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129248688</v>
+        <v>129248920</v>
       </c>
       <c r="B21" t="n">
-        <v>79139</v>
+        <v>79663</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,38 +2723,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>967</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>445078</v>
+        <v>445066</v>
       </c>
       <c r="R21" t="n">
-        <v>6734933</v>
+        <v>6734914</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>3 bilder</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4715,32 +4715,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129240788</v>
+        <v>129238322</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445491</v>
+        <v>445325</v>
       </c>
       <c r="R40" t="n">
-        <v>6735426</v>
+        <v>6735153</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4822,7 +4822,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129238576</v>
+        <v>129238704</v>
       </c>
       <c r="B41" t="n">
         <v>79044</v>
@@ -4857,10 +4857,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445336</v>
+        <v>445349</v>
       </c>
       <c r="R41" t="n">
-        <v>6735162</v>
+        <v>6735178</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4903,6 +4903,11 @@
       <c r="AB41" t="inlineStr">
         <is>
           <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4929,32 +4934,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129239093</v>
+        <v>129240788</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4964,10 +4969,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445324</v>
+        <v>445491</v>
       </c>
       <c r="R42" t="n">
-        <v>6735285</v>
+        <v>6735426</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4999,7 +5004,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5009,7 +5014,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5036,7 +5041,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129238322</v>
+        <v>129238576</v>
       </c>
       <c r="B43" t="n">
         <v>79044</v>
@@ -5071,10 +5076,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445325</v>
+        <v>445336</v>
       </c>
       <c r="R43" t="n">
-        <v>6735153</v>
+        <v>6735162</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5143,7 +5148,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129238704</v>
+        <v>129239093</v>
       </c>
       <c r="B44" t="n">
         <v>79044</v>
@@ -5178,10 +5183,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>445349</v>
+        <v>445324</v>
       </c>
       <c r="R44" t="n">
-        <v>6735178</v>
+        <v>6735285</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5224,11 +5229,6 @@
       <c r="AB44" t="inlineStr">
         <is>
           <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5362,7 +5362,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129237683</v>
+        <v>129238645</v>
       </c>
       <c r="B46" t="n">
         <v>79044</v>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>445282</v>
+        <v>445322</v>
       </c>
       <c r="R46" t="n">
-        <v>6735211</v>
+        <v>6735197</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5469,7 +5469,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129238645</v>
+        <v>129237683</v>
       </c>
       <c r="B47" t="n">
         <v>79044</v>
@@ -5504,10 +5504,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>445322</v>
+        <v>445282</v>
       </c>
       <c r="R47" t="n">
-        <v>6735197</v>
+        <v>6735211</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5576,10 +5576,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129243087</v>
+        <v>129237617</v>
       </c>
       <c r="B48" t="n">
-        <v>78802</v>
+        <v>79663</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5587,21 +5587,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445378</v>
+        <v>445279</v>
       </c>
       <c r="R48" t="n">
-        <v>6734906</v>
+        <v>6735197</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5683,10 +5683,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129237277</v>
+        <v>129237483</v>
       </c>
       <c r="B49" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5694,21 +5694,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5718,10 +5718,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445252</v>
+        <v>445260</v>
       </c>
       <c r="R49" t="n">
-        <v>6735079</v>
+        <v>6735185</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5790,10 +5790,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129237617</v>
+        <v>129237299</v>
       </c>
       <c r="B50" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5801,21 +5801,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5825,10 +5825,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>445279</v>
+        <v>445260</v>
       </c>
       <c r="R50" t="n">
-        <v>6735197</v>
+        <v>6735095</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5897,10 +5897,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129237483</v>
+        <v>129243087</v>
       </c>
       <c r="B51" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5908,21 +5908,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5932,10 +5932,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>445260</v>
+        <v>445378</v>
       </c>
       <c r="R51" t="n">
-        <v>6735185</v>
+        <v>6734906</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6004,10 +6004,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129237299</v>
+        <v>129237277</v>
       </c>
       <c r="B52" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6015,21 +6015,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445260</v>
+        <v>445252</v>
       </c>
       <c r="R52" t="n">
-        <v>6735095</v>
+        <v>6735079</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6870,7 +6870,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129240967</v>
+        <v>129240566</v>
       </c>
       <c r="B60" t="n">
         <v>79044</v>
@@ -6905,10 +6905,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445414</v>
+        <v>445481</v>
       </c>
       <c r="R60" t="n">
-        <v>6735285</v>
+        <v>6735582</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6977,7 +6977,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129239929</v>
+        <v>129240474</v>
       </c>
       <c r="B61" t="n">
         <v>79044</v>
@@ -7012,10 +7012,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>445421</v>
+        <v>445438</v>
       </c>
       <c r="R61" t="n">
-        <v>6735402</v>
+        <v>6735509</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7057,12 +7057,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7089,7 +7084,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129240566</v>
+        <v>129240967</v>
       </c>
       <c r="B62" t="n">
         <v>79044</v>
@@ -7124,10 +7119,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>445481</v>
+        <v>445414</v>
       </c>
       <c r="R62" t="n">
-        <v>6735582</v>
+        <v>6735285</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7196,7 +7191,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129240474</v>
+        <v>129239929</v>
       </c>
       <c r="B63" t="n">
         <v>79044</v>
@@ -7231,10 +7226,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>445438</v>
+        <v>445421</v>
       </c>
       <c r="R63" t="n">
-        <v>6735509</v>
+        <v>6735402</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7266,7 +7261,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7276,7 +7271,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7624,10 +7624,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129238475</v>
+        <v>129247898</v>
       </c>
       <c r="B67" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7635,21 +7635,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7659,10 +7659,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445322</v>
+        <v>445107</v>
       </c>
       <c r="R67" t="n">
-        <v>6735128</v>
+        <v>6735004</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7731,10 +7731,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129238815</v>
+        <v>129238475</v>
       </c>
       <c r="B68" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7742,42 +7742,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445313</v>
+        <v>445322</v>
       </c>
       <c r="R68" t="n">
-        <v>6735262</v>
+        <v>6735128</v>
       </c>
       <c r="S68" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7843,10 +7838,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129247898</v>
+        <v>129238815</v>
       </c>
       <c r="B69" t="n">
-        <v>79663</v>
+        <v>57887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7854,37 +7849,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>445107</v>
+        <v>445313</v>
       </c>
       <c r="R69" t="n">
-        <v>6735004</v>
+        <v>6735262</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8276,10 +8276,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129244655</v>
+        <v>129237274</v>
       </c>
       <c r="B73" t="n">
-        <v>79634</v>
+        <v>79663</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8287,21 +8287,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8311,10 +8311,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445217</v>
+        <v>445252</v>
       </c>
       <c r="R73" t="n">
-        <v>6734997</v>
+        <v>6735079</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8346,7 +8346,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8383,7 +8383,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129238788</v>
+        <v>129239479</v>
       </c>
       <c r="B74" t="n">
         <v>79044</v>
@@ -8418,10 +8418,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>445316</v>
+        <v>445379</v>
       </c>
       <c r="R74" t="n">
-        <v>6735207</v>
+        <v>6735294</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8464,11 +8464,6 @@
       <c r="AB74" t="inlineStr">
         <is>
           <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Rikligt i närområdet</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8495,32 +8490,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129237286</v>
+        <v>129238788</v>
       </c>
       <c r="B75" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8530,10 +8525,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>445252</v>
+        <v>445316</v>
       </c>
       <c r="R75" t="n">
-        <v>6735079</v>
+        <v>6735207</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8565,7 +8560,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8575,7 +8570,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Rikligt i närområdet</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8602,32 +8602,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129237274</v>
+        <v>129237286</v>
       </c>
       <c r="B76" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8709,10 +8709,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129239479</v>
+        <v>129244655</v>
       </c>
       <c r="B77" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8720,21 +8720,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8744,10 +8744,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>445379</v>
+        <v>445217</v>
       </c>
       <c r="R77" t="n">
-        <v>6735294</v>
+        <v>6734997</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8779,7 +8779,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8816,32 +8816,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129243245</v>
+        <v>129243104</v>
       </c>
       <c r="B78" t="n">
-        <v>78801</v>
+        <v>8450</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>445422</v>
+        <v>445374</v>
       </c>
       <c r="R78" t="n">
-        <v>6734878</v>
+        <v>6734891</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8923,32 +8923,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129243104</v>
+        <v>129243192</v>
       </c>
       <c r="B79" t="n">
-        <v>8450</v>
+        <v>78802</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8958,10 +8958,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>445374</v>
+        <v>445401</v>
       </c>
       <c r="R79" t="n">
-        <v>6734891</v>
+        <v>6734884</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9030,10 +9030,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129243192</v>
+        <v>129243245</v>
       </c>
       <c r="B80" t="n">
-        <v>78802</v>
+        <v>78801</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9041,21 +9041,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9065,10 +9065,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445401</v>
+        <v>445422</v>
       </c>
       <c r="R80" t="n">
-        <v>6734884</v>
+        <v>6734878</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9244,7 +9244,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129237533</v>
+        <v>129237650</v>
       </c>
       <c r="B82" t="n">
         <v>79044</v>
@@ -9279,10 +9279,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445256</v>
+        <v>445279</v>
       </c>
       <c r="R82" t="n">
-        <v>6735194</v>
+        <v>6735197</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9351,7 +9351,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129238241</v>
+        <v>129237533</v>
       </c>
       <c r="B83" t="n">
         <v>79044</v>
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445313</v>
+        <v>445256</v>
       </c>
       <c r="R83" t="n">
-        <v>6735165</v>
+        <v>6735194</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9458,32 +9458,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129239850</v>
+        <v>129238241</v>
       </c>
       <c r="B84" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445369</v>
+        <v>445313</v>
       </c>
       <c r="R84" t="n">
-        <v>6735411</v>
+        <v>6735165</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9565,7 +9565,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129242957</v>
+        <v>129239850</v>
       </c>
       <c r="B85" t="n">
         <v>8450</v>
@@ -9600,10 +9600,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445292</v>
+        <v>445369</v>
       </c>
       <c r="R85" t="n">
-        <v>6734957</v>
+        <v>6735411</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9635,7 +9635,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9645,7 +9645,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9672,32 +9672,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129237829</v>
+        <v>129242957</v>
       </c>
       <c r="B86" t="n">
-        <v>79634</v>
+        <v>8450</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9707,10 +9707,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445225</v>
+        <v>445292</v>
       </c>
       <c r="R86" t="n">
-        <v>6735226</v>
+        <v>6734957</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9742,7 +9742,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9752,7 +9752,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9779,10 +9779,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129237650</v>
+        <v>129237829</v>
       </c>
       <c r="B87" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9790,21 +9790,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9814,10 +9814,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445279</v>
+        <v>445225</v>
       </c>
       <c r="R87" t="n">
-        <v>6735197</v>
+        <v>6735226</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11331,10 +11331,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129238933</v>
+        <v>129237880</v>
       </c>
       <c r="B101" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11342,34 +11342,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445307</v>
+        <v>445206</v>
       </c>
       <c r="R101" t="n">
-        <v>6735277</v>
+        <v>6735207</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11401,7 +11406,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11411,12 +11416,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter 3 bilder, sista på två tallstammar</t>
+          <t>Bild, torraka med hack</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11443,10 +11448,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129237880</v>
+        <v>129238933</v>
       </c>
       <c r="B102" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11454,39 +11459,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445206</v>
+        <v>445307</v>
       </c>
       <c r="R102" t="n">
-        <v>6735207</v>
+        <v>6735277</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11528,12 +11528,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Bild, torraka med hack</t>
+          <t>Rikligt i en radie av ca 50 meter 3 bilder, sista på två tallstammar</t>
         </is>
       </c>
       <c r="AD102" t="b">

--- a/artfynd/A 43504-2025 artfynd.xlsx
+++ b/artfynd/A 43504-2025 artfynd.xlsx
@@ -4379,38 +4379,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129243809</v>
+        <v>129239467</v>
       </c>
       <c r="B37" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4419,10 +4419,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445358</v>
+        <v>445379</v>
       </c>
       <c r="R37" t="n">
-        <v>6735035</v>
+        <v>6735294</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4491,27 +4491,27 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129237782</v>
+        <v>129243809</v>
       </c>
       <c r="B38" t="n">
-        <v>58097</v>
+        <v>57724</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4522,7 +4522,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445267</v>
+        <v>445358</v>
       </c>
       <c r="R38" t="n">
-        <v>6735219</v>
+        <v>6735035</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4603,10 +4603,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129239467</v>
+        <v>129237782</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>58097</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4614,27 +4614,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445379</v>
+        <v>445267</v>
       </c>
       <c r="R39" t="n">
-        <v>6735294</v>
+        <v>6735219</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4715,32 +4715,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129238322</v>
+        <v>129240788</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445325</v>
+        <v>445491</v>
       </c>
       <c r="R40" t="n">
-        <v>6735153</v>
+        <v>6735426</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4822,7 +4822,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129238704</v>
+        <v>129238576</v>
       </c>
       <c r="B41" t="n">
         <v>79044</v>
@@ -4857,10 +4857,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445349</v>
+        <v>445336</v>
       </c>
       <c r="R41" t="n">
-        <v>6735178</v>
+        <v>6735162</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4903,11 +4903,6 @@
       <c r="AB41" t="inlineStr">
         <is>
           <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4934,32 +4929,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129240788</v>
+        <v>129238322</v>
       </c>
       <c r="B42" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4969,10 +4964,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445491</v>
+        <v>445325</v>
       </c>
       <c r="R42" t="n">
-        <v>6735426</v>
+        <v>6735153</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5004,7 +4999,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5014,7 +5009,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5041,7 +5036,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129238576</v>
+        <v>129239093</v>
       </c>
       <c r="B43" t="n">
         <v>79044</v>
@@ -5076,10 +5071,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445336</v>
+        <v>445324</v>
       </c>
       <c r="R43" t="n">
-        <v>6735162</v>
+        <v>6735285</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5148,7 +5143,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129239093</v>
+        <v>129238704</v>
       </c>
       <c r="B44" t="n">
         <v>79044</v>
@@ -5183,10 +5178,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>445324</v>
+        <v>445349</v>
       </c>
       <c r="R44" t="n">
-        <v>6735285</v>
+        <v>6735178</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5229,6 +5224,11 @@
       <c r="AB44" t="inlineStr">
         <is>
           <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5362,7 +5362,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129238645</v>
+        <v>129237683</v>
       </c>
       <c r="B46" t="n">
         <v>79044</v>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>445322</v>
+        <v>445282</v>
       </c>
       <c r="R46" t="n">
-        <v>6735197</v>
+        <v>6735211</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5469,7 +5469,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129237683</v>
+        <v>129238645</v>
       </c>
       <c r="B47" t="n">
         <v>79044</v>
@@ -5504,10 +5504,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>445282</v>
+        <v>445322</v>
       </c>
       <c r="R47" t="n">
-        <v>6735211</v>
+        <v>6735197</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5576,10 +5576,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129237617</v>
+        <v>129237483</v>
       </c>
       <c r="B48" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5587,21 +5587,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445279</v>
+        <v>445260</v>
       </c>
       <c r="R48" t="n">
-        <v>6735197</v>
+        <v>6735185</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5683,7 +5683,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129237483</v>
+        <v>129237299</v>
       </c>
       <c r="B49" t="n">
         <v>79044</v>
@@ -5721,7 +5721,7 @@
         <v>445260</v>
       </c>
       <c r="R49" t="n">
-        <v>6735185</v>
+        <v>6735095</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5790,10 +5790,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129237299</v>
+        <v>129237617</v>
       </c>
       <c r="B50" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5801,21 +5801,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5825,10 +5825,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>445260</v>
+        <v>445279</v>
       </c>
       <c r="R50" t="n">
-        <v>6735095</v>
+        <v>6735197</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6870,7 +6870,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129240566</v>
+        <v>129239929</v>
       </c>
       <c r="B60" t="n">
         <v>79044</v>
@@ -6905,10 +6905,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445481</v>
+        <v>445421</v>
       </c>
       <c r="R60" t="n">
-        <v>6735582</v>
+        <v>6735402</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6940,7 +6940,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6950,7 +6950,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7191,7 +7196,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129239929</v>
+        <v>129240566</v>
       </c>
       <c r="B63" t="n">
         <v>79044</v>
@@ -7226,10 +7231,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>445421</v>
+        <v>445481</v>
       </c>
       <c r="R63" t="n">
-        <v>6735402</v>
+        <v>6735582</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7261,7 +7266,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7271,12 +7276,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7950,32 +7950,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129244530</v>
+        <v>129238778</v>
       </c>
       <c r="B70" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>445217</v>
+        <v>445322</v>
       </c>
       <c r="R70" t="n">
-        <v>6734997</v>
+        <v>6735197</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8020,7 +8020,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8057,32 +8057,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129238778</v>
+        <v>129244530</v>
       </c>
       <c r="B71" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8092,10 +8092,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445322</v>
+        <v>445217</v>
       </c>
       <c r="R71" t="n">
-        <v>6735197</v>
+        <v>6734997</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8276,32 +8276,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129237274</v>
+        <v>129237286</v>
       </c>
       <c r="B73" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8383,10 +8383,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129239479</v>
+        <v>129244655</v>
       </c>
       <c r="B74" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8394,21 +8394,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8418,10 +8418,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>445379</v>
+        <v>445217</v>
       </c>
       <c r="R74" t="n">
-        <v>6735294</v>
+        <v>6734997</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8602,32 +8602,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129237286</v>
+        <v>129237274</v>
       </c>
       <c r="B76" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8709,10 +8709,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129244655</v>
+        <v>129239479</v>
       </c>
       <c r="B77" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8720,21 +8720,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8744,10 +8744,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>445217</v>
+        <v>445379</v>
       </c>
       <c r="R77" t="n">
-        <v>6734997</v>
+        <v>6735294</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8779,7 +8779,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8816,32 +8816,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129243104</v>
+        <v>129243245</v>
       </c>
       <c r="B78" t="n">
-        <v>8450</v>
+        <v>78801</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>445374</v>
+        <v>445422</v>
       </c>
       <c r="R78" t="n">
-        <v>6734891</v>
+        <v>6734878</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9030,32 +9030,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129243245</v>
+        <v>129243104</v>
       </c>
       <c r="B80" t="n">
-        <v>78801</v>
+        <v>8450</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9065,10 +9065,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445422</v>
+        <v>445374</v>
       </c>
       <c r="R80" t="n">
-        <v>6734878</v>
+        <v>6734891</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9244,32 +9244,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129237650</v>
+        <v>129239850</v>
       </c>
       <c r="B82" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9279,10 +9279,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445279</v>
+        <v>445369</v>
       </c>
       <c r="R82" t="n">
-        <v>6735197</v>
+        <v>6735411</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9351,32 +9351,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129237533</v>
+        <v>129242957</v>
       </c>
       <c r="B83" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445256</v>
+        <v>445292</v>
       </c>
       <c r="R83" t="n">
-        <v>6735194</v>
+        <v>6734957</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9458,7 +9458,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129238241</v>
+        <v>129237650</v>
       </c>
       <c r="B84" t="n">
         <v>79044</v>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445313</v>
+        <v>445279</v>
       </c>
       <c r="R84" t="n">
-        <v>6735165</v>
+        <v>6735197</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9528,7 +9528,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9565,32 +9565,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129239850</v>
+        <v>129238241</v>
       </c>
       <c r="B85" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9600,10 +9600,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445369</v>
+        <v>445313</v>
       </c>
       <c r="R85" t="n">
-        <v>6735411</v>
+        <v>6735165</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9672,32 +9672,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129242957</v>
+        <v>129237533</v>
       </c>
       <c r="B86" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9707,10 +9707,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445292</v>
+        <v>445256</v>
       </c>
       <c r="R86" t="n">
-        <v>6734957</v>
+        <v>6735194</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9742,7 +9742,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9752,7 +9752,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10207,32 +10207,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129240662</v>
+        <v>129239096</v>
       </c>
       <c r="B91" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10242,10 +10242,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>445517</v>
+        <v>445324</v>
       </c>
       <c r="R91" t="n">
-        <v>6735559</v>
+        <v>6735285</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10277,7 +10277,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10287,7 +10287,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10314,10 +10314,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129248776</v>
+        <v>129240662</v>
       </c>
       <c r="B92" t="n">
-        <v>57724</v>
+        <v>79663</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10325,39 +10325,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>445137</v>
+        <v>445517</v>
       </c>
       <c r="R92" t="n">
-        <v>6734922</v>
+        <v>6735559</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10389,7 +10384,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10399,7 +10394,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10426,45 +10421,50 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129239096</v>
+        <v>129248776</v>
       </c>
       <c r="B93" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>445324</v>
+        <v>445137</v>
       </c>
       <c r="R93" t="n">
-        <v>6735285</v>
+        <v>6734922</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10496,7 +10496,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10533,10 +10533,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129243051</v>
+        <v>129239693</v>
       </c>
       <c r="B94" t="n">
-        <v>79139</v>
+        <v>79044</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10544,37 +10544,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445339</v>
+        <v>445362</v>
       </c>
       <c r="R94" t="n">
-        <v>6734920</v>
+        <v>6735341</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10606,7 +10603,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10616,12 +10613,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>3 bilder</t>
+          <t>5 bilder, sumpskog</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10630,7 +10627,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10649,10 +10645,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129239693</v>
+        <v>129243051</v>
       </c>
       <c r="B95" t="n">
-        <v>79044</v>
+        <v>79139</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10660,34 +10656,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445362</v>
+        <v>445339</v>
       </c>
       <c r="R95" t="n">
-        <v>6735341</v>
+        <v>6734920</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10719,7 +10718,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10729,12 +10728,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>5 bilder, sumpskog</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10743,6 +10742,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -11331,10 +11331,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129237880</v>
+        <v>129238933</v>
       </c>
       <c r="B101" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11342,39 +11342,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445206</v>
+        <v>445307</v>
       </c>
       <c r="R101" t="n">
-        <v>6735207</v>
+        <v>6735277</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11406,7 +11401,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11416,12 +11411,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Bild, torraka med hack</t>
+          <t>Rikligt i en radie av ca 50 meter 3 bilder, sista på två tallstammar</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11448,10 +11443,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129238933</v>
+        <v>129237880</v>
       </c>
       <c r="B102" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11459,34 +11454,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445307</v>
+        <v>445206</v>
       </c>
       <c r="R102" t="n">
-        <v>6735277</v>
+        <v>6735207</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11528,12 +11528,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter 3 bilder, sista på två tallstammar</t>
+          <t>Bild, torraka med hack</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11563,7 +11563,7 @@
         <v>129248843</v>
       </c>
       <c r="B103" t="n">
-        <v>91571</v>
+        <v>91574</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12250,10 +12250,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129243188</v>
+        <v>129238770</v>
       </c>
       <c r="B109" t="n">
-        <v>79139</v>
+        <v>57724</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12261,34 +12261,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>967</v>
+        <v>100049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>445401</v>
+        <v>445322</v>
       </c>
       <c r="R109" t="n">
-        <v>6734884</v>
+        <v>6735197</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12320,7 +12325,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12330,12 +12335,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>3 bilder</t>
+          <t>Bild på torraka, färska hack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12362,10 +12367,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129238770</v>
+        <v>129243188</v>
       </c>
       <c r="B110" t="n">
-        <v>57724</v>
+        <v>79139</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12373,39 +12378,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>967</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>445322</v>
+        <v>445401</v>
       </c>
       <c r="R110" t="n">
-        <v>6735197</v>
+        <v>6734884</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12437,7 +12437,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12447,12 +12447,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Bild på torraka, färska hack</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12937,10 +12937,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129237612</v>
+        <v>129240918</v>
       </c>
       <c r="B115" t="n">
-        <v>78802</v>
+        <v>57724</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12948,34 +12948,39 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>445279</v>
+        <v>445417</v>
       </c>
       <c r="R115" t="n">
-        <v>6735197</v>
+        <v>6735368</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13007,7 +13012,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13017,12 +13022,12 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Bild på två stubbar med äldre tall i bakgrund</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13049,10 +13054,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129238380</v>
+        <v>129237612</v>
       </c>
       <c r="B116" t="n">
-        <v>79634</v>
+        <v>78802</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13060,21 +13065,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13084,10 +13089,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>445322</v>
+        <v>445279</v>
       </c>
       <c r="R116" t="n">
-        <v>6735151</v>
+        <v>6735197</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13119,7 +13124,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13129,12 +13134,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Bild på grov kolad stuppe/låga, tall</t>
+          <t>Bild på två stubbar med äldre tall i bakgrund</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13161,10 +13166,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129240918</v>
+        <v>129238380</v>
       </c>
       <c r="B117" t="n">
-        <v>57724</v>
+        <v>79634</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13172,39 +13177,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>445417</v>
+        <v>445322</v>
       </c>
       <c r="R117" t="n">
-        <v>6735368</v>
+        <v>6735151</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13236,7 +13236,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13246,12 +13246,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild på grov kolad stuppe/låga, tall</t>
         </is>
       </c>
       <c r="AD117" t="b">

--- a/artfynd/A 43504-2025 artfynd.xlsx
+++ b/artfynd/A 43504-2025 artfynd.xlsx
@@ -4165,32 +4165,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129237525</v>
+        <v>129237324</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445251</v>
+        <v>445263</v>
       </c>
       <c r="R35" t="n">
-        <v>6735185</v>
+        <v>6735122</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4272,32 +4272,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129237324</v>
+        <v>129237525</v>
       </c>
       <c r="B36" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4307,10 +4307,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445263</v>
+        <v>445251</v>
       </c>
       <c r="R36" t="n">
-        <v>6735122</v>
+        <v>6735185</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4491,27 +4491,27 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129243809</v>
+        <v>129237782</v>
       </c>
       <c r="B38" t="n">
-        <v>57724</v>
+        <v>58097</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4522,7 +4522,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445358</v>
+        <v>445267</v>
       </c>
       <c r="R38" t="n">
-        <v>6735035</v>
+        <v>6735219</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4603,27 +4603,27 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129237782</v>
+        <v>129243809</v>
       </c>
       <c r="B39" t="n">
-        <v>58097</v>
+        <v>57724</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4634,7 +4634,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445267</v>
+        <v>445358</v>
       </c>
       <c r="R39" t="n">
-        <v>6735219</v>
+        <v>6735035</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4715,32 +4715,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129240788</v>
+        <v>129238704</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445491</v>
+        <v>445349</v>
       </c>
       <c r="R40" t="n">
-        <v>6735426</v>
+        <v>6735178</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4795,7 +4795,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5143,32 +5148,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129238704</v>
+        <v>129240788</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5178,10 +5183,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>445349</v>
+        <v>445491</v>
       </c>
       <c r="R44" t="n">
-        <v>6735178</v>
+        <v>6735426</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5213,7 +5218,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5223,12 +5228,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i närområdet</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5362,7 +5362,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129237683</v>
+        <v>129238645</v>
       </c>
       <c r="B46" t="n">
         <v>79044</v>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>445282</v>
+        <v>445322</v>
       </c>
       <c r="R46" t="n">
-        <v>6735211</v>
+        <v>6735197</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5469,7 +5469,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129238645</v>
+        <v>129237683</v>
       </c>
       <c r="B47" t="n">
         <v>79044</v>
@@ -5504,10 +5504,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>445322</v>
+        <v>445282</v>
       </c>
       <c r="R47" t="n">
-        <v>6735197</v>
+        <v>6735211</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5576,10 +5576,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129237483</v>
+        <v>129237617</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5587,21 +5587,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445260</v>
+        <v>445279</v>
       </c>
       <c r="R48" t="n">
-        <v>6735185</v>
+        <v>6735197</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5683,7 +5683,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129237299</v>
+        <v>129237483</v>
       </c>
       <c r="B49" t="n">
         <v>79044</v>
@@ -5721,7 +5721,7 @@
         <v>445260</v>
       </c>
       <c r="R49" t="n">
-        <v>6735095</v>
+        <v>6735185</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5790,10 +5790,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129237617</v>
+        <v>129237299</v>
       </c>
       <c r="B50" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5801,21 +5801,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5825,10 +5825,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>445279</v>
+        <v>445260</v>
       </c>
       <c r="R50" t="n">
-        <v>6735197</v>
+        <v>6735095</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6111,10 +6111,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129243753</v>
+        <v>129239857</v>
       </c>
       <c r="B53" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6122,34 +6122,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445384</v>
+        <v>445369</v>
       </c>
       <c r="R53" t="n">
-        <v>6734985</v>
+        <v>6735411</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6181,7 +6186,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6191,7 +6196,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6218,7 +6223,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129239740</v>
+        <v>129243753</v>
       </c>
       <c r="B54" t="n">
         <v>79044</v>
@@ -6253,10 +6258,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>445356</v>
+        <v>445384</v>
       </c>
       <c r="R54" t="n">
-        <v>6735366</v>
+        <v>6734985</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6288,7 +6293,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6298,7 +6303,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6325,10 +6330,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129239857</v>
+        <v>129239740</v>
       </c>
       <c r="B55" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6336,39 +6341,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445369</v>
+        <v>445356</v>
       </c>
       <c r="R55" t="n">
-        <v>6735411</v>
+        <v>6735366</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6870,10 +6870,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129239929</v>
+        <v>129243054</v>
       </c>
       <c r="B60" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6881,21 +6881,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6905,10 +6905,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445421</v>
+        <v>445339</v>
       </c>
       <c r="R60" t="n">
-        <v>6735402</v>
+        <v>6734920</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6940,7 +6940,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6950,12 +6950,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6982,7 +6977,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129240474</v>
+        <v>129240566</v>
       </c>
       <c r="B61" t="n">
         <v>79044</v>
@@ -7017,10 +7012,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>445438</v>
+        <v>445481</v>
       </c>
       <c r="R61" t="n">
-        <v>6735509</v>
+        <v>6735582</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7089,7 +7084,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129240967</v>
+        <v>129239929</v>
       </c>
       <c r="B62" t="n">
         <v>79044</v>
@@ -7124,10 +7119,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>445414</v>
+        <v>445421</v>
       </c>
       <c r="R62" t="n">
-        <v>6735285</v>
+        <v>6735402</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7159,7 +7154,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7169,7 +7164,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7196,7 +7196,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129240566</v>
+        <v>129240474</v>
       </c>
       <c r="B63" t="n">
         <v>79044</v>
@@ -7231,10 +7231,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>445481</v>
+        <v>445438</v>
       </c>
       <c r="R63" t="n">
-        <v>6735582</v>
+        <v>6735509</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7303,10 +7303,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129243054</v>
+        <v>129240967</v>
       </c>
       <c r="B64" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7314,21 +7314,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>445339</v>
+        <v>445414</v>
       </c>
       <c r="R64" t="n">
-        <v>6734920</v>
+        <v>6735285</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7950,32 +7950,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129238778</v>
+        <v>129244530</v>
       </c>
       <c r="B70" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>445322</v>
+        <v>445217</v>
       </c>
       <c r="R70" t="n">
-        <v>6735197</v>
+        <v>6734997</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8020,7 +8020,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8057,32 +8057,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129244530</v>
+        <v>129238778</v>
       </c>
       <c r="B71" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8092,10 +8092,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445217</v>
+        <v>445322</v>
       </c>
       <c r="R71" t="n">
-        <v>6734997</v>
+        <v>6735197</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8276,32 +8276,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129237286</v>
+        <v>129238788</v>
       </c>
       <c r="B73" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8311,10 +8311,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445252</v>
+        <v>445316</v>
       </c>
       <c r="R73" t="n">
-        <v>6735079</v>
+        <v>6735207</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8346,7 +8346,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8356,7 +8356,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Rikligt i närområdet</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8383,10 +8388,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129244655</v>
+        <v>129237274</v>
       </c>
       <c r="B74" t="n">
-        <v>79634</v>
+        <v>79663</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8394,21 +8399,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8418,10 +8423,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>445217</v>
+        <v>445252</v>
       </c>
       <c r="R74" t="n">
-        <v>6734997</v>
+        <v>6735079</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8453,7 +8458,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8463,7 +8468,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8490,7 +8495,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129238788</v>
+        <v>129239479</v>
       </c>
       <c r="B75" t="n">
         <v>79044</v>
@@ -8525,10 +8530,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>445316</v>
+        <v>445379</v>
       </c>
       <c r="R75" t="n">
-        <v>6735207</v>
+        <v>6735294</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8571,11 +8576,6 @@
       <c r="AB75" t="inlineStr">
         <is>
           <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Rikligt i närområdet</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8602,32 +8602,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129237274</v>
+        <v>129237286</v>
       </c>
       <c r="B76" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8709,10 +8709,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129239479</v>
+        <v>129244655</v>
       </c>
       <c r="B77" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8720,21 +8720,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8744,10 +8744,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>445379</v>
+        <v>445217</v>
       </c>
       <c r="R77" t="n">
-        <v>6735294</v>
+        <v>6734997</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8779,7 +8779,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8816,32 +8816,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129243245</v>
+        <v>129243104</v>
       </c>
       <c r="B78" t="n">
-        <v>78801</v>
+        <v>8450</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>445422</v>
+        <v>445374</v>
       </c>
       <c r="R78" t="n">
-        <v>6734878</v>
+        <v>6734891</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8923,10 +8923,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129243192</v>
+        <v>129243245</v>
       </c>
       <c r="B79" t="n">
-        <v>78802</v>
+        <v>78801</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8934,21 +8934,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8958,10 +8958,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>445401</v>
+        <v>445422</v>
       </c>
       <c r="R79" t="n">
-        <v>6734884</v>
+        <v>6734878</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9030,32 +9030,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129243104</v>
+        <v>129243192</v>
       </c>
       <c r="B80" t="n">
-        <v>8450</v>
+        <v>78802</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9065,10 +9065,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445374</v>
+        <v>445401</v>
       </c>
       <c r="R80" t="n">
-        <v>6734891</v>
+        <v>6734884</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9244,32 +9244,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129239850</v>
+        <v>129238241</v>
       </c>
       <c r="B82" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9279,10 +9279,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445369</v>
+        <v>445313</v>
       </c>
       <c r="R82" t="n">
-        <v>6735411</v>
+        <v>6735165</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9351,32 +9351,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129242957</v>
+        <v>129237533</v>
       </c>
       <c r="B83" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445292</v>
+        <v>445256</v>
       </c>
       <c r="R83" t="n">
-        <v>6734957</v>
+        <v>6735194</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9565,32 +9565,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129238241</v>
+        <v>129239850</v>
       </c>
       <c r="B85" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9600,10 +9600,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445313</v>
+        <v>445369</v>
       </c>
       <c r="R85" t="n">
-        <v>6735165</v>
+        <v>6735411</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9672,32 +9672,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129237533</v>
+        <v>129242957</v>
       </c>
       <c r="B86" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9707,10 +9707,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445256</v>
+        <v>445292</v>
       </c>
       <c r="R86" t="n">
-        <v>6735194</v>
+        <v>6734957</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9742,7 +9742,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9752,7 +9752,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10207,32 +10207,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129239096</v>
+        <v>129240662</v>
       </c>
       <c r="B91" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10242,10 +10242,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>445324</v>
+        <v>445517</v>
       </c>
       <c r="R91" t="n">
-        <v>6735285</v>
+        <v>6735559</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10277,7 +10277,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10287,7 +10287,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10314,10 +10314,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129240662</v>
+        <v>129248776</v>
       </c>
       <c r="B92" t="n">
-        <v>79663</v>
+        <v>57724</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10325,34 +10325,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>445517</v>
+        <v>445137</v>
       </c>
       <c r="R92" t="n">
-        <v>6735559</v>
+        <v>6734922</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10384,7 +10389,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10394,7 +10399,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10421,50 +10426,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129248776</v>
+        <v>129239096</v>
       </c>
       <c r="B93" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>445137</v>
+        <v>445324</v>
       </c>
       <c r="R93" t="n">
-        <v>6734922</v>
+        <v>6735285</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10496,7 +10496,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10533,10 +10533,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129239693</v>
+        <v>129243051</v>
       </c>
       <c r="B94" t="n">
-        <v>79044</v>
+        <v>79139</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10544,34 +10544,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445362</v>
+        <v>445339</v>
       </c>
       <c r="R94" t="n">
-        <v>6735341</v>
+        <v>6734920</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10603,7 +10606,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10613,12 +10616,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>5 bilder, sumpskog</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10627,6 +10630,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10645,10 +10649,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129243051</v>
+        <v>129239693</v>
       </c>
       <c r="B95" t="n">
-        <v>79139</v>
+        <v>79044</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10656,37 +10660,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445339</v>
+        <v>445362</v>
       </c>
       <c r="R95" t="n">
-        <v>6734920</v>
+        <v>6735341</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10718,7 +10719,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10728,12 +10729,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>3 bilder</t>
+          <t>5 bilder, sumpskog</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10742,7 +10743,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -12250,10 +12250,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129238770</v>
+        <v>129243188</v>
       </c>
       <c r="B109" t="n">
-        <v>57724</v>
+        <v>79139</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12261,39 +12261,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100049</v>
+        <v>967</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>445322</v>
+        <v>445401</v>
       </c>
       <c r="R109" t="n">
-        <v>6735197</v>
+        <v>6734884</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12325,7 +12320,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12335,12 +12330,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Bild på torraka, färska hack</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12367,10 +12362,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129243188</v>
+        <v>129238770</v>
       </c>
       <c r="B110" t="n">
-        <v>79139</v>
+        <v>57724</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12378,34 +12373,39 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>967</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>445401</v>
+        <v>445322</v>
       </c>
       <c r="R110" t="n">
-        <v>6734884</v>
+        <v>6735197</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12437,7 +12437,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12447,12 +12447,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>3 bilder</t>
+          <t>Bild på torraka, färska hack</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12713,10 +12713,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129237668</v>
+        <v>129243085</v>
       </c>
       <c r="B113" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12724,21 +12724,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12748,10 +12748,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>445302</v>
+        <v>445378</v>
       </c>
       <c r="R113" t="n">
-        <v>6735183</v>
+        <v>6734906</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12783,7 +12783,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12793,12 +12793,12 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Bild på äldre tall, stam uppåt</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12825,10 +12825,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129243085</v>
+        <v>129237668</v>
       </c>
       <c r="B114" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12836,21 +12836,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12860,10 +12860,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>445378</v>
+        <v>445302</v>
       </c>
       <c r="R114" t="n">
-        <v>6734906</v>
+        <v>6735183</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12895,7 +12895,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild på äldre tall, stam uppåt</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12937,10 +12937,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129240918</v>
+        <v>129237612</v>
       </c>
       <c r="B115" t="n">
-        <v>57724</v>
+        <v>78802</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12948,39 +12948,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>445417</v>
+        <v>445279</v>
       </c>
       <c r="R115" t="n">
-        <v>6735368</v>
+        <v>6735197</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13012,7 +13007,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13022,12 +13017,12 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild på två stubbar med äldre tall i bakgrund</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13054,10 +13049,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129237612</v>
+        <v>129238380</v>
       </c>
       <c r="B116" t="n">
-        <v>78802</v>
+        <v>79634</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13065,21 +13060,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13089,10 +13084,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>445279</v>
+        <v>445322</v>
       </c>
       <c r="R116" t="n">
-        <v>6735197</v>
+        <v>6735151</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13124,7 +13119,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13134,12 +13129,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Bild på två stubbar med äldre tall i bakgrund</t>
+          <t>Bild på grov kolad stuppe/låga, tall</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13166,10 +13161,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129238380</v>
+        <v>129240918</v>
       </c>
       <c r="B117" t="n">
-        <v>79634</v>
+        <v>57724</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13177,34 +13172,39 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>445322</v>
+        <v>445417</v>
       </c>
       <c r="R117" t="n">
-        <v>6735151</v>
+        <v>6735368</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13236,7 +13236,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13246,12 +13246,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Bild på grov kolad stuppe/låga, tall</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD117" t="b">

--- a/artfynd/A 43504-2025 artfynd.xlsx
+++ b/artfynd/A 43504-2025 artfynd.xlsx
@@ -4379,38 +4379,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129239467</v>
+        <v>129243809</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4419,10 +4419,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445379</v>
+        <v>445358</v>
       </c>
       <c r="R37" t="n">
-        <v>6735294</v>
+        <v>6735035</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4491,10 +4491,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129237782</v>
+        <v>129239467</v>
       </c>
       <c r="B38" t="n">
-        <v>58097</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4502,27 +4502,27 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445267</v>
+        <v>445379</v>
       </c>
       <c r="R38" t="n">
-        <v>6735219</v>
+        <v>6735294</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4603,27 +4603,27 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129243809</v>
+        <v>129237782</v>
       </c>
       <c r="B39" t="n">
-        <v>57724</v>
+        <v>58097</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4634,7 +4634,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445358</v>
+        <v>445267</v>
       </c>
       <c r="R39" t="n">
-        <v>6735035</v>
+        <v>6735219</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4715,7 +4715,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129238704</v>
+        <v>129238576</v>
       </c>
       <c r="B40" t="n">
         <v>79044</v>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445349</v>
+        <v>445336</v>
       </c>
       <c r="R40" t="n">
-        <v>6735178</v>
+        <v>6735162</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4796,11 +4796,6 @@
       <c r="AB40" t="inlineStr">
         <is>
           <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4827,7 +4822,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129238576</v>
+        <v>129238322</v>
       </c>
       <c r="B41" t="n">
         <v>79044</v>
@@ -4862,10 +4857,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445336</v>
+        <v>445325</v>
       </c>
       <c r="R41" t="n">
-        <v>6735162</v>
+        <v>6735153</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4934,7 +4929,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129238322</v>
+        <v>129239093</v>
       </c>
       <c r="B42" t="n">
         <v>79044</v>
@@ -4969,10 +4964,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445325</v>
+        <v>445324</v>
       </c>
       <c r="R42" t="n">
-        <v>6735153</v>
+        <v>6735285</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5041,7 +5036,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129239093</v>
+        <v>129238704</v>
       </c>
       <c r="B43" t="n">
         <v>79044</v>
@@ -5076,10 +5071,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445324</v>
+        <v>445349</v>
       </c>
       <c r="R43" t="n">
-        <v>6735285</v>
+        <v>6735178</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5122,6 +5117,11 @@
       <c r="AB43" t="inlineStr">
         <is>
           <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5362,7 +5362,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129238645</v>
+        <v>129237683</v>
       </c>
       <c r="B46" t="n">
         <v>79044</v>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>445322</v>
+        <v>445282</v>
       </c>
       <c r="R46" t="n">
-        <v>6735197</v>
+        <v>6735211</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5469,7 +5469,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129237683</v>
+        <v>129238645</v>
       </c>
       <c r="B47" t="n">
         <v>79044</v>
@@ -5504,10 +5504,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>445282</v>
+        <v>445322</v>
       </c>
       <c r="R47" t="n">
-        <v>6735211</v>
+        <v>6735197</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6870,10 +6870,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129243054</v>
+        <v>129239929</v>
       </c>
       <c r="B60" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6881,21 +6881,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6905,10 +6905,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445339</v>
+        <v>445421</v>
       </c>
       <c r="R60" t="n">
-        <v>6734920</v>
+        <v>6735402</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6940,7 +6940,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6950,7 +6950,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7084,7 +7089,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129239929</v>
+        <v>129240474</v>
       </c>
       <c r="B62" t="n">
         <v>79044</v>
@@ -7119,10 +7124,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>445421</v>
+        <v>445438</v>
       </c>
       <c r="R62" t="n">
-        <v>6735402</v>
+        <v>6735509</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7154,7 +7159,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7164,12 +7169,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7196,7 +7196,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129240474</v>
+        <v>129240967</v>
       </c>
       <c r="B63" t="n">
         <v>79044</v>
@@ -7231,10 +7231,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>445438</v>
+        <v>445414</v>
       </c>
       <c r="R63" t="n">
-        <v>6735509</v>
+        <v>6735285</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7303,10 +7303,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129240967</v>
+        <v>129243054</v>
       </c>
       <c r="B64" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7314,21 +7314,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>445414</v>
+        <v>445339</v>
       </c>
       <c r="R64" t="n">
-        <v>6735285</v>
+        <v>6734920</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8388,10 +8388,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129237274</v>
+        <v>129244655</v>
       </c>
       <c r="B74" t="n">
-        <v>79663</v>
+        <v>79634</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8399,21 +8399,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8423,10 +8423,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>445252</v>
+        <v>445217</v>
       </c>
       <c r="R74" t="n">
-        <v>6735079</v>
+        <v>6734997</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8602,32 +8602,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129237286</v>
+        <v>129237274</v>
       </c>
       <c r="B76" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8709,32 +8709,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129244655</v>
+        <v>129237286</v>
       </c>
       <c r="B77" t="n">
-        <v>79634</v>
+        <v>8450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8744,10 +8744,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>445217</v>
+        <v>445252</v>
       </c>
       <c r="R77" t="n">
-        <v>6734997</v>
+        <v>6735079</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8779,7 +8779,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8816,32 +8816,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129243104</v>
+        <v>129243192</v>
       </c>
       <c r="B78" t="n">
-        <v>8450</v>
+        <v>78802</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>445374</v>
+        <v>445401</v>
       </c>
       <c r="R78" t="n">
-        <v>6734891</v>
+        <v>6734884</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9030,32 +9030,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129243192</v>
+        <v>129243104</v>
       </c>
       <c r="B80" t="n">
-        <v>78802</v>
+        <v>8450</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9065,10 +9065,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445401</v>
+        <v>445374</v>
       </c>
       <c r="R80" t="n">
-        <v>6734884</v>
+        <v>6734891</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9244,7 +9244,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129238241</v>
+        <v>129237650</v>
       </c>
       <c r="B82" t="n">
         <v>79044</v>
@@ -9279,10 +9279,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445313</v>
+        <v>445279</v>
       </c>
       <c r="R82" t="n">
-        <v>6735165</v>
+        <v>6735197</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9351,7 +9351,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129237533</v>
+        <v>129238241</v>
       </c>
       <c r="B83" t="n">
         <v>79044</v>
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445256</v>
+        <v>445313</v>
       </c>
       <c r="R83" t="n">
-        <v>6735194</v>
+        <v>6735165</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9458,7 +9458,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129237650</v>
+        <v>129237533</v>
       </c>
       <c r="B84" t="n">
         <v>79044</v>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445279</v>
+        <v>445256</v>
       </c>
       <c r="R84" t="n">
-        <v>6735197</v>
+        <v>6735194</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9886,10 +9886,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129243589</v>
+        <v>129247020</v>
       </c>
       <c r="B88" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9897,21 +9897,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9921,10 +9921,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>445385</v>
+        <v>445135</v>
       </c>
       <c r="R88" t="n">
-        <v>6734971</v>
+        <v>6734998</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9956,7 +9956,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9966,7 +9966,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9993,7 +9993,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129247020</v>
+        <v>129243217</v>
       </c>
       <c r="B89" t="n">
         <v>78802</v>
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>445135</v>
+        <v>445422</v>
       </c>
       <c r="R89" t="n">
-        <v>6734998</v>
+        <v>6734878</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10063,7 +10063,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10100,10 +10100,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129243217</v>
+        <v>129243589</v>
       </c>
       <c r="B90" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10111,21 +10111,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10135,10 +10135,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>445422</v>
+        <v>445385</v>
       </c>
       <c r="R90" t="n">
-        <v>6734878</v>
+        <v>6734971</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11331,10 +11331,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129238933</v>
+        <v>129237880</v>
       </c>
       <c r="B101" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11342,34 +11342,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445307</v>
+        <v>445206</v>
       </c>
       <c r="R101" t="n">
-        <v>6735277</v>
+        <v>6735207</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11401,7 +11406,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11411,12 +11416,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter 3 bilder, sista på två tallstammar</t>
+          <t>Bild, torraka med hack</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11443,10 +11448,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129237880</v>
+        <v>129238933</v>
       </c>
       <c r="B102" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11454,39 +11459,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445206</v>
+        <v>445307</v>
       </c>
       <c r="R102" t="n">
-        <v>6735207</v>
+        <v>6735277</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11528,12 +11528,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Bild, torraka med hack</t>
+          <t>Rikligt i en radie av ca 50 meter 3 bilder, sista på två tallstammar</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11676,7 +11676,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129243098</v>
+        <v>129238758</v>
       </c>
       <c r="B104" t="n">
         <v>57724</v>
@@ -11707,7 +11707,7 @@
       <c r="I104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -11716,10 +11716,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445374</v>
+        <v>445349</v>
       </c>
       <c r="R104" t="n">
-        <v>6734891</v>
+        <v>6735194</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11751,7 +11751,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11761,12 +11761,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>2 bilder på torraka med hack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11793,7 +11793,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129238758</v>
+        <v>129243098</v>
       </c>
       <c r="B105" t="n">
         <v>57724</v>
@@ -11824,7 +11824,7 @@
       <c r="I105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -11833,10 +11833,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445349</v>
+        <v>445374</v>
       </c>
       <c r="R105" t="n">
-        <v>6735194</v>
+        <v>6734891</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11868,7 +11868,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11878,12 +11878,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>2 bilder på torraka med hack</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12937,10 +12937,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129237612</v>
+        <v>129240918</v>
       </c>
       <c r="B115" t="n">
-        <v>78802</v>
+        <v>57724</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12948,34 +12948,39 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>445279</v>
+        <v>445417</v>
       </c>
       <c r="R115" t="n">
-        <v>6735197</v>
+        <v>6735368</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13007,7 +13012,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13017,12 +13022,12 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Bild på två stubbar med äldre tall i bakgrund</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13049,10 +13054,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129238380</v>
+        <v>129237612</v>
       </c>
       <c r="B116" t="n">
-        <v>79634</v>
+        <v>78802</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13060,21 +13065,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13084,10 +13089,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>445322</v>
+        <v>445279</v>
       </c>
       <c r="R116" t="n">
-        <v>6735151</v>
+        <v>6735197</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13119,7 +13124,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13129,12 +13134,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Bild på grov kolad stuppe/låga, tall</t>
+          <t>Bild på två stubbar med äldre tall i bakgrund</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13161,10 +13166,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129240918</v>
+        <v>129238380</v>
       </c>
       <c r="B117" t="n">
-        <v>57724</v>
+        <v>79634</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13172,39 +13177,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>445417</v>
+        <v>445322</v>
       </c>
       <c r="R117" t="n">
-        <v>6735368</v>
+        <v>6735151</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13236,7 +13236,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13246,12 +13246,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild på grov kolad stuppe/låga, tall</t>
         </is>
       </c>
       <c r="AD117" t="b">

--- a/artfynd/A 43504-2025 artfynd.xlsx
+++ b/artfynd/A 43504-2025 artfynd.xlsx
@@ -2596,10 +2596,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129248688</v>
+        <v>129248920</v>
       </c>
       <c r="B20" t="n">
-        <v>79139</v>
+        <v>79663</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2607,38 +2607,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>967</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445078</v>
+        <v>445066</v>
       </c>
       <c r="R20" t="n">
-        <v>6734933</v>
+        <v>6734914</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2685,7 +2681,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>3 bilder</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2712,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129248920</v>
+        <v>129248688</v>
       </c>
       <c r="B21" t="n">
-        <v>79663</v>
+        <v>79139</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,34 +2719,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>967</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>445066</v>
+        <v>445078</v>
       </c>
       <c r="R21" t="n">
-        <v>6734914</v>
+        <v>6734933</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4491,10 +4491,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129239467</v>
+        <v>129237782</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>58097</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4502,27 +4502,27 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445379</v>
+        <v>445267</v>
       </c>
       <c r="R38" t="n">
-        <v>6735294</v>
+        <v>6735219</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4603,10 +4603,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129237782</v>
+        <v>129239467</v>
       </c>
       <c r="B39" t="n">
-        <v>58097</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4614,27 +4614,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445267</v>
+        <v>445379</v>
       </c>
       <c r="R39" t="n">
-        <v>6735219</v>
+        <v>6735294</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5576,10 +5576,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129237617</v>
+        <v>129237483</v>
       </c>
       <c r="B48" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5587,21 +5587,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445279</v>
+        <v>445260</v>
       </c>
       <c r="R48" t="n">
-        <v>6735197</v>
+        <v>6735185</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5683,7 +5683,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129237483</v>
+        <v>129237299</v>
       </c>
       <c r="B49" t="n">
         <v>79044</v>
@@ -5721,7 +5721,7 @@
         <v>445260</v>
       </c>
       <c r="R49" t="n">
-        <v>6735185</v>
+        <v>6735095</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5790,10 +5790,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129237299</v>
+        <v>129237617</v>
       </c>
       <c r="B50" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5801,21 +5801,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5825,10 +5825,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>445260</v>
+        <v>445279</v>
       </c>
       <c r="R50" t="n">
-        <v>6735095</v>
+        <v>6735197</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6437,45 +6437,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129237544</v>
+        <v>129242999</v>
       </c>
       <c r="B56" t="n">
-        <v>79044</v>
+        <v>58097</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>445264</v>
+        <v>445292</v>
       </c>
       <c r="R56" t="n">
-        <v>6735197</v>
+        <v>6734957</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6507,7 +6512,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6517,7 +6522,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6544,7 +6549,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129240724</v>
+        <v>129237544</v>
       </c>
       <c r="B57" t="n">
         <v>79044</v>
@@ -6579,10 +6584,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445509</v>
+        <v>445264</v>
       </c>
       <c r="R57" t="n">
-        <v>6735455</v>
+        <v>6735197</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6614,7 +6619,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6624,7 +6629,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6651,50 +6656,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129242999</v>
+        <v>129240724</v>
       </c>
       <c r="B58" t="n">
-        <v>58097</v>
+        <v>79044</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>445292</v>
+        <v>445509</v>
       </c>
       <c r="R58" t="n">
-        <v>6734957</v>
+        <v>6735455</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6870,7 +6870,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129239929</v>
+        <v>129240566</v>
       </c>
       <c r="B60" t="n">
         <v>79044</v>
@@ -6905,10 +6905,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445421</v>
+        <v>445481</v>
       </c>
       <c r="R60" t="n">
-        <v>6735402</v>
+        <v>6735582</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6940,7 +6940,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6950,12 +6950,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6982,7 +6977,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129240566</v>
+        <v>129239929</v>
       </c>
       <c r="B61" t="n">
         <v>79044</v>
@@ -7017,10 +7012,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>445481</v>
+        <v>445421</v>
       </c>
       <c r="R61" t="n">
-        <v>6735582</v>
+        <v>6735402</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7052,7 +7047,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7062,7 +7057,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7410,32 +7410,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129237820</v>
+        <v>129240494</v>
       </c>
       <c r="B65" t="n">
-        <v>78801</v>
+        <v>8450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7445,10 +7445,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445225</v>
+        <v>445440</v>
       </c>
       <c r="R65" t="n">
-        <v>6735226</v>
+        <v>6735522</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7480,7 +7480,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7517,32 +7517,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129240494</v>
+        <v>129237820</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>78801</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7552,10 +7552,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445440</v>
+        <v>445225</v>
       </c>
       <c r="R66" t="n">
-        <v>6735522</v>
+        <v>6735226</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7587,7 +7587,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7624,10 +7624,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129247898</v>
+        <v>129238815</v>
       </c>
       <c r="B67" t="n">
-        <v>79663</v>
+        <v>57887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7635,37 +7635,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445107</v>
+        <v>445313</v>
       </c>
       <c r="R67" t="n">
-        <v>6735004</v>
+        <v>6735262</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7694,7 +7699,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7704,7 +7709,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7731,10 +7736,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129238475</v>
+        <v>129247898</v>
       </c>
       <c r="B68" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7742,21 +7747,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7766,10 +7771,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445322</v>
+        <v>445107</v>
       </c>
       <c r="R68" t="n">
-        <v>6735128</v>
+        <v>6735004</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7801,7 +7806,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7811,7 +7816,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7838,10 +7843,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129238815</v>
+        <v>129238475</v>
       </c>
       <c r="B69" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7849,42 +7854,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>445313</v>
+        <v>445322</v>
       </c>
       <c r="R69" t="n">
-        <v>6735262</v>
+        <v>6735128</v>
       </c>
       <c r="S69" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8388,10 +8388,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129244655</v>
+        <v>129237274</v>
       </c>
       <c r="B74" t="n">
-        <v>79634</v>
+        <v>79663</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8399,21 +8399,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8423,10 +8423,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>445217</v>
+        <v>445252</v>
       </c>
       <c r="R74" t="n">
-        <v>6734997</v>
+        <v>6735079</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8602,32 +8602,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129237274</v>
+        <v>129237286</v>
       </c>
       <c r="B76" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8709,32 +8709,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129237286</v>
+        <v>129244655</v>
       </c>
       <c r="B77" t="n">
-        <v>8450</v>
+        <v>79634</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8744,10 +8744,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>445252</v>
+        <v>445217</v>
       </c>
       <c r="R77" t="n">
-        <v>6735079</v>
+        <v>6734997</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8779,7 +8779,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8816,32 +8816,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129243192</v>
+        <v>129243104</v>
       </c>
       <c r="B78" t="n">
-        <v>78802</v>
+        <v>8450</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>445401</v>
+        <v>445374</v>
       </c>
       <c r="R78" t="n">
-        <v>6734884</v>
+        <v>6734891</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9030,32 +9030,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129243104</v>
+        <v>129243192</v>
       </c>
       <c r="B80" t="n">
-        <v>8450</v>
+        <v>78802</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9065,10 +9065,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445374</v>
+        <v>445401</v>
       </c>
       <c r="R80" t="n">
-        <v>6734891</v>
+        <v>6734884</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9244,7 +9244,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129237650</v>
+        <v>129238241</v>
       </c>
       <c r="B82" t="n">
         <v>79044</v>
@@ -9279,10 +9279,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445279</v>
+        <v>445313</v>
       </c>
       <c r="R82" t="n">
-        <v>6735197</v>
+        <v>6735165</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9351,32 +9351,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129238241</v>
+        <v>129239850</v>
       </c>
       <c r="B83" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445313</v>
+        <v>445369</v>
       </c>
       <c r="R83" t="n">
-        <v>6735165</v>
+        <v>6735411</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9458,32 +9458,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129237533</v>
+        <v>129242957</v>
       </c>
       <c r="B84" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445256</v>
+        <v>445292</v>
       </c>
       <c r="R84" t="n">
-        <v>6735194</v>
+        <v>6734957</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9528,7 +9528,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9565,32 +9565,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129239850</v>
+        <v>129237650</v>
       </c>
       <c r="B85" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9600,10 +9600,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445369</v>
+        <v>445279</v>
       </c>
       <c r="R85" t="n">
-        <v>6735411</v>
+        <v>6735197</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9635,7 +9635,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9645,7 +9645,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9672,32 +9672,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129242957</v>
+        <v>129237533</v>
       </c>
       <c r="B86" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9707,10 +9707,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445292</v>
+        <v>445256</v>
       </c>
       <c r="R86" t="n">
-        <v>6734957</v>
+        <v>6735194</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9742,7 +9742,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9752,7 +9752,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9886,10 +9886,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129247020</v>
+        <v>129243589</v>
       </c>
       <c r="B88" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9897,21 +9897,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9921,10 +9921,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>445135</v>
+        <v>445385</v>
       </c>
       <c r="R88" t="n">
-        <v>6734998</v>
+        <v>6734971</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9956,7 +9956,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9966,7 +9966,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9993,7 +9993,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129243217</v>
+        <v>129247020</v>
       </c>
       <c r="B89" t="n">
         <v>78802</v>
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>445422</v>
+        <v>445135</v>
       </c>
       <c r="R89" t="n">
-        <v>6734878</v>
+        <v>6734998</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10063,7 +10063,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10100,10 +10100,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129243589</v>
+        <v>129243217</v>
       </c>
       <c r="B90" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10111,21 +10111,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10135,10 +10135,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>445385</v>
+        <v>445422</v>
       </c>
       <c r="R90" t="n">
-        <v>6734971</v>
+        <v>6734878</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10207,10 +10207,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129240662</v>
+        <v>129248776</v>
       </c>
       <c r="B91" t="n">
-        <v>79663</v>
+        <v>57724</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10218,34 +10218,39 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>445517</v>
+        <v>445137</v>
       </c>
       <c r="R91" t="n">
-        <v>6735559</v>
+        <v>6734922</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10277,7 +10282,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10287,7 +10292,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10314,10 +10319,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129248776</v>
+        <v>129240662</v>
       </c>
       <c r="B92" t="n">
-        <v>57724</v>
+        <v>79663</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10325,39 +10330,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>445137</v>
+        <v>445517</v>
       </c>
       <c r="R92" t="n">
-        <v>6734922</v>
+        <v>6735559</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10399,7 +10399,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10533,10 +10533,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129243051</v>
+        <v>129239693</v>
       </c>
       <c r="B94" t="n">
-        <v>79139</v>
+        <v>79044</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10544,37 +10544,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445339</v>
+        <v>445362</v>
       </c>
       <c r="R94" t="n">
-        <v>6734920</v>
+        <v>6735341</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10606,7 +10603,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10616,12 +10613,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>3 bilder</t>
+          <t>5 bilder, sumpskog</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10630,7 +10627,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10649,10 +10645,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129239693</v>
+        <v>129243051</v>
       </c>
       <c r="B95" t="n">
-        <v>79044</v>
+        <v>79139</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10660,34 +10656,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445362</v>
+        <v>445339</v>
       </c>
       <c r="R95" t="n">
-        <v>6735341</v>
+        <v>6734920</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10719,7 +10718,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10729,12 +10728,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>5 bilder, sumpskog</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10743,6 +10742,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -11560,10 +11560,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129248843</v>
+        <v>129243098</v>
       </c>
       <c r="B103" t="n">
-        <v>91574</v>
+        <v>57724</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11571,26 +11571,27 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -11599,10 +11600,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445140</v>
+        <v>445374</v>
       </c>
       <c r="R103" t="n">
-        <v>6734876</v>
+        <v>6734891</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11634,7 +11635,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11644,7 +11645,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
@@ -11793,10 +11794,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129243098</v>
+        <v>129248843</v>
       </c>
       <c r="B105" t="n">
-        <v>57724</v>
+        <v>91574</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11804,27 +11805,26 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -11833,10 +11833,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445374</v>
+        <v>445140</v>
       </c>
       <c r="R105" t="n">
-        <v>6734891</v>
+        <v>6734876</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11868,7 +11868,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11878,7 +11878,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
@@ -12250,10 +12250,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129243188</v>
+        <v>129238770</v>
       </c>
       <c r="B109" t="n">
-        <v>79139</v>
+        <v>57724</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12261,34 +12261,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>967</v>
+        <v>100049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>445401</v>
+        <v>445322</v>
       </c>
       <c r="R109" t="n">
-        <v>6734884</v>
+        <v>6735197</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12320,7 +12325,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12330,12 +12335,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>3 bilder</t>
+          <t>Bild på torraka, färska hack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12362,10 +12367,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129238770</v>
+        <v>129243188</v>
       </c>
       <c r="B110" t="n">
-        <v>57724</v>
+        <v>79139</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12373,39 +12378,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>967</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>445322</v>
+        <v>445401</v>
       </c>
       <c r="R110" t="n">
-        <v>6735197</v>
+        <v>6734884</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12437,7 +12437,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12447,12 +12447,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Bild på torraka, färska hack</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12713,10 +12713,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129243085</v>
+        <v>129237668</v>
       </c>
       <c r="B113" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12724,21 +12724,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12748,10 +12748,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>445378</v>
+        <v>445302</v>
       </c>
       <c r="R113" t="n">
-        <v>6734906</v>
+        <v>6735183</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12783,7 +12783,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12793,12 +12793,12 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild på äldre tall, stam uppåt</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12825,10 +12825,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129237668</v>
+        <v>129243085</v>
       </c>
       <c r="B114" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12836,21 +12836,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12860,10 +12860,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>445302</v>
+        <v>445378</v>
       </c>
       <c r="R114" t="n">
-        <v>6735183</v>
+        <v>6734906</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12895,7 +12895,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Bild på äldre tall, stam uppåt</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD114" t="b">

--- a/artfynd/A 43504-2025 artfynd.xlsx
+++ b/artfynd/A 43504-2025 artfynd.xlsx
@@ -2596,10 +2596,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129248920</v>
+        <v>129248688</v>
       </c>
       <c r="B20" t="n">
-        <v>79663</v>
+        <v>79139</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2607,34 +2607,38 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>967</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445066</v>
+        <v>445078</v>
       </c>
       <c r="R20" t="n">
-        <v>6734914</v>
+        <v>6734933</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,7 +2685,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2712,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129248688</v>
+        <v>129248920</v>
       </c>
       <c r="B21" t="n">
-        <v>79139</v>
+        <v>79663</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,38 +2723,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>967</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>445078</v>
+        <v>445066</v>
       </c>
       <c r="R21" t="n">
-        <v>6734933</v>
+        <v>6734914</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>3 bilder</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4165,32 +4165,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129237324</v>
+        <v>129237525</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445263</v>
+        <v>445251</v>
       </c>
       <c r="R35" t="n">
-        <v>6735122</v>
+        <v>6735185</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4272,32 +4272,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129237525</v>
+        <v>129237324</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4307,10 +4307,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445251</v>
+        <v>445263</v>
       </c>
       <c r="R36" t="n">
-        <v>6735185</v>
+        <v>6735122</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4491,10 +4491,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129237782</v>
+        <v>129239467</v>
       </c>
       <c r="B38" t="n">
-        <v>58097</v>
+        <v>8450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4502,27 +4502,27 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445267</v>
+        <v>445379</v>
       </c>
       <c r="R38" t="n">
-        <v>6735219</v>
+        <v>6735294</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4603,10 +4603,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129239467</v>
+        <v>129237782</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>58097</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4614,27 +4614,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445379</v>
+        <v>445267</v>
       </c>
       <c r="R39" t="n">
-        <v>6735294</v>
+        <v>6735219</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4715,7 +4715,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129238576</v>
+        <v>129239093</v>
       </c>
       <c r="B40" t="n">
         <v>79044</v>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445336</v>
+        <v>445324</v>
       </c>
       <c r="R40" t="n">
-        <v>6735162</v>
+        <v>6735285</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4822,7 +4822,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129238322</v>
+        <v>129238704</v>
       </c>
       <c r="B41" t="n">
         <v>79044</v>
@@ -4857,10 +4857,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445325</v>
+        <v>445349</v>
       </c>
       <c r="R41" t="n">
-        <v>6735153</v>
+        <v>6735178</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4903,6 +4903,11 @@
       <c r="AB41" t="inlineStr">
         <is>
           <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4929,7 +4934,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129239093</v>
+        <v>129238322</v>
       </c>
       <c r="B42" t="n">
         <v>79044</v>
@@ -4964,10 +4969,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445324</v>
+        <v>445325</v>
       </c>
       <c r="R42" t="n">
-        <v>6735285</v>
+        <v>6735153</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5036,7 +5041,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129238704</v>
+        <v>129238576</v>
       </c>
       <c r="B43" t="n">
         <v>79044</v>
@@ -5071,10 +5076,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445349</v>
+        <v>445336</v>
       </c>
       <c r="R43" t="n">
-        <v>6735178</v>
+        <v>6735162</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5117,11 +5122,6 @@
       <c r="AB43" t="inlineStr">
         <is>
           <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5362,7 +5362,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129237683</v>
+        <v>129238645</v>
       </c>
       <c r="B46" t="n">
         <v>79044</v>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>445282</v>
+        <v>445322</v>
       </c>
       <c r="R46" t="n">
-        <v>6735211</v>
+        <v>6735197</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5469,7 +5469,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129238645</v>
+        <v>129237683</v>
       </c>
       <c r="B47" t="n">
         <v>79044</v>
@@ -5504,10 +5504,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>445322</v>
+        <v>445282</v>
       </c>
       <c r="R47" t="n">
-        <v>6735197</v>
+        <v>6735211</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5683,10 +5683,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129237299</v>
+        <v>129237617</v>
       </c>
       <c r="B49" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5694,21 +5694,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5718,10 +5718,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445260</v>
+        <v>445279</v>
       </c>
       <c r="R49" t="n">
-        <v>6735095</v>
+        <v>6735197</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5790,10 +5790,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129237617</v>
+        <v>129237299</v>
       </c>
       <c r="B50" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5801,21 +5801,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5825,10 +5825,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>445279</v>
+        <v>445260</v>
       </c>
       <c r="R50" t="n">
-        <v>6735197</v>
+        <v>6735095</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6111,10 +6111,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129239857</v>
+        <v>129239740</v>
       </c>
       <c r="B53" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6122,39 +6122,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445369</v>
+        <v>445356</v>
       </c>
       <c r="R53" t="n">
-        <v>6735411</v>
+        <v>6735366</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6330,10 +6325,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129239740</v>
+        <v>129239857</v>
       </c>
       <c r="B55" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6341,34 +6336,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445356</v>
+        <v>445369</v>
       </c>
       <c r="R55" t="n">
-        <v>6735366</v>
+        <v>6735411</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6549,7 +6549,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129237544</v>
+        <v>129240724</v>
       </c>
       <c r="B57" t="n">
         <v>79044</v>
@@ -6584,10 +6584,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445264</v>
+        <v>445509</v>
       </c>
       <c r="R57" t="n">
-        <v>6735197</v>
+        <v>6735455</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6656,7 +6656,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129240724</v>
+        <v>129237544</v>
       </c>
       <c r="B58" t="n">
         <v>79044</v>
@@ -6691,10 +6691,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>445509</v>
+        <v>445264</v>
       </c>
       <c r="R58" t="n">
-        <v>6735455</v>
+        <v>6735197</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6870,7 +6870,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129240566</v>
+        <v>129240967</v>
       </c>
       <c r="B60" t="n">
         <v>79044</v>
@@ -6905,10 +6905,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445481</v>
+        <v>445414</v>
       </c>
       <c r="R60" t="n">
-        <v>6735582</v>
+        <v>6735285</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6977,7 +6977,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129239929</v>
+        <v>129240474</v>
       </c>
       <c r="B61" t="n">
         <v>79044</v>
@@ -7012,10 +7012,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>445421</v>
+        <v>445438</v>
       </c>
       <c r="R61" t="n">
-        <v>6735402</v>
+        <v>6735509</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7057,12 +7057,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7089,7 +7084,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129240474</v>
+        <v>129239929</v>
       </c>
       <c r="B62" t="n">
         <v>79044</v>
@@ -7124,10 +7119,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>445438</v>
+        <v>445421</v>
       </c>
       <c r="R62" t="n">
-        <v>6735509</v>
+        <v>6735402</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7159,7 +7154,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7169,7 +7164,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7196,7 +7196,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129240967</v>
+        <v>129240566</v>
       </c>
       <c r="B63" t="n">
         <v>79044</v>
@@ -7231,10 +7231,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>445414</v>
+        <v>445481</v>
       </c>
       <c r="R63" t="n">
-        <v>6735285</v>
+        <v>6735582</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7410,32 +7410,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129240494</v>
+        <v>129237820</v>
       </c>
       <c r="B65" t="n">
-        <v>8450</v>
+        <v>78801</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7445,10 +7445,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445440</v>
+        <v>445225</v>
       </c>
       <c r="R65" t="n">
-        <v>6735522</v>
+        <v>6735226</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7480,7 +7480,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7517,32 +7517,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129237820</v>
+        <v>129240494</v>
       </c>
       <c r="B66" t="n">
-        <v>78801</v>
+        <v>8450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7552,10 +7552,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445225</v>
+        <v>445440</v>
       </c>
       <c r="R66" t="n">
-        <v>6735226</v>
+        <v>6735522</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7587,7 +7587,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7624,10 +7624,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129238815</v>
+        <v>129238475</v>
       </c>
       <c r="B67" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7635,42 +7635,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445313</v>
+        <v>445322</v>
       </c>
       <c r="R67" t="n">
-        <v>6735262</v>
+        <v>6735128</v>
       </c>
       <c r="S67" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7843,10 +7838,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129238475</v>
+        <v>129238815</v>
       </c>
       <c r="B69" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7854,37 +7849,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>445322</v>
+        <v>445313</v>
       </c>
       <c r="R69" t="n">
-        <v>6735128</v>
+        <v>6735262</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8276,10 +8276,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129238788</v>
+        <v>129237274</v>
       </c>
       <c r="B73" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8287,21 +8287,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8311,10 +8311,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445316</v>
+        <v>445252</v>
       </c>
       <c r="R73" t="n">
-        <v>6735207</v>
+        <v>6735079</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8346,7 +8346,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8356,12 +8356,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Rikligt i närområdet</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8388,10 +8383,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129237274</v>
+        <v>129239479</v>
       </c>
       <c r="B74" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8399,21 +8394,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8423,10 +8418,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>445252</v>
+        <v>445379</v>
       </c>
       <c r="R74" t="n">
-        <v>6735079</v>
+        <v>6735294</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8458,7 +8453,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8468,7 +8463,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8495,7 +8490,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129239479</v>
+        <v>129238788</v>
       </c>
       <c r="B75" t="n">
         <v>79044</v>
@@ -8530,10 +8525,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>445379</v>
+        <v>445316</v>
       </c>
       <c r="R75" t="n">
-        <v>6735294</v>
+        <v>6735207</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8576,6 +8571,11 @@
       <c r="AB75" t="inlineStr">
         <is>
           <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Rikligt i närområdet</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9351,32 +9351,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129239850</v>
+        <v>129237639</v>
       </c>
       <c r="B83" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445369</v>
+        <v>445279</v>
       </c>
       <c r="R83" t="n">
-        <v>6735411</v>
+        <v>6735197</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9458,32 +9458,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129242957</v>
+        <v>129237533</v>
       </c>
       <c r="B84" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445292</v>
+        <v>445256</v>
       </c>
       <c r="R84" t="n">
-        <v>6734957</v>
+        <v>6735194</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9528,7 +9528,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9565,32 +9565,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129237650</v>
+        <v>129239850</v>
       </c>
       <c r="B85" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9600,10 +9600,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445279</v>
+        <v>445369</v>
       </c>
       <c r="R85" t="n">
-        <v>6735197</v>
+        <v>6735411</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9635,7 +9635,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9645,7 +9645,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9672,32 +9672,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129237533</v>
+        <v>129242957</v>
       </c>
       <c r="B86" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9707,10 +9707,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445256</v>
+        <v>445292</v>
       </c>
       <c r="R86" t="n">
-        <v>6735194</v>
+        <v>6734957</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9742,7 +9742,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9752,7 +9752,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10533,10 +10533,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129239693</v>
+        <v>129243051</v>
       </c>
       <c r="B94" t="n">
-        <v>79044</v>
+        <v>79139</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10544,34 +10544,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445362</v>
+        <v>445339</v>
       </c>
       <c r="R94" t="n">
-        <v>6735341</v>
+        <v>6734920</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10603,7 +10606,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10613,12 +10616,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>5 bilder, sumpskog</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10627,6 +10630,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10645,10 +10649,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129243051</v>
+        <v>129239693</v>
       </c>
       <c r="B95" t="n">
-        <v>79139</v>
+        <v>79044</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10656,37 +10660,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445339</v>
+        <v>445362</v>
       </c>
       <c r="R95" t="n">
-        <v>6734920</v>
+        <v>6735341</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10718,7 +10719,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10728,12 +10729,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>3 bilder</t>
+          <t>5 bilder, sumpskog</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10742,7 +10743,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -11331,10 +11331,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129237880</v>
+        <v>129238933</v>
       </c>
       <c r="B101" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11342,39 +11342,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445206</v>
+        <v>445307</v>
       </c>
       <c r="R101" t="n">
-        <v>6735207</v>
+        <v>6735277</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11406,7 +11401,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11416,12 +11411,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Bild, torraka med hack</t>
+          <t>Rikligt i en radie av ca 50 meter 3 bilder, sista på två tallstammar</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11448,10 +11443,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129238933</v>
+        <v>129237880</v>
       </c>
       <c r="B102" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11459,34 +11454,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445307</v>
+        <v>445206</v>
       </c>
       <c r="R102" t="n">
-        <v>6735277</v>
+        <v>6735207</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11528,12 +11528,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter 3 bilder, sista på två tallstammar</t>
+          <t>Bild, torraka med hack</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11560,10 +11560,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129243098</v>
+        <v>129248843</v>
       </c>
       <c r="B103" t="n">
-        <v>57724</v>
+        <v>91574</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11571,27 +11571,26 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -11600,10 +11599,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445374</v>
+        <v>445140</v>
       </c>
       <c r="R103" t="n">
-        <v>6734891</v>
+        <v>6734876</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11635,7 +11634,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11645,7 +11644,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
@@ -11677,7 +11676,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129238758</v>
+        <v>129243098</v>
       </c>
       <c r="B104" t="n">
         <v>57724</v>
@@ -11708,7 +11707,7 @@
       <c r="I104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -11717,10 +11716,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445349</v>
+        <v>445374</v>
       </c>
       <c r="R104" t="n">
-        <v>6735194</v>
+        <v>6734891</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11752,7 +11751,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11762,12 +11761,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>2 bilder på torraka med hack</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11794,10 +11793,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129248843</v>
+        <v>129238758</v>
       </c>
       <c r="B105" t="n">
-        <v>91574</v>
+        <v>57724</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11805,26 +11804,27 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -11833,10 +11833,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445140</v>
+        <v>445349</v>
       </c>
       <c r="R105" t="n">
-        <v>6734876</v>
+        <v>6735194</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11868,7 +11868,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11878,12 +11878,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>2 bilder på torraka med hack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12250,10 +12250,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129238770</v>
+        <v>129243188</v>
       </c>
       <c r="B109" t="n">
-        <v>57724</v>
+        <v>79139</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12261,39 +12261,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100049</v>
+        <v>967</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>445322</v>
+        <v>445401</v>
       </c>
       <c r="R109" t="n">
-        <v>6735197</v>
+        <v>6734884</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12325,7 +12320,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12335,12 +12330,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Bild på torraka, färska hack</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12367,10 +12362,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129243188</v>
+        <v>129238770</v>
       </c>
       <c r="B110" t="n">
-        <v>79139</v>
+        <v>57724</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12378,34 +12373,39 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>967</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>445401</v>
+        <v>445322</v>
       </c>
       <c r="R110" t="n">
-        <v>6734884</v>
+        <v>6735197</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12437,7 +12437,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12447,12 +12447,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>3 bilder</t>
+          <t>Bild på torraka, färska hack</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 43504-2025 artfynd.xlsx
+++ b/artfynd/A 43504-2025 artfynd.xlsx
@@ -4379,38 +4379,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129243809</v>
+        <v>129239467</v>
       </c>
       <c r="B37" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4419,10 +4419,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445358</v>
+        <v>445379</v>
       </c>
       <c r="R37" t="n">
-        <v>6735035</v>
+        <v>6735294</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4491,10 +4491,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129239467</v>
+        <v>129237782</v>
       </c>
       <c r="B38" t="n">
-        <v>8450</v>
+        <v>58097</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4502,27 +4502,27 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445379</v>
+        <v>445267</v>
       </c>
       <c r="R38" t="n">
-        <v>6735294</v>
+        <v>6735219</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4603,27 +4603,27 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129237782</v>
+        <v>129243809</v>
       </c>
       <c r="B39" t="n">
-        <v>58097</v>
+        <v>57724</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4634,7 +4634,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445267</v>
+        <v>445358</v>
       </c>
       <c r="R39" t="n">
-        <v>6735219</v>
+        <v>6735035</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4715,32 +4715,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129239093</v>
+        <v>129240788</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445324</v>
+        <v>445491</v>
       </c>
       <c r="R40" t="n">
-        <v>6735285</v>
+        <v>6735426</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4822,7 +4822,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129238704</v>
+        <v>129238576</v>
       </c>
       <c r="B41" t="n">
         <v>79044</v>
@@ -4857,10 +4857,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445349</v>
+        <v>445336</v>
       </c>
       <c r="R41" t="n">
-        <v>6735178</v>
+        <v>6735162</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4903,11 +4903,6 @@
       <c r="AB41" t="inlineStr">
         <is>
           <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5041,7 +5036,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129238576</v>
+        <v>129239093</v>
       </c>
       <c r="B43" t="n">
         <v>79044</v>
@@ -5076,10 +5071,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445336</v>
+        <v>445324</v>
       </c>
       <c r="R43" t="n">
-        <v>6735162</v>
+        <v>6735285</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5148,32 +5143,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129240788</v>
+        <v>129238704</v>
       </c>
       <c r="B44" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5183,10 +5178,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>445491</v>
+        <v>445349</v>
       </c>
       <c r="R44" t="n">
-        <v>6735426</v>
+        <v>6735178</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5218,7 +5213,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5228,7 +5223,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5362,7 +5362,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129238645</v>
+        <v>129237683</v>
       </c>
       <c r="B46" t="n">
         <v>79044</v>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>445322</v>
+        <v>445282</v>
       </c>
       <c r="R46" t="n">
-        <v>6735197</v>
+        <v>6735211</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5469,7 +5469,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129237683</v>
+        <v>129238645</v>
       </c>
       <c r="B47" t="n">
         <v>79044</v>
@@ -5504,10 +5504,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>445282</v>
+        <v>445322</v>
       </c>
       <c r="R47" t="n">
-        <v>6735211</v>
+        <v>6735197</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5576,10 +5576,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129237483</v>
+        <v>129243087</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5587,21 +5587,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445260</v>
+        <v>445378</v>
       </c>
       <c r="R48" t="n">
-        <v>6735185</v>
+        <v>6734906</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5683,10 +5683,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129237617</v>
+        <v>129237277</v>
       </c>
       <c r="B49" t="n">
-        <v>79663</v>
+        <v>79634</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5694,21 +5694,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5718,10 +5718,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445279</v>
+        <v>445252</v>
       </c>
       <c r="R49" t="n">
-        <v>6735197</v>
+        <v>6735079</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5790,7 +5790,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129237299</v>
+        <v>129237483</v>
       </c>
       <c r="B50" t="n">
         <v>79044</v>
@@ -5828,7 +5828,7 @@
         <v>445260</v>
       </c>
       <c r="R50" t="n">
-        <v>6735095</v>
+        <v>6735185</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5897,10 +5897,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129243087</v>
+        <v>129237299</v>
       </c>
       <c r="B51" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5908,21 +5908,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5932,10 +5932,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>445378</v>
+        <v>445260</v>
       </c>
       <c r="R51" t="n">
-        <v>6734906</v>
+        <v>6735095</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6004,10 +6004,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129237277</v>
+        <v>129237617</v>
       </c>
       <c r="B52" t="n">
-        <v>79634</v>
+        <v>79663</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6015,21 +6015,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445252</v>
+        <v>445279</v>
       </c>
       <c r="R52" t="n">
-        <v>6735079</v>
+        <v>6735197</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6111,7 +6111,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129239740</v>
+        <v>129243753</v>
       </c>
       <c r="B53" t="n">
         <v>79044</v>
@@ -6146,10 +6146,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445356</v>
+        <v>445384</v>
       </c>
       <c r="R53" t="n">
-        <v>6735366</v>
+        <v>6734985</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6218,7 +6218,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129243753</v>
+        <v>129239740</v>
       </c>
       <c r="B54" t="n">
         <v>79044</v>
@@ -6253,10 +6253,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>445384</v>
+        <v>445356</v>
       </c>
       <c r="R54" t="n">
-        <v>6734985</v>
+        <v>6735366</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6549,7 +6549,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129240724</v>
+        <v>129237544</v>
       </c>
       <c r="B57" t="n">
         <v>79044</v>
@@ -6584,10 +6584,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445509</v>
+        <v>445264</v>
       </c>
       <c r="R57" t="n">
-        <v>6735455</v>
+        <v>6735197</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6656,7 +6656,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129237544</v>
+        <v>129240724</v>
       </c>
       <c r="B58" t="n">
         <v>79044</v>
@@ -6691,10 +6691,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>445264</v>
+        <v>445509</v>
       </c>
       <c r="R58" t="n">
-        <v>6735197</v>
+        <v>6735455</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6870,7 +6870,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129240967</v>
+        <v>129240566</v>
       </c>
       <c r="B60" t="n">
         <v>79044</v>
@@ -6905,10 +6905,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445414</v>
+        <v>445481</v>
       </c>
       <c r="R60" t="n">
-        <v>6735285</v>
+        <v>6735582</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6977,7 +6977,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129240474</v>
+        <v>129239929</v>
       </c>
       <c r="B61" t="n">
         <v>79044</v>
@@ -7012,10 +7012,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>445438</v>
+        <v>445421</v>
       </c>
       <c r="R61" t="n">
-        <v>6735509</v>
+        <v>6735402</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7057,7 +7057,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7084,7 +7089,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129239929</v>
+        <v>129240474</v>
       </c>
       <c r="B62" t="n">
         <v>79044</v>
@@ -7119,10 +7124,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>445421</v>
+        <v>445438</v>
       </c>
       <c r="R62" t="n">
-        <v>6735402</v>
+        <v>6735509</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7154,7 +7159,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7164,12 +7169,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7196,7 +7196,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129240566</v>
+        <v>129240967</v>
       </c>
       <c r="B63" t="n">
         <v>79044</v>
@@ -7231,10 +7231,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>445481</v>
+        <v>445414</v>
       </c>
       <c r="R63" t="n">
-        <v>6735582</v>
+        <v>6735285</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7624,10 +7624,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129238475</v>
+        <v>129247898</v>
       </c>
       <c r="B67" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7635,21 +7635,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7659,10 +7659,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445322</v>
+        <v>445107</v>
       </c>
       <c r="R67" t="n">
-        <v>6735128</v>
+        <v>6735004</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7731,10 +7731,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129247898</v>
+        <v>129238475</v>
       </c>
       <c r="B68" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7742,21 +7742,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7766,10 +7766,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445107</v>
+        <v>445322</v>
       </c>
       <c r="R68" t="n">
-        <v>6735004</v>
+        <v>6735128</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8923,10 +8923,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129243245</v>
+        <v>129243192</v>
       </c>
       <c r="B79" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8934,21 +8934,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8958,10 +8958,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>445422</v>
+        <v>445401</v>
       </c>
       <c r="R79" t="n">
-        <v>6734878</v>
+        <v>6734884</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9030,10 +9030,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129243192</v>
+        <v>129243245</v>
       </c>
       <c r="B80" t="n">
-        <v>78802</v>
+        <v>78801</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9041,21 +9041,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9065,10 +9065,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445401</v>
+        <v>445422</v>
       </c>
       <c r="R80" t="n">
-        <v>6734884</v>
+        <v>6734878</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9244,32 +9244,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129238241</v>
+        <v>129239850</v>
       </c>
       <c r="B82" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9279,10 +9279,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445313</v>
+        <v>445369</v>
       </c>
       <c r="R82" t="n">
-        <v>6735165</v>
+        <v>6735411</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9351,32 +9351,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129237639</v>
+        <v>129242957</v>
       </c>
       <c r="B83" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445279</v>
+        <v>445292</v>
       </c>
       <c r="R83" t="n">
-        <v>6735197</v>
+        <v>6734957</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9458,7 +9458,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129237533</v>
+        <v>129237650</v>
       </c>
       <c r="B84" t="n">
         <v>79044</v>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445256</v>
+        <v>445279</v>
       </c>
       <c r="R84" t="n">
-        <v>6735194</v>
+        <v>6735197</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9565,32 +9565,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129239850</v>
+        <v>129238241</v>
       </c>
       <c r="B85" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9600,10 +9600,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445369</v>
+        <v>445313</v>
       </c>
       <c r="R85" t="n">
-        <v>6735411</v>
+        <v>6735165</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9672,32 +9672,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129242957</v>
+        <v>129237533</v>
       </c>
       <c r="B86" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9707,10 +9707,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445292</v>
+        <v>445256</v>
       </c>
       <c r="R86" t="n">
-        <v>6734957</v>
+        <v>6735194</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9742,7 +9742,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9752,7 +9752,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9886,10 +9886,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129243589</v>
+        <v>129247020</v>
       </c>
       <c r="B88" t="n">
-        <v>79044</v>
+        <v>78802</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9897,21 +9897,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9921,10 +9921,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>445385</v>
+        <v>445135</v>
       </c>
       <c r="R88" t="n">
-        <v>6734971</v>
+        <v>6734998</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9956,7 +9956,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9966,7 +9966,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9993,7 +9993,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129247020</v>
+        <v>129243217</v>
       </c>
       <c r="B89" t="n">
         <v>78802</v>
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>445135</v>
+        <v>445422</v>
       </c>
       <c r="R89" t="n">
-        <v>6734998</v>
+        <v>6734878</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10063,7 +10063,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10100,10 +10100,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129243217</v>
+        <v>129243589</v>
       </c>
       <c r="B90" t="n">
-        <v>78802</v>
+        <v>79044</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10111,21 +10111,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10135,10 +10135,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>445422</v>
+        <v>445385</v>
       </c>
       <c r="R90" t="n">
-        <v>6734878</v>
+        <v>6734971</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10319,32 +10319,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129240662</v>
+        <v>129239096</v>
       </c>
       <c r="B92" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10354,10 +10354,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>445517</v>
+        <v>445324</v>
       </c>
       <c r="R92" t="n">
-        <v>6735559</v>
+        <v>6735285</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10399,7 +10399,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10426,32 +10426,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129239096</v>
+        <v>129240662</v>
       </c>
       <c r="B93" t="n">
-        <v>8450</v>
+        <v>79663</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10461,10 +10461,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>445324</v>
+        <v>445517</v>
       </c>
       <c r="R93" t="n">
-        <v>6735285</v>
+        <v>6735559</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10496,7 +10496,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10533,10 +10533,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129243051</v>
+        <v>129239693</v>
       </c>
       <c r="B94" t="n">
-        <v>79139</v>
+        <v>79044</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10544,37 +10544,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445339</v>
+        <v>445362</v>
       </c>
       <c r="R94" t="n">
-        <v>6734920</v>
+        <v>6735341</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10606,7 +10603,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10616,12 +10613,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>3 bilder</t>
+          <t>5 bilder, sumpskog</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10630,7 +10627,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10649,10 +10645,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129239693</v>
+        <v>129243051</v>
       </c>
       <c r="B95" t="n">
-        <v>79044</v>
+        <v>79139</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10660,34 +10656,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445362</v>
+        <v>445339</v>
       </c>
       <c r="R95" t="n">
-        <v>6735341</v>
+        <v>6734920</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10719,7 +10718,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10729,12 +10728,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>5 bilder, sumpskog</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10743,6 +10742,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -11560,10 +11560,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129248843</v>
+        <v>129237273</v>
       </c>
       <c r="B103" t="n">
-        <v>91574</v>
+        <v>78802</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11571,38 +11571,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445140</v>
+        <v>445252</v>
       </c>
       <c r="R103" t="n">
-        <v>6734876</v>
+        <v>6735079</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11634,7 +11630,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11644,12 +11640,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild 4, högstubbe</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11676,10 +11672,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129243098</v>
+        <v>129237350</v>
       </c>
       <c r="B104" t="n">
-        <v>57724</v>
+        <v>78802</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11687,39 +11683,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445374</v>
+        <v>445248</v>
       </c>
       <c r="R104" t="n">
-        <v>6734891</v>
+        <v>6735139</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11751,7 +11742,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11761,12 +11752,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild 5, högstubbe</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11793,10 +11784,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129238758</v>
+        <v>129248843</v>
       </c>
       <c r="B105" t="n">
-        <v>57724</v>
+        <v>91574</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11804,27 +11795,26 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -11833,10 +11823,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445349</v>
+        <v>445140</v>
       </c>
       <c r="R105" t="n">
-        <v>6735194</v>
+        <v>6734876</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11868,7 +11858,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11878,12 +11868,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>2 bilder på torraka med hack</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11910,10 +11900,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129237273</v>
+        <v>129243098</v>
       </c>
       <c r="B106" t="n">
-        <v>78802</v>
+        <v>57724</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11921,34 +11911,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445252</v>
+        <v>445374</v>
       </c>
       <c r="R106" t="n">
-        <v>6735079</v>
+        <v>6734891</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11980,7 +11975,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11990,12 +11985,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Bild 4, högstubbe</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12022,10 +12017,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129237350</v>
+        <v>129238758</v>
       </c>
       <c r="B107" t="n">
-        <v>78802</v>
+        <v>57724</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12033,34 +12028,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445248</v>
+        <v>445349</v>
       </c>
       <c r="R107" t="n">
-        <v>6735139</v>
+        <v>6735194</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12092,7 +12092,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12102,12 +12102,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Bild 5, högstubbe</t>
+          <t>2 bilder på torraka med hack</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12250,10 +12250,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129243188</v>
+        <v>129238770</v>
       </c>
       <c r="B109" t="n">
-        <v>79139</v>
+        <v>57724</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12261,34 +12261,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>967</v>
+        <v>100049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>445401</v>
+        <v>445322</v>
       </c>
       <c r="R109" t="n">
-        <v>6734884</v>
+        <v>6735197</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12320,7 +12325,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12330,12 +12335,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>3 bilder</t>
+          <t>Bild på torraka, färska hack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12362,10 +12367,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129238770</v>
+        <v>129243188</v>
       </c>
       <c r="B110" t="n">
-        <v>57724</v>
+        <v>79139</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12373,39 +12378,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>967</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>445322</v>
+        <v>445401</v>
       </c>
       <c r="R110" t="n">
-        <v>6735197</v>
+        <v>6734884</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12437,7 +12437,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12447,12 +12447,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Bild på torraka, färska hack</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 43504-2025 artfynd.xlsx
+++ b/artfynd/A 43504-2025 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>129249084</v>
       </c>
       <c r="B8" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>129250233</v>
       </c>
       <c r="B9" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>129248937</v>
       </c>
       <c r="B10" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>129249372</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>129254011</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>129253379</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>129249212</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>129249287</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>129248989</v>
       </c>
       <c r="B16" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>129251241</v>
       </c>
       <c r="B18" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>129254098</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>129248688</v>
       </c>
       <c r="B20" t="n">
-        <v>79139</v>
+        <v>79165</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>129248920</v>
       </c>
       <c r="B21" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>129250170</v>
       </c>
       <c r="B22" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>129237525</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4379,38 +4379,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129239467</v>
+        <v>129243809</v>
       </c>
       <c r="B37" t="n">
-        <v>8450</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4419,10 +4419,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445379</v>
+        <v>445358</v>
       </c>
       <c r="R37" t="n">
-        <v>6735294</v>
+        <v>6735035</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4494,7 +4494,7 @@
         <v>129237782</v>
       </c>
       <c r="B38" t="n">
-        <v>58097</v>
+        <v>58100</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4603,38 +4603,38 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129243809</v>
+        <v>129239467</v>
       </c>
       <c r="B39" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445358</v>
+        <v>445379</v>
       </c>
       <c r="R39" t="n">
-        <v>6735035</v>
+        <v>6735294</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4715,32 +4715,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129240788</v>
+        <v>129238576</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>79070</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445491</v>
+        <v>445336</v>
       </c>
       <c r="R40" t="n">
-        <v>6735426</v>
+        <v>6735162</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4822,10 +4822,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129238576</v>
+        <v>129238322</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4857,10 +4857,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445336</v>
+        <v>445325</v>
       </c>
       <c r="R41" t="n">
-        <v>6735162</v>
+        <v>6735153</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4929,10 +4929,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129238322</v>
+        <v>129239093</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4964,10 +4964,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445325</v>
+        <v>445324</v>
       </c>
       <c r="R42" t="n">
-        <v>6735153</v>
+        <v>6735285</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5036,10 +5036,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129239093</v>
+        <v>129238704</v>
       </c>
       <c r="B43" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5071,10 +5071,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445324</v>
+        <v>445349</v>
       </c>
       <c r="R43" t="n">
-        <v>6735285</v>
+        <v>6735178</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5117,6 +5117,11 @@
       <c r="AB43" t="inlineStr">
         <is>
           <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i närområdet</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5143,32 +5148,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129238704</v>
+        <v>129240788</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5178,10 +5183,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>445349</v>
+        <v>445491</v>
       </c>
       <c r="R44" t="n">
-        <v>6735178</v>
+        <v>6735426</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5213,7 +5218,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5223,12 +5228,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i närområdet</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5258,7 +5258,7 @@
         <v>129237826</v>
       </c>
       <c r="B45" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5362,10 +5362,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129237683</v>
+        <v>129238645</v>
       </c>
       <c r="B46" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>445282</v>
+        <v>445322</v>
       </c>
       <c r="R46" t="n">
-        <v>6735211</v>
+        <v>6735197</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5469,10 +5469,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129238645</v>
+        <v>129237683</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5504,10 +5504,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>445322</v>
+        <v>445282</v>
       </c>
       <c r="R47" t="n">
-        <v>6735197</v>
+        <v>6735211</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5579,7 +5579,7 @@
         <v>129243087</v>
       </c>
       <c r="B48" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>129237277</v>
       </c>
       <c r="B49" t="n">
-        <v>79634</v>
+        <v>79660</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         <v>129237483</v>
       </c>
       <c r="B50" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>129237299</v>
       </c>
       <c r="B51" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         <v>129237617</v>
       </c>
       <c r="B52" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>129243753</v>
       </c>
       <c r="B53" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>129239740</v>
       </c>
       <c r="B54" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>129239857</v>
       </c>
       <c r="B55" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6437,50 +6437,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129242999</v>
+        <v>129240724</v>
       </c>
       <c r="B56" t="n">
-        <v>58097</v>
+        <v>79070</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>445292</v>
+        <v>445509</v>
       </c>
       <c r="R56" t="n">
-        <v>6734957</v>
+        <v>6735455</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6512,7 +6507,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6522,7 +6517,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6552,7 +6547,7 @@
         <v>129237544</v>
       </c>
       <c r="B57" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6656,45 +6651,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129240724</v>
+        <v>129242999</v>
       </c>
       <c r="B58" t="n">
-        <v>79044</v>
+        <v>58100</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>445509</v>
+        <v>445292</v>
       </c>
       <c r="R58" t="n">
-        <v>6735455</v>
+        <v>6734957</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6766,7 +6766,7 @@
         <v>129237764</v>
       </c>
       <c r="B59" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6870,10 +6870,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129240566</v>
+        <v>129243054</v>
       </c>
       <c r="B60" t="n">
-        <v>79044</v>
+        <v>78828</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6881,21 +6881,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6905,10 +6905,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445481</v>
+        <v>445339</v>
       </c>
       <c r="R60" t="n">
-        <v>6735582</v>
+        <v>6734920</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6940,7 +6940,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6977,10 +6977,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129239929</v>
+        <v>129240566</v>
       </c>
       <c r="B61" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7012,10 +7012,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>445421</v>
+        <v>445481</v>
       </c>
       <c r="R61" t="n">
-        <v>6735402</v>
+        <v>6735582</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7057,12 +7057,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7089,10 +7084,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129240474</v>
+        <v>129239929</v>
       </c>
       <c r="B62" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7124,10 +7119,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>445438</v>
+        <v>445421</v>
       </c>
       <c r="R62" t="n">
-        <v>6735509</v>
+        <v>6735402</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7159,7 +7154,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7169,7 +7164,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7196,10 +7196,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129240967</v>
+        <v>129240474</v>
       </c>
       <c r="B63" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7231,10 +7231,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>445414</v>
+        <v>445438</v>
       </c>
       <c r="R63" t="n">
-        <v>6735285</v>
+        <v>6735509</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7303,10 +7303,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129243054</v>
+        <v>129240967</v>
       </c>
       <c r="B64" t="n">
-        <v>78802</v>
+        <v>79070</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7314,21 +7314,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>445339</v>
+        <v>445414</v>
       </c>
       <c r="R64" t="n">
-        <v>6734920</v>
+        <v>6735285</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7413,7 +7413,7 @@
         <v>129237820</v>
       </c>
       <c r="B65" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>129247898</v>
       </c>
       <c r="B67" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>129238475</v>
       </c>
       <c r="B68" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         <v>129238815</v>
       </c>
       <c r="B69" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>129244530</v>
       </c>
       <c r="B70" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
         <v>129240193</v>
       </c>
       <c r="B72" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8276,10 +8276,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129237274</v>
+        <v>129238788</v>
       </c>
       <c r="B73" t="n">
-        <v>79663</v>
+        <v>79070</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8287,21 +8287,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8311,10 +8311,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445252</v>
+        <v>445316</v>
       </c>
       <c r="R73" t="n">
-        <v>6735079</v>
+        <v>6735207</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8346,7 +8346,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8356,7 +8356,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Rikligt i närområdet</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8383,10 +8388,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129239479</v>
+        <v>129237274</v>
       </c>
       <c r="B74" t="n">
-        <v>79044</v>
+        <v>79689</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8394,21 +8399,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8418,10 +8423,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>445379</v>
+        <v>445252</v>
       </c>
       <c r="R74" t="n">
-        <v>6735294</v>
+        <v>6735079</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8453,7 +8458,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8463,7 +8468,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8490,32 +8495,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129238788</v>
+        <v>129237286</v>
       </c>
       <c r="B75" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8525,10 +8530,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>445316</v>
+        <v>445252</v>
       </c>
       <c r="R75" t="n">
-        <v>6735207</v>
+        <v>6735079</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8560,7 +8565,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8570,12 +8575,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Rikligt i närområdet</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8602,32 +8602,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129237286</v>
+        <v>129244655</v>
       </c>
       <c r="B76" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8637,10 +8637,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>445252</v>
+        <v>445217</v>
       </c>
       <c r="R76" t="n">
-        <v>6735079</v>
+        <v>6734997</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8672,7 +8672,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8709,10 +8709,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129244655</v>
+        <v>129239479</v>
       </c>
       <c r="B77" t="n">
-        <v>79634</v>
+        <v>79070</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8720,21 +8720,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8744,10 +8744,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>445217</v>
+        <v>445379</v>
       </c>
       <c r="R77" t="n">
-        <v>6734997</v>
+        <v>6735294</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8779,7 +8779,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8816,32 +8816,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129243104</v>
+        <v>129243245</v>
       </c>
       <c r="B78" t="n">
-        <v>8450</v>
+        <v>78827</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>445374</v>
+        <v>445422</v>
       </c>
       <c r="R78" t="n">
-        <v>6734891</v>
+        <v>6734878</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8923,32 +8923,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129243192</v>
+        <v>129243104</v>
       </c>
       <c r="B79" t="n">
-        <v>78802</v>
+        <v>8450</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8958,10 +8958,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>445401</v>
+        <v>445374</v>
       </c>
       <c r="R79" t="n">
-        <v>6734884</v>
+        <v>6734891</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9030,10 +9030,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129243245</v>
+        <v>129243192</v>
       </c>
       <c r="B80" t="n">
-        <v>78801</v>
+        <v>78828</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9041,21 +9041,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9065,10 +9065,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445422</v>
+        <v>445401</v>
       </c>
       <c r="R80" t="n">
-        <v>6734878</v>
+        <v>6734884</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9140,7 +9140,7 @@
         <v>129237621</v>
       </c>
       <c r="B81" t="n">
-        <v>79634</v>
+        <v>79660</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9244,32 +9244,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129239850</v>
+        <v>129237829</v>
       </c>
       <c r="B82" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9279,10 +9279,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445369</v>
+        <v>445225</v>
       </c>
       <c r="R82" t="n">
-        <v>6735411</v>
+        <v>6735226</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9314,7 +9314,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9351,32 +9351,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129242957</v>
+        <v>129237650</v>
       </c>
       <c r="B83" t="n">
-        <v>8450</v>
+        <v>79070</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445292</v>
+        <v>445279</v>
       </c>
       <c r="R83" t="n">
-        <v>6734957</v>
+        <v>6735197</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9458,10 +9458,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129237650</v>
+        <v>129238241</v>
       </c>
       <c r="B84" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445279</v>
+        <v>445313</v>
       </c>
       <c r="R84" t="n">
-        <v>6735197</v>
+        <v>6735165</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9528,7 +9528,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9565,10 +9565,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129238241</v>
+        <v>129237533</v>
       </c>
       <c r="B85" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9600,10 +9600,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445313</v>
+        <v>445256</v>
       </c>
       <c r="R85" t="n">
-        <v>6735165</v>
+        <v>6735194</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9635,7 +9635,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9645,7 +9645,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9672,32 +9672,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129237533</v>
+        <v>129239850</v>
       </c>
       <c r="B86" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9707,10 +9707,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445256</v>
+        <v>445369</v>
       </c>
       <c r="R86" t="n">
-        <v>6735194</v>
+        <v>6735411</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9742,7 +9742,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9752,7 +9752,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9779,32 +9779,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129237829</v>
+        <v>129242957</v>
       </c>
       <c r="B87" t="n">
-        <v>79634</v>
+        <v>8450</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9814,10 +9814,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445225</v>
+        <v>445292</v>
       </c>
       <c r="R87" t="n">
-        <v>6735226</v>
+        <v>6734957</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9889,7 +9889,7 @@
         <v>129247020</v>
       </c>
       <c r="B88" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9993,10 +9993,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129243217</v>
+        <v>129243589</v>
       </c>
       <c r="B89" t="n">
-        <v>78802</v>
+        <v>79070</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10004,21 +10004,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>445422</v>
+        <v>445385</v>
       </c>
       <c r="R89" t="n">
-        <v>6734878</v>
+        <v>6734971</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10100,10 +10100,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129243589</v>
+        <v>129243217</v>
       </c>
       <c r="B90" t="n">
-        <v>79044</v>
+        <v>78828</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10111,21 +10111,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10135,10 +10135,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>445385</v>
+        <v>445422</v>
       </c>
       <c r="R90" t="n">
-        <v>6734971</v>
+        <v>6734878</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10210,7 +10210,7 @@
         <v>129248776</v>
       </c>
       <c r="B91" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10319,32 +10319,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129239096</v>
+        <v>129240662</v>
       </c>
       <c r="B92" t="n">
-        <v>8450</v>
+        <v>79689</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10354,10 +10354,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>445324</v>
+        <v>445517</v>
       </c>
       <c r="R92" t="n">
-        <v>6735285</v>
+        <v>6735559</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10399,7 +10399,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10426,32 +10426,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129240662</v>
+        <v>129239096</v>
       </c>
       <c r="B93" t="n">
-        <v>79663</v>
+        <v>8450</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10461,10 +10461,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>445517</v>
+        <v>445324</v>
       </c>
       <c r="R93" t="n">
-        <v>6735559</v>
+        <v>6735285</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10496,7 +10496,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10536,7 +10536,7 @@
         <v>129239693</v>
       </c>
       <c r="B94" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>129243051</v>
       </c>
       <c r="B95" t="n">
-        <v>79139</v>
+        <v>79165</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>129240510</v>
       </c>
       <c r="B96" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>129240492</v>
       </c>
       <c r="B97" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>129240471</v>
       </c>
       <c r="B98" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>129240554</v>
       </c>
       <c r="B99" t="n">
-        <v>79634</v>
+        <v>79660</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>129240621</v>
       </c>
       <c r="B100" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11331,10 +11331,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129238933</v>
+        <v>129237880</v>
       </c>
       <c r="B101" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11342,34 +11342,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445307</v>
+        <v>445206</v>
       </c>
       <c r="R101" t="n">
-        <v>6735277</v>
+        <v>6735207</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11401,7 +11406,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11411,12 +11416,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter 3 bilder, sista på två tallstammar</t>
+          <t>Bild, torraka med hack</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11443,10 +11448,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129237880</v>
+        <v>129238933</v>
       </c>
       <c r="B102" t="n">
-        <v>57724</v>
+        <v>79070</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11454,39 +11459,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445206</v>
+        <v>445307</v>
       </c>
       <c r="R102" t="n">
-        <v>6735207</v>
+        <v>6735277</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11528,12 +11528,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Bild, torraka med hack</t>
+          <t>Rikligt i en radie av ca 50 meter 3 bilder, sista på två tallstammar</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11560,10 +11560,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129237273</v>
+        <v>129248843</v>
       </c>
       <c r="B103" t="n">
-        <v>78802</v>
+        <v>91602</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11571,34 +11571,38 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445252</v>
+        <v>445140</v>
       </c>
       <c r="R103" t="n">
-        <v>6735079</v>
+        <v>6734876</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11630,7 +11634,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11640,12 +11644,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Bild 4, högstubbe</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11672,10 +11676,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129237350</v>
+        <v>129243098</v>
       </c>
       <c r="B104" t="n">
-        <v>78802</v>
+        <v>57727</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11683,34 +11687,39 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445248</v>
+        <v>445374</v>
       </c>
       <c r="R104" t="n">
-        <v>6735139</v>
+        <v>6734891</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11742,7 +11751,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11752,12 +11761,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Bild 5, högstubbe</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11784,10 +11793,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129248843</v>
+        <v>129238758</v>
       </c>
       <c r="B105" t="n">
-        <v>91574</v>
+        <v>57727</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11795,26 +11804,27 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -11823,10 +11833,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445140</v>
+        <v>445349</v>
       </c>
       <c r="R105" t="n">
-        <v>6734876</v>
+        <v>6735194</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11858,7 +11868,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11868,12 +11878,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>2 bilder på torraka med hack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11900,10 +11910,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129243098</v>
+        <v>129237273</v>
       </c>
       <c r="B106" t="n">
-        <v>57724</v>
+        <v>78828</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11911,39 +11921,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445374</v>
+        <v>445252</v>
       </c>
       <c r="R106" t="n">
-        <v>6734891</v>
+        <v>6735079</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11975,7 +11980,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11985,12 +11990,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild 4, högstubbe</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12017,10 +12022,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129238758</v>
+        <v>129237350</v>
       </c>
       <c r="B107" t="n">
-        <v>57724</v>
+        <v>78828</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12028,39 +12033,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445349</v>
+        <v>445248</v>
       </c>
       <c r="R107" t="n">
-        <v>6735194</v>
+        <v>6735139</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12092,7 +12092,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12102,12 +12102,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>2 bilder på torraka med hack</t>
+          <t>Bild 5, högstubbe</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12137,7 +12137,7 @@
         <v>129238052</v>
       </c>
       <c r="B108" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12250,10 +12250,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129238770</v>
+        <v>129243188</v>
       </c>
       <c r="B109" t="n">
-        <v>57724</v>
+        <v>79165</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12261,39 +12261,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100049</v>
+        <v>967</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>445322</v>
+        <v>445401</v>
       </c>
       <c r="R109" t="n">
-        <v>6735197</v>
+        <v>6734884</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12325,7 +12320,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12335,12 +12330,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Bild på torraka, färska hack</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12367,10 +12362,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129243188</v>
+        <v>129238770</v>
       </c>
       <c r="B110" t="n">
-        <v>79139</v>
+        <v>57727</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12378,34 +12373,39 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>967</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>445401</v>
+        <v>445322</v>
       </c>
       <c r="R110" t="n">
-        <v>6734884</v>
+        <v>6735197</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12437,7 +12437,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12447,12 +12447,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>3 bilder</t>
+          <t>Bild på torraka, färska hack</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12482,7 +12482,7 @@
         <v>129239898</v>
       </c>
       <c r="B111" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>129239384</v>
       </c>
       <c r="B112" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
         <v>129237668</v>
       </c>
       <c r="B113" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>129243085</v>
       </c>
       <c r="B114" t="n">
-        <v>79634</v>
+        <v>79660</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12940,7 +12940,7 @@
         <v>129240918</v>
       </c>
       <c r="B115" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         <v>129237612</v>
       </c>
       <c r="B116" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>129238380</v>
       </c>
       <c r="B117" t="n">
-        <v>79634</v>
+        <v>79660</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>

--- a/artfynd/A 43504-2025 artfynd.xlsx
+++ b/artfynd/A 43504-2025 artfynd.xlsx
@@ -4165,32 +4165,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129237525</v>
+        <v>129237324</v>
       </c>
       <c r="B35" t="n">
-        <v>79070</v>
+        <v>8450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445251</v>
+        <v>445263</v>
       </c>
       <c r="R35" t="n">
-        <v>6735185</v>
+        <v>6735122</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4272,32 +4272,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129237324</v>
+        <v>129237525</v>
       </c>
       <c r="B36" t="n">
-        <v>8450</v>
+        <v>79070</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4307,10 +4307,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445263</v>
+        <v>445251</v>
       </c>
       <c r="R36" t="n">
-        <v>6735122</v>
+        <v>6735185</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5576,10 +5576,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129243087</v>
+        <v>129237617</v>
       </c>
       <c r="B48" t="n">
-        <v>78828</v>
+        <v>79689</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5587,21 +5587,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445378</v>
+        <v>445279</v>
       </c>
       <c r="R48" t="n">
-        <v>6734906</v>
+        <v>6735197</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5683,10 +5683,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129237277</v>
+        <v>129243087</v>
       </c>
       <c r="B49" t="n">
-        <v>79660</v>
+        <v>78828</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5694,21 +5694,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5718,10 +5718,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445252</v>
+        <v>445378</v>
       </c>
       <c r="R49" t="n">
-        <v>6735079</v>
+        <v>6734906</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5753,7 +5753,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5790,10 +5790,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129237483</v>
+        <v>129237277</v>
       </c>
       <c r="B50" t="n">
-        <v>79070</v>
+        <v>79660</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5801,21 +5801,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5825,10 +5825,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>445260</v>
+        <v>445252</v>
       </c>
       <c r="R50" t="n">
-        <v>6735185</v>
+        <v>6735079</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5897,7 +5897,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129237299</v>
+        <v>129237483</v>
       </c>
       <c r="B51" t="n">
         <v>79070</v>
@@ -5935,7 +5935,7 @@
         <v>445260</v>
       </c>
       <c r="R51" t="n">
-        <v>6735095</v>
+        <v>6735185</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6004,10 +6004,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129237617</v>
+        <v>129237299</v>
       </c>
       <c r="B52" t="n">
-        <v>79689</v>
+        <v>79070</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6015,21 +6015,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445279</v>
+        <v>445260</v>
       </c>
       <c r="R52" t="n">
-        <v>6735197</v>
+        <v>6735095</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7624,10 +7624,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129247898</v>
+        <v>129238815</v>
       </c>
       <c r="B67" t="n">
-        <v>79689</v>
+        <v>57890</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7635,37 +7635,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445107</v>
+        <v>445313</v>
       </c>
       <c r="R67" t="n">
-        <v>6735004</v>
+        <v>6735262</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7694,7 +7699,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7704,7 +7709,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7731,10 +7736,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129238475</v>
+        <v>129247898</v>
       </c>
       <c r="B68" t="n">
-        <v>79070</v>
+        <v>79689</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7742,21 +7747,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7766,10 +7771,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445322</v>
+        <v>445107</v>
       </c>
       <c r="R68" t="n">
-        <v>6735128</v>
+        <v>6735004</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7801,7 +7806,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7811,7 +7816,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7838,10 +7843,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129238815</v>
+        <v>129238475</v>
       </c>
       <c r="B69" t="n">
-        <v>57890</v>
+        <v>79070</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7849,42 +7854,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>445313</v>
+        <v>445322</v>
       </c>
       <c r="R69" t="n">
-        <v>6735262</v>
+        <v>6735128</v>
       </c>
       <c r="S69" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7950,32 +7950,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129244530</v>
+        <v>129238778</v>
       </c>
       <c r="B70" t="n">
-        <v>79689</v>
+        <v>8450</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>445217</v>
+        <v>445322</v>
       </c>
       <c r="R70" t="n">
-        <v>6734997</v>
+        <v>6735197</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8020,7 +8020,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8030,7 +8030,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8057,32 +8057,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129238778</v>
+        <v>129244530</v>
       </c>
       <c r="B71" t="n">
-        <v>8450</v>
+        <v>79689</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8092,10 +8092,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445322</v>
+        <v>445217</v>
       </c>
       <c r="R71" t="n">
-        <v>6735197</v>
+        <v>6734997</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8495,32 +8495,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129237286</v>
+        <v>129239479</v>
       </c>
       <c r="B75" t="n">
-        <v>8450</v>
+        <v>79070</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8530,10 +8530,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>445252</v>
+        <v>445379</v>
       </c>
       <c r="R75" t="n">
-        <v>6735079</v>
+        <v>6735294</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8602,32 +8602,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129244655</v>
+        <v>129237286</v>
       </c>
       <c r="B76" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8637,10 +8637,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>445217</v>
+        <v>445252</v>
       </c>
       <c r="R76" t="n">
-        <v>6734997</v>
+        <v>6735079</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8672,7 +8672,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8709,10 +8709,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129239479</v>
+        <v>129244655</v>
       </c>
       <c r="B77" t="n">
-        <v>79070</v>
+        <v>79660</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8720,21 +8720,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8744,10 +8744,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>445379</v>
+        <v>445217</v>
       </c>
       <c r="R77" t="n">
-        <v>6735294</v>
+        <v>6734997</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8779,7 +8779,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9244,10 +9244,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129237829</v>
+        <v>129237650</v>
       </c>
       <c r="B82" t="n">
-        <v>79660</v>
+        <v>79070</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9255,21 +9255,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9279,10 +9279,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445225</v>
+        <v>445279</v>
       </c>
       <c r="R82" t="n">
-        <v>6735226</v>
+        <v>6735197</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9351,7 +9351,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129237650</v>
+        <v>129238241</v>
       </c>
       <c r="B83" t="n">
         <v>79070</v>
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445279</v>
+        <v>445313</v>
       </c>
       <c r="R83" t="n">
-        <v>6735197</v>
+        <v>6735165</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9458,7 +9458,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129238241</v>
+        <v>129237533</v>
       </c>
       <c r="B84" t="n">
         <v>79070</v>
@@ -9493,10 +9493,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445313</v>
+        <v>445256</v>
       </c>
       <c r="R84" t="n">
-        <v>6735165</v>
+        <v>6735194</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9528,7 +9528,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9565,32 +9565,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129237533</v>
+        <v>129239850</v>
       </c>
       <c r="B85" t="n">
-        <v>79070</v>
+        <v>8450</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9600,10 +9600,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445256</v>
+        <v>445369</v>
       </c>
       <c r="R85" t="n">
-        <v>6735194</v>
+        <v>6735411</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9635,7 +9635,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9645,7 +9645,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9672,7 +9672,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129239850</v>
+        <v>129242957</v>
       </c>
       <c r="B86" t="n">
         <v>8450</v>
@@ -9707,10 +9707,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445369</v>
+        <v>445292</v>
       </c>
       <c r="R86" t="n">
-        <v>6735411</v>
+        <v>6734957</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9742,7 +9742,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9752,7 +9752,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9779,32 +9779,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129242957</v>
+        <v>129237829</v>
       </c>
       <c r="B87" t="n">
-        <v>8450</v>
+        <v>79660</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9814,10 +9814,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445292</v>
+        <v>445225</v>
       </c>
       <c r="R87" t="n">
-        <v>6734957</v>
+        <v>6735226</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10207,50 +10207,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129248776</v>
+        <v>129239096</v>
       </c>
       <c r="B91" t="n">
-        <v>57727</v>
+        <v>8450</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>445137</v>
+        <v>445324</v>
       </c>
       <c r="R91" t="n">
-        <v>6734922</v>
+        <v>6735285</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10282,7 +10277,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10292,7 +10287,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10319,10 +10314,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129240662</v>
+        <v>129248776</v>
       </c>
       <c r="B92" t="n">
-        <v>79689</v>
+        <v>57727</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10330,34 +10325,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>445517</v>
+        <v>445137</v>
       </c>
       <c r="R92" t="n">
-        <v>6735559</v>
+        <v>6734922</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10399,7 +10399,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10426,32 +10426,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129239096</v>
+        <v>129240662</v>
       </c>
       <c r="B93" t="n">
-        <v>8450</v>
+        <v>79689</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10461,10 +10461,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>445324</v>
+        <v>445517</v>
       </c>
       <c r="R93" t="n">
-        <v>6735285</v>
+        <v>6735559</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10496,7 +10496,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10533,10 +10533,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129239693</v>
+        <v>129243051</v>
       </c>
       <c r="B94" t="n">
-        <v>79070</v>
+        <v>79165</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10544,34 +10544,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445362</v>
+        <v>445339</v>
       </c>
       <c r="R94" t="n">
-        <v>6735341</v>
+        <v>6734920</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10603,7 +10606,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10613,12 +10616,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>5 bilder, sumpskog</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10627,6 +10630,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10645,10 +10649,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129243051</v>
+        <v>129239693</v>
       </c>
       <c r="B95" t="n">
-        <v>79165</v>
+        <v>79070</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10656,37 +10660,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445339</v>
+        <v>445362</v>
       </c>
       <c r="R95" t="n">
-        <v>6734920</v>
+        <v>6735341</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10718,7 +10719,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10728,12 +10729,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>3 bilder</t>
+          <t>5 bilder, sumpskog</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10742,7 +10743,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -11560,10 +11560,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129248843</v>
+        <v>129237273</v>
       </c>
       <c r="B103" t="n">
-        <v>91602</v>
+        <v>78828</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11571,38 +11571,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445140</v>
+        <v>445252</v>
       </c>
       <c r="R103" t="n">
-        <v>6734876</v>
+        <v>6735079</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11634,7 +11630,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11644,12 +11640,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild 4, högstubbe</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11676,10 +11672,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129243098</v>
+        <v>129237350</v>
       </c>
       <c r="B104" t="n">
-        <v>57727</v>
+        <v>78828</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11687,39 +11683,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445374</v>
+        <v>445248</v>
       </c>
       <c r="R104" t="n">
-        <v>6734891</v>
+        <v>6735139</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11751,7 +11742,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11761,12 +11752,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild 5, högstubbe</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11793,10 +11784,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129238758</v>
+        <v>129248843</v>
       </c>
       <c r="B105" t="n">
-        <v>57727</v>
+        <v>91602</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11804,27 +11795,26 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -11833,10 +11823,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445349</v>
+        <v>445140</v>
       </c>
       <c r="R105" t="n">
-        <v>6735194</v>
+        <v>6734876</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11868,7 +11858,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11878,12 +11868,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>2 bilder på torraka med hack</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11910,10 +11900,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129237273</v>
+        <v>129243098</v>
       </c>
       <c r="B106" t="n">
-        <v>78828</v>
+        <v>57727</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11921,34 +11911,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445252</v>
+        <v>445374</v>
       </c>
       <c r="R106" t="n">
-        <v>6735079</v>
+        <v>6734891</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11980,7 +11975,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11990,12 +11985,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Bild 4, högstubbe</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12022,10 +12017,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129237350</v>
+        <v>129238758</v>
       </c>
       <c r="B107" t="n">
-        <v>78828</v>
+        <v>57727</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12033,34 +12028,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445248</v>
+        <v>445349</v>
       </c>
       <c r="R107" t="n">
-        <v>6735139</v>
+        <v>6735194</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12092,7 +12092,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12102,12 +12102,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Bild 5, högstubbe</t>
+          <t>2 bilder på torraka med hack</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12713,10 +12713,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129237668</v>
+        <v>129243085</v>
       </c>
       <c r="B113" t="n">
-        <v>79070</v>
+        <v>79660</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12724,21 +12724,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12748,10 +12748,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>445302</v>
+        <v>445378</v>
       </c>
       <c r="R113" t="n">
-        <v>6735183</v>
+        <v>6734906</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12783,7 +12783,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12793,12 +12793,12 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Bild på äldre tall, stam uppåt</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12825,10 +12825,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129243085</v>
+        <v>129237668</v>
       </c>
       <c r="B114" t="n">
-        <v>79660</v>
+        <v>79070</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12836,21 +12836,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12860,10 +12860,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>445378</v>
+        <v>445302</v>
       </c>
       <c r="R114" t="n">
-        <v>6734906</v>
+        <v>6735183</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12895,7 +12895,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild på äldre tall, stam uppåt</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12937,10 +12937,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129240918</v>
+        <v>129237612</v>
       </c>
       <c r="B115" t="n">
-        <v>57727</v>
+        <v>78828</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12948,39 +12948,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>445417</v>
+        <v>445279</v>
       </c>
       <c r="R115" t="n">
-        <v>6735368</v>
+        <v>6735197</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13012,7 +13007,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13022,12 +13017,12 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild på två stubbar med äldre tall i bakgrund</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13054,10 +13049,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129237612</v>
+        <v>129238380</v>
       </c>
       <c r="B116" t="n">
-        <v>78828</v>
+        <v>79660</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13065,21 +13060,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13089,10 +13084,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>445279</v>
+        <v>445322</v>
       </c>
       <c r="R116" t="n">
-        <v>6735197</v>
+        <v>6735151</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13124,7 +13119,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13134,12 +13129,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Bild på två stubbar med äldre tall i bakgrund</t>
+          <t>Bild på grov kolad stuppe/låga, tall</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13166,10 +13161,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129238380</v>
+        <v>129240918</v>
       </c>
       <c r="B117" t="n">
-        <v>79660</v>
+        <v>57727</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13177,34 +13172,39 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>445322</v>
+        <v>445417</v>
       </c>
       <c r="R117" t="n">
-        <v>6735151</v>
+        <v>6735368</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13236,7 +13236,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13246,12 +13246,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Bild på grov kolad stuppe/låga, tall</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD117" t="b">

--- a/artfynd/A 43504-2025 artfynd.xlsx
+++ b/artfynd/A 43504-2025 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>129249084</v>
       </c>
       <c r="B8" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>129250233</v>
       </c>
       <c r="B9" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>129248937</v>
       </c>
       <c r="B10" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>129249372</v>
       </c>
       <c r="B11" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>129254011</v>
       </c>
       <c r="B12" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>129253379</v>
       </c>
       <c r="B13" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>129249212</v>
       </c>
       <c r="B14" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>129249287</v>
       </c>
       <c r="B15" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>129248989</v>
       </c>
       <c r="B16" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>129251241</v>
       </c>
       <c r="B18" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>129254098</v>
       </c>
       <c r="B19" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>129248688</v>
       </c>
       <c r="B20" t="n">
-        <v>79165</v>
+        <v>79170</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>129248920</v>
       </c>
       <c r="B21" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>129250170</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4165,32 +4165,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129237324</v>
+        <v>129237525</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>79075</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445263</v>
+        <v>445251</v>
       </c>
       <c r="R35" t="n">
-        <v>6735122</v>
+        <v>6735185</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4272,32 +4272,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129237525</v>
+        <v>129237324</v>
       </c>
       <c r="B36" t="n">
-        <v>79070</v>
+        <v>8450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4307,10 +4307,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445251</v>
+        <v>445263</v>
       </c>
       <c r="R36" t="n">
-        <v>6735185</v>
+        <v>6735122</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4379,27 +4379,27 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129243809</v>
+        <v>129237782</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>58105</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4410,7 +4410,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4419,10 +4419,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445358</v>
+        <v>445267</v>
       </c>
       <c r="R37" t="n">
-        <v>6735035</v>
+        <v>6735219</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4491,27 +4491,27 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129237782</v>
+        <v>129243809</v>
       </c>
       <c r="B38" t="n">
-        <v>58100</v>
+        <v>57732</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4522,7 +4522,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445267</v>
+        <v>445358</v>
       </c>
       <c r="R38" t="n">
-        <v>6735219</v>
+        <v>6735035</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4718,7 +4718,7 @@
         <v>129238576</v>
       </c>
       <c r="B40" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>129238322</v>
       </c>
       <c r="B41" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>129239093</v>
       </c>
       <c r="B42" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>129238704</v>
       </c>
       <c r="B43" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>129237826</v>
       </c>
       <c r="B45" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5362,10 +5362,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129238645</v>
+        <v>129237683</v>
       </c>
       <c r="B46" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>445322</v>
+        <v>445282</v>
       </c>
       <c r="R46" t="n">
-        <v>6735197</v>
+        <v>6735211</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5469,10 +5469,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129237683</v>
+        <v>129238645</v>
       </c>
       <c r="B47" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5504,10 +5504,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>445282</v>
+        <v>445322</v>
       </c>
       <c r="R47" t="n">
-        <v>6735211</v>
+        <v>6735197</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5576,10 +5576,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129237617</v>
+        <v>129237483</v>
       </c>
       <c r="B48" t="n">
-        <v>79689</v>
+        <v>79075</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5587,21 +5587,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445279</v>
+        <v>445260</v>
       </c>
       <c r="R48" t="n">
-        <v>6735197</v>
+        <v>6735185</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5683,10 +5683,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129243087</v>
+        <v>129237299</v>
       </c>
       <c r="B49" t="n">
-        <v>78828</v>
+        <v>79075</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5694,21 +5694,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5718,10 +5718,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445378</v>
+        <v>445260</v>
       </c>
       <c r="R49" t="n">
-        <v>6734906</v>
+        <v>6735095</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5753,7 +5753,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5790,10 +5790,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129237277</v>
+        <v>129237617</v>
       </c>
       <c r="B50" t="n">
-        <v>79660</v>
+        <v>79694</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5801,21 +5801,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5825,10 +5825,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>445252</v>
+        <v>445279</v>
       </c>
       <c r="R50" t="n">
-        <v>6735079</v>
+        <v>6735197</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5897,10 +5897,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129237483</v>
+        <v>129237277</v>
       </c>
       <c r="B51" t="n">
-        <v>79070</v>
+        <v>79665</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5908,21 +5908,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5932,10 +5932,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>445260</v>
+        <v>445252</v>
       </c>
       <c r="R51" t="n">
-        <v>6735185</v>
+        <v>6735079</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6004,10 +6004,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129237299</v>
+        <v>129243087</v>
       </c>
       <c r="B52" t="n">
-        <v>79070</v>
+        <v>78833</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6015,21 +6015,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445260</v>
+        <v>445378</v>
       </c>
       <c r="R52" t="n">
-        <v>6735095</v>
+        <v>6734906</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6114,7 +6114,7 @@
         <v>129243753</v>
       </c>
       <c r="B53" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>129239740</v>
       </c>
       <c r="B54" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>129239857</v>
       </c>
       <c r="B55" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6437,10 +6437,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129240724</v>
+        <v>129237544</v>
       </c>
       <c r="B56" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6472,10 +6472,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>445509</v>
+        <v>445264</v>
       </c>
       <c r="R56" t="n">
-        <v>6735455</v>
+        <v>6735197</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6507,7 +6507,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6544,10 +6544,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129237544</v>
+        <v>129240724</v>
       </c>
       <c r="B57" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445264</v>
+        <v>445509</v>
       </c>
       <c r="R57" t="n">
-        <v>6735197</v>
+        <v>6735455</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6654,7 +6654,7 @@
         <v>129242999</v>
       </c>
       <c r="B58" t="n">
-        <v>58100</v>
+        <v>58105</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>129237764</v>
       </c>
       <c r="B59" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6870,10 +6870,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129243054</v>
+        <v>129240566</v>
       </c>
       <c r="B60" t="n">
-        <v>78828</v>
+        <v>79075</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6881,21 +6881,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6905,10 +6905,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445339</v>
+        <v>445481</v>
       </c>
       <c r="R60" t="n">
-        <v>6734920</v>
+        <v>6735582</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6940,7 +6940,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6977,10 +6977,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129240566</v>
+        <v>129239929</v>
       </c>
       <c r="B61" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7012,10 +7012,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>445481</v>
+        <v>445421</v>
       </c>
       <c r="R61" t="n">
-        <v>6735582</v>
+        <v>6735402</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7057,7 +7057,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7084,10 +7089,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129239929</v>
+        <v>129240474</v>
       </c>
       <c r="B62" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7119,10 +7124,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>445421</v>
+        <v>445438</v>
       </c>
       <c r="R62" t="n">
-        <v>6735402</v>
+        <v>6735509</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7154,7 +7159,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7164,12 +7169,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7196,10 +7196,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129240474</v>
+        <v>129240967</v>
       </c>
       <c r="B63" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7231,10 +7231,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>445438</v>
+        <v>445414</v>
       </c>
       <c r="R63" t="n">
-        <v>6735509</v>
+        <v>6735285</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7303,10 +7303,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129240967</v>
+        <v>129243054</v>
       </c>
       <c r="B64" t="n">
-        <v>79070</v>
+        <v>78833</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7314,21 +7314,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>445414</v>
+        <v>445339</v>
       </c>
       <c r="R64" t="n">
-        <v>6735285</v>
+        <v>6734920</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7413,7 +7413,7 @@
         <v>129237820</v>
       </c>
       <c r="B65" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7624,10 +7624,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129238815</v>
+        <v>129247898</v>
       </c>
       <c r="B67" t="n">
-        <v>57890</v>
+        <v>79694</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7635,42 +7635,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445313</v>
+        <v>445107</v>
       </c>
       <c r="R67" t="n">
-        <v>6735262</v>
+        <v>6735004</v>
       </c>
       <c r="S67" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7699,7 +7694,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7709,7 +7704,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7736,10 +7731,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129247898</v>
+        <v>129238475</v>
       </c>
       <c r="B68" t="n">
-        <v>79689</v>
+        <v>79075</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7747,21 +7742,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7771,10 +7766,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445107</v>
+        <v>445322</v>
       </c>
       <c r="R68" t="n">
-        <v>6735004</v>
+        <v>6735128</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7806,7 +7801,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7816,7 +7811,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7843,10 +7838,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129238475</v>
+        <v>129238815</v>
       </c>
       <c r="B69" t="n">
-        <v>79070</v>
+        <v>57895</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7854,37 +7849,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>445322</v>
+        <v>445313</v>
       </c>
       <c r="R69" t="n">
-        <v>6735128</v>
+        <v>6735262</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>129244530</v>
       </c>
       <c r="B71" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
         <v>129240193</v>
       </c>
       <c r="B72" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
         <v>129238788</v>
       </c>
       <c r="B73" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>129237274</v>
       </c>
       <c r="B74" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>129239479</v>
       </c>
       <c r="B75" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8602,32 +8602,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129237286</v>
+        <v>129244655</v>
       </c>
       <c r="B76" t="n">
-        <v>8450</v>
+        <v>79665</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8637,10 +8637,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>445252</v>
+        <v>445217</v>
       </c>
       <c r="R76" t="n">
-        <v>6735079</v>
+        <v>6734997</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8672,7 +8672,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8709,32 +8709,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129244655</v>
+        <v>129237286</v>
       </c>
       <c r="B77" t="n">
-        <v>79660</v>
+        <v>8450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8744,10 +8744,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>445217</v>
+        <v>445252</v>
       </c>
       <c r="R77" t="n">
-        <v>6734997</v>
+        <v>6735079</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8779,7 +8779,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8819,7 +8819,7 @@
         <v>129243245</v>
       </c>
       <c r="B78" t="n">
-        <v>78827</v>
+        <v>78832</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>129243192</v>
       </c>
       <c r="B80" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>129237621</v>
       </c>
       <c r="B81" t="n">
-        <v>79660</v>
+        <v>79665</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>129237650</v>
       </c>
       <c r="B82" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>129238241</v>
       </c>
       <c r="B83" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>129237533</v>
       </c>
       <c r="B84" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>129237829</v>
       </c>
       <c r="B87" t="n">
-        <v>79660</v>
+        <v>79665</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9886,10 +9886,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129247020</v>
+        <v>129243589</v>
       </c>
       <c r="B88" t="n">
-        <v>78828</v>
+        <v>79075</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9897,21 +9897,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9921,10 +9921,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>445135</v>
+        <v>445385</v>
       </c>
       <c r="R88" t="n">
-        <v>6734998</v>
+        <v>6734971</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9956,7 +9956,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9966,7 +9966,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9993,10 +9993,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129243589</v>
+        <v>129247020</v>
       </c>
       <c r="B89" t="n">
-        <v>79070</v>
+        <v>78833</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10004,21 +10004,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>445385</v>
+        <v>445135</v>
       </c>
       <c r="R89" t="n">
-        <v>6734971</v>
+        <v>6734998</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10063,7 +10063,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10103,7 +10103,7 @@
         <v>129243217</v>
       </c>
       <c r="B90" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10314,10 +10314,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129248776</v>
+        <v>129240662</v>
       </c>
       <c r="B92" t="n">
-        <v>57727</v>
+        <v>79694</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10325,39 +10325,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>445137</v>
+        <v>445517</v>
       </c>
       <c r="R92" t="n">
-        <v>6734922</v>
+        <v>6735559</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10389,7 +10384,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10399,7 +10394,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10426,10 +10421,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129240662</v>
+        <v>129248776</v>
       </c>
       <c r="B93" t="n">
-        <v>79689</v>
+        <v>57732</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10437,34 +10432,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>445517</v>
+        <v>445137</v>
       </c>
       <c r="R93" t="n">
-        <v>6735559</v>
+        <v>6734922</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10496,7 +10496,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10536,7 +10536,7 @@
         <v>129243051</v>
       </c>
       <c r="B94" t="n">
-        <v>79165</v>
+        <v>79170</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>129239693</v>
       </c>
       <c r="B95" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>129240510</v>
       </c>
       <c r="B96" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>129240492</v>
       </c>
       <c r="B97" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10995,10 +10995,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129240471</v>
+        <v>129240554</v>
       </c>
       <c r="B98" t="n">
-        <v>78828</v>
+        <v>79665</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11006,21 +11006,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11030,10 +11030,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>445438</v>
+        <v>445435</v>
       </c>
       <c r="R98" t="n">
-        <v>6735509</v>
+        <v>6735582</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11080,7 +11080,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>2 bilder, kolad stubbe samt på spiklav</t>
+          <t>1 bild på högstubbe med låga i bakgrund</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11107,10 +11107,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129240554</v>
+        <v>129240471</v>
       </c>
       <c r="B99" t="n">
-        <v>79660</v>
+        <v>78833</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11118,21 +11118,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11142,10 +11142,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>445435</v>
+        <v>445438</v>
       </c>
       <c r="R99" t="n">
-        <v>6735582</v>
+        <v>6735509</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11192,7 +11192,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>1 bild på högstubbe med låga i bakgrund</t>
+          <t>2 bilder, kolad stubbe samt på spiklav</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11222,7 +11222,7 @@
         <v>129240621</v>
       </c>
       <c r="B100" t="n">
-        <v>78828</v>
+        <v>78833</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11331,10 +11331,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129237880</v>
+        <v>129238933</v>
       </c>
       <c r="B101" t="n">
-        <v>57727</v>
+        <v>79075</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11342,39 +11342,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445206</v>
+        <v>445307</v>
       </c>
       <c r="R101" t="n">
-        <v>6735207</v>
+        <v>6735277</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11406,7 +11401,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11416,12 +11411,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Bild, torraka med hack</t>
+          <t>Rikligt i en radie av ca 50 meter 3 bilder, sista på två tallstammar</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11448,10 +11443,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129238933</v>
+        <v>129237880</v>
       </c>
       <c r="B102" t="n">
-        <v>79070</v>
+        <v>57732</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11459,34 +11454,39 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445307</v>
+        <v>445206</v>
       </c>
       <c r="R102" t="n">
-        <v>6735277</v>
+        <v>6735207</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11528,12 +11528,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter 3 bilder, sista på två tallstammar</t>
+          <t>Bild, torraka med hack</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11560,10 +11560,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129237273</v>
+        <v>129238758</v>
       </c>
       <c r="B103" t="n">
-        <v>78828</v>
+        <v>57732</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11571,34 +11571,39 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445252</v>
+        <v>445349</v>
       </c>
       <c r="R103" t="n">
-        <v>6735079</v>
+        <v>6735194</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11630,7 +11635,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11640,12 +11645,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Bild 4, högstubbe</t>
+          <t>2 bilder på torraka med hack</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11672,10 +11677,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129237350</v>
+        <v>129248843</v>
       </c>
       <c r="B104" t="n">
-        <v>78828</v>
+        <v>91608</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11683,34 +11688,38 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445248</v>
+        <v>445140</v>
       </c>
       <c r="R104" t="n">
-        <v>6735139</v>
+        <v>6734876</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11742,7 +11751,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11752,12 +11761,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Bild 5, högstubbe</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11784,10 +11793,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129248843</v>
+        <v>129243098</v>
       </c>
       <c r="B105" t="n">
-        <v>91602</v>
+        <v>57732</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11795,26 +11804,27 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -11823,10 +11833,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445140</v>
+        <v>445374</v>
       </c>
       <c r="R105" t="n">
-        <v>6734876</v>
+        <v>6734891</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11858,7 +11868,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11868,7 +11878,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
@@ -11900,10 +11910,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129243098</v>
+        <v>129237273</v>
       </c>
       <c r="B106" t="n">
-        <v>57727</v>
+        <v>78833</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11911,39 +11921,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445374</v>
+        <v>445252</v>
       </c>
       <c r="R106" t="n">
-        <v>6734891</v>
+        <v>6735079</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11975,7 +11980,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11985,12 +11990,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild 4, högstubbe</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12017,10 +12022,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129238758</v>
+        <v>129237350</v>
       </c>
       <c r="B107" t="n">
-        <v>57727</v>
+        <v>78833</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12028,39 +12033,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445349</v>
+        <v>445248</v>
       </c>
       <c r="R107" t="n">
-        <v>6735194</v>
+        <v>6735139</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12092,7 +12092,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12102,12 +12102,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>2 bilder på torraka med hack</t>
+          <t>Bild 5, högstubbe</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12137,7 +12137,7 @@
         <v>129238052</v>
       </c>
       <c r="B108" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>129243188</v>
       </c>
       <c r="B109" t="n">
-        <v>79165</v>
+        <v>79170</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>129238770</v>
       </c>
       <c r="B110" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12482,7 +12482,7 @@
         <v>129239898</v>
       </c>
       <c r="B111" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>129239384</v>
       </c>
       <c r="B112" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12713,10 +12713,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129243085</v>
+        <v>129237668</v>
       </c>
       <c r="B113" t="n">
-        <v>79660</v>
+        <v>79075</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12724,21 +12724,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12748,10 +12748,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>445378</v>
+        <v>445302</v>
       </c>
       <c r="R113" t="n">
-        <v>6734906</v>
+        <v>6735183</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12783,7 +12783,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12793,12 +12793,12 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild på äldre tall, stam uppåt</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12825,10 +12825,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129237668</v>
+        <v>129243085</v>
       </c>
       <c r="B114" t="n">
-        <v>79070</v>
+        <v>79665</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12836,21 +12836,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12860,10 +12860,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>445302</v>
+        <v>445378</v>
       </c>
       <c r="R114" t="n">
-        <v>6735183</v>
+        <v>6734906</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12895,7 +12895,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Bild på äldre tall, stam uppåt</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12937,10 +12937,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129237612</v>
+        <v>129240918</v>
       </c>
       <c r="B115" t="n">
-        <v>78828</v>
+        <v>57732</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12948,34 +12948,39 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>445279</v>
+        <v>445417</v>
       </c>
       <c r="R115" t="n">
-        <v>6735197</v>
+        <v>6735368</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13007,7 +13012,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13017,12 +13022,12 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Bild på två stubbar med äldre tall i bakgrund</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13052,7 +13057,7 @@
         <v>129238380</v>
       </c>
       <c r="B116" t="n">
-        <v>79660</v>
+        <v>79665</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13161,10 +13166,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129240918</v>
+        <v>129237612</v>
       </c>
       <c r="B117" t="n">
-        <v>57727</v>
+        <v>78833</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13172,39 +13177,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>445417</v>
+        <v>445279</v>
       </c>
       <c r="R117" t="n">
-        <v>6735368</v>
+        <v>6735197</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13236,7 +13236,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13246,12 +13246,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild på två stubbar med äldre tall i bakgrund</t>
         </is>
       </c>
       <c r="AD117" t="b">

--- a/artfynd/A 43504-2025 artfynd.xlsx
+++ b/artfynd/A 43504-2025 artfynd.xlsx
@@ -2151,7 +2151,7 @@
         <v>129248989</v>
       </c>
       <c r="B16" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>129251241</v>
       </c>
       <c r="B18" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>129254098</v>
       </c>
       <c r="B19" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>129248688</v>
       </c>
       <c r="B20" t="n">
-        <v>79170</v>
+        <v>79171</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>129248920</v>
       </c>
       <c r="B21" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>129250170</v>
       </c>
       <c r="B22" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>129243051</v>
       </c>
       <c r="B94" t="n">
-        <v>79170</v>
+        <v>79171</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>129239693</v>
       </c>
       <c r="B95" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>129240510</v>
       </c>
       <c r="B96" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10878,10 +10878,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129240492</v>
+        <v>129240554</v>
       </c>
       <c r="B97" t="n">
-        <v>57732</v>
+        <v>79666</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10889,39 +10889,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>445440</v>
+        <v>445435</v>
       </c>
       <c r="R97" t="n">
-        <v>6735522</v>
+        <v>6735582</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10968,7 +10963,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>1 bild på högstubbe med låga i bakgrund</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10995,10 +10990,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129240554</v>
+        <v>129240471</v>
       </c>
       <c r="B98" t="n">
-        <v>79665</v>
+        <v>78834</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11006,21 +11001,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11030,10 +11025,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>445435</v>
+        <v>445438</v>
       </c>
       <c r="R98" t="n">
-        <v>6735582</v>
+        <v>6735509</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11080,7 +11075,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>1 bild på högstubbe med låga i bakgrund</t>
+          <t>2 bilder, kolad stubbe samt på spiklav</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11107,10 +11102,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129240471</v>
+        <v>129240492</v>
       </c>
       <c r="B99" t="n">
-        <v>78833</v>
+        <v>57733</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11118,34 +11113,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>445438</v>
+        <v>445440</v>
       </c>
       <c r="R99" t="n">
-        <v>6735509</v>
+        <v>6735522</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11192,7 +11192,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>2 bilder, kolad stubbe samt på spiklav</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11222,7 +11222,7 @@
         <v>129240621</v>
       </c>
       <c r="B100" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11331,10 +11331,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129238933</v>
+        <v>129237880</v>
       </c>
       <c r="B101" t="n">
-        <v>79075</v>
+        <v>57733</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11342,34 +11342,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445307</v>
+        <v>445206</v>
       </c>
       <c r="R101" t="n">
-        <v>6735277</v>
+        <v>6735207</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11401,7 +11406,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11411,12 +11416,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter 3 bilder, sista på två tallstammar</t>
+          <t>Bild, torraka med hack</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11443,10 +11448,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129237880</v>
+        <v>129238933</v>
       </c>
       <c r="B102" t="n">
-        <v>57732</v>
+        <v>79076</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11454,39 +11459,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445206</v>
+        <v>445307</v>
       </c>
       <c r="R102" t="n">
-        <v>6735207</v>
+        <v>6735277</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11528,12 +11528,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Bild, torraka med hack</t>
+          <t>Rikligt i en radie av ca 50 meter 3 bilder, sista på två tallstammar</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11560,10 +11560,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129238758</v>
+        <v>129237273</v>
       </c>
       <c r="B103" t="n">
-        <v>57732</v>
+        <v>78834</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11571,39 +11571,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445349</v>
+        <v>445252</v>
       </c>
       <c r="R103" t="n">
-        <v>6735194</v>
+        <v>6735079</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11635,7 +11630,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11645,12 +11640,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>2 bilder på torraka med hack</t>
+          <t>Bild 4, högstubbe</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11677,10 +11672,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129248843</v>
+        <v>129237350</v>
       </c>
       <c r="B104" t="n">
-        <v>91608</v>
+        <v>78834</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11688,38 +11683,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445140</v>
+        <v>445248</v>
       </c>
       <c r="R104" t="n">
-        <v>6734876</v>
+        <v>6735139</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11751,7 +11742,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11761,12 +11752,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild 5, högstubbe</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11793,10 +11784,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129243098</v>
+        <v>129248843</v>
       </c>
       <c r="B105" t="n">
-        <v>57732</v>
+        <v>91609</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11804,27 +11795,26 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -11833,10 +11823,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445374</v>
+        <v>445140</v>
       </c>
       <c r="R105" t="n">
-        <v>6734891</v>
+        <v>6734876</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11868,7 +11858,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11878,7 +11868,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
@@ -11910,10 +11900,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129237273</v>
+        <v>129243098</v>
       </c>
       <c r="B106" t="n">
-        <v>78833</v>
+        <v>57733</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11921,34 +11911,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445252</v>
+        <v>445374</v>
       </c>
       <c r="R106" t="n">
-        <v>6735079</v>
+        <v>6734891</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11980,7 +11975,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11990,12 +11985,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Bild 4, högstubbe</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12022,10 +12017,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129237350</v>
+        <v>129238758</v>
       </c>
       <c r="B107" t="n">
-        <v>78833</v>
+        <v>57733</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12033,34 +12028,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445248</v>
+        <v>445349</v>
       </c>
       <c r="R107" t="n">
-        <v>6735139</v>
+        <v>6735194</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12092,7 +12092,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12102,12 +12102,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Bild 5, högstubbe</t>
+          <t>2 bilder på torraka med hack</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12137,7 +12137,7 @@
         <v>129238052</v>
       </c>
       <c r="B108" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>129243188</v>
       </c>
       <c r="B109" t="n">
-        <v>79170</v>
+        <v>79171</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>129238770</v>
       </c>
       <c r="B110" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12482,7 +12482,7 @@
         <v>129239898</v>
       </c>
       <c r="B111" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>129239384</v>
       </c>
       <c r="B112" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
         <v>129237668</v>
       </c>
       <c r="B113" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>129243085</v>
       </c>
       <c r="B114" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12937,10 +12937,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129240918</v>
+        <v>129238380</v>
       </c>
       <c r="B115" t="n">
-        <v>57732</v>
+        <v>79666</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12948,39 +12948,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>445417</v>
+        <v>445322</v>
       </c>
       <c r="R115" t="n">
-        <v>6735368</v>
+        <v>6735151</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13012,7 +13007,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13022,12 +13017,12 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild på grov kolad stuppe/låga, tall</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13054,10 +13049,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129238380</v>
+        <v>129237612</v>
       </c>
       <c r="B116" t="n">
-        <v>79665</v>
+        <v>78834</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13065,21 +13060,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13089,10 +13084,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>445322</v>
+        <v>445279</v>
       </c>
       <c r="R116" t="n">
-        <v>6735151</v>
+        <v>6735197</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13124,7 +13119,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13134,12 +13129,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Bild på grov kolad stuppe/låga, tall</t>
+          <t>Bild på två stubbar med äldre tall i bakgrund</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13166,10 +13161,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129237612</v>
+        <v>129240918</v>
       </c>
       <c r="B117" t="n">
-        <v>78833</v>
+        <v>57733</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13177,34 +13172,39 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>445279</v>
+        <v>445417</v>
       </c>
       <c r="R117" t="n">
-        <v>6735197</v>
+        <v>6735368</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13236,7 +13236,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13246,12 +13246,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Bild på två stubbar med äldre tall i bakgrund</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD117" t="b">

--- a/artfynd/A 43504-2025 artfynd.xlsx
+++ b/artfynd/A 43504-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY117"/>
+  <dimension ref="A1:AY126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121395839</v>
+        <v>121395811</v>
       </c>
       <c r="B2" t="n">
-        <v>78000</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444833</v>
+        <v>444979</v>
       </c>
       <c r="R2" t="n">
-        <v>6735281</v>
+        <v>6735134</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,50 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121395727</v>
+        <v>129249212</v>
       </c>
       <c r="B3" t="n">
-        <v>78715</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>V Finngruvan, Dlr</t>
+          <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445072</v>
+        <v>444962</v>
       </c>
       <c r="R3" t="n">
-        <v>6734932</v>
+        <v>6735315</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +837,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,62 +867,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121395811</v>
+        <v>129249287</v>
       </c>
       <c r="B4" t="n">
-        <v>78261</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>V Finngruvan, Dlr</t>
+          <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444979</v>
+        <v>444980</v>
       </c>
       <c r="R4" t="n">
-        <v>6735134</v>
+        <v>6735302</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,12 +944,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,62 +974,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121395704</v>
+        <v>129249372</v>
       </c>
       <c r="B5" t="n">
-        <v>79234</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>V Finngruvan, Dlr</t>
+          <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444835</v>
+        <v>444977</v>
       </c>
       <c r="R5" t="n">
-        <v>6735278</v>
+        <v>6735277</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,12 +1051,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,62 +1081,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121395835</v>
+        <v>129253379</v>
       </c>
       <c r="B6" t="n">
-        <v>77548</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>V Finngruvan, Dlr</t>
+          <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445072</v>
+        <v>444917</v>
       </c>
       <c r="R6" t="n">
-        <v>6734932</v>
+        <v>6735361</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,12 +1158,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,62 +1188,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121395717</v>
+        <v>129254011</v>
       </c>
       <c r="B7" t="n">
-        <v>79205</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>V Finngruvan, Dlr</t>
+          <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444891</v>
+        <v>444965</v>
       </c>
       <c r="R7" t="n">
-        <v>6735211</v>
+        <v>6735354</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,12 +1265,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,44 +1295,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129249084</v>
+        <v>129254098</v>
       </c>
       <c r="B8" t="n">
-        <v>79694</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1322,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445098</v>
+        <v>444984</v>
       </c>
       <c r="R8" t="n">
-        <v>6735011</v>
+        <v>6735330</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,6 +1388,11 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1 bild, gran med stenar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129250233</v>
+        <v>121395839</v>
       </c>
       <c r="B9" t="n">
-        <v>78833</v>
+        <v>78730</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,34 +1430,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kringlogmyrkölen, Dlr</t>
+          <t>V Finngruvan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444881</v>
+        <v>444833</v>
       </c>
       <c r="R9" t="n">
-        <v>6735300</v>
+        <v>6735281</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,22 +1484,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:54</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:54</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1489,22 +1504,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129248937</v>
+        <v>121395704</v>
       </c>
       <c r="B10" t="n">
-        <v>57732</v>
+        <v>79946</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1512,39 +1527,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kringlogmyrkölen, Dlr</t>
+          <t>V Finngruvan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445066</v>
+        <v>444835</v>
       </c>
       <c r="R10" t="n">
-        <v>6734914</v>
+        <v>6735278</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1571,22 +1581,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:54</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:54</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1601,22 +1601,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129249372</v>
+        <v>121395834</v>
       </c>
       <c r="B11" t="n">
-        <v>79075</v>
+        <v>78334</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1624,34 +1624,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kringlogmyrkölen, Dlr</t>
+          <t>V Finngruvan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444977</v>
+        <v>444993</v>
       </c>
       <c r="R11" t="n">
-        <v>6735277</v>
+        <v>6735102</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1678,22 +1678,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:54</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:54</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1708,57 +1698,62 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129254011</v>
+        <v>129250170</v>
       </c>
       <c r="B12" t="n">
-        <v>79075</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444965</v>
+        <v>444948</v>
       </c>
       <c r="R12" t="n">
-        <v>6735354</v>
+        <v>6735278</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,6 +1796,11 @@
       <c r="AB12" t="inlineStr">
         <is>
           <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>1 bild och 1 miljöbild</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,32 +1827,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129253379</v>
+        <v>129253634</v>
       </c>
       <c r="B13" t="n">
-        <v>79075</v>
+        <v>8455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1908,6 +1908,11 @@
       <c r="AB13" t="inlineStr">
         <is>
           <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2 Miljöbilder</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1934,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129249212</v>
+        <v>129250233</v>
       </c>
       <c r="B14" t="n">
-        <v>79075</v>
+        <v>79085</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1945,21 +1950,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1969,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444962</v>
+        <v>444881</v>
       </c>
       <c r="R14" t="n">
-        <v>6735315</v>
+        <v>6735300</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2041,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129249287</v>
+        <v>129251241</v>
       </c>
       <c r="B15" t="n">
-        <v>79075</v>
+        <v>79085</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,21 +2057,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2076,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444980</v>
+        <v>444800</v>
       </c>
       <c r="R15" t="n">
-        <v>6735302</v>
+        <v>6735299</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2122,6 +2127,11 @@
       <c r="AB15" t="inlineStr">
         <is>
           <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>1 bild kolad stubbe med hål</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2148,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129248989</v>
+        <v>121395717</v>
       </c>
       <c r="B16" t="n">
-        <v>78834</v>
+        <v>79917</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2159,34 +2169,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kringlogmyrkölen, Dlr</t>
+          <t>V Finngruvan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445037</v>
+        <v>444891</v>
       </c>
       <c r="R16" t="n">
-        <v>6734946</v>
+        <v>6735211</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2213,27 +2223,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:54</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>1 bild, tall i bakgrund</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2248,57 +2243,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129253634</v>
+        <v>121395813</v>
       </c>
       <c r="B17" t="n">
-        <v>8450</v>
+        <v>78993</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kringlogmyrkölen, Dlr</t>
+          <t>V Finngruvan, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444917</v>
+        <v>445102</v>
       </c>
       <c r="R17" t="n">
-        <v>6735361</v>
+        <v>6734936</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2325,27 +2320,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:54</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>2 Miljöbilder</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2360,22 +2340,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129251241</v>
+        <v>121395725</v>
       </c>
       <c r="B18" t="n">
-        <v>78834</v>
+        <v>79422</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2383,34 +2363,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>967</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kringlogmyrkölen, Dlr</t>
+          <t>V Finngruvan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444800</v>
+        <v>445338</v>
       </c>
       <c r="R18" t="n">
-        <v>6735299</v>
+        <v>6734924</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2437,27 +2417,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:54</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>1 bild kolad stubbe med hål</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2472,22 +2437,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129254098</v>
+        <v>121395727</v>
       </c>
       <c r="B19" t="n">
-        <v>79076</v>
+        <v>79422</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2495,34 +2460,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kringlogmyrkölen, Dlr</t>
+          <t>V Finngruvan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444984</v>
+        <v>445072</v>
       </c>
       <c r="R19" t="n">
-        <v>6735330</v>
+        <v>6734932</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2549,27 +2514,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>15:54</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>15:54</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>1 bild, gran med stenar</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2584,22 +2534,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129248688</v>
+        <v>129243051</v>
       </c>
       <c r="B20" t="n">
-        <v>79171</v>
+        <v>79422</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2624,21 +2574,20 @@
           <t>(L.) Hue</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445078</v>
+        <v>445339</v>
       </c>
       <c r="R20" t="n">
-        <v>6734933</v>
+        <v>6734920</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2670,7 +2619,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2680,7 +2629,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2694,6 +2643,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2712,10 +2662,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129248920</v>
+        <v>129243188</v>
       </c>
       <c r="B21" t="n">
-        <v>79695</v>
+        <v>79422</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,21 +2673,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>967</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2747,10 +2697,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>445066</v>
+        <v>445401</v>
       </c>
       <c r="R21" t="n">
-        <v>6734914</v>
+        <v>6734884</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2782,7 +2732,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2792,12 +2742,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2824,10 +2774,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129250170</v>
+        <v>129248688</v>
       </c>
       <c r="B22" t="n">
-        <v>57733</v>
+        <v>79422</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2835,27 +2785,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>967</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2864,10 +2813,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444948</v>
+        <v>445078</v>
       </c>
       <c r="R22" t="n">
-        <v>6735278</v>
+        <v>6734933</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2914,7 +2863,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>1 bild och 1 miljöbild</t>
+          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2941,37 +2890,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121395755</v>
+        <v>121395765</v>
       </c>
       <c r="B23" t="n">
-        <v>8436</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>1049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2981,10 +2925,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445181</v>
+        <v>445396</v>
       </c>
       <c r="R23" t="n">
-        <v>6735098</v>
+        <v>6735226</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3043,15 +2987,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121395684</v>
+        <v>129248843</v>
       </c>
       <c r="B24" t="n">
-        <v>74722</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3059,34 +2998,38 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>V Finngruvan, Dlr</t>
+          <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445389</v>
+        <v>445140</v>
       </c>
       <c r="R24" t="n">
-        <v>6735366</v>
+        <v>6734876</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3113,12 +3056,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3133,49 +3091,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121395797</v>
+        <v>121395694</v>
       </c>
       <c r="B25" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3185,10 +3138,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445402</v>
+        <v>445273</v>
       </c>
       <c r="R25" t="n">
-        <v>6735245</v>
+        <v>6735201</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3247,37 +3200,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121395718</v>
+        <v>121395796</v>
       </c>
       <c r="B26" t="n">
-        <v>79205</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3287,10 +3235,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445198</v>
+        <v>445111</v>
       </c>
       <c r="R26" t="n">
-        <v>6734721</v>
+        <v>6735066</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3349,37 +3297,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121395832</v>
+        <v>121395797</v>
       </c>
       <c r="B27" t="n">
-        <v>77548</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3389,10 +3332,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445235</v>
+        <v>445402</v>
       </c>
       <c r="R27" t="n">
-        <v>6734869</v>
+        <v>6735245</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3451,19 +3394,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121395796</v>
+        <v>129237299</v>
       </c>
       <c r="B28" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3487,14 +3425,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>V Finngruvan, Dlr</t>
+          <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445111</v>
+        <v>445260</v>
       </c>
       <c r="R28" t="n">
-        <v>6735066</v>
+        <v>6735095</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3521,12 +3459,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3541,62 +3489,57 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121395813</v>
+        <v>129237477</v>
       </c>
       <c r="B29" t="n">
-        <v>78261</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>V Finngruvan, Dlr</t>
+          <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445102</v>
+        <v>445260</v>
       </c>
       <c r="R29" t="n">
-        <v>6734936</v>
+        <v>6735185</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3623,12 +3566,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3643,62 +3596,57 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121395705</v>
+        <v>129237525</v>
       </c>
       <c r="B30" t="n">
-        <v>79234</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>V Finngruvan, Dlr</t>
+          <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445198</v>
+        <v>445251</v>
       </c>
       <c r="R30" t="n">
-        <v>6734721</v>
+        <v>6735185</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3725,12 +3673,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3745,62 +3703,57 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121395838</v>
+        <v>129237533</v>
       </c>
       <c r="B31" t="n">
-        <v>78000</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>V Finngruvan, Dlr</t>
+          <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>445229</v>
+        <v>445256</v>
       </c>
       <c r="R31" t="n">
-        <v>6734862</v>
+        <v>6735194</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3827,12 +3780,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3847,62 +3810,57 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121395765</v>
+        <v>129237544</v>
       </c>
       <c r="B32" t="n">
-        <v>80573</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>V Finngruvan, Dlr</t>
+          <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>445396</v>
+        <v>445264</v>
       </c>
       <c r="R32" t="n">
-        <v>6735226</v>
+        <v>6735197</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3929,12 +3887,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3949,62 +3917,57 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121395725</v>
+        <v>129237639</v>
       </c>
       <c r="B33" t="n">
-        <v>78715</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>V Finngruvan, Dlr</t>
+          <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445338</v>
+        <v>445279</v>
       </c>
       <c r="R33" t="n">
-        <v>6734924</v>
+        <v>6735197</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4031,12 +3994,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4051,62 +4024,57 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121395694</v>
+        <v>129237668</v>
       </c>
       <c r="B34" t="n">
-        <v>90693</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>V Finngruvan, Dlr</t>
+          <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>445273</v>
+        <v>445302</v>
       </c>
       <c r="R34" t="n">
-        <v>6735201</v>
+        <v>6735183</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4133,12 +4101,27 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Bild på äldre tall, stam uppåt</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4153,26 +4136,26 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129237525</v>
+        <v>129237683</v>
       </c>
       <c r="B35" t="n">
-        <v>79075</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4200,10 +4183,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445251</v>
+        <v>445282</v>
       </c>
       <c r="R35" t="n">
-        <v>6735185</v>
+        <v>6735211</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4272,32 +4255,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129237324</v>
+        <v>129237747</v>
       </c>
       <c r="B36" t="n">
-        <v>8450</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4307,10 +4290,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445263</v>
+        <v>445275</v>
       </c>
       <c r="R36" t="n">
-        <v>6735122</v>
+        <v>6735223</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4353,6 +4336,11 @@
       <c r="AB36" t="inlineStr">
         <is>
           <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Bild på två tallstammar</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4379,50 +4367,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129237782</v>
+        <v>129238241</v>
       </c>
       <c r="B37" t="n">
-        <v>58105</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445267</v>
+        <v>445313</v>
       </c>
       <c r="R37" t="n">
-        <v>6735219</v>
+        <v>6735165</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4454,7 +4437,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4464,7 +4447,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4491,50 +4474,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129243809</v>
+        <v>129238272</v>
       </c>
       <c r="B38" t="n">
-        <v>57732</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445358</v>
+        <v>445325</v>
       </c>
       <c r="R38" t="n">
-        <v>6735035</v>
+        <v>6735153</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4566,7 +4544,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4576,7 +4554,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4603,50 +4581,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129239467</v>
+        <v>129238475</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445379</v>
+        <v>445322</v>
       </c>
       <c r="R39" t="n">
-        <v>6735294</v>
+        <v>6735128</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4715,14 +4688,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129238576</v>
+        <v>129238503</v>
       </c>
       <c r="B40" t="n">
-        <v>79075</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4750,10 +4723,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445336</v>
+        <v>445358</v>
       </c>
       <c r="R40" t="n">
-        <v>6735162</v>
+        <v>6735135</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4822,14 +4795,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129238322</v>
+        <v>129238576</v>
       </c>
       <c r="B41" t="n">
-        <v>79075</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4857,10 +4830,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445325</v>
+        <v>445336</v>
       </c>
       <c r="R41" t="n">
-        <v>6735153</v>
+        <v>6735162</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4929,14 +4902,14 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129239093</v>
+        <v>129238645</v>
       </c>
       <c r="B42" t="n">
-        <v>79075</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -4964,10 +4937,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445324</v>
+        <v>445322</v>
       </c>
       <c r="R42" t="n">
-        <v>6735285</v>
+        <v>6735197</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5039,11 +5012,11 @@
         <v>129238704</v>
       </c>
       <c r="B43" t="n">
-        <v>79075</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -5148,32 +5121,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129240788</v>
+        <v>129238788</v>
       </c>
       <c r="B44" t="n">
-        <v>8450</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5183,10 +5156,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>445491</v>
+        <v>445316</v>
       </c>
       <c r="R44" t="n">
-        <v>6735426</v>
+        <v>6735207</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5218,7 +5191,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5228,7 +5201,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Rikligt i närområdet</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5255,32 +5233,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129237826</v>
+        <v>129238933</v>
       </c>
       <c r="B45" t="n">
-        <v>79694</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5290,10 +5268,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>445225</v>
+        <v>445307</v>
       </c>
       <c r="R45" t="n">
-        <v>6735226</v>
+        <v>6735277</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5325,7 +5303,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5335,7 +5313,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter 3 bilder, sista på två tallstammar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5362,14 +5345,14 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129237683</v>
+        <v>129239093</v>
       </c>
       <c r="B46" t="n">
-        <v>79075</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -5397,10 +5380,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>445282</v>
+        <v>445324</v>
       </c>
       <c r="R46" t="n">
-        <v>6735211</v>
+        <v>6735285</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5432,7 +5415,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5442,7 +5425,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5469,14 +5452,14 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129238645</v>
+        <v>129239479</v>
       </c>
       <c r="B47" t="n">
-        <v>79075</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -5504,10 +5487,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>445322</v>
+        <v>445379</v>
       </c>
       <c r="R47" t="n">
-        <v>6735197</v>
+        <v>6735294</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5576,14 +5559,14 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129237483</v>
+        <v>129239693</v>
       </c>
       <c r="B48" t="n">
-        <v>79075</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5611,10 +5594,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445260</v>
+        <v>445362</v>
       </c>
       <c r="R48" t="n">
-        <v>6735185</v>
+        <v>6735341</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5646,7 +5629,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5656,7 +5639,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>5 bilder, sumpskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5683,14 +5671,14 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129237299</v>
+        <v>129239740</v>
       </c>
       <c r="B49" t="n">
-        <v>79075</v>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -5718,10 +5706,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445260</v>
+        <v>445356</v>
       </c>
       <c r="R49" t="n">
-        <v>6735095</v>
+        <v>6735366</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5753,7 +5741,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5763,7 +5751,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5790,32 +5778,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129237617</v>
+        <v>129239929</v>
       </c>
       <c r="B50" t="n">
-        <v>79694</v>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5825,10 +5813,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>445279</v>
+        <v>445421</v>
       </c>
       <c r="R50" t="n">
-        <v>6735197</v>
+        <v>6735402</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5860,7 +5848,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5870,7 +5858,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5897,32 +5890,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129237277</v>
+        <v>129240474</v>
       </c>
       <c r="B51" t="n">
-        <v>79665</v>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5932,10 +5925,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>445252</v>
+        <v>445438</v>
       </c>
       <c r="R51" t="n">
-        <v>6735079</v>
+        <v>6735509</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5967,7 +5960,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5977,7 +5970,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6004,32 +5997,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129243087</v>
+        <v>129240724</v>
       </c>
       <c r="B52" t="n">
-        <v>78833</v>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6039,10 +6032,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445378</v>
+        <v>445509</v>
       </c>
       <c r="R52" t="n">
-        <v>6734906</v>
+        <v>6735455</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6074,7 +6067,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6084,7 +6077,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6111,14 +6104,14 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129243753</v>
+        <v>129240967</v>
       </c>
       <c r="B53" t="n">
-        <v>79075</v>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -6146,10 +6139,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445384</v>
+        <v>445414</v>
       </c>
       <c r="R53" t="n">
-        <v>6734985</v>
+        <v>6735285</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6181,7 +6174,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6191,7 +6184,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6218,14 +6211,14 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129239740</v>
+        <v>129241052</v>
       </c>
       <c r="B54" t="n">
-        <v>79075</v>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -6253,10 +6246,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>445356</v>
+        <v>445405</v>
       </c>
       <c r="R54" t="n">
-        <v>6735366</v>
+        <v>6735187</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6288,7 +6281,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6298,7 +6291,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>1 bild på gran med garnlav</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6325,50 +6323,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129239857</v>
+        <v>129243562</v>
       </c>
       <c r="B55" t="n">
-        <v>57732</v>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445369</v>
+        <v>445397</v>
       </c>
       <c r="R55" t="n">
-        <v>6735411</v>
+        <v>6734968</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6400,7 +6393,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6410,7 +6403,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6437,14 +6430,14 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129237544</v>
+        <v>129243589</v>
       </c>
       <c r="B56" t="n">
-        <v>79075</v>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -6472,10 +6465,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>445264</v>
+        <v>445385</v>
       </c>
       <c r="R56" t="n">
-        <v>6735197</v>
+        <v>6734971</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6507,7 +6500,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6517,7 +6510,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6544,14 +6537,14 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129240724</v>
+        <v>129243753</v>
       </c>
       <c r="B57" t="n">
-        <v>79075</v>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -6579,10 +6572,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445509</v>
+        <v>445384</v>
       </c>
       <c r="R57" t="n">
-        <v>6735455</v>
+        <v>6734985</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6614,7 +6607,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6624,7 +6617,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6651,50 +6644,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129242999</v>
+        <v>129243781</v>
       </c>
       <c r="B58" t="n">
-        <v>58105</v>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>445292</v>
+        <v>445390</v>
       </c>
       <c r="R58" t="n">
-        <v>6734957</v>
+        <v>6734995</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6737,6 +6725,11 @@
       <c r="AB58" t="inlineStr">
         <is>
           <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>1 bild, garn på tallstam</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6763,10 +6756,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129237764</v>
+        <v>121395838</v>
       </c>
       <c r="B59" t="n">
-        <v>79075</v>
+        <v>78730</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6774,34 +6767,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kringlogmyrkölen, Dlr</t>
+          <t>V Finngruvan, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>445275</v>
+        <v>445229</v>
       </c>
       <c r="R59" t="n">
-        <v>6735223</v>
+        <v>6734862</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6828,22 +6821,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>09:32</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>09:32</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6858,22 +6841,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129240566</v>
+        <v>121395684</v>
       </c>
       <c r="B60" t="n">
-        <v>79075</v>
+        <v>83307</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6881,34 +6864,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kringlogmyrkölen, Dlr</t>
+          <t>V Finngruvan, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445481</v>
+        <v>445389</v>
       </c>
       <c r="R60" t="n">
-        <v>6735582</v>
+        <v>6735366</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6935,22 +6918,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>12:54</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>12:54</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6965,22 +6938,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129239929</v>
+        <v>129237820</v>
       </c>
       <c r="B61" t="n">
-        <v>79075</v>
+        <v>79084</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6988,21 +6961,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7012,10 +6985,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>445421</v>
+        <v>445225</v>
       </c>
       <c r="R61" t="n">
-        <v>6735402</v>
+        <v>6735226</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7047,7 +7020,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7057,12 +7030,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av ca 50 meter</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7089,10 +7057,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129240474</v>
+        <v>129243245</v>
       </c>
       <c r="B62" t="n">
-        <v>79075</v>
+        <v>79084</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7100,21 +7068,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7124,10 +7092,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>445438</v>
+        <v>445422</v>
       </c>
       <c r="R62" t="n">
-        <v>6735509</v>
+        <v>6734878</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7159,7 +7127,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7169,7 +7137,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7196,10 +7164,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129240967</v>
+        <v>121395705</v>
       </c>
       <c r="B63" t="n">
-        <v>79075</v>
+        <v>79946</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7207,34 +7175,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kringlogmyrkölen, Dlr</t>
+          <t>V Finngruvan, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>445414</v>
+        <v>445198</v>
       </c>
       <c r="R63" t="n">
-        <v>6735285</v>
+        <v>6734721</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7261,22 +7229,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>12:54</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>12:54</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7291,22 +7249,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129243054</v>
+        <v>129237274</v>
       </c>
       <c r="B64" t="n">
-        <v>78833</v>
+        <v>79946</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7314,21 +7272,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7338,10 +7296,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>445339</v>
+        <v>445252</v>
       </c>
       <c r="R64" t="n">
-        <v>6734920</v>
+        <v>6735079</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7373,7 +7331,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7383,7 +7341,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7410,10 +7368,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129237820</v>
+        <v>129237617</v>
       </c>
       <c r="B65" t="n">
-        <v>78832</v>
+        <v>79946</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7421,21 +7379,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7445,10 +7403,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445225</v>
+        <v>445279</v>
       </c>
       <c r="R65" t="n">
-        <v>6735226</v>
+        <v>6735197</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7517,32 +7475,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129240494</v>
+        <v>129237826</v>
       </c>
       <c r="B66" t="n">
-        <v>8450</v>
+        <v>79946</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7552,10 +7510,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445440</v>
+        <v>445225</v>
       </c>
       <c r="R66" t="n">
-        <v>6735522</v>
+        <v>6735226</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7587,7 +7545,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7597,7 +7555,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7624,10 +7582,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129247898</v>
+        <v>129244530</v>
       </c>
       <c r="B67" t="n">
-        <v>79694</v>
+        <v>79946</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7659,10 +7617,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445107</v>
+        <v>445217</v>
       </c>
       <c r="R67" t="n">
-        <v>6735004</v>
+        <v>6734997</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7731,10 +7689,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129238475</v>
+        <v>129247898</v>
       </c>
       <c r="B68" t="n">
-        <v>79075</v>
+        <v>79946</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7742,21 +7700,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7766,10 +7724,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445322</v>
+        <v>445107</v>
       </c>
       <c r="R68" t="n">
-        <v>6735128</v>
+        <v>6735004</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7801,7 +7759,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7811,7 +7769,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7838,10 +7796,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129238815</v>
+        <v>129248920</v>
       </c>
       <c r="B69" t="n">
-        <v>57895</v>
+        <v>79946</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7849,42 +7807,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>445313</v>
+        <v>445066</v>
       </c>
       <c r="R69" t="n">
-        <v>6735262</v>
+        <v>6734914</v>
       </c>
       <c r="S69" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7913,7 +7866,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7923,7 +7876,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7950,32 +7908,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129238778</v>
+        <v>129249084</v>
       </c>
       <c r="B70" t="n">
-        <v>8450</v>
+        <v>79946</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7985,10 +7943,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>445322</v>
+        <v>445098</v>
       </c>
       <c r="R70" t="n">
-        <v>6735197</v>
+        <v>6735011</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8020,7 +7978,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8030,7 +7988,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8057,10 +8015,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129244530</v>
+        <v>121395832</v>
       </c>
       <c r="B71" t="n">
-        <v>79694</v>
+        <v>78334</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8068,34 +8026,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Kringlogmyrkölen, Dlr</t>
+          <t>V Finngruvan, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445217</v>
+        <v>445235</v>
       </c>
       <c r="R71" t="n">
-        <v>6734997</v>
+        <v>6734869</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8122,22 +8080,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>15:54</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>15:54</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8152,22 +8100,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129240193</v>
+        <v>121395835</v>
       </c>
       <c r="B72" t="n">
-        <v>57732</v>
+        <v>78334</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8175,39 +8123,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>6487</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kringlogmyrkölen, Dlr</t>
+          <t>V Finngruvan, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>445445</v>
+        <v>445072</v>
       </c>
       <c r="R72" t="n">
-        <v>6735438</v>
+        <v>6734932</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8234,22 +8177,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>12:54</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>12:54</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8264,54 +8197,59 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129238788</v>
+        <v>129237880</v>
       </c>
       <c r="B73" t="n">
-        <v>79075</v>
+        <v>57950</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445316</v>
+        <v>445206</v>
       </c>
       <c r="R73" t="n">
         <v>6735207</v>
@@ -8346,7 +8284,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8356,12 +8294,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Rikligt i närområdet</t>
+          <t>Bild, torraka med hack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8388,45 +8326,50 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129237274</v>
+        <v>129238758</v>
       </c>
       <c r="B74" t="n">
-        <v>79694</v>
+        <v>57950</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>445252</v>
+        <v>445349</v>
       </c>
       <c r="R74" t="n">
-        <v>6735079</v>
+        <v>6735194</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8458,7 +8401,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8468,7 +8411,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>2 bilder på torraka med hack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8495,45 +8443,50 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129239479</v>
+        <v>129238770</v>
       </c>
       <c r="B75" t="n">
-        <v>79075</v>
+        <v>57950</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>445379</v>
+        <v>445322</v>
       </c>
       <c r="R75" t="n">
-        <v>6735294</v>
+        <v>6735197</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8576,6 +8529,11 @@
       <c r="AB75" t="inlineStr">
         <is>
           <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Bild på torraka, färska hack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8602,45 +8560,50 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129244655</v>
+        <v>129239384</v>
       </c>
       <c r="B76" t="n">
-        <v>79665</v>
+        <v>57950</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>445217</v>
+        <v>445379</v>
       </c>
       <c r="R76" t="n">
-        <v>6734997</v>
+        <v>6735294</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8672,7 +8635,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8682,7 +8645,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>2 bilder</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8709,10 +8677,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129237286</v>
+        <v>129239857</v>
       </c>
       <c r="B77" t="n">
-        <v>8450</v>
+        <v>57950</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8720,34 +8688,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>445252</v>
+        <v>445369</v>
       </c>
       <c r="R77" t="n">
-        <v>6735079</v>
+        <v>6735411</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8779,7 +8752,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8789,7 +8762,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8816,45 +8789,50 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129243245</v>
+        <v>129239898</v>
       </c>
       <c r="B78" t="n">
-        <v>78832</v>
+        <v>57950</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>445422</v>
+        <v>445362</v>
       </c>
       <c r="R78" t="n">
-        <v>6734878</v>
+        <v>6735431</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8886,7 +8864,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8896,7 +8874,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>2 bilder, låga, torraka</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8923,10 +8906,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129243104</v>
+        <v>129240193</v>
       </c>
       <c r="B79" t="n">
-        <v>8450</v>
+        <v>57950</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8934,34 +8917,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>445374</v>
+        <v>445445</v>
       </c>
       <c r="R79" t="n">
-        <v>6734891</v>
+        <v>6735438</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8993,7 +8981,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9003,7 +8991,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9030,45 +9018,50 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129243192</v>
+        <v>129240918</v>
       </c>
       <c r="B80" t="n">
-        <v>78833</v>
+        <v>57950</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445401</v>
+        <v>445417</v>
       </c>
       <c r="R80" t="n">
-        <v>6734884</v>
+        <v>6735368</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9100,7 +9093,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9110,7 +9103,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9137,45 +9135,50 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129237621</v>
+        <v>129243098</v>
       </c>
       <c r="B81" t="n">
-        <v>79665</v>
+        <v>57950</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>445279</v>
+        <v>445374</v>
       </c>
       <c r="R81" t="n">
-        <v>6735197</v>
+        <v>6734891</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9207,7 +9210,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9217,7 +9220,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9244,45 +9252,50 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129237650</v>
+        <v>129243524</v>
       </c>
       <c r="B82" t="n">
-        <v>79075</v>
+        <v>57950</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445279</v>
+        <v>445421</v>
       </c>
       <c r="R82" t="n">
-        <v>6735197</v>
+        <v>6734963</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9314,7 +9327,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9324,7 +9337,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9351,45 +9369,50 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129238241</v>
+        <v>129243809</v>
       </c>
       <c r="B83" t="n">
-        <v>79075</v>
+        <v>57950</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445313</v>
+        <v>445358</v>
       </c>
       <c r="R83" t="n">
-        <v>6735165</v>
+        <v>6735035</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9421,7 +9444,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9431,7 +9454,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9458,45 +9481,50 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129237533</v>
+        <v>129248776</v>
       </c>
       <c r="B84" t="n">
-        <v>79075</v>
+        <v>57950</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445256</v>
+        <v>445137</v>
       </c>
       <c r="R84" t="n">
-        <v>6735194</v>
+        <v>6734922</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9528,7 +9556,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9538,7 +9566,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9565,10 +9593,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129239850</v>
+        <v>129248887</v>
       </c>
       <c r="B85" t="n">
-        <v>8450</v>
+        <v>57950</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9576,34 +9604,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445369</v>
+        <v>445081</v>
       </c>
       <c r="R85" t="n">
-        <v>6735411</v>
+        <v>6734878</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9635,7 +9668,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9645,7 +9678,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9672,10 +9710,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129242957</v>
+        <v>129248937</v>
       </c>
       <c r="B86" t="n">
-        <v>8450</v>
+        <v>57950</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9683,34 +9721,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445292</v>
+        <v>445066</v>
       </c>
       <c r="R86" t="n">
-        <v>6734957</v>
+        <v>6734914</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9742,7 +9785,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9752,7 +9795,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9779,45 +9822,50 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129237829</v>
+        <v>129237782</v>
       </c>
       <c r="B87" t="n">
-        <v>79665</v>
+        <v>58327</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>103015</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445225</v>
+        <v>445267</v>
       </c>
       <c r="R87" t="n">
-        <v>6735226</v>
+        <v>6735219</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9886,45 +9934,50 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129243589</v>
+        <v>129242999</v>
       </c>
       <c r="B88" t="n">
-        <v>79075</v>
+        <v>58327</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>445385</v>
+        <v>445292</v>
       </c>
       <c r="R88" t="n">
-        <v>6734971</v>
+        <v>6734957</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9993,10 +10046,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129247020</v>
+        <v>129238052</v>
       </c>
       <c r="B89" t="n">
-        <v>78833</v>
+        <v>58114</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10004,37 +10057,46 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>445135</v>
+        <v>445240</v>
       </c>
       <c r="R89" t="n">
-        <v>6734998</v>
+        <v>6735230</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10063,7 +10125,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10073,7 +10135,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10100,10 +10162,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129243217</v>
+        <v>129238815</v>
       </c>
       <c r="B90" t="n">
-        <v>78833</v>
+        <v>58114</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10111,37 +10173,42 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>445422</v>
+        <v>445313</v>
       </c>
       <c r="R90" t="n">
-        <v>6734878</v>
+        <v>6735262</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10170,7 +10237,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10180,7 +10247,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10207,10 +10274,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129239096</v>
+        <v>121395755</v>
       </c>
       <c r="B91" t="n">
-        <v>8450</v>
+        <v>8455</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10238,14 +10305,14 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Kringlogmyrkölen, Dlr</t>
+          <t>V Finngruvan, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>445324</v>
+        <v>445181</v>
       </c>
       <c r="R91" t="n">
-        <v>6735285</v>
+        <v>6735098</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10272,22 +10339,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>10:56</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>10:56</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10302,44 +10359,44 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129240662</v>
+        <v>129237286</v>
       </c>
       <c r="B92" t="n">
-        <v>79694</v>
+        <v>8455</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10349,10 +10406,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>445517</v>
+        <v>445252</v>
       </c>
       <c r="R92" t="n">
-        <v>6735559</v>
+        <v>6735079</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10384,7 +10441,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10394,7 +10451,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10421,50 +10478,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129248776</v>
+        <v>129237324</v>
       </c>
       <c r="B93" t="n">
-        <v>57732</v>
+        <v>8455</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>445137</v>
+        <v>445263</v>
       </c>
       <c r="R93" t="n">
-        <v>6734922</v>
+        <v>6735122</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10496,7 +10548,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10506,7 +10558,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10533,48 +10585,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129243051</v>
+        <v>129238778</v>
       </c>
       <c r="B94" t="n">
-        <v>79171</v>
+        <v>8455</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>967</v>
+        <v>106545</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445339</v>
+        <v>445322</v>
       </c>
       <c r="R94" t="n">
-        <v>6734920</v>
+        <v>6735197</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10606,7 +10655,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10616,12 +10665,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>3 bilder</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10630,7 +10674,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10649,32 +10692,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129239693</v>
+        <v>129239096</v>
       </c>
       <c r="B95" t="n">
-        <v>79076</v>
+        <v>8455</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10684,10 +10727,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445362</v>
+        <v>445324</v>
       </c>
       <c r="R95" t="n">
-        <v>6735341</v>
+        <v>6735285</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10730,11 +10773,6 @@
       <c r="AB95" t="inlineStr">
         <is>
           <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>5 bilder, sumpskog</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10761,50 +10799,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129240510</v>
+        <v>129239392</v>
       </c>
       <c r="B96" t="n">
-        <v>57733</v>
+        <v>8455</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>445439</v>
+        <v>445379</v>
       </c>
       <c r="R96" t="n">
-        <v>6735533</v>
+        <v>6735294</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10836,7 +10869,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10846,12 +10879,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>1 bild med kolad stubbe i bakgrund</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10878,32 +10906,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129240554</v>
+        <v>129239850</v>
       </c>
       <c r="B97" t="n">
-        <v>79666</v>
+        <v>8455</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10913,10 +10941,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>445435</v>
+        <v>445369</v>
       </c>
       <c r="R97" t="n">
-        <v>6735582</v>
+        <v>6735411</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10948,7 +10976,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10958,12 +10986,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>1 bild på högstubbe med låga i bakgrund</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10990,32 +11013,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129240471</v>
+        <v>129239980</v>
       </c>
       <c r="B98" t="n">
-        <v>78834</v>
+        <v>8455</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11025,10 +11048,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>445438</v>
+        <v>445467</v>
       </c>
       <c r="R98" t="n">
-        <v>6735509</v>
+        <v>6735385</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11071,11 +11094,6 @@
       <c r="AB98" t="inlineStr">
         <is>
           <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>2 bilder, kolad stubbe samt på spiklav</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11102,50 +11120,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129240492</v>
+        <v>129240788</v>
       </c>
       <c r="B99" t="n">
-        <v>57733</v>
+        <v>8455</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>445440</v>
+        <v>445491</v>
       </c>
       <c r="R99" t="n">
-        <v>6735522</v>
+        <v>6735426</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11188,11 +11201,6 @@
       <c r="AB99" t="inlineStr">
         <is>
           <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>1 bild</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11219,32 +11227,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129240621</v>
+        <v>129242957</v>
       </c>
       <c r="B100" t="n">
-        <v>78834</v>
+        <v>8455</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11254,10 +11262,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>445517</v>
+        <v>445292</v>
       </c>
       <c r="R100" t="n">
-        <v>6735559</v>
+        <v>6734957</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11289,7 +11297,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11299,12 +11307,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>1 bild, kolad stubbe</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11331,50 +11334,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129237880</v>
+        <v>129243104</v>
       </c>
       <c r="B101" t="n">
-        <v>57733</v>
+        <v>8455</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445206</v>
+        <v>445374</v>
       </c>
       <c r="R101" t="n">
-        <v>6735207</v>
+        <v>6734891</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11406,7 +11404,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11416,12 +11414,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Bild, torraka med hack</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11448,32 +11441,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129238933</v>
+        <v>129248893</v>
       </c>
       <c r="B102" t="n">
-        <v>79076</v>
+        <v>8455</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11483,10 +11476,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445307</v>
+        <v>445081</v>
       </c>
       <c r="R102" t="n">
-        <v>6735277</v>
+        <v>6734878</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11518,7 +11511,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11528,12 +11521,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 50 meter 3 bilder, sista på två tallstammar</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11563,7 +11551,7 @@
         <v>129237273</v>
       </c>
       <c r="B103" t="n">
-        <v>78834</v>
+        <v>79085</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11675,7 +11663,7 @@
         <v>129237350</v>
       </c>
       <c r="B104" t="n">
-        <v>78834</v>
+        <v>79085</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11784,10 +11772,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129248843</v>
+        <v>129237612</v>
       </c>
       <c r="B105" t="n">
-        <v>91609</v>
+        <v>79085</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11795,38 +11783,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445140</v>
+        <v>445279</v>
       </c>
       <c r="R105" t="n">
-        <v>6734876</v>
+        <v>6735197</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11858,7 +11842,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11868,12 +11852,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild på två stubbar med äldre tall i bakgrund</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11900,10 +11884,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129243098</v>
+        <v>129240471</v>
       </c>
       <c r="B106" t="n">
-        <v>57733</v>
+        <v>79085</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11911,39 +11895,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445374</v>
+        <v>445438</v>
       </c>
       <c r="R106" t="n">
-        <v>6734891</v>
+        <v>6735509</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11975,7 +11954,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11985,12 +11964,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>2 bilder, kolad stubbe samt på spiklav</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12017,10 +11996,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129238758</v>
+        <v>129243054</v>
       </c>
       <c r="B107" t="n">
-        <v>57733</v>
+        <v>79085</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12028,39 +12007,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445349</v>
+        <v>445339</v>
       </c>
       <c r="R107" t="n">
-        <v>6735194</v>
+        <v>6734920</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12092,7 +12066,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12102,12 +12076,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>2 bilder på torraka med hack</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12134,10 +12103,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129238052</v>
+        <v>129243087</v>
       </c>
       <c r="B108" t="n">
-        <v>57896</v>
+        <v>79085</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12145,46 +12114,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>445240</v>
+        <v>445378</v>
       </c>
       <c r="R108" t="n">
-        <v>6735230</v>
+        <v>6734906</v>
       </c>
       <c r="S108" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12213,7 +12173,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12223,7 +12183,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12250,10 +12210,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129243188</v>
+        <v>129243192</v>
       </c>
       <c r="B109" t="n">
-        <v>79171</v>
+        <v>79085</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12261,21 +12221,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>967</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12331,11 +12291,6 @@
       <c r="AB109" t="inlineStr">
         <is>
           <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>3 bilder</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12362,10 +12317,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129238770</v>
+        <v>129243217</v>
       </c>
       <c r="B110" t="n">
-        <v>57733</v>
+        <v>79085</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12373,39 +12328,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>445322</v>
+        <v>445422</v>
       </c>
       <c r="R110" t="n">
-        <v>6735197</v>
+        <v>6734878</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12437,7 +12387,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12447,12 +12397,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Bild på torraka, färska hack</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12479,10 +12424,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129239898</v>
+        <v>129247020</v>
       </c>
       <c r="B111" t="n">
-        <v>57733</v>
+        <v>79085</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12490,39 +12435,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>445362</v>
+        <v>445135</v>
       </c>
       <c r="R111" t="n">
-        <v>6735431</v>
+        <v>6734998</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12554,7 +12494,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12564,12 +12504,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>2 bilder, låga, torraka</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12596,10 +12531,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129239384</v>
+        <v>129248989</v>
       </c>
       <c r="B112" t="n">
-        <v>57733</v>
+        <v>79085</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12607,39 +12542,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>445379</v>
+        <v>445037</v>
       </c>
       <c r="R112" t="n">
-        <v>6735294</v>
+        <v>6734946</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12671,7 +12601,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12681,12 +12611,12 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>2 bilder</t>
+          <t>1 bild, tall i bakgrund</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12713,10 +12643,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129237668</v>
+        <v>121395718</v>
       </c>
       <c r="B113" t="n">
-        <v>79076</v>
+        <v>79917</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12724,34 +12654,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Kringlogmyrkölen, Dlr</t>
+          <t>V Finngruvan, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>445302</v>
+        <v>445198</v>
       </c>
       <c r="R113" t="n">
-        <v>6735183</v>
+        <v>6734721</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12778,27 +12708,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>09:32</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Bild på äldre tall, stam uppåt</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12813,22 +12728,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129243085</v>
+        <v>129237277</v>
       </c>
       <c r="B114" t="n">
-        <v>79666</v>
+        <v>79917</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12860,10 +12775,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>445378</v>
+        <v>445252</v>
       </c>
       <c r="R114" t="n">
-        <v>6734906</v>
+        <v>6735079</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12895,7 +12810,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12905,12 +12820,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:48</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>1 bild</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12937,10 +12847,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129238380</v>
+        <v>129237621</v>
       </c>
       <c r="B115" t="n">
-        <v>79666</v>
+        <v>79917</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12972,10 +12882,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>445322</v>
+        <v>445279</v>
       </c>
       <c r="R115" t="n">
-        <v>6735151</v>
+        <v>6735197</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13007,7 +12917,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13017,12 +12927,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Bild på grov kolad stuppe/låga, tall</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13049,10 +12954,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129237612</v>
+        <v>129237829</v>
       </c>
       <c r="B116" t="n">
-        <v>78834</v>
+        <v>79917</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13060,21 +12965,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13084,10 +12989,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>445279</v>
+        <v>445225</v>
       </c>
       <c r="R116" t="n">
-        <v>6735197</v>
+        <v>6735226</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13130,11 +13035,6 @@
       <c r="AB116" t="inlineStr">
         <is>
           <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Bild på två stubbar med äldre tall i bakgrund</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13161,10 +13061,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129240918</v>
+        <v>129238380</v>
       </c>
       <c r="B117" t="n">
-        <v>57733</v>
+        <v>79917</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13172,39 +13072,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Kringlogmyrkölen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>445417</v>
+        <v>445322</v>
       </c>
       <c r="R117" t="n">
-        <v>6735368</v>
+        <v>6735151</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13236,7 +13131,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13246,12 +13141,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Bild på grov kolad stuppe/låga, tall</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13275,6 +13170,1009 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>129243085</v>
+      </c>
+      <c r="B118" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Kringlogmyrkölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>445378</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6734906</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>1 bild</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>129244433</v>
+      </c>
+      <c r="B119" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Kringlogmyrkölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>445217</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6734997</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>1 bild på högstubbe</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>129240566</v>
+      </c>
+      <c r="B120" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Kringlogmyrkölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>445481</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6735582</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>129240662</v>
+      </c>
+      <c r="B121" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Kringlogmyrkölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>445517</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6735559</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>129240492</v>
+      </c>
+      <c r="B122" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Kringlogmyrkölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>445440</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6735522</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>1 bild</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>129240510</v>
+      </c>
+      <c r="B123" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Kringlogmyrkölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>445439</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6735533</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>1 bild med kolad stubbe i bakgrund</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>129240494</v>
+      </c>
+      <c r="B124" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Kringlogmyrkölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>445440</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6735522</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>129240621</v>
+      </c>
+      <c r="B125" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Kringlogmyrkölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>445517</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6735559</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>1 bild, kolad stubbe</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>129240554</v>
+      </c>
+      <c r="B126" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Kringlogmyrkölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>445435</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6735582</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>1 bild på högstubbe med låga i bakgrund</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43504-2025 artfynd.xlsx
+++ b/artfynd/A 43504-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY126"/>
+  <dimension ref="A1:AZ126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121395811</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121395813</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121395725</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121395727</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1176,6 +1201,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129243051</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,6 +1318,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129243188</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1404,6 +1439,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129248688</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1501,6 +1541,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121395765</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1617,6 +1662,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129248843</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1714,6 +1764,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121395694</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1811,6 +1866,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121395796</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1908,6 +1968,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121395797</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2015,6 +2080,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129237299</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2122,6 +2192,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129237477</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2229,6 +2304,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129237525</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2336,6 +2416,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129237533</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2443,6 +2528,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129237544</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2550,6 +2640,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129237639</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2662,6 +2757,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129237668</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2769,6 +2869,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129237683</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2881,6 +2986,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129237747</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2988,6 +3098,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129238241</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3095,6 +3210,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129238272</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3202,6 +3322,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129238475</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3309,6 +3434,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129238503</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3416,6 +3546,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129238576</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3523,6 +3658,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129238645</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3635,6 +3775,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129238704</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3747,6 +3892,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129238788</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3859,6 +4009,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129238933</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3966,6 +4121,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129239093</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4073,6 +4233,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129239479</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4185,6 +4350,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129239693</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4292,6 +4462,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129239740</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4404,6 +4579,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129239929</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4511,6 +4691,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129240474</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4618,6 +4803,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129240566</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4725,6 +4915,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129240724</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4832,6 +5027,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129240967</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4944,6 +5144,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129241052</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5051,6 +5256,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129243562</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5158,6 +5368,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129243589</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5265,6 +5480,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129243753</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5377,6 +5597,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129243781</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5484,6 +5709,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129249212</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5591,6 +5821,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129249287</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5698,6 +5933,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129249372</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5805,6 +6045,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129253379</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5912,6 +6157,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254011</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6024,6 +6274,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129254098</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6121,6 +6376,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121395838</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6218,6 +6478,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121395839</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6315,6 +6580,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121395684</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6422,6 +6692,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129237820</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6529,6 +6804,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129243245</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6626,6 +6906,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121395704</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6723,6 +7008,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121395705</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6830,6 +7120,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129237274</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6937,6 +7232,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129237617</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7044,6 +7344,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129237826</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7151,6 +7456,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129240662</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7258,6 +7568,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129244530</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7365,6 +7680,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129247898</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7477,6 +7797,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129248920</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7584,6 +7909,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129249084</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7681,6 +8011,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121395832</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7778,6 +8113,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121395834</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7875,6 +8215,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121395835</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7992,6 +8337,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129237880</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8109,6 +8459,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129238758</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8226,6 +8581,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129238770</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8343,6 +8703,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129239384</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8455,6 +8820,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129239857</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8572,6 +8942,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129239898</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8684,6 +9059,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129240193</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8801,6 +9181,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129240492</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8918,6 +9303,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129240510</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9035,6 +9425,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129240918</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9152,6 +9547,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129243098</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9269,6 +9669,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129243524</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9381,6 +9786,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129243809</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9493,6 +9903,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129248776</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9610,6 +10025,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129248887</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9722,6 +10142,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129248937</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9839,6 +10264,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129250170</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9951,6 +10381,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129237782</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10063,6 +10498,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129242999</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10179,6 +10619,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129238052</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10291,6 +10736,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129238815</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10388,6 +10838,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121395755</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10495,6 +10950,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129237286</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10602,6 +11062,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129237324</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10709,6 +11174,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129238778</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10816,6 +11286,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129239096</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10923,6 +11398,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129239392</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11030,6 +11510,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129239850</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11137,6 +11622,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129239980</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11244,6 +11734,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129240494</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11351,6 +11846,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129240788</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11458,6 +11958,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129242957</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11565,6 +12070,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129243104</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11672,6 +12182,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129248893</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11784,6 +12299,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129253634</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11896,6 +12416,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129237273</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12008,6 +12533,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129237350</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12120,6 +12650,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129237612</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12232,6 +12767,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129240471</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12344,6 +12884,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129240621</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12451,6 +12996,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129243054</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12558,6 +13108,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129243087</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12665,6 +13220,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129243192</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12772,6 +13332,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129243217</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12879,6 +13444,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129247020</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12991,6 +13561,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129248989</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13098,6 +13673,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129250233</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13210,6 +13790,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129251241</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13307,6 +13892,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121395717</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13404,6 +13994,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121395718</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13511,6 +14106,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129237277</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13618,6 +14218,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129237621</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13725,6 +14330,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129237829</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13837,6 +14447,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129238380</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13949,6 +14564,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129240554</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14061,6 +14681,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129243085</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14173,8 +14798,140 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129244433</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>